--- a/zero-data/io_lists/ZERO mocked IO-List.xlsx
+++ b/zero-data/io_lists/ZERO mocked IO-List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\Git\zero\zero-data\io_lists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66B4F66-0E40-4B8B-9AD5-3710699F5F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B93BC-BED7-4CB7-88A5-ADCEC14CA31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Internal lists" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IO-List'!$A$1:$BV$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IO-List'!$A$1:$BV$154</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="746">
   <si>
     <t>Revision</t>
   </si>
@@ -1708,6 +1708,681 @@
   <si>
     <t>24 Vdc DB General Service 14E1 Current Measurement</t>
   </si>
+  <si>
+    <t>KEB10</t>
+  </si>
+  <si>
+    <t>DI20</t>
+  </si>
+  <si>
+    <t>DI21</t>
+  </si>
+  <si>
+    <t>AFT THRUSTER</t>
+  </si>
+  <si>
+    <t>DI22</t>
+  </si>
+  <si>
+    <t>Azimuth0positionsensorAftThruster</t>
+  </si>
+  <si>
+    <t>Azimuth 0 position sensor Aft Thruster</t>
+  </si>
+  <si>
+    <t>PS HELM CONSOLE</t>
+  </si>
+  <si>
+    <t>AzimuthPositionFeedbackAbsoluteEncoderAFTThruster</t>
+  </si>
+  <si>
+    <t>PitchPositionFeedbackAbsoluteEncoderAFTThruster</t>
+  </si>
+  <si>
+    <t>Azimuth Position Feedback Absolute Encoder AFT Thruster</t>
+  </si>
+  <si>
+    <t>Pitch Position Feedback Absolute Encoder AFT Thruster</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalAFTThruster(Aradex1)</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalAFTThruster(Aradex2)</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveSpeedSignalAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveEnableAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpRun(Clockwise)AFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveRightRotationDirectionAFTThuster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveLeftRotationDirectionAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveForwardDirectionAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveReverseDirectionAFTThruster</t>
+  </si>
+  <si>
+    <t>FlushValveMainThruster</t>
+  </si>
+  <si>
+    <t>AftThrusterAradex1(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>AftThrusterAradex2(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal AFT Thruster (Aradex1)</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal AFT Thruster (Aradex2)</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Speed Signal AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Enable AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Run ( Clockwise ) AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Right Rotation Direction AFT Thuster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Left Rotation Direction AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Forward Direction AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Reverse Direction AFT Thruster</t>
+  </si>
+  <si>
+    <t>Flush Valve Main Thruster</t>
+  </si>
+  <si>
+    <t>Aft Thruster Aradex1 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>Aft Thruster Aradex2 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>KEB11</t>
+  </si>
+  <si>
+    <t>Azimuth0positionsensorFWDThruster</t>
+  </si>
+  <si>
+    <t>AzimuthPositionFeedbackAbsoluteEncoderFWDThruster</t>
+  </si>
+  <si>
+    <t>PitchPositionFeedbackAbsoluteEncoderFWDThruster</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalFWDThruster(Aradex1)</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalFWDThruster(Aradex2)</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveSpeedSignalFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveEnableFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpRun(Clockwise)FWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveRightRotationDirectionFWDThuster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveLeftRotationDirectionFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveForwardDirectionFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveReverseDirectionFWDThruster</t>
+  </si>
+  <si>
+    <t>FlushValveFWDThruster</t>
+  </si>
+  <si>
+    <t>FWDThrusterAradex1(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>FWDThrusterAradex2(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>FWD THRUSTER</t>
+  </si>
+  <si>
+    <t>SB HELM CONSOLE</t>
+  </si>
+  <si>
+    <t>Azimuth 0 position sensor FWD Thruster</t>
+  </si>
+  <si>
+    <t>Azimuth Position Feedback Absolute Encoder FWD Thruster</t>
+  </si>
+  <si>
+    <t>Pitch Position Feedback Absolute Encoder FWD Thruster</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal FWD Thruster (Aradex1)</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal FWD Thruster (Aradex2)</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Speed Signal FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Enable FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Run ( Clockwise ) FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Right Rotation Direction FWD Thuster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Left Rotation Direction FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Forward Direction FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Reverse Direction FWD Thruster</t>
+  </si>
+  <si>
+    <t>Flush Valve FWD Thruster</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex1 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex2 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>KEB12</t>
+  </si>
+  <si>
+    <t>PSHelmStationSelect</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmManeuveringModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmStationSelect</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmManeuveringModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>PSHelmStationSelected</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmMoeveringModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmStationSelected</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmMoeveringModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>PS Helm Station Select</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Maneuvering Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Station Select</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Maneuvering Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>PS Helm Station Selected</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Moevering Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Station Selected</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Moevering Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>KEB13</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmManeuveringModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmManeuveringModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmMoeveringModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmMoeveringModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Maneuvering Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Maneuvering Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Moevering Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Moevering Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>AI20</t>
+  </si>
+  <si>
+    <t>AI21</t>
+  </si>
+  <si>
+    <t>DO60</t>
+  </si>
+  <si>
+    <t>DO61</t>
+  </si>
+  <si>
+    <t>AO61</t>
+  </si>
+  <si>
+    <t>AO62</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 1 speed feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 2 speed feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 1 speed feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 2 speed feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 1 torque feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 2 torque feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 1 torque feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 2 torque feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster regeneration speed control</t>
+  </si>
+  <si>
+    <t>AFT Thruster regeneration torque control</t>
+  </si>
+  <si>
+    <t>FWD Thruster regeneration speed control</t>
+  </si>
+  <si>
+    <t>FWD Thruster regeneration torque control</t>
+  </si>
+  <si>
+    <t>AFT Thruster max torque regeneration</t>
+  </si>
+  <si>
+    <t>AFT Thruster min torque regeneration</t>
+  </si>
+  <si>
+    <t>FWD Thruster max torque regeneration</t>
+  </si>
+  <si>
+    <t>FWD Thruster min torque regeneration</t>
+  </si>
+  <si>
+    <t>AFT Thruster max pitch</t>
+  </si>
+  <si>
+    <t>AFT Thruster min pitch</t>
+  </si>
+  <si>
+    <t>AFT Thruster torque constant</t>
+  </si>
+  <si>
+    <t>FWD Thruster max pitch</t>
+  </si>
+  <si>
+    <t>FWD Thruster min pitch</t>
+  </si>
+  <si>
+    <t>FWD Thruster torque constant</t>
+  </si>
+  <si>
+    <t>AFT Thruster high trust control</t>
+  </si>
+  <si>
+    <t>AFT Thruster normal control</t>
+  </si>
+  <si>
+    <t>AFT Thruster motorsail control</t>
+  </si>
+  <si>
+    <t>FWD Thruster high trust control</t>
+  </si>
+  <si>
+    <t>FWD Thruster normal control</t>
+  </si>
+  <si>
+    <t>FWD Thruster motorsail control</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>AFT Thruster pitch rate of change</t>
+  </si>
+  <si>
+    <t>FWD Thruster pitch rate of change</t>
+  </si>
+  <si>
+    <t>helm-console/ps</t>
+  </si>
+  <si>
+    <t>helm-console/sb</t>
+  </si>
+  <si>
+    <t>thruster/aft</t>
+  </si>
+  <si>
+    <t>thruster/fwd</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm Master/Slave</t>
+  </si>
 </sst>
 </file>
 
@@ -1717,7 +2392,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
@@ -1853,8 +2528,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1918,6 +2605,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2351,7 +3056,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2560,6 +3265,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3719,20 +4429,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BV8979"/>
+  <dimension ref="A1:BV8785"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="51" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="53" customWidth="1"/>
-    <col min="3" max="3" width="18" style="54" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="54" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="54" customWidth="1"/>
     <col min="5" max="5" width="8.140625" style="54" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="54" customWidth="1"/>
+    <col min="6" max="6" width="15" style="54" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" style="54" customWidth="1"/>
     <col min="8" max="8" width="6.85546875" style="54" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="49.7109375" style="11" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" style="58" customWidth="1"/>
+    <col min="10" max="10" width="68.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="58" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" style="10" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="17.7109375" style="10" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="25.140625" style="60" bestFit="1" customWidth="1"/>
@@ -3745,9 +4455,9 @@
     <col min="21" max="21" width="11.28515625" style="61" customWidth="1"/>
     <col min="22" max="22" width="11.28515625" style="63" customWidth="1"/>
     <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="48.28515625" customWidth="1"/>
-    <col min="26" max="26" width="48.7109375" customWidth="1"/>
+    <col min="26" max="26" width="57.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.28515625" style="12" customWidth="1"/>
     <col min="28" max="28" width="11.85546875" style="54" customWidth="1"/>
     <col min="29" max="29" width="10.85546875" style="64" customWidth="1"/>
@@ -3795,197 +4505,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" s="16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="106" t="s">
+      <c r="C1" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="F1" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="110" t="s">
+      <c r="H1" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="122" t="s">
+      <c r="I1" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="115" t="s">
+      <c r="J1" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="124" t="s">
+      <c r="L1" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="125"/>
-      <c r="N1" s="106" t="s">
+      <c r="M1" s="130"/>
+      <c r="N1" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="106" t="s">
+      <c r="P1" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="106" t="s">
+      <c r="Q1" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="106" t="s">
+      <c r="R1" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="106" t="s">
+      <c r="S1" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="113" t="s">
+      <c r="T1" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="116" t="s">
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="121" t="s">
         <v>438</v>
       </c>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="114" t="s">
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="114"/>
-      <c r="AC1" s="114"/>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
-      <c r="AG1" s="114"/>
-      <c r="AH1" s="114"/>
-      <c r="AI1" s="119" t="s">
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="115" t="s">
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="120" t="s">
         <v>66</v>
       </c>
-      <c r="AL1" s="115" t="s">
+      <c r="AL1" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="AM1" s="112" t="s">
+      <c r="AM1" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="AN1" s="121" t="s">
+      <c r="AN1" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="121"/>
-      <c r="AP1" s="121"/>
-      <c r="AQ1" s="121"/>
-      <c r="AR1" s="121"/>
-      <c r="AS1" s="106" t="s">
+      <c r="AO1" s="126"/>
+      <c r="AP1" s="126"/>
+      <c r="AQ1" s="126"/>
+      <c r="AR1" s="126"/>
+      <c r="AS1" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="AT1" s="106" t="s">
+      <c r="AT1" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="AU1" s="106" t="s">
+      <c r="AU1" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="AV1" s="106" t="s">
+      <c r="AV1" s="111" t="s">
         <v>73</v>
       </c>
-      <c r="AW1" s="120" t="s">
+      <c r="AW1" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="AX1" s="109" t="s">
+      <c r="AX1" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="AY1" s="110" t="s">
+      <c r="AY1" s="115" t="s">
         <v>76</v>
       </c>
-      <c r="AZ1" s="110" t="s">
+      <c r="AZ1" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="BA1" s="110" t="s">
+      <c r="BA1" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="BB1" s="110" t="s">
+      <c r="BB1" s="115" t="s">
         <v>79</v>
       </c>
-      <c r="BC1" s="108" t="s">
+      <c r="BC1" s="113" t="s">
         <v>80</v>
       </c>
-      <c r="BD1" s="108"/>
-      <c r="BE1" s="108"/>
-      <c r="BF1" s="108" t="s">
+      <c r="BD1" s="113"/>
+      <c r="BE1" s="113"/>
+      <c r="BF1" s="113" t="s">
         <v>81</v>
       </c>
-      <c r="BG1" s="108"/>
-      <c r="BH1" s="108"/>
-      <c r="BI1" s="108" t="s">
+      <c r="BG1" s="113"/>
+      <c r="BH1" s="113"/>
+      <c r="BI1" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="BJ1" s="108"/>
-      <c r="BK1" s="108"/>
-      <c r="BL1" s="108" t="s">
+      <c r="BJ1" s="113"/>
+      <c r="BK1" s="113"/>
+      <c r="BL1" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="BM1" s="108"/>
-      <c r="BN1" s="108"/>
-      <c r="BO1" s="108" t="s">
+      <c r="BM1" s="113"/>
+      <c r="BN1" s="113"/>
+      <c r="BO1" s="113" t="s">
         <v>84</v>
       </c>
-      <c r="BP1" s="108"/>
-      <c r="BQ1" s="108"/>
-      <c r="BR1" s="112" t="s">
+      <c r="BP1" s="113"/>
+      <c r="BQ1" s="113"/>
+      <c r="BR1" s="117" t="s">
         <v>85</v>
       </c>
-      <c r="BS1" s="110" t="s">
+      <c r="BS1" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="BT1" s="111" t="s">
+      <c r="BT1" s="116" t="s">
         <v>87</v>
       </c>
-      <c r="BU1" s="107" t="s">
+      <c r="BU1" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="BV1" s="107" t="s">
+      <c r="BV1" s="112" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:74" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="126"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="123"/>
+    <row r="2" spans="1:74" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="131"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="128"/>
       <c r="L2" s="97" t="s">
         <v>93</v>
       </c>
       <c r="M2" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="106"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
       <c r="T2" s="17" t="s">
         <v>90</v>
       </c>
@@ -4037,9 +4747,9 @@
       <c r="AJ2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="115"/>
-      <c r="AL2" s="115"/>
-      <c r="AM2" s="112"/>
+      <c r="AK2" s="120"/>
+      <c r="AL2" s="120"/>
+      <c r="AM2" s="117"/>
       <c r="AN2" s="18" t="s">
         <v>103</v>
       </c>
@@ -4055,16 +4765,16 @@
       <c r="AR2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="AS2" s="106"/>
-      <c r="AT2" s="106"/>
-      <c r="AU2" s="106"/>
-      <c r="AV2" s="106"/>
-      <c r="AW2" s="120"/>
-      <c r="AX2" s="109"/>
-      <c r="AY2" s="110"/>
-      <c r="AZ2" s="110"/>
-      <c r="BA2" s="110"/>
-      <c r="BB2" s="110"/>
+      <c r="AS2" s="111"/>
+      <c r="AT2" s="111"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
+      <c r="AW2" s="125"/>
+      <c r="AX2" s="114"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
+      <c r="BB2" s="115"/>
       <c r="BC2" s="21" t="s">
         <v>56</v>
       </c>
@@ -4110,11 +4820,11 @@
       <c r="BQ2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="BR2" s="112"/>
-      <c r="BS2" s="110"/>
-      <c r="BT2" s="111"/>
-      <c r="BU2" s="107"/>
-      <c r="BV2" s="107"/>
+      <c r="BR2" s="117"/>
+      <c r="BS2" s="115"/>
+      <c r="BT2" s="116"/>
+      <c r="BU2" s="112"/>
+      <c r="BV2" s="112"/>
     </row>
     <row r="3" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
@@ -6401,945 +7111,4335 @@
       <c r="BT26" s="11"/>
     </row>
     <row r="27" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="F27" s="55"/>
+      <c r="J27" s="109" t="s">
+        <v>526</v>
+      </c>
+      <c r="K27" s="57"/>
+      <c r="N27" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P27" s="107" t="s">
+        <v>527</v>
+      </c>
       <c r="W27" s="65"/>
-      <c r="X27" s="104"/>
-      <c r="Y27" s="54"/>
-      <c r="Z27" s="66"/>
+      <c r="X27" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y27" s="6" t="str">
+        <f>"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N27,"spare"),"",IF(X27&lt;&gt;"",X27,N27))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z27" s="64" t="str">
+        <f>IF(COUNTIF(N27,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J27,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Azimuth0positionsensor</v>
+      </c>
     </row>
     <row r="28" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J28" s="109" t="s">
+        <v>529</v>
+      </c>
+      <c r="N28" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P28" s="107" t="s">
+        <v>531</v>
+      </c>
       <c r="W28" s="65"/>
-      <c r="X28" s="104"/>
-      <c r="Y28" s="54"/>
-      <c r="Z28" s="66"/>
+      <c r="X28" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y28" s="6" t="str">
+        <f t="shared" ref="Y28:Y91" si="25">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N28,"spare"),"",IF(X28&lt;&gt;"",X28,N28))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z28" s="64" t="str">
+        <f t="shared" ref="Z28:Z56" si="26">IF(COUNTIF(N28,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J28,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.AzimuthPositionFeedbackAbsoluteEncoder</v>
+      </c>
     </row>
     <row r="29" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A29" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J29" s="109" t="s">
+        <v>530</v>
+      </c>
+      <c r="N29" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P29" s="107" t="s">
+        <v>532</v>
+      </c>
       <c r="W29" s="65"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="54"/>
-      <c r="Z29" s="66"/>
+      <c r="X29" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y29" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z29" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.PitchPositionFeedbackAbsoluteEncoder</v>
+      </c>
     </row>
     <row r="30" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J30" s="109" t="s">
+        <v>533</v>
+      </c>
+      <c r="N30" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P30" s="107" t="s">
+        <v>545</v>
+      </c>
       <c r="W30" s="65"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="54"/>
-      <c r="Z30" s="66"/>
+      <c r="X30" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y30" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z30" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex1)</v>
+      </c>
     </row>
     <row r="31" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J31" s="109" t="s">
+        <v>534</v>
+      </c>
+      <c r="N31" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P31" s="107" t="s">
+        <v>546</v>
+      </c>
       <c r="W31" s="65"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="54"/>
-      <c r="Z31" s="66"/>
+      <c r="X31" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y31" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z31" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex2)</v>
+      </c>
     </row>
     <row r="32" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A32" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="J32" s="109" t="s">
+        <v>535</v>
+      </c>
+      <c r="N32" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P32" s="107" t="s">
+        <v>547</v>
+      </c>
       <c r="W32" s="65"/>
-      <c r="X32" s="104"/>
-      <c r="Y32" s="54"/>
-      <c r="Z32" s="66"/>
-    </row>
-    <row r="33" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X32" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y32" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z32" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveSpeedSignal</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A33" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J33" s="110" t="s">
+        <v>536</v>
+      </c>
+      <c r="N33" s="59" t="s">
+        <v>524</v>
+      </c>
+      <c r="P33" s="59" t="s">
+        <v>548</v>
+      </c>
       <c r="W33" s="65"/>
-      <c r="X33" s="104"/>
-      <c r="Y33" s="54"/>
-      <c r="Z33" s="66"/>
-    </row>
-    <row r="34" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X33" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y33" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z33" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveEnable</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A34" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J34" s="110" t="s">
+        <v>537</v>
+      </c>
+      <c r="N34" s="59" t="s">
+        <v>524</v>
+      </c>
+      <c r="P34" s="59" t="s">
+        <v>549</v>
+      </c>
       <c r="W34" s="65"/>
-      <c r="X34" s="104"/>
-      <c r="Y34" s="54"/>
-      <c r="Z34" s="66"/>
-    </row>
-    <row r="35" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X34" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y34" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z34" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpRun(Clockwise)</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A35" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J35" s="109" t="s">
+        <v>538</v>
+      </c>
+      <c r="N35" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P35" s="107" t="s">
+        <v>550</v>
+      </c>
       <c r="W35" s="65"/>
-      <c r="X35" s="104"/>
-      <c r="Y35" s="54"/>
-      <c r="Z35" s="66"/>
-    </row>
-    <row r="36" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X35" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y35" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z35" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveRightRotationDirection</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J36" s="109" t="s">
+        <v>539</v>
+      </c>
+      <c r="N36" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P36" s="107" t="s">
+        <v>551</v>
+      </c>
       <c r="W36" s="65"/>
-      <c r="X36" s="104"/>
-      <c r="Y36" s="54"/>
-      <c r="Z36" s="66"/>
-    </row>
-    <row r="37" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X36" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y36" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z36" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveLeftRotationDirection</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A37" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J37" s="109" t="s">
+        <v>540</v>
+      </c>
+      <c r="N37" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P37" s="107" t="s">
+        <v>552</v>
+      </c>
       <c r="W37" s="65"/>
-      <c r="X37" s="104"/>
-      <c r="Y37" s="54"/>
-      <c r="Z37" s="66"/>
-    </row>
-    <row r="38" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X37" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y37" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z37" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveForwardDirection</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A38" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J38" s="109" t="s">
+        <v>541</v>
+      </c>
+      <c r="N38" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P38" s="107" t="s">
+        <v>553</v>
+      </c>
       <c r="W38" s="65"/>
-      <c r="X38" s="104"/>
-      <c r="Y38" s="54"/>
-      <c r="Z38" s="66"/>
-    </row>
-    <row r="39" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X38" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y38" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z38" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveReverseDirection</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A39" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J39" s="109" t="s">
+        <v>542</v>
+      </c>
+      <c r="N39" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P39" s="107" t="s">
+        <v>554</v>
+      </c>
       <c r="W39" s="65"/>
-      <c r="X39" s="104"/>
-      <c r="Y39" s="54"/>
-      <c r="Z39" s="66"/>
-    </row>
-    <row r="40" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X39" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y39" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z39" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.FlushValve</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J40" s="109" t="s">
+        <v>543</v>
+      </c>
+      <c r="N40" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P40" s="107" t="s">
+        <v>555</v>
+      </c>
       <c r="W40" s="65"/>
-      <c r="X40" s="104"/>
-      <c r="Y40" s="54"/>
-      <c r="Z40" s="66"/>
-    </row>
-    <row r="41" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X40" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y40" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z40" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex1(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A41" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J41" s="109" t="s">
+        <v>544</v>
+      </c>
+      <c r="N41" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P41" s="107" t="s">
+        <v>556</v>
+      </c>
       <c r="W41" s="65"/>
-      <c r="X41" s="104"/>
-      <c r="Y41" s="54"/>
-      <c r="Z41" s="66"/>
-    </row>
-    <row r="42" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X41" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y41" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z41" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex2(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A42" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="J42" s="109" t="s">
+        <v>558</v>
+      </c>
+      <c r="N42" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P42" s="107" t="s">
+        <v>575</v>
+      </c>
       <c r="W42" s="65"/>
-      <c r="X42" s="104"/>
-      <c r="Y42" s="54"/>
-      <c r="Z42" s="66"/>
-    </row>
-    <row r="43" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X42" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y42" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z42" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Azimuth0positionsensor</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A43" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J43" s="109" t="s">
+        <v>559</v>
+      </c>
+      <c r="N43" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P43" s="107" t="s">
+        <v>576</v>
+      </c>
       <c r="W43" s="65"/>
-      <c r="X43" s="104"/>
-      <c r="Y43" s="54"/>
-      <c r="Z43" s="66"/>
-    </row>
-    <row r="44" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X43" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y43" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z43" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.AzimuthPositionFeedbackAbsoluteEncoder</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A44" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J44" s="109" t="s">
+        <v>560</v>
+      </c>
+      <c r="N44" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P44" s="107" t="s">
+        <v>577</v>
+      </c>
       <c r="W44" s="65"/>
-      <c r="X44" s="104"/>
-      <c r="Y44" s="54"/>
-      <c r="Z44" s="66"/>
-    </row>
-    <row r="45" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X44" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y44" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z44" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.PitchPositionFeedbackAbsoluteEncoder</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A45" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J45" s="109" t="s">
+        <v>561</v>
+      </c>
+      <c r="N45" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P45" s="107" t="s">
+        <v>578</v>
+      </c>
       <c r="W45" s="65"/>
-      <c r="X45" s="104"/>
-      <c r="Y45" s="54"/>
-      <c r="Z45" s="66"/>
-    </row>
-    <row r="46" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X45" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y45" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z45" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex1)</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A46" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J46" s="109" t="s">
+        <v>562</v>
+      </c>
+      <c r="N46" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P46" s="107" t="s">
+        <v>579</v>
+      </c>
       <c r="W46" s="65"/>
-      <c r="X46" s="104"/>
-      <c r="Y46" s="54"/>
-      <c r="Z46" s="66"/>
-    </row>
-    <row r="47" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X46" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y46" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z46" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex2)</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C47" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="J47" s="110" t="s">
+        <v>563</v>
+      </c>
+      <c r="N47" s="59" t="s">
+        <v>573</v>
+      </c>
+      <c r="P47" s="59" t="s">
+        <v>580</v>
+      </c>
       <c r="W47" s="65"/>
-      <c r="X47" s="104"/>
-      <c r="Y47" s="54"/>
-      <c r="Z47" s="66"/>
-    </row>
-    <row r="48" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X47" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y47" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z47" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveSpeedSignal</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A48" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J48" s="110" t="s">
+        <v>564</v>
+      </c>
+      <c r="N48" s="59" t="s">
+        <v>573</v>
+      </c>
+      <c r="P48" s="59" t="s">
+        <v>581</v>
+      </c>
       <c r="W48" s="65"/>
-      <c r="X48" s="104"/>
-      <c r="Y48" s="54"/>
-      <c r="Z48" s="66"/>
-    </row>
-    <row r="49" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X48" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y48" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z48" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveEnable</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A49" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C49" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J49" s="110" t="s">
+        <v>565</v>
+      </c>
+      <c r="N49" s="59" t="s">
+        <v>573</v>
+      </c>
+      <c r="P49" s="59" t="s">
+        <v>582</v>
+      </c>
       <c r="W49" s="65"/>
-      <c r="X49" s="104"/>
-      <c r="Y49" s="54"/>
-      <c r="Z49" s="66"/>
-    </row>
-    <row r="50" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X49" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y49" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z49" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpRun(Clockwise)</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A50" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C50" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J50" s="109" t="s">
+        <v>566</v>
+      </c>
+      <c r="N50" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P50" s="107" t="s">
+        <v>583</v>
+      </c>
       <c r="W50" s="65"/>
-      <c r="X50" s="104"/>
-      <c r="Y50" s="54"/>
-      <c r="Z50" s="66"/>
-    </row>
-    <row r="51" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X50" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y50" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z50" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveRightRotationDirection</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A51" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C51" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J51" s="109" t="s">
+        <v>567</v>
+      </c>
+      <c r="N51" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P51" s="107" t="s">
+        <v>584</v>
+      </c>
       <c r="W51" s="65"/>
-      <c r="X51" s="104"/>
-      <c r="Y51" s="54"/>
-      <c r="Z51" s="66"/>
-    </row>
-    <row r="52" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X51" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y51" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z51" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveLeftRotationDirection</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A52" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C52" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J52" s="109" t="s">
+        <v>568</v>
+      </c>
+      <c r="N52" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P52" s="107" t="s">
+        <v>585</v>
+      </c>
       <c r="W52" s="65"/>
-      <c r="X52" s="104"/>
-      <c r="Y52" s="54"/>
-      <c r="Z52" s="66"/>
-    </row>
-    <row r="53" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X52" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y52" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z52" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveForwardDirection</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A53" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J53" s="109" t="s">
+        <v>569</v>
+      </c>
+      <c r="N53" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P53" s="107" t="s">
+        <v>586</v>
+      </c>
       <c r="W53" s="65"/>
-      <c r="X53" s="104"/>
-      <c r="Y53" s="54"/>
-      <c r="Z53" s="66"/>
-    </row>
-    <row r="54" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X53" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y53" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z53" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveReverseDirection</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A54" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C54" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J54" s="109" t="s">
+        <v>570</v>
+      </c>
+      <c r="N54" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P54" s="107" t="s">
+        <v>587</v>
+      </c>
       <c r="W54" s="65"/>
-      <c r="X54" s="104"/>
-      <c r="Y54" s="54"/>
-      <c r="Z54" s="66"/>
-    </row>
-    <row r="55" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X54" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y54" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z54" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.FlushValve</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A55" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C55" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J55" s="109" t="s">
+        <v>571</v>
+      </c>
+      <c r="N55" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P55" s="107" t="s">
+        <v>588</v>
+      </c>
       <c r="W55" s="65"/>
-      <c r="X55" s="104"/>
-      <c r="Y55" s="54"/>
-      <c r="Z55" s="66"/>
-    </row>
-    <row r="56" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X55" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y55" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z55" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex1(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A56" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C56" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J56" s="109" t="s">
+        <v>572</v>
+      </c>
+      <c r="N56" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P56" s="107" t="s">
+        <v>589</v>
+      </c>
       <c r="W56" s="65"/>
-      <c r="X56" s="104"/>
-      <c r="Y56" s="54"/>
-      <c r="Z56" s="66"/>
-    </row>
-    <row r="57" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X56" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y56" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z56" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex2(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A57" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="108" t="s">
+        <v>590</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J57" s="109" t="s">
+        <v>591</v>
+      </c>
+      <c r="N57" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P57" s="107" t="s">
+        <v>611</v>
+      </c>
       <c r="W57" s="65"/>
-      <c r="X57" s="104"/>
-      <c r="Y57" s="54"/>
-      <c r="Z57" s="66"/>
-    </row>
-    <row r="58" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X57" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y57" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z57" s="64" t="str">
+        <f>IF(COUNTIF(N57,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J57,"(SB|Sb|PS|Ps) ?Helm ?",""),"(\.| |/)","_"))</f>
+        <v>$.StationSelect</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A58" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J58" s="109" t="s">
+        <v>592</v>
+      </c>
+      <c r="N58" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P58" s="107" t="s">
+        <v>612</v>
+      </c>
       <c r="W58" s="65"/>
-      <c r="X58" s="104"/>
-      <c r="Y58" s="54"/>
-      <c r="Z58" s="66"/>
-    </row>
-    <row r="59" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X58" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y58" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z58" s="64" t="str">
+        <f t="shared" ref="Z58:Z112" si="27">IF(COUNTIF(N58,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J58,"(SB|Sb|PS|Ps) ?Helm ?",""),"(\.| |/)","_"))</f>
+        <v>$.PropulsionModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A59" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C59" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J59" s="109" t="s">
+        <v>593</v>
+      </c>
+      <c r="N59" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P59" s="107" t="s">
+        <v>613</v>
+      </c>
       <c r="W59" s="65"/>
-      <c r="X59" s="104"/>
-      <c r="Y59" s="54"/>
-      <c r="Z59" s="66"/>
-    </row>
-    <row r="60" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X59" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y59" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z59" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A60" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C60" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J60" s="109" t="s">
+        <v>594</v>
+      </c>
+      <c r="N60" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P60" s="107" t="s">
+        <v>614</v>
+      </c>
       <c r="W60" s="65"/>
-      <c r="X60" s="104"/>
-      <c r="Y60" s="54"/>
-      <c r="Z60" s="66"/>
-    </row>
-    <row r="61" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X60" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y60" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z60" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A61" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C61" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J61" s="109" t="s">
+        <v>596</v>
+      </c>
+      <c r="N61" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P61" s="107" t="s">
+        <v>616</v>
+      </c>
       <c r="W61" s="65"/>
-      <c r="X61" s="104"/>
-      <c r="Y61" s="54"/>
-      <c r="Z61" s="66"/>
-    </row>
-    <row r="62" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X61" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y61" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z61" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A62" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C62" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J62" s="109" t="s">
+        <v>597</v>
+      </c>
+      <c r="N62" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P62" s="107" t="s">
+        <v>617</v>
+      </c>
       <c r="W62" s="65"/>
-      <c r="X62" s="104"/>
-      <c r="Y62" s="54"/>
-      <c r="Z62" s="66"/>
-    </row>
-    <row r="63" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X62" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y62" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z62" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A63" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C63" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J63" s="109" t="s">
+        <v>598</v>
+      </c>
+      <c r="N63" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P63" s="107" t="s">
+        <v>618</v>
+      </c>
       <c r="W63" s="65"/>
-      <c r="X63" s="104"/>
-      <c r="Y63" s="54"/>
-      <c r="Z63" s="66"/>
-    </row>
-    <row r="64" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X63" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y63" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z63" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A64" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C64" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J64" s="109" t="s">
+        <v>599</v>
+      </c>
+      <c r="N64" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P64" s="107" t="s">
+        <v>619</v>
+      </c>
       <c r="W64" s="65"/>
-      <c r="X64" s="104"/>
-      <c r="Y64" s="54"/>
-      <c r="Z64" s="66"/>
-    </row>
-    <row r="65" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X64" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y64" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z64" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A65" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C65" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J65" s="109" t="s">
+        <v>600</v>
+      </c>
+      <c r="N65" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P65" s="107" t="s">
+        <v>620</v>
+      </c>
       <c r="W65" s="65"/>
-      <c r="X65" s="104"/>
-      <c r="Y65" s="54"/>
-      <c r="Z65" s="66"/>
-    </row>
-    <row r="66" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X65" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y65" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z65" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A66" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C66" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J66" s="109" t="s">
+        <v>601</v>
+      </c>
+      <c r="N66" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P66" s="107" t="s">
+        <v>621</v>
+      </c>
       <c r="W66" s="65"/>
-      <c r="X66" s="104"/>
-      <c r="Y66" s="54"/>
-      <c r="Z66" s="66"/>
-    </row>
-    <row r="67" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X66" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y66" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z66" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A67" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C67" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J67" s="109" t="s">
+        <v>602</v>
+      </c>
+      <c r="N67" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P67" s="107" t="s">
+        <v>622</v>
+      </c>
       <c r="W67" s="65"/>
-      <c r="X67" s="104"/>
-      <c r="Y67" s="54"/>
-      <c r="Z67" s="66"/>
-    </row>
-    <row r="68" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X67" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y67" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z67" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A68" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C68" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J68" s="109" t="s">
+        <v>603</v>
+      </c>
+      <c r="N68" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P68" s="107" t="s">
+        <v>623</v>
+      </c>
       <c r="W68" s="65"/>
-      <c r="X68" s="104"/>
-      <c r="Y68" s="54"/>
-      <c r="Z68" s="66"/>
-    </row>
-    <row r="69" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X68" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y68" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z68" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.StationSelected</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A69" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C69" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J69" s="109" t="s">
+        <v>604</v>
+      </c>
+      <c r="N69" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P69" s="107" t="s">
+        <v>624</v>
+      </c>
       <c r="W69" s="65"/>
-      <c r="X69" s="104"/>
-      <c r="Y69" s="54"/>
-      <c r="Z69" s="66"/>
-    </row>
-    <row r="70" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X69" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y69" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z69" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A70" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C70" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J70" s="109" t="s">
+        <v>605</v>
+      </c>
+      <c r="N70" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P70" s="107" t="s">
+        <v>625</v>
+      </c>
       <c r="W70" s="65"/>
-      <c r="X70" s="104"/>
-      <c r="Y70" s="54"/>
-      <c r="Z70" s="66"/>
-    </row>
-    <row r="71" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X70" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y70" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z70" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A71" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C71" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J71" s="109" t="s">
+        <v>606</v>
+      </c>
+      <c r="N71" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P71" s="107" t="s">
+        <v>626</v>
+      </c>
       <c r="W71" s="65"/>
-      <c r="X71" s="104"/>
-      <c r="Y71" s="54"/>
-      <c r="Z71" s="66"/>
-    </row>
-    <row r="72" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X71" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y71" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z71" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A72" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C72" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J72" s="109" t="s">
+        <v>608</v>
+      </c>
+      <c r="N72" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P72" s="107" t="s">
+        <v>628</v>
+      </c>
       <c r="W72" s="65"/>
-      <c r="X72" s="104"/>
-      <c r="Y72" s="54"/>
-      <c r="Z72" s="66"/>
-    </row>
-    <row r="73" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X72" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y72" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z72" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A73" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J73" s="109" t="s">
+        <v>609</v>
+      </c>
+      <c r="N73" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P73" s="107" t="s">
+        <v>629</v>
+      </c>
       <c r="W73" s="65"/>
-      <c r="X73" s="104"/>
-      <c r="Y73" s="54"/>
-      <c r="Z73" s="66"/>
-    </row>
-    <row r="74" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X73" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y73" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z73" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A74" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J74" s="109" t="s">
+        <v>610</v>
+      </c>
+      <c r="N74" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P74" s="107" t="s">
+        <v>630</v>
+      </c>
       <c r="W74" s="65"/>
-      <c r="X74" s="104"/>
-      <c r="Y74" s="54"/>
-      <c r="Z74" s="66"/>
-    </row>
-    <row r="75" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X74" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y74" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z74" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A75" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C75" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J75" s="109" t="s">
+        <v>595</v>
+      </c>
+      <c r="N75" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P75" s="107" t="s">
+        <v>615</v>
+      </c>
       <c r="W75" s="65"/>
-      <c r="X75" s="104"/>
-      <c r="Y75" s="54"/>
-      <c r="Z75" s="66"/>
-    </row>
-    <row r="76" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X75" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y75" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z75" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.StationSelect</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A76" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C76" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J76" s="109" t="s">
+        <v>632</v>
+      </c>
+      <c r="N76" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P76" s="107" t="s">
+        <v>648</v>
+      </c>
       <c r="W76" s="65"/>
-      <c r="X76" s="104"/>
-      <c r="Y76" s="54"/>
-      <c r="Z76" s="66"/>
-    </row>
-    <row r="77" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X76" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y76" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z76" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A77" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J77" s="109" t="s">
+        <v>633</v>
+      </c>
+      <c r="N77" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P77" s="107" t="s">
+        <v>649</v>
+      </c>
       <c r="W77" s="65"/>
-      <c r="X77" s="104"/>
-      <c r="Y77" s="54"/>
-      <c r="Z77" s="66"/>
-    </row>
-    <row r="78" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X77" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y77" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z77" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A78" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C78" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J78" s="109" t="s">
+        <v>634</v>
+      </c>
+      <c r="N78" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P78" s="107" t="s">
+        <v>650</v>
+      </c>
       <c r="W78" s="65"/>
-      <c r="X78" s="104"/>
-      <c r="Y78" s="54"/>
-      <c r="Z78" s="66"/>
-    </row>
-    <row r="79" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X78" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y78" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z78" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A79" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C79" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J79" s="109" t="s">
+        <v>635</v>
+      </c>
+      <c r="N79" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P79" s="107" t="s">
+        <v>651</v>
+      </c>
       <c r="W79" s="65"/>
-      <c r="X79" s="104"/>
-      <c r="Y79" s="54"/>
-      <c r="Z79" s="66"/>
-    </row>
-    <row r="80" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X79" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y79" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z79" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A80" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C80" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J80" s="109" t="s">
+        <v>636</v>
+      </c>
+      <c r="N80" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P80" s="107" t="s">
+        <v>652</v>
+      </c>
       <c r="W80" s="65"/>
-      <c r="X80" s="104"/>
-      <c r="Y80" s="54"/>
-      <c r="Z80" s="66"/>
-    </row>
-    <row r="81" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X80" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y80" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z80" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A81" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C81" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J81" s="109" t="s">
+        <v>637</v>
+      </c>
+      <c r="N81" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P81" s="107" t="s">
+        <v>653</v>
+      </c>
       <c r="W81" s="65"/>
-      <c r="X81" s="104"/>
-      <c r="Y81" s="54"/>
-      <c r="Z81" s="66"/>
-    </row>
-    <row r="82" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X81" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y81" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z81" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A82" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C82" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J82" s="109" t="s">
+        <v>638</v>
+      </c>
+      <c r="N82" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P82" s="107" t="s">
+        <v>654</v>
+      </c>
       <c r="W82" s="65"/>
-      <c r="X82" s="104"/>
-      <c r="Y82" s="54"/>
-      <c r="Z82" s="66"/>
-    </row>
-    <row r="83" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X82" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y82" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z82" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A83" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C83" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J83" s="109" t="s">
+        <v>639</v>
+      </c>
+      <c r="N83" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P83" s="107" t="s">
+        <v>655</v>
+      </c>
       <c r="W83" s="65"/>
-      <c r="X83" s="104"/>
-      <c r="Y83" s="54"/>
-      <c r="Z83" s="66"/>
-    </row>
-    <row r="84" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X83" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y83" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z83" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A84" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C84" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J84" s="109" t="s">
+        <v>640</v>
+      </c>
+      <c r="N84" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P84" s="107" t="s">
+        <v>656</v>
+      </c>
       <c r="W84" s="65"/>
-      <c r="X84" s="104"/>
-      <c r="Y84" s="54"/>
-      <c r="Z84" s="66"/>
-    </row>
-    <row r="85" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X84" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y84" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z84" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A85" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C85" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J85" s="109" t="s">
+        <v>641</v>
+      </c>
+      <c r="N85" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P85" s="107" t="s">
+        <v>657</v>
+      </c>
       <c r="W85" s="65"/>
-      <c r="X85" s="104"/>
-      <c r="Y85" s="54"/>
-      <c r="Z85" s="66"/>
-    </row>
-    <row r="86" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X85" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y85" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z85" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A86" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C86" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J86" s="109" t="s">
+        <v>607</v>
+      </c>
+      <c r="N86" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P86" s="107" t="s">
+        <v>627</v>
+      </c>
       <c r="W86" s="65"/>
-      <c r="X86" s="104"/>
-      <c r="Y86" s="54"/>
-      <c r="Z86" s="66"/>
-    </row>
-    <row r="87" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X86" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y86" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z86" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.StationSelected</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A87" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C87" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J87" s="109" t="s">
+        <v>642</v>
+      </c>
+      <c r="N87" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P87" s="107" t="s">
+        <v>658</v>
+      </c>
       <c r="W87" s="65"/>
-      <c r="X87" s="104"/>
-      <c r="Y87" s="54"/>
-      <c r="Z87" s="66"/>
-    </row>
-    <row r="88" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X87" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y87" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z87" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A88" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C88" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J88" s="109" t="s">
+        <v>643</v>
+      </c>
+      <c r="N88" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P88" s="107" t="s">
+        <v>659</v>
+      </c>
       <c r="W88" s="65"/>
-      <c r="X88" s="104"/>
-      <c r="Y88" s="54"/>
-      <c r="Z88" s="66"/>
-    </row>
-    <row r="89" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X88" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y88" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z88" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A89" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C89" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J89" s="109" t="s">
+        <v>644</v>
+      </c>
+      <c r="N89" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P89" s="107" t="s">
+        <v>660</v>
+      </c>
       <c r="W89" s="65"/>
-      <c r="X89" s="104"/>
-      <c r="Y89" s="54"/>
-      <c r="Z89" s="66"/>
-    </row>
-    <row r="90" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X89" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y89" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z89" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A90" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C90" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J90" s="109" t="s">
+        <v>645</v>
+      </c>
+      <c r="N90" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P90" s="107" t="s">
+        <v>661</v>
+      </c>
       <c r="W90" s="65"/>
-      <c r="X90" s="104"/>
-      <c r="Y90" s="54"/>
-      <c r="Z90" s="66"/>
-    </row>
-    <row r="91" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X90" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y90" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z90" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A91" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C91" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J91" s="109" t="s">
+        <v>646</v>
+      </c>
+      <c r="N91" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P91" s="107" t="s">
+        <v>662</v>
+      </c>
       <c r="W91" s="65"/>
-      <c r="X91" s="104"/>
-      <c r="Y91" s="54"/>
-      <c r="Z91" s="66"/>
-    </row>
-    <row r="92" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X91" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y91" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z91" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A92" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C92" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J92" s="109" t="s">
+        <v>647</v>
+      </c>
+      <c r="N92" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P92" s="107" t="s">
+        <v>663</v>
+      </c>
       <c r="W92" s="65"/>
-      <c r="X92" s="104"/>
-      <c r="Y92" s="54"/>
-      <c r="Z92" s="66"/>
-    </row>
-    <row r="93" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X92" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y92" s="6" t="str">
+        <f t="shared" ref="Y92:Y154" si="28">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N92,"spare"),"",IF(X92&lt;&gt;"",X92,N92))," ","-"))</f>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z92" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A93" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C93" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="N93" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W93" s="65"/>
-      <c r="X93" s="104"/>
-      <c r="Y93" s="54"/>
-      <c r="Z93" s="66"/>
-    </row>
-    <row r="94" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X93" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y93" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z93" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A94" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C94" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="N94" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W94" s="65"/>
-      <c r="X94" s="104"/>
-      <c r="Y94" s="54"/>
-      <c r="Z94" s="66"/>
-    </row>
-    <row r="95" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X94" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y94" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z94" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A95" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C95" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E95" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="N95" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W95" s="65"/>
-      <c r="X95" s="104"/>
-      <c r="Y95" s="54"/>
-      <c r="Z95" s="66"/>
-    </row>
-    <row r="96" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X95" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y95" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z95" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A96" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E96" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="N96" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W96" s="65"/>
-      <c r="X96" s="104"/>
-      <c r="Y96" s="54"/>
-      <c r="Z96" s="66"/>
-    </row>
-    <row r="97" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X96" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y96" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z96" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A97" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="N97" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W97" s="65"/>
-      <c r="X97" s="104"/>
-      <c r="Y97" s="54"/>
-      <c r="Z97" s="66"/>
-    </row>
-    <row r="98" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X97" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y97" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z97" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A98" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C98" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="N98" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W98" s="65"/>
-      <c r="X98" s="104"/>
-      <c r="Y98" s="54"/>
-      <c r="Z98" s="66"/>
-    </row>
-    <row r="99" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X98" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y98" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z98" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A99" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C99" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E99" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="N99" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W99" s="65"/>
-      <c r="X99" s="104"/>
-      <c r="Y99" s="54"/>
-      <c r="Z99" s="66"/>
-    </row>
-    <row r="100" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X99" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y99" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z99" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A100" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C100" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E100" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="N100" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W100" s="65"/>
-      <c r="X100" s="104"/>
-      <c r="Y100" s="54"/>
-      <c r="Z100" s="66"/>
-    </row>
-    <row r="101" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X100" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y100" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z100" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A101" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C101" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="N101" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W101" s="65"/>
-      <c r="X101" s="104"/>
-      <c r="Y101" s="54"/>
-      <c r="Z101" s="66"/>
-    </row>
-    <row r="102" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X101" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y101" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z101" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A102" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C102" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="N102" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W102" s="65"/>
-      <c r="X102" s="104"/>
-      <c r="Y102" s="54"/>
-      <c r="Z102" s="66"/>
-    </row>
-    <row r="103" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X102" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y102" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z102" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A103" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C103" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="N103" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W103" s="65"/>
-      <c r="X103" s="104"/>
-      <c r="Y103" s="54"/>
-      <c r="Z103" s="66"/>
-    </row>
-    <row r="104" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X103" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y103" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z103" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A104" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C104" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E104" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="N104" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W104" s="65"/>
-      <c r="X104" s="104"/>
-      <c r="Y104" s="54"/>
-      <c r="Z104" s="66"/>
-    </row>
-    <row r="105" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X104" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y104" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z104" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A105" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C105" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="N105" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W105" s="65"/>
-      <c r="X105" s="104"/>
-      <c r="Y105" s="54"/>
-      <c r="Z105" s="66"/>
-    </row>
-    <row r="106" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X105" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y105" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z105" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A106" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C106" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="N106" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W106" s="65"/>
-      <c r="X106" s="104"/>
-      <c r="Y106" s="54"/>
-      <c r="Z106" s="66"/>
-    </row>
-    <row r="107" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X106" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y106" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z106" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A107" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C107" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="N107" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W107" s="65"/>
-      <c r="X107" s="104"/>
-      <c r="Y107" s="54"/>
-      <c r="Z107" s="66"/>
-    </row>
-    <row r="108" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X107" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y107" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z107" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A108" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C108" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E108" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J108" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="N108" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W108" s="65"/>
-      <c r="X108" s="104"/>
-      <c r="Y108" s="54"/>
-      <c r="Z108" s="66"/>
-    </row>
-    <row r="109" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X108" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y108" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z108" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A109" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C109" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J109" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="N109" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W109" s="65"/>
-      <c r="X109" s="104"/>
-      <c r="Y109" s="54"/>
-      <c r="Z109" s="66"/>
-    </row>
-    <row r="110" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X109" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y109" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z109" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A110" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C110" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J110" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="N110" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W110" s="65"/>
-      <c r="X110" s="104"/>
-      <c r="Y110" s="54"/>
-      <c r="Z110" s="66"/>
-    </row>
-    <row r="111" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X110" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y110" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z110" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A111" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C111" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E111" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J111" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="N111" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W111" s="65"/>
-      <c r="X111" s="104"/>
-      <c r="Y111" s="54"/>
-      <c r="Z111" s="66"/>
-    </row>
-    <row r="112" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X111" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y111" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z111" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A112" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C112" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E112" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J112" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="N112" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W112" s="65"/>
-      <c r="X112" s="104"/>
-      <c r="Y112" s="54"/>
-      <c r="Z112" s="66"/>
-    </row>
-    <row r="113" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X112" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y112" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z112" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A113" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C113" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E113" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="N113" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W113" s="65"/>
-      <c r="X113" s="104"/>
-      <c r="Y113" s="54"/>
-      <c r="Z113" s="66"/>
-    </row>
-    <row r="114" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X113" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y113" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z113" s="64" t="str">
+        <f t="shared" ref="Z113:Z116" si="29">IF(COUNTIF(N113,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J113,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Aradex_1_speed_feedback</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A114" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C114" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E114" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="N114" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W114" s="65"/>
-      <c r="X114" s="104"/>
-      <c r="Y114" s="54"/>
-      <c r="Z114" s="66"/>
-    </row>
-    <row r="115" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X114" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y114" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z114" s="64" t="str">
+        <f t="shared" si="29"/>
+        <v>$.Aradex_2_speed_feedback</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A115" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C115" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E115" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="N115" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W115" s="65"/>
-      <c r="X115" s="104"/>
-      <c r="Y115" s="54"/>
-      <c r="Z115" s="66"/>
-    </row>
-    <row r="116" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X115" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y115" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z115" s="64" t="str">
+        <f t="shared" si="29"/>
+        <v>$.Aradex_1_speed_feedback</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A116" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C116" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E116" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="N116" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W116" s="65"/>
-      <c r="X116" s="104"/>
-      <c r="Y116" s="54"/>
-      <c r="Z116" s="66"/>
-    </row>
-    <row r="117" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X116" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y116" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z116" s="64" t="str">
+        <f t="shared" si="29"/>
+        <v>$.Aradex_2_speed_feedback</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A117" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C117" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E117" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J117" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="N117" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W117" s="65"/>
-      <c r="X117" s="104"/>
-      <c r="Y117" s="54"/>
-      <c r="Z117" s="66"/>
-    </row>
-    <row r="118" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X117" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y117" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z117" s="64" t="str">
+        <f t="shared" ref="Z117:Z128" si="30">IF(COUNTIF(N117,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J117,"(SB|Sb|PS|Ps) ?Helm ?",""),"(\.| |/)","_"))</f>
+        <v>$.AFT_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A118" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C118" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E118" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="N118" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W118" s="65"/>
-      <c r="X118" s="104"/>
-      <c r="Y118" s="54"/>
-      <c r="Z118" s="66"/>
-    </row>
-    <row r="119" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X118" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y118" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z118" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWD_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A119" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C119" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E119" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="N119" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W119" s="65"/>
-      <c r="X119" s="104"/>
-      <c r="Y119" s="54"/>
-      <c r="Z119" s="66"/>
-    </row>
-    <row r="120" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X119" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y119" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z119" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.AFT_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A120" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C120" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E120" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="N120" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W120" s="65"/>
-      <c r="X120" s="104"/>
-      <c r="Y120" s="54"/>
-      <c r="Z120" s="66"/>
-    </row>
-    <row r="121" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X120" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y120" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z120" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWD_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A121" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C121" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J121" s="106" t="s">
+        <v>694</v>
+      </c>
+      <c r="N121" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P121" s="107" t="s">
+        <v>702</v>
+      </c>
       <c r="W121" s="65"/>
-      <c r="X121" s="104"/>
-      <c r="Y121" s="54"/>
-      <c r="Z121" s="66"/>
-    </row>
-    <row r="122" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X121" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y121" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z121" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A122" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C122" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J122" s="106" t="s">
+        <v>695</v>
+      </c>
+      <c r="N122" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P122" s="107" t="s">
+        <v>707</v>
+      </c>
       <c r="W122" s="65"/>
-      <c r="X122" s="104"/>
-      <c r="Y122" s="54"/>
-      <c r="Z122" s="66"/>
-    </row>
-    <row r="123" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X122" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y122" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z122" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A123" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J123" s="106" t="s">
+        <v>696</v>
+      </c>
+      <c r="N123" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P123" s="107" t="s">
+        <v>703</v>
+      </c>
       <c r="W123" s="65"/>
-      <c r="X123" s="104"/>
-      <c r="Y123" s="54"/>
-      <c r="Z123" s="66"/>
-    </row>
-    <row r="124" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X123" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y123" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z123" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A124" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C124" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J124" s="106" t="s">
+        <v>699</v>
+      </c>
+      <c r="N124" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P124" s="107" t="s">
+        <v>708</v>
+      </c>
       <c r="W124" s="65"/>
-      <c r="X124" s="104"/>
-      <c r="Y124" s="54"/>
-      <c r="Z124" s="66"/>
-    </row>
-    <row r="125" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X124" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y124" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z124" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A125" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C125" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J125" s="106" t="s">
+        <v>697</v>
+      </c>
+      <c r="N125" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P125" s="107" t="s">
+        <v>704</v>
+      </c>
       <c r="W125" s="65"/>
-      <c r="X125" s="104"/>
-      <c r="Y125" s="54"/>
-      <c r="Z125" s="66"/>
-    </row>
-    <row r="126" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X125" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y125" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z125" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A126" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C126" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J126" s="106" t="s">
+        <v>700</v>
+      </c>
+      <c r="N126" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P126" s="107" t="s">
+        <v>709</v>
+      </c>
       <c r="W126" s="65"/>
-      <c r="X126" s="104"/>
-      <c r="Y126" s="54"/>
-      <c r="Z126" s="66"/>
-    </row>
-    <row r="127" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X126" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y126" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z126" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A127" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C127" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J127" s="106" t="s">
+        <v>698</v>
+      </c>
+      <c r="N127" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P127" s="107" t="s">
+        <v>705</v>
+      </c>
       <c r="W127" s="65"/>
-      <c r="X127" s="104"/>
-      <c r="Y127" s="54"/>
-      <c r="Z127" s="66"/>
-    </row>
-    <row r="128" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X127" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y127" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z127" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A128" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J128" s="106" t="s">
+        <v>701</v>
+      </c>
+      <c r="N128" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P128" s="107" t="s">
+        <v>706</v>
+      </c>
       <c r="W128" s="65"/>
-      <c r="X128" s="104"/>
-      <c r="Y128" s="54"/>
-      <c r="Z128" s="66"/>
-    </row>
-    <row r="129" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X128" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y128" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z128" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A129" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C129" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E129" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="N129" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W129" s="65"/>
-      <c r="X129" s="104"/>
-      <c r="Y129" s="54"/>
-      <c r="Z129" s="66"/>
-    </row>
-    <row r="130" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X129" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y129" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z129" s="64" t="str">
+        <f t="shared" ref="Z129:Z154" si="31">IF(COUNTIF(N129,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J129,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Aradex_1_torque_feedback</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A130" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C130" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E130" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="N130" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W130" s="65"/>
-      <c r="X130" s="104"/>
-      <c r="Y130" s="54"/>
-      <c r="Z130" s="66"/>
-    </row>
-    <row r="131" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X130" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y130" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z130" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Aradex_2_torque_feedback</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A131" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C131" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E131" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="N131" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W131" s="65"/>
-      <c r="X131" s="104"/>
-      <c r="Y131" s="54"/>
-      <c r="Z131" s="66"/>
-    </row>
-    <row r="132" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X131" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y131" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z131" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Aradex_1_torque_feedback</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A132" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C132" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E132" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J132" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="N132" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W132" s="65"/>
-      <c r="X132" s="104"/>
-      <c r="Y132" s="54"/>
-      <c r="Z132" s="66"/>
-    </row>
-    <row r="133" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X132" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y132" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z132" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Aradex_2_torque_feedback</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A133" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C133" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E133" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J133" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="N133" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W133" s="65"/>
-      <c r="X133" s="104"/>
-      <c r="Y133" s="54"/>
-      <c r="Z133" s="66"/>
-    </row>
-    <row r="134" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X133" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y133" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z133" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_speed_control</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A134" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C134" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E134" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="N134" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W134" s="65"/>
-      <c r="X134" s="104"/>
-      <c r="Y134" s="54"/>
-      <c r="Z134" s="66"/>
-    </row>
-    <row r="135" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X134" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y134" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z134" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_torque_control</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A135" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C135" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E135" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="N135" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W135" s="65"/>
-      <c r="X135" s="104"/>
-      <c r="Y135" s="54"/>
-      <c r="Z135" s="66"/>
-    </row>
-    <row r="136" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X135" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y135" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z135" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_speed_control</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A136" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C136" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E136" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J136" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="N136" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W136" s="65"/>
-      <c r="X136" s="104"/>
-      <c r="Y136" s="54"/>
-      <c r="Z136" s="66"/>
-    </row>
-    <row r="137" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X136" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y136" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z136" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_torque_control</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A137" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C137" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E137" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J137" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="N137" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W137" s="65"/>
-      <c r="X137" s="104"/>
-      <c r="Y137" s="54"/>
-      <c r="Z137" s="66"/>
-    </row>
-    <row r="138" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X137" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y137" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z137" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A138" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C138" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E138" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J138" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="N138" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W138" s="65"/>
-      <c r="X138" s="104"/>
-      <c r="Y138" s="54"/>
-      <c r="Z138" s="66"/>
-    </row>
-    <row r="139" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X138" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y138" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z138" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A139" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C139" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E139" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J139" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="N139" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W139" s="65"/>
-      <c r="X139" s="104"/>
-      <c r="Y139" s="54"/>
-      <c r="Z139" s="66"/>
-    </row>
-    <row r="140" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X139" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y139" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z139" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A140" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C140" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E140" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J140" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="N140" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W140" s="65"/>
-      <c r="X140" s="104"/>
-      <c r="Y140" s="54"/>
-      <c r="Z140" s="66"/>
-    </row>
-    <row r="141" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X140" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y140" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z140" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A141" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C141" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E141" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J141" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="N141" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W141" s="65"/>
-      <c r="X141" s="104"/>
-      <c r="Y141" s="54"/>
-      <c r="Z141" s="66"/>
-    </row>
-    <row r="142" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X141" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y141" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z141" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.pitch_rate_of_change</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A142" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C142" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E142" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J142" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="N142" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W142" s="65"/>
-      <c r="X142" s="104"/>
-      <c r="Y142" s="54"/>
-      <c r="Z142" s="66"/>
-    </row>
-    <row r="143" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X142" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y142" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z142" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_pitch</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A143" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C143" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E143" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J143" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="N143" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W143" s="65"/>
-      <c r="X143" s="104"/>
-      <c r="Y143" s="54"/>
-      <c r="Z143" s="66"/>
-    </row>
-    <row r="144" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X143" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y143" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z143" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_pitch</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A144" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C144" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E144" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J144" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="N144" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W144" s="65"/>
-      <c r="X144" s="104"/>
-      <c r="Y144" s="54"/>
-      <c r="Z144" s="66"/>
-    </row>
-    <row r="145" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X144" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y144" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z144" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.torque_constant</v>
+      </c>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A145" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C145" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E145" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J145" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="N145" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W145" s="65"/>
-      <c r="X145" s="104"/>
-      <c r="Y145" s="54"/>
-      <c r="Z145" s="66"/>
-    </row>
-    <row r="146" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X145" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y145" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z145" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.pitch_rate_of_change</v>
+      </c>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A146" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C146" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E146" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J146" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="N146" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W146" s="65"/>
-      <c r="X146" s="104"/>
-      <c r="Y146" s="54"/>
-      <c r="Z146" s="66"/>
-    </row>
-    <row r="147" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X146" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y146" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z146" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_pitch</v>
+      </c>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A147" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C147" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E147" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J147" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="N147" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W147" s="65"/>
-      <c r="X147" s="104"/>
-      <c r="Y147" s="54"/>
-      <c r="Z147" s="66"/>
-    </row>
-    <row r="148" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X147" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y147" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z147" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_pitch</v>
+      </c>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A148" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C148" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E148" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J148" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="N148" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W148" s="65"/>
-      <c r="X148" s="104"/>
-      <c r="Y148" s="54"/>
-      <c r="Z148" s="66"/>
-    </row>
-    <row r="149" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X148" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y148" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z148" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.torque_constant</v>
+      </c>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A149" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C149" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E149" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J149" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="N149" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W149" s="65"/>
-      <c r="X149" s="104"/>
-      <c r="Y149" s="54"/>
-      <c r="Z149" s="66"/>
-    </row>
-    <row r="150" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X149" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y149" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z149" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.high_trust_control</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A150" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C150" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E150" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J150" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="N150" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W150" s="65"/>
-      <c r="X150" s="104"/>
-      <c r="Y150" s="54"/>
-      <c r="Z150" s="66"/>
-    </row>
-    <row r="151" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X150" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y150" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z150" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.normal_control</v>
+      </c>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A151" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C151" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E151" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J151" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="N151" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W151" s="65"/>
-      <c r="X151" s="104"/>
-      <c r="Y151" s="54"/>
-      <c r="Z151" s="66"/>
-    </row>
-    <row r="152" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X151" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y151" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z151" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.motorsail_control</v>
+      </c>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A152" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C152" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E152" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="N152" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W152" s="65"/>
-      <c r="X152" s="104"/>
-      <c r="Y152" s="54"/>
-      <c r="Z152" s="66"/>
-    </row>
-    <row r="153" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X152" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y152" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z152" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.high_trust_control</v>
+      </c>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A153" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C153" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E153" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="N153" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W153" s="65"/>
-      <c r="X153" s="104"/>
-      <c r="Y153" s="54"/>
-      <c r="Z153" s="66"/>
-    </row>
-    <row r="154" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X153" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y153" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z153" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.normal_control</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A154" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C154" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E154" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J154" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="N154" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W154" s="65"/>
-      <c r="X154" s="104"/>
-      <c r="Y154" s="54"/>
-      <c r="Z154" s="66"/>
-    </row>
-    <row r="155" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X154" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y154" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z154" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.motorsail_control</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W155" s="65"/>
       <c r="X155" s="104"/>
-      <c r="Y155" s="54"/>
+      <c r="Y155" s="6"/>
       <c r="Z155" s="66"/>
     </row>
-    <row r="156" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W156" s="65"/>
       <c r="X156" s="104"/>
-      <c r="Y156" s="54"/>
+      <c r="Y156" s="6"/>
       <c r="Z156" s="66"/>
     </row>
-    <row r="157" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W157" s="65"/>
       <c r="X157" s="104"/>
-      <c r="Y157" s="54"/>
+      <c r="Y157" s="6"/>
       <c r="Z157" s="66"/>
     </row>
-    <row r="158" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W158" s="65"/>
       <c r="X158" s="104"/>
-      <c r="Y158" s="54"/>
+      <c r="Y158" s="6"/>
       <c r="Z158" s="66"/>
     </row>
-    <row r="159" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W159" s="65"/>
       <c r="X159" s="104"/>
-      <c r="Y159" s="54"/>
+      <c r="Y159" s="6"/>
       <c r="Z159" s="66"/>
     </row>
-    <row r="160" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W160" s="65"/>
       <c r="X160" s="104"/>
-      <c r="Y160" s="54"/>
+      <c r="Y160" s="6"/>
       <c r="Z160" s="66"/>
     </row>
     <row r="161" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W161" s="65"/>
       <c r="X161" s="104"/>
-      <c r="Y161" s="54"/>
+      <c r="Y161" s="6"/>
       <c r="Z161" s="66"/>
     </row>
     <row r="162" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W162" s="65"/>
       <c r="X162" s="104"/>
-      <c r="Y162" s="54"/>
+      <c r="Y162" s="6"/>
       <c r="Z162" s="66"/>
     </row>
     <row r="163" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W163" s="65"/>
       <c r="X163" s="104"/>
-      <c r="Y163" s="54"/>
+      <c r="Y163" s="6"/>
       <c r="Z163" s="66"/>
     </row>
     <row r="164" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W164" s="65"/>
       <c r="X164" s="104"/>
-      <c r="Y164" s="54"/>
+      <c r="Y164" s="6"/>
       <c r="Z164" s="66"/>
     </row>
     <row r="165" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W165" s="65"/>
       <c r="X165" s="104"/>
-      <c r="Y165" s="54"/>
+      <c r="Y165" s="6"/>
       <c r="Z165" s="66"/>
     </row>
     <row r="166" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W166" s="65"/>
       <c r="X166" s="104"/>
-      <c r="Y166" s="54"/>
+      <c r="Y166" s="6"/>
       <c r="Z166" s="66"/>
     </row>
     <row r="167" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W167" s="65"/>
       <c r="X167" s="104"/>
-      <c r="Y167" s="54"/>
+      <c r="Y167" s="6"/>
       <c r="Z167" s="66"/>
     </row>
     <row r="168" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W168" s="65"/>
       <c r="X168" s="104"/>
-      <c r="Y168" s="54"/>
+      <c r="Y168" s="6"/>
       <c r="Z168" s="66"/>
     </row>
     <row r="169" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W169" s="65"/>
       <c r="X169" s="104"/>
-      <c r="Y169" s="54"/>
+      <c r="Y169" s="6"/>
       <c r="Z169" s="66"/>
     </row>
     <row r="170" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W170" s="65"/>
       <c r="X170" s="104"/>
-      <c r="Y170" s="54"/>
+      <c r="Y170" s="6"/>
       <c r="Z170" s="66"/>
     </row>
     <row r="171" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W171" s="65"/>
       <c r="X171" s="104"/>
-      <c r="Y171" s="54"/>
+      <c r="Y171" s="6"/>
       <c r="Z171" s="66"/>
     </row>
     <row r="172" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W172" s="65"/>
       <c r="X172" s="104"/>
-      <c r="Y172" s="54"/>
+      <c r="Y172" s="6"/>
       <c r="Z172" s="66"/>
     </row>
     <row r="173" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W173" s="65"/>
       <c r="X173" s="104"/>
-      <c r="Y173" s="54"/>
+      <c r="Y173" s="6"/>
       <c r="Z173" s="66"/>
     </row>
     <row r="174" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W174" s="65"/>
       <c r="X174" s="104"/>
-      <c r="Y174" s="54"/>
+      <c r="Y174" s="6"/>
       <c r="Z174" s="66"/>
     </row>
     <row r="175" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W175" s="65"/>
       <c r="X175" s="104"/>
-      <c r="Y175" s="54"/>
+      <c r="Y175" s="6"/>
       <c r="Z175" s="66"/>
     </row>
     <row r="176" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W176" s="65"/>
       <c r="X176" s="104"/>
-      <c r="Y176" s="54"/>
+      <c r="Y176" s="6"/>
       <c r="Z176" s="66"/>
     </row>
     <row r="177" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W177" s="65"/>
       <c r="X177" s="104"/>
-      <c r="Y177" s="54"/>
+      <c r="Y177" s="6"/>
       <c r="Z177" s="66"/>
     </row>
     <row r="178" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W178" s="65"/>
       <c r="X178" s="104"/>
-      <c r="Y178" s="54"/>
+      <c r="Y178" s="6"/>
       <c r="Z178" s="66"/>
     </row>
     <row r="179" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W179" s="65"/>
       <c r="X179" s="104"/>
-      <c r="Y179" s="54"/>
+      <c r="Y179" s="6"/>
       <c r="Z179" s="66"/>
     </row>
     <row r="180" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W180" s="65"/>
       <c r="X180" s="104"/>
-      <c r="Y180" s="54"/>
+      <c r="Y180" s="6"/>
       <c r="Z180" s="66"/>
     </row>
     <row r="181" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W181" s="65"/>
       <c r="X181" s="104"/>
-      <c r="Y181" s="54"/>
+      <c r="Y181" s="6"/>
       <c r="Z181" s="66"/>
     </row>
     <row r="182" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W182" s="65"/>
       <c r="X182" s="104"/>
-      <c r="Y182" s="54"/>
+      <c r="Y182" s="6"/>
       <c r="Z182" s="66"/>
     </row>
     <row r="183" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W183" s="65"/>
       <c r="X183" s="104"/>
-      <c r="Y183" s="54"/>
+      <c r="Y183" s="6"/>
       <c r="Z183" s="66"/>
     </row>
     <row r="184" spans="23:26" x14ac:dyDescent="0.25">
@@ -58954,1174 +63054,36 @@
       <c r="Y8785" s="54"/>
       <c r="Z8785" s="66"/>
     </row>
-    <row r="8786" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8786" s="65"/>
-      <c r="X8786" s="104"/>
-      <c r="Y8786" s="54"/>
-      <c r="Z8786" s="66"/>
-    </row>
-    <row r="8787" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8787" s="65"/>
-      <c r="X8787" s="104"/>
-      <c r="Y8787" s="54"/>
-      <c r="Z8787" s="66"/>
-    </row>
-    <row r="8788" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8788" s="65"/>
-      <c r="X8788" s="104"/>
-      <c r="Y8788" s="54"/>
-      <c r="Z8788" s="66"/>
-    </row>
-    <row r="8789" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8789" s="65"/>
-      <c r="X8789" s="104"/>
-      <c r="Y8789" s="54"/>
-      <c r="Z8789" s="66"/>
-    </row>
-    <row r="8790" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8790" s="65"/>
-      <c r="X8790" s="104"/>
-      <c r="Y8790" s="54"/>
-      <c r="Z8790" s="66"/>
-    </row>
-    <row r="8791" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8791" s="65"/>
-      <c r="X8791" s="104"/>
-      <c r="Y8791" s="54"/>
-      <c r="Z8791" s="66"/>
-    </row>
-    <row r="8792" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8792" s="65"/>
-      <c r="X8792" s="104"/>
-      <c r="Y8792" s="54"/>
-      <c r="Z8792" s="66"/>
-    </row>
-    <row r="8793" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8793" s="65"/>
-      <c r="X8793" s="104"/>
-      <c r="Y8793" s="54"/>
-      <c r="Z8793" s="66"/>
-    </row>
-    <row r="8794" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8794" s="65"/>
-      <c r="X8794" s="104"/>
-      <c r="Y8794" s="54"/>
-      <c r="Z8794" s="66"/>
-    </row>
-    <row r="8795" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8795" s="65"/>
-      <c r="X8795" s="104"/>
-      <c r="Y8795" s="54"/>
-      <c r="Z8795" s="66"/>
-    </row>
-    <row r="8796" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8796" s="65"/>
-      <c r="X8796" s="104"/>
-      <c r="Y8796" s="54"/>
-      <c r="Z8796" s="66"/>
-    </row>
-    <row r="8797" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8797" s="65"/>
-      <c r="X8797" s="104"/>
-      <c r="Y8797" s="54"/>
-      <c r="Z8797" s="66"/>
-    </row>
-    <row r="8798" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8798" s="65"/>
-      <c r="X8798" s="104"/>
-      <c r="Y8798" s="54"/>
-      <c r="Z8798" s="66"/>
-    </row>
-    <row r="8799" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8799" s="65"/>
-      <c r="X8799" s="104"/>
-      <c r="Y8799" s="54"/>
-      <c r="Z8799" s="66"/>
-    </row>
-    <row r="8800" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8800" s="65"/>
-      <c r="X8800" s="104"/>
-      <c r="Y8800" s="54"/>
-      <c r="Z8800" s="66"/>
-    </row>
-    <row r="8801" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8801" s="65"/>
-      <c r="X8801" s="104"/>
-      <c r="Y8801" s="54"/>
-      <c r="Z8801" s="66"/>
-    </row>
-    <row r="8802" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8802" s="65"/>
-      <c r="X8802" s="104"/>
-      <c r="Y8802" s="54"/>
-      <c r="Z8802" s="66"/>
-    </row>
-    <row r="8803" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8803" s="65"/>
-      <c r="X8803" s="104"/>
-      <c r="Y8803" s="54"/>
-      <c r="Z8803" s="66"/>
-    </row>
-    <row r="8804" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8804" s="65"/>
-      <c r="X8804" s="104"/>
-      <c r="Y8804" s="54"/>
-      <c r="Z8804" s="66"/>
-    </row>
-    <row r="8805" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8805" s="65"/>
-      <c r="X8805" s="104"/>
-      <c r="Y8805" s="54"/>
-      <c r="Z8805" s="66"/>
-    </row>
-    <row r="8806" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8806" s="65"/>
-      <c r="X8806" s="104"/>
-      <c r="Y8806" s="54"/>
-      <c r="Z8806" s="66"/>
-    </row>
-    <row r="8807" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8807" s="65"/>
-      <c r="X8807" s="104"/>
-      <c r="Y8807" s="54"/>
-      <c r="Z8807" s="66"/>
-    </row>
-    <row r="8808" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8808" s="65"/>
-      <c r="X8808" s="104"/>
-      <c r="Y8808" s="54"/>
-      <c r="Z8808" s="66"/>
-    </row>
-    <row r="8809" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8809" s="65"/>
-      <c r="X8809" s="104"/>
-      <c r="Y8809" s="54"/>
-      <c r="Z8809" s="66"/>
-    </row>
-    <row r="8810" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8810" s="65"/>
-      <c r="X8810" s="104"/>
-      <c r="Y8810" s="54"/>
-      <c r="Z8810" s="66"/>
-    </row>
-    <row r="8811" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8811" s="65"/>
-      <c r="X8811" s="104"/>
-      <c r="Y8811" s="54"/>
-      <c r="Z8811" s="66"/>
-    </row>
-    <row r="8812" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8812" s="65"/>
-      <c r="X8812" s="104"/>
-      <c r="Y8812" s="54"/>
-      <c r="Z8812" s="66"/>
-    </row>
-    <row r="8813" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8813" s="65"/>
-      <c r="X8813" s="104"/>
-      <c r="Y8813" s="54"/>
-      <c r="Z8813" s="66"/>
-    </row>
-    <row r="8814" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8814" s="65"/>
-      <c r="X8814" s="104"/>
-      <c r="Y8814" s="54"/>
-      <c r="Z8814" s="66"/>
-    </row>
-    <row r="8815" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8815" s="65"/>
-      <c r="X8815" s="104"/>
-      <c r="Y8815" s="54"/>
-      <c r="Z8815" s="66"/>
-    </row>
-    <row r="8816" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8816" s="65"/>
-      <c r="X8816" s="104"/>
-      <c r="Y8816" s="54"/>
-      <c r="Z8816" s="66"/>
-    </row>
-    <row r="8817" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8817" s="65"/>
-      <c r="X8817" s="104"/>
-      <c r="Y8817" s="54"/>
-      <c r="Z8817" s="66"/>
-    </row>
-    <row r="8818" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8818" s="65"/>
-      <c r="X8818" s="104"/>
-      <c r="Y8818" s="54"/>
-      <c r="Z8818" s="66"/>
-    </row>
-    <row r="8819" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8819" s="65"/>
-      <c r="X8819" s="104"/>
-      <c r="Y8819" s="54"/>
-      <c r="Z8819" s="66"/>
-    </row>
-    <row r="8820" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8820" s="65"/>
-      <c r="X8820" s="104"/>
-      <c r="Y8820" s="54"/>
-      <c r="Z8820" s="66"/>
-    </row>
-    <row r="8821" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8821" s="65"/>
-      <c r="X8821" s="104"/>
-      <c r="Y8821" s="54"/>
-      <c r="Z8821" s="66"/>
-    </row>
-    <row r="8822" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8822" s="65"/>
-      <c r="X8822" s="104"/>
-      <c r="Y8822" s="54"/>
-      <c r="Z8822" s="66"/>
-    </row>
-    <row r="8823" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8823" s="65"/>
-      <c r="X8823" s="104"/>
-      <c r="Y8823" s="54"/>
-      <c r="Z8823" s="66"/>
-    </row>
-    <row r="8824" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8824" s="65"/>
-      <c r="X8824" s="104"/>
-      <c r="Y8824" s="54"/>
-      <c r="Z8824" s="66"/>
-    </row>
-    <row r="8825" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8825" s="65"/>
-      <c r="X8825" s="104"/>
-      <c r="Y8825" s="54"/>
-      <c r="Z8825" s="66"/>
-    </row>
-    <row r="8826" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8826" s="65"/>
-      <c r="X8826" s="104"/>
-      <c r="Y8826" s="54"/>
-      <c r="Z8826" s="66"/>
-    </row>
-    <row r="8827" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8827" s="65"/>
-      <c r="X8827" s="104"/>
-      <c r="Y8827" s="54"/>
-      <c r="Z8827" s="66"/>
-    </row>
-    <row r="8828" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8828" s="65"/>
-      <c r="X8828" s="104"/>
-      <c r="Y8828" s="54"/>
-      <c r="Z8828" s="66"/>
-    </row>
-    <row r="8829" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8829" s="65"/>
-      <c r="X8829" s="104"/>
-      <c r="Y8829" s="54"/>
-      <c r="Z8829" s="66"/>
-    </row>
-    <row r="8830" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8830" s="65"/>
-      <c r="X8830" s="104"/>
-      <c r="Y8830" s="54"/>
-      <c r="Z8830" s="66"/>
-    </row>
-    <row r="8831" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8831" s="65"/>
-      <c r="X8831" s="104"/>
-      <c r="Y8831" s="54"/>
-      <c r="Z8831" s="66"/>
-    </row>
-    <row r="8832" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8832" s="65"/>
-      <c r="X8832" s="104"/>
-      <c r="Y8832" s="54"/>
-      <c r="Z8832" s="66"/>
-    </row>
-    <row r="8833" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8833" s="65"/>
-      <c r="X8833" s="104"/>
-      <c r="Y8833" s="54"/>
-      <c r="Z8833" s="66"/>
-    </row>
-    <row r="8834" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8834" s="65"/>
-      <c r="X8834" s="104"/>
-      <c r="Y8834" s="54"/>
-      <c r="Z8834" s="66"/>
-    </row>
-    <row r="8835" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8835" s="65"/>
-      <c r="X8835" s="104"/>
-      <c r="Y8835" s="54"/>
-      <c r="Z8835" s="66"/>
-    </row>
-    <row r="8836" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8836" s="65"/>
-      <c r="X8836" s="104"/>
-      <c r="Y8836" s="54"/>
-      <c r="Z8836" s="66"/>
-    </row>
-    <row r="8837" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8837" s="65"/>
-      <c r="X8837" s="104"/>
-      <c r="Y8837" s="54"/>
-      <c r="Z8837" s="66"/>
-    </row>
-    <row r="8838" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8838" s="65"/>
-      <c r="X8838" s="104"/>
-      <c r="Y8838" s="54"/>
-      <c r="Z8838" s="66"/>
-    </row>
-    <row r="8839" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8839" s="65"/>
-      <c r="X8839" s="104"/>
-      <c r="Y8839" s="54"/>
-      <c r="Z8839" s="66"/>
-    </row>
-    <row r="8840" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8840" s="65"/>
-      <c r="X8840" s="104"/>
-      <c r="Y8840" s="54"/>
-      <c r="Z8840" s="66"/>
-    </row>
-    <row r="8841" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8841" s="65"/>
-      <c r="X8841" s="104"/>
-      <c r="Y8841" s="54"/>
-      <c r="Z8841" s="66"/>
-    </row>
-    <row r="8842" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8842" s="65"/>
-      <c r="X8842" s="104"/>
-      <c r="Y8842" s="54"/>
-      <c r="Z8842" s="66"/>
-    </row>
-    <row r="8843" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8843" s="65"/>
-      <c r="X8843" s="104"/>
-      <c r="Y8843" s="54"/>
-      <c r="Z8843" s="66"/>
-    </row>
-    <row r="8844" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8844" s="65"/>
-      <c r="X8844" s="104"/>
-      <c r="Y8844" s="54"/>
-      <c r="Z8844" s="66"/>
-    </row>
-    <row r="8845" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8845" s="65"/>
-      <c r="X8845" s="104"/>
-      <c r="Y8845" s="54"/>
-      <c r="Z8845" s="66"/>
-    </row>
-    <row r="8846" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8846" s="65"/>
-      <c r="X8846" s="104"/>
-      <c r="Y8846" s="54"/>
-      <c r="Z8846" s="66"/>
-    </row>
-    <row r="8847" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8847" s="65"/>
-      <c r="X8847" s="104"/>
-      <c r="Y8847" s="54"/>
-      <c r="Z8847" s="66"/>
-    </row>
-    <row r="8848" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8848" s="65"/>
-      <c r="X8848" s="104"/>
-      <c r="Y8848" s="54"/>
-      <c r="Z8848" s="66"/>
-    </row>
-    <row r="8849" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8849" s="65"/>
-      <c r="X8849" s="104"/>
-      <c r="Y8849" s="54"/>
-      <c r="Z8849" s="66"/>
-    </row>
-    <row r="8850" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8850" s="65"/>
-      <c r="X8850" s="104"/>
-      <c r="Y8850" s="54"/>
-      <c r="Z8850" s="66"/>
-    </row>
-    <row r="8851" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8851" s="65"/>
-      <c r="X8851" s="104"/>
-      <c r="Y8851" s="54"/>
-      <c r="Z8851" s="66"/>
-    </row>
-    <row r="8852" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8852" s="65"/>
-      <c r="X8852" s="104"/>
-      <c r="Y8852" s="54"/>
-      <c r="Z8852" s="66"/>
-    </row>
-    <row r="8853" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8853" s="65"/>
-      <c r="X8853" s="104"/>
-      <c r="Y8853" s="54"/>
-      <c r="Z8853" s="66"/>
-    </row>
-    <row r="8854" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8854" s="65"/>
-      <c r="X8854" s="104"/>
-      <c r="Y8854" s="54"/>
-      <c r="Z8854" s="66"/>
-    </row>
-    <row r="8855" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8855" s="65"/>
-      <c r="X8855" s="104"/>
-      <c r="Y8855" s="54"/>
-      <c r="Z8855" s="66"/>
-    </row>
-    <row r="8856" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8856" s="65"/>
-      <c r="X8856" s="104"/>
-      <c r="Y8856" s="54"/>
-      <c r="Z8856" s="66"/>
-    </row>
-    <row r="8857" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8857" s="65"/>
-      <c r="X8857" s="104"/>
-      <c r="Y8857" s="54"/>
-      <c r="Z8857" s="66"/>
-    </row>
-    <row r="8858" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8858" s="65"/>
-      <c r="X8858" s="104"/>
-      <c r="Y8858" s="54"/>
-      <c r="Z8858" s="66"/>
-    </row>
-    <row r="8859" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8859" s="65"/>
-      <c r="X8859" s="104"/>
-      <c r="Y8859" s="54"/>
-      <c r="Z8859" s="66"/>
-    </row>
-    <row r="8860" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8860" s="65"/>
-      <c r="X8860" s="104"/>
-      <c r="Y8860" s="54"/>
-      <c r="Z8860" s="66"/>
-    </row>
-    <row r="8861" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8861" s="65"/>
-      <c r="X8861" s="104"/>
-      <c r="Y8861" s="54"/>
-      <c r="Z8861" s="66"/>
-    </row>
-    <row r="8862" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8862" s="65"/>
-      <c r="X8862" s="104"/>
-      <c r="Y8862" s="54"/>
-      <c r="Z8862" s="66"/>
-    </row>
-    <row r="8863" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8863" s="65"/>
-      <c r="X8863" s="104"/>
-      <c r="Y8863" s="54"/>
-      <c r="Z8863" s="66"/>
-    </row>
-    <row r="8864" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8864" s="65"/>
-      <c r="X8864" s="104"/>
-      <c r="Y8864" s="54"/>
-      <c r="Z8864" s="66"/>
-    </row>
-    <row r="8865" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8865" s="65"/>
-      <c r="X8865" s="104"/>
-      <c r="Y8865" s="54"/>
-      <c r="Z8865" s="66"/>
-    </row>
-    <row r="8866" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8866" s="65"/>
-      <c r="X8866" s="104"/>
-      <c r="Y8866" s="54"/>
-      <c r="Z8866" s="66"/>
-    </row>
-    <row r="8867" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8867" s="65"/>
-      <c r="X8867" s="104"/>
-      <c r="Y8867" s="54"/>
-      <c r="Z8867" s="66"/>
-    </row>
-    <row r="8868" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8868" s="65"/>
-      <c r="X8868" s="104"/>
-      <c r="Y8868" s="54"/>
-      <c r="Z8868" s="66"/>
-    </row>
-    <row r="8869" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8869" s="65"/>
-      <c r="X8869" s="104"/>
-      <c r="Y8869" s="54"/>
-      <c r="Z8869" s="66"/>
-    </row>
-    <row r="8870" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8870" s="65"/>
-      <c r="X8870" s="104"/>
-      <c r="Y8870" s="54"/>
-      <c r="Z8870" s="66"/>
-    </row>
-    <row r="8871" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8871" s="65"/>
-      <c r="X8871" s="104"/>
-      <c r="Y8871" s="54"/>
-      <c r="Z8871" s="66"/>
-    </row>
-    <row r="8872" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8872" s="65"/>
-      <c r="X8872" s="104"/>
-      <c r="Y8872" s="54"/>
-      <c r="Z8872" s="66"/>
-    </row>
-    <row r="8873" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8873" s="65"/>
-      <c r="X8873" s="104"/>
-      <c r="Y8873" s="54"/>
-      <c r="Z8873" s="66"/>
-    </row>
-    <row r="8874" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8874" s="65"/>
-      <c r="X8874" s="104"/>
-      <c r="Y8874" s="54"/>
-      <c r="Z8874" s="66"/>
-    </row>
-    <row r="8875" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8875" s="65"/>
-      <c r="X8875" s="104"/>
-      <c r="Y8875" s="54"/>
-      <c r="Z8875" s="66"/>
-    </row>
-    <row r="8876" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8876" s="65"/>
-      <c r="X8876" s="104"/>
-      <c r="Y8876" s="54"/>
-      <c r="Z8876" s="66"/>
-    </row>
-    <row r="8877" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8877" s="65"/>
-      <c r="X8877" s="104"/>
-      <c r="Y8877" s="54"/>
-      <c r="Z8877" s="66"/>
-    </row>
-    <row r="8878" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8878" s="65"/>
-      <c r="X8878" s="104"/>
-      <c r="Y8878" s="54"/>
-      <c r="Z8878" s="66"/>
-    </row>
-    <row r="8879" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8879" s="65"/>
-      <c r="X8879" s="104"/>
-      <c r="Y8879" s="54"/>
-      <c r="Z8879" s="66"/>
-    </row>
-    <row r="8880" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8880" s="65"/>
-      <c r="X8880" s="104"/>
-      <c r="Y8880" s="54"/>
-      <c r="Z8880" s="66"/>
-    </row>
-    <row r="8881" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8881" s="65"/>
-      <c r="X8881" s="104"/>
-      <c r="Y8881" s="54"/>
-      <c r="Z8881" s="66"/>
-    </row>
-    <row r="8882" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8882" s="65"/>
-      <c r="X8882" s="104"/>
-      <c r="Y8882" s="54"/>
-      <c r="Z8882" s="66"/>
-    </row>
-    <row r="8883" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8883" s="65"/>
-      <c r="X8883" s="104"/>
-      <c r="Y8883" s="54"/>
-      <c r="Z8883" s="66"/>
-    </row>
-    <row r="8884" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8884" s="65"/>
-      <c r="X8884" s="104"/>
-      <c r="Y8884" s="54"/>
-      <c r="Z8884" s="66"/>
-    </row>
-    <row r="8885" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8885" s="65"/>
-      <c r="X8885" s="104"/>
-      <c r="Y8885" s="54"/>
-      <c r="Z8885" s="66"/>
-    </row>
-    <row r="8886" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8886" s="65"/>
-      <c r="X8886" s="104"/>
-      <c r="Y8886" s="54"/>
-      <c r="Z8886" s="66"/>
-    </row>
-    <row r="8887" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8887" s="65"/>
-      <c r="X8887" s="104"/>
-      <c r="Y8887" s="54"/>
-      <c r="Z8887" s="66"/>
-    </row>
-    <row r="8888" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8888" s="65"/>
-      <c r="X8888" s="104"/>
-      <c r="Y8888" s="54"/>
-      <c r="Z8888" s="66"/>
-    </row>
-    <row r="8889" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8889" s="65"/>
-      <c r="X8889" s="104"/>
-      <c r="Y8889" s="54"/>
-      <c r="Z8889" s="66"/>
-    </row>
-    <row r="8890" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8890" s="65"/>
-      <c r="X8890" s="104"/>
-      <c r="Y8890" s="54"/>
-      <c r="Z8890" s="66"/>
-    </row>
-    <row r="8891" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8891" s="65"/>
-      <c r="X8891" s="104"/>
-      <c r="Y8891" s="54"/>
-      <c r="Z8891" s="66"/>
-    </row>
-    <row r="8892" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8892" s="65"/>
-      <c r="X8892" s="104"/>
-      <c r="Y8892" s="54"/>
-      <c r="Z8892" s="66"/>
-    </row>
-    <row r="8893" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8893" s="65"/>
-      <c r="X8893" s="104"/>
-      <c r="Y8893" s="54"/>
-      <c r="Z8893" s="66"/>
-    </row>
-    <row r="8894" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8894" s="65"/>
-      <c r="X8894" s="104"/>
-      <c r="Y8894" s="54"/>
-      <c r="Z8894" s="66"/>
-    </row>
-    <row r="8895" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8895" s="65"/>
-      <c r="X8895" s="104"/>
-      <c r="Y8895" s="54"/>
-      <c r="Z8895" s="66"/>
-    </row>
-    <row r="8896" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8896" s="65"/>
-      <c r="X8896" s="104"/>
-      <c r="Y8896" s="54"/>
-      <c r="Z8896" s="66"/>
-    </row>
-    <row r="8897" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8897" s="65"/>
-      <c r="X8897" s="104"/>
-      <c r="Y8897" s="54"/>
-      <c r="Z8897" s="66"/>
-    </row>
-    <row r="8898" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8898" s="65"/>
-      <c r="X8898" s="104"/>
-      <c r="Y8898" s="54"/>
-      <c r="Z8898" s="66"/>
-    </row>
-    <row r="8899" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8899" s="65"/>
-      <c r="X8899" s="104"/>
-      <c r="Y8899" s="54"/>
-      <c r="Z8899" s="66"/>
-    </row>
-    <row r="8900" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8900" s="65"/>
-      <c r="X8900" s="104"/>
-      <c r="Y8900" s="54"/>
-      <c r="Z8900" s="66"/>
-    </row>
-    <row r="8901" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8901" s="65"/>
-      <c r="X8901" s="104"/>
-      <c r="Y8901" s="54"/>
-      <c r="Z8901" s="66"/>
-    </row>
-    <row r="8902" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8902" s="65"/>
-      <c r="X8902" s="104"/>
-      <c r="Y8902" s="54"/>
-      <c r="Z8902" s="66"/>
-    </row>
-    <row r="8903" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8903" s="65"/>
-      <c r="X8903" s="104"/>
-      <c r="Y8903" s="54"/>
-      <c r="Z8903" s="66"/>
-    </row>
-    <row r="8904" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8904" s="65"/>
-      <c r="X8904" s="104"/>
-      <c r="Y8904" s="54"/>
-      <c r="Z8904" s="66"/>
-    </row>
-    <row r="8905" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8905" s="65"/>
-      <c r="X8905" s="104"/>
-      <c r="Y8905" s="54"/>
-      <c r="Z8905" s="66"/>
-    </row>
-    <row r="8906" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8906" s="65"/>
-      <c r="X8906" s="104"/>
-      <c r="Y8906" s="54"/>
-      <c r="Z8906" s="66"/>
-    </row>
-    <row r="8907" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8907" s="65"/>
-      <c r="X8907" s="104"/>
-      <c r="Y8907" s="54"/>
-      <c r="Z8907" s="66"/>
-    </row>
-    <row r="8908" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8908" s="65"/>
-      <c r="X8908" s="104"/>
-      <c r="Y8908" s="54"/>
-      <c r="Z8908" s="66"/>
-    </row>
-    <row r="8909" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8909" s="65"/>
-      <c r="X8909" s="104"/>
-      <c r="Y8909" s="54"/>
-      <c r="Z8909" s="66"/>
-    </row>
-    <row r="8910" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8910" s="65"/>
-      <c r="X8910" s="104"/>
-      <c r="Y8910" s="54"/>
-      <c r="Z8910" s="66"/>
-    </row>
-    <row r="8911" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8911" s="65"/>
-      <c r="X8911" s="104"/>
-      <c r="Y8911" s="54"/>
-      <c r="Z8911" s="66"/>
-    </row>
-    <row r="8912" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8912" s="65"/>
-      <c r="X8912" s="104"/>
-      <c r="Y8912" s="54"/>
-      <c r="Z8912" s="66"/>
-    </row>
-    <row r="8913" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8913" s="65"/>
-      <c r="X8913" s="104"/>
-      <c r="Y8913" s="54"/>
-      <c r="Z8913" s="66"/>
-    </row>
-    <row r="8914" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8914" s="65"/>
-      <c r="X8914" s="104"/>
-      <c r="Y8914" s="54"/>
-      <c r="Z8914" s="66"/>
-    </row>
-    <row r="8915" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8915" s="65"/>
-      <c r="X8915" s="104"/>
-      <c r="Y8915" s="54"/>
-      <c r="Z8915" s="66"/>
-    </row>
-    <row r="8916" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8916" s="65"/>
-      <c r="X8916" s="104"/>
-      <c r="Y8916" s="54"/>
-      <c r="Z8916" s="66"/>
-    </row>
-    <row r="8917" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8917" s="65"/>
-      <c r="X8917" s="104"/>
-      <c r="Y8917" s="54"/>
-      <c r="Z8917" s="66"/>
-    </row>
-    <row r="8918" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8918" s="65"/>
-      <c r="X8918" s="104"/>
-      <c r="Y8918" s="54"/>
-      <c r="Z8918" s="66"/>
-    </row>
-    <row r="8919" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8919" s="65"/>
-      <c r="X8919" s="104"/>
-      <c r="Y8919" s="54"/>
-      <c r="Z8919" s="66"/>
-    </row>
-    <row r="8920" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8920" s="65"/>
-      <c r="X8920" s="104"/>
-      <c r="Y8920" s="54"/>
-      <c r="Z8920" s="66"/>
-    </row>
-    <row r="8921" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8921" s="65"/>
-      <c r="X8921" s="104"/>
-      <c r="Y8921" s="54"/>
-      <c r="Z8921" s="66"/>
-    </row>
-    <row r="8922" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8922" s="65"/>
-      <c r="X8922" s="104"/>
-      <c r="Y8922" s="54"/>
-      <c r="Z8922" s="66"/>
-    </row>
-    <row r="8923" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8923" s="65"/>
-      <c r="X8923" s="104"/>
-      <c r="Y8923" s="54"/>
-      <c r="Z8923" s="66"/>
-    </row>
-    <row r="8924" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8924" s="65"/>
-      <c r="X8924" s="104"/>
-      <c r="Y8924" s="54"/>
-      <c r="Z8924" s="66"/>
-    </row>
-    <row r="8925" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8925" s="65"/>
-      <c r="X8925" s="104"/>
-      <c r="Y8925" s="54"/>
-      <c r="Z8925" s="66"/>
-    </row>
-    <row r="8926" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8926" s="65"/>
-      <c r="X8926" s="104"/>
-      <c r="Y8926" s="54"/>
-      <c r="Z8926" s="66"/>
-    </row>
-    <row r="8927" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8927" s="65"/>
-      <c r="X8927" s="104"/>
-      <c r="Y8927" s="54"/>
-      <c r="Z8927" s="66"/>
-    </row>
-    <row r="8928" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8928" s="65"/>
-      <c r="X8928" s="104"/>
-      <c r="Y8928" s="54"/>
-      <c r="Z8928" s="66"/>
-    </row>
-    <row r="8929" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8929" s="65"/>
-      <c r="X8929" s="104"/>
-      <c r="Y8929" s="54"/>
-      <c r="Z8929" s="66"/>
-    </row>
-    <row r="8930" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8930" s="65"/>
-      <c r="X8930" s="104"/>
-      <c r="Y8930" s="54"/>
-      <c r="Z8930" s="66"/>
-    </row>
-    <row r="8931" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8931" s="65"/>
-      <c r="X8931" s="104"/>
-      <c r="Y8931" s="54"/>
-      <c r="Z8931" s="66"/>
-    </row>
-    <row r="8932" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8932" s="65"/>
-      <c r="X8932" s="104"/>
-      <c r="Y8932" s="54"/>
-      <c r="Z8932" s="66"/>
-    </row>
-    <row r="8933" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8933" s="65"/>
-      <c r="X8933" s="104"/>
-      <c r="Y8933" s="54"/>
-      <c r="Z8933" s="66"/>
-    </row>
-    <row r="8934" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8934" s="65"/>
-      <c r="X8934" s="104"/>
-      <c r="Y8934" s="54"/>
-      <c r="Z8934" s="66"/>
-    </row>
-    <row r="8935" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8935" s="65"/>
-      <c r="X8935" s="104"/>
-      <c r="Y8935" s="54"/>
-      <c r="Z8935" s="66"/>
-    </row>
-    <row r="8936" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8936" s="65"/>
-      <c r="X8936" s="104"/>
-      <c r="Y8936" s="54"/>
-      <c r="Z8936" s="66"/>
-    </row>
-    <row r="8937" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8937" s="65"/>
-      <c r="X8937" s="104"/>
-      <c r="Y8937" s="54"/>
-      <c r="Z8937" s="66"/>
-    </row>
-    <row r="8938" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8938" s="65"/>
-      <c r="X8938" s="104"/>
-      <c r="Y8938" s="54"/>
-      <c r="Z8938" s="66"/>
-    </row>
-    <row r="8939" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8939" s="65"/>
-      <c r="X8939" s="104"/>
-      <c r="Y8939" s="54"/>
-      <c r="Z8939" s="66"/>
-    </row>
-    <row r="8940" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8940" s="65"/>
-      <c r="X8940" s="104"/>
-      <c r="Y8940" s="54"/>
-      <c r="Z8940" s="66"/>
-    </row>
-    <row r="8941" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8941" s="65"/>
-      <c r="X8941" s="104"/>
-      <c r="Y8941" s="54"/>
-      <c r="Z8941" s="66"/>
-    </row>
-    <row r="8942" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8942" s="65"/>
-      <c r="X8942" s="104"/>
-      <c r="Y8942" s="54"/>
-      <c r="Z8942" s="66"/>
-    </row>
-    <row r="8943" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8943" s="65"/>
-      <c r="X8943" s="104"/>
-      <c r="Y8943" s="54"/>
-      <c r="Z8943" s="66"/>
-    </row>
-    <row r="8944" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8944" s="65"/>
-      <c r="X8944" s="104"/>
-      <c r="Y8944" s="54"/>
-      <c r="Z8944" s="66"/>
-    </row>
-    <row r="8945" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8945" s="65"/>
-      <c r="X8945" s="104"/>
-      <c r="Y8945" s="54"/>
-      <c r="Z8945" s="66"/>
-    </row>
-    <row r="8946" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8946" s="65"/>
-      <c r="X8946" s="104"/>
-      <c r="Y8946" s="54"/>
-      <c r="Z8946" s="66"/>
-    </row>
-    <row r="8947" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8947" s="65"/>
-      <c r="X8947" s="104"/>
-      <c r="Y8947" s="54"/>
-      <c r="Z8947" s="66"/>
-    </row>
-    <row r="8948" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8948" s="65"/>
-      <c r="X8948" s="104"/>
-      <c r="Y8948" s="54"/>
-      <c r="Z8948" s="66"/>
-    </row>
-    <row r="8949" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8949" s="65"/>
-      <c r="X8949" s="104"/>
-      <c r="Y8949" s="54"/>
-      <c r="Z8949" s="66"/>
-    </row>
-    <row r="8950" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8950" s="65"/>
-      <c r="X8950" s="104"/>
-      <c r="Y8950" s="54"/>
-      <c r="Z8950" s="66"/>
-    </row>
-    <row r="8951" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8951" s="65"/>
-      <c r="X8951" s="104"/>
-      <c r="Y8951" s="54"/>
-      <c r="Z8951" s="66"/>
-    </row>
-    <row r="8952" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8952" s="65"/>
-      <c r="X8952" s="104"/>
-      <c r="Y8952" s="54"/>
-      <c r="Z8952" s="66"/>
-    </row>
-    <row r="8953" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8953" s="65"/>
-      <c r="X8953" s="104"/>
-      <c r="Y8953" s="54"/>
-      <c r="Z8953" s="66"/>
-    </row>
-    <row r="8954" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8954" s="65"/>
-      <c r="X8954" s="104"/>
-      <c r="Y8954" s="54"/>
-      <c r="Z8954" s="66"/>
-    </row>
-    <row r="8955" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8955" s="65"/>
-      <c r="X8955" s="104"/>
-      <c r="Y8955" s="54"/>
-      <c r="Z8955" s="66"/>
-    </row>
-    <row r="8956" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8956" s="65"/>
-      <c r="X8956" s="104"/>
-      <c r="Y8956" s="54"/>
-      <c r="Z8956" s="66"/>
-    </row>
-    <row r="8957" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8957" s="65"/>
-      <c r="X8957" s="104"/>
-      <c r="Y8957" s="54"/>
-      <c r="Z8957" s="66"/>
-    </row>
-    <row r="8958" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8958" s="65"/>
-      <c r="X8958" s="104"/>
-      <c r="Y8958" s="54"/>
-      <c r="Z8958" s="66"/>
-    </row>
-    <row r="8959" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8959" s="65"/>
-      <c r="X8959" s="104"/>
-      <c r="Y8959" s="54"/>
-      <c r="Z8959" s="66"/>
-    </row>
-    <row r="8960" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8960" s="65"/>
-      <c r="X8960" s="104"/>
-      <c r="Y8960" s="54"/>
-      <c r="Z8960" s="66"/>
-    </row>
-    <row r="8961" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8961" s="65"/>
-      <c r="X8961" s="104"/>
-      <c r="Y8961" s="54"/>
-      <c r="Z8961" s="66"/>
-    </row>
-    <row r="8962" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8962" s="65"/>
-      <c r="X8962" s="104"/>
-      <c r="Y8962" s="54"/>
-      <c r="Z8962" s="66"/>
-    </row>
-    <row r="8963" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8963" s="65"/>
-      <c r="X8963" s="104"/>
-      <c r="Y8963" s="54"/>
-      <c r="Z8963" s="66"/>
-    </row>
-    <row r="8964" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8964" s="65"/>
-      <c r="X8964" s="104"/>
-      <c r="Y8964" s="54"/>
-      <c r="Z8964" s="66"/>
-    </row>
-    <row r="8965" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8965" s="65"/>
-      <c r="X8965" s="104"/>
-      <c r="Y8965" s="54"/>
-      <c r="Z8965" s="66"/>
-    </row>
-    <row r="8966" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8966" s="65"/>
-      <c r="X8966" s="104"/>
-      <c r="Y8966" s="54"/>
-      <c r="Z8966" s="66"/>
-    </row>
-    <row r="8967" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8967" s="65"/>
-      <c r="X8967" s="104"/>
-      <c r="Y8967" s="54"/>
-      <c r="Z8967" s="66"/>
-    </row>
-    <row r="8968" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8968" s="65"/>
-      <c r="X8968" s="104"/>
-      <c r="Y8968" s="54"/>
-      <c r="Z8968" s="66"/>
-    </row>
-    <row r="8969" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8969" s="65"/>
-      <c r="X8969" s="104"/>
-      <c r="Y8969" s="54"/>
-      <c r="Z8969" s="66"/>
-    </row>
-    <row r="8970" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8970" s="65"/>
-      <c r="X8970" s="104"/>
-      <c r="Y8970" s="54"/>
-      <c r="Z8970" s="66"/>
-    </row>
-    <row r="8971" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8971" s="65"/>
-      <c r="X8971" s="104"/>
-      <c r="Y8971" s="54"/>
-      <c r="Z8971" s="66"/>
-    </row>
-    <row r="8972" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8972" s="65"/>
-      <c r="X8972" s="104"/>
-      <c r="Y8972" s="54"/>
-      <c r="Z8972" s="66"/>
-    </row>
-    <row r="8973" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8973" s="65"/>
-      <c r="X8973" s="104"/>
-      <c r="Y8973" s="54"/>
-      <c r="Z8973" s="66"/>
-    </row>
-    <row r="8974" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8974" s="65"/>
-      <c r="X8974" s="104"/>
-      <c r="Y8974" s="54"/>
-      <c r="Z8974" s="66"/>
-    </row>
-    <row r="8975" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8975" s="65"/>
-      <c r="X8975" s="104"/>
-      <c r="Y8975" s="54"/>
-      <c r="Z8975" s="66"/>
-    </row>
-    <row r="8976" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8976" s="65"/>
-      <c r="X8976" s="104"/>
-      <c r="Y8976" s="54"/>
-      <c r="Z8976" s="66"/>
-    </row>
-    <row r="8977" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8977" s="65"/>
-      <c r="X8977" s="104"/>
-      <c r="Y8977" s="54"/>
-      <c r="Z8977" s="66"/>
-    </row>
-    <row r="8978" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8978" s="65"/>
-      <c r="X8978" s="104"/>
-      <c r="Y8978" s="54"/>
-      <c r="Z8978" s="66"/>
-    </row>
-    <row r="8979" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8979" s="65"/>
-      <c r="X8979" s="104"/>
-      <c r="Y8979" s="54"/>
-      <c r="Z8979" s="66"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BV24" xr:uid="{00000000-0009-0000-0000-000002000000}">
+  <autoFilter ref="A1:BV154" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="11" showButton="0"/>
+    <filterColumn colId="19" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="22" showButton="0"/>
     <filterColumn colId="23" showButton="0"/>
     <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+    <filterColumn colId="27" showButton="0"/>
+    <filterColumn colId="28" showButton="0"/>
+    <filterColumn colId="29" showButton="0"/>
+    <filterColumn colId="30" showButton="0"/>
+    <filterColumn colId="31" showButton="0"/>
+    <filterColumn colId="32" showButton="0"/>
+    <filterColumn colId="34" showButton="0"/>
+    <filterColumn colId="39" showButton="0"/>
+    <filterColumn colId="40" showButton="0"/>
+    <filterColumn colId="41" showButton="0"/>
+    <filterColumn colId="42" showButton="0"/>
+    <filterColumn colId="54" showButton="0"/>
+    <filterColumn colId="55" showButton="0"/>
+    <filterColumn colId="57" showButton="0"/>
+    <filterColumn colId="58" showButton="0"/>
+    <filterColumn colId="60" showButton="0"/>
+    <filterColumn colId="61" showButton="0"/>
+    <filterColumn colId="63" showButton="0"/>
+    <filterColumn colId="64" showButton="0"/>
+    <filterColumn colId="66" showButton="0"/>
+    <filterColumn colId="67" showButton="0"/>
   </autoFilter>
   <mergeCells count="46">
     <mergeCell ref="A1:A2"/>
@@ -60172,7 +63134,7 @@
     <mergeCell ref="R1:R2"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation operator="equal" allowBlank="1" showErrorMessage="1" sqref="BC1:BC2 J1:J2" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -60182,7 +63144,7 @@
   <pageSetup paperSize="8" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
           <x14:formula1>
             <xm:f>'Internal lists'!$F$2:$F$5</xm:f>
@@ -60264,10 +63226,10 @@
       <c r="A4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="135" t="s">
+      <c r="B4" s="140" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="135"/>
+      <c r="C4" s="140"/>
       <c r="D4" s="26" t="s">
         <v>59</v>
       </c>
@@ -60276,13 +63238,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="127" t="s">
+      <c r="B5" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="127"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="28" t="s">
         <v>158</v>
       </c>
@@ -60291,16 +63253,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="127"/>
-      <c r="B6" s="127"/>
-      <c r="C6" s="127"/>
+      <c r="A6" s="132"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
       <c r="D6" s="28"/>
       <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="127"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="28" t="s">
         <v>160</v>
       </c>
@@ -60309,9 +63271,9 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
+      <c r="A8" s="132"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
       <c r="D8" s="28" t="s">
         <v>162</v>
       </c>
@@ -60320,9 +63282,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
+      <c r="A9" s="132"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
       <c r="D9" s="28" t="s">
         <v>163</v>
       </c>
@@ -60331,9 +63293,9 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="127"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
+      <c r="A10" s="132"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
       <c r="D10" s="28" t="s">
         <v>164</v>
       </c>
@@ -60342,9 +63304,9 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
       <c r="D11" s="31" t="s">
         <v>165</v>
       </c>
@@ -60356,7 +63318,7 @@
       <c r="A12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="132" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="31" t="s">
@@ -60373,7 +63335,7 @@
       <c r="A13" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="127"/>
+      <c r="B13" s="132"/>
       <c r="C13" s="31" t="s">
         <v>104</v>
       </c>
@@ -60388,7 +63350,7 @@
       <c r="A14" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="127"/>
+      <c r="B14" s="132"/>
       <c r="C14" s="31" t="s">
         <v>105</v>
       </c>
@@ -60403,7 +63365,7 @@
       <c r="A15" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="127"/>
+      <c r="B15" s="132"/>
       <c r="C15" s="31" t="s">
         <v>106</v>
       </c>
@@ -60418,7 +63380,7 @@
       <c r="A16" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="127"/>
+      <c r="B16" s="132"/>
       <c r="C16" s="31" t="s">
         <v>107</v>
       </c>
@@ -60433,10 +63395,10 @@
       <c r="A17" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="127"/>
+      <c r="C17" s="132"/>
       <c r="D17" s="31" t="s">
         <v>177</v>
       </c>
@@ -60448,10 +63410,10 @@
       <c r="A18" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="127" t="s">
+      <c r="B18" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="127"/>
+      <c r="C18" s="132"/>
       <c r="D18" s="31" t="s">
         <v>180</v>
       </c>
@@ -60463,10 +63425,10 @@
       <c r="A19" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="132" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="127"/>
+      <c r="C19" s="132"/>
       <c r="D19" s="31" t="s">
         <v>183</v>
       </c>
@@ -60478,10 +63440,10 @@
       <c r="A20" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="127" t="s">
+      <c r="B20" s="132" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="127"/>
+      <c r="C20" s="132"/>
       <c r="D20" s="31" t="s">
         <v>186</v>
       </c>
@@ -60493,10 +63455,10 @@
       <c r="A21" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="127" t="s">
+      <c r="B21" s="132" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="127"/>
+      <c r="C21" s="132"/>
       <c r="D21" s="31" t="s">
         <v>189</v>
       </c>
@@ -60508,10 +63470,10 @@
       <c r="A22" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="127" t="s">
+      <c r="B22" s="132" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="127"/>
+      <c r="C22" s="132"/>
       <c r="D22" s="31" t="s">
         <v>192</v>
       </c>
@@ -60520,13 +63482,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="127" t="s">
+      <c r="A23" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="127" t="s">
+      <c r="B23" s="132" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="127"/>
+      <c r="C23" s="132"/>
       <c r="D23" s="28" t="s">
         <v>194</v>
       </c>
@@ -60535,9 +63497,9 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="127"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
+      <c r="A24" s="132"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
       <c r="D24" s="28" t="s">
         <v>196</v>
       </c>
@@ -60546,9 +63508,9 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="127"/>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
+      <c r="A25" s="132"/>
+      <c r="B25" s="132"/>
+      <c r="C25" s="132"/>
       <c r="D25" s="28" t="s">
         <v>198</v>
       </c>
@@ -60557,9 +63519,9 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="127"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="132"/>
       <c r="D26" s="28" t="s">
         <v>199</v>
       </c>
@@ -60568,9 +63530,9 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="127"/>
-      <c r="B27" s="127"/>
-      <c r="C27" s="127"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="132"/>
+      <c r="C27" s="132"/>
       <c r="D27" s="28" t="s">
         <v>200</v>
       </c>
@@ -60579,9 +63541,9 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="127"/>
-      <c r="B28" s="127"/>
-      <c r="C28" s="127"/>
+      <c r="A28" s="132"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
       <c r="D28" s="28" t="s">
         <v>201</v>
       </c>
@@ -60590,9 +63552,9 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="127"/>
-      <c r="B29" s="127"/>
-      <c r="C29" s="127"/>
+      <c r="A29" s="132"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
       <c r="D29" s="28" t="s">
         <v>202</v>
       </c>
@@ -60601,9 +63563,9 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="127"/>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127"/>
+      <c r="A30" s="132"/>
+      <c r="B30" s="132"/>
+      <c r="C30" s="132"/>
       <c r="D30" s="28" t="s">
         <v>203</v>
       </c>
@@ -60612,9 +63574,9 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="127"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="132"/>
+      <c r="C31" s="132"/>
       <c r="D31" s="28" t="s">
         <v>204</v>
       </c>
@@ -60623,9 +63585,9 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="127"/>
-      <c r="B32" s="127"/>
-      <c r="C32" s="127"/>
+      <c r="A32" s="132"/>
+      <c r="B32" s="132"/>
+      <c r="C32" s="132"/>
       <c r="D32" s="28" t="s">
         <v>205</v>
       </c>
@@ -60634,9 +63596,9 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="127"/>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
+      <c r="A33" s="132"/>
+      <c r="B33" s="132"/>
+      <c r="C33" s="132"/>
       <c r="D33" s="28" t="s">
         <v>206</v>
       </c>
@@ -60645,16 +63607,16 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="127"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="127"/>
+      <c r="A34" s="132"/>
+      <c r="B34" s="132"/>
+      <c r="C34" s="132"/>
       <c r="D34" s="28"/>
       <c r="E34" s="30"/>
     </row>
     <row r="35" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="127"/>
-      <c r="B35" s="127"/>
-      <c r="C35" s="127"/>
+      <c r="A35" s="132"/>
+      <c r="B35" s="132"/>
+      <c r="C35" s="132"/>
       <c r="D35" s="28" t="s">
         <v>208</v>
       </c>
@@ -60663,9 +63625,9 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="127"/>
-      <c r="B36" s="127"/>
-      <c r="C36" s="127"/>
+      <c r="A36" s="132"/>
+      <c r="B36" s="132"/>
+      <c r="C36" s="132"/>
       <c r="D36" s="31" t="s">
         <v>210</v>
       </c>
@@ -60677,10 +63639,10 @@
       <c r="A37" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="128" t="s">
+      <c r="B37" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="128"/>
+      <c r="C37" s="133"/>
       <c r="D37" s="31" t="s">
         <v>212</v>
       </c>
@@ -60692,10 +63654,10 @@
       <c r="A38" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B38" s="127" t="s">
+      <c r="B38" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="127"/>
+      <c r="C38" s="132"/>
       <c r="D38" s="31" t="s">
         <v>214</v>
       </c>
@@ -60707,10 +63669,10 @@
       <c r="A39" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="127" t="s">
+      <c r="B39" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="127"/>
+      <c r="C39" s="132"/>
       <c r="D39" s="31" t="s">
         <v>216</v>
       </c>
@@ -60719,13 +63681,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="127" t="s">
+      <c r="A40" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B40" s="127" t="s">
+      <c r="B40" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="127"/>
+      <c r="C40" s="132"/>
       <c r="D40" s="28" t="s">
         <v>218</v>
       </c>
@@ -60734,9 +63696,9 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="127"/>
-      <c r="B41" s="127"/>
-      <c r="C41" s="127"/>
+      <c r="A41" s="132"/>
+      <c r="B41" s="132"/>
+      <c r="C41" s="132"/>
       <c r="D41" s="28" t="s">
         <v>220</v>
       </c>
@@ -60745,9 +63707,9 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="127"/>
-      <c r="B42" s="127"/>
-      <c r="C42" s="127"/>
+      <c r="A42" s="132"/>
+      <c r="B42" s="132"/>
+      <c r="C42" s="132"/>
       <c r="D42" s="28" t="s">
         <v>222</v>
       </c>
@@ -60756,9 +63718,9 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="127"/>
-      <c r="B43" s="127"/>
-      <c r="C43" s="127"/>
+      <c r="A43" s="132"/>
+      <c r="B43" s="132"/>
+      <c r="C43" s="132"/>
       <c r="D43" s="28" t="s">
         <v>224</v>
       </c>
@@ -60767,9 +63729,9 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="127"/>
-      <c r="B44" s="127"/>
-      <c r="C44" s="127"/>
+      <c r="A44" s="132"/>
+      <c r="B44" s="132"/>
+      <c r="C44" s="132"/>
       <c r="D44" s="28" t="s">
         <v>226</v>
       </c>
@@ -60781,10 +63743,10 @@
       <c r="A45" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="127" t="s">
+      <c r="B45" s="132" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="127"/>
+      <c r="C45" s="132"/>
       <c r="D45" s="27" t="s">
         <v>227</v>
       </c>
@@ -60841,7 +63803,7 @@
       <c r="A49" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="132" t="s">
+      <c r="B49" s="137" t="s">
         <v>237</v>
       </c>
       <c r="C49" s="31" t="s">
@@ -60855,11 +63817,11 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="127" t="s">
+      <c r="A50" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B50" s="132"/>
-      <c r="C50" s="133" t="s">
+      <c r="B50" s="137"/>
+      <c r="C50" s="138" t="s">
         <v>108</v>
       </c>
       <c r="D50" s="40" t="s">
@@ -60870,9 +63832,9 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="127"/>
-      <c r="B51" s="132"/>
-      <c r="C51" s="133"/>
+      <c r="A51" s="132"/>
+      <c r="B51" s="137"/>
+      <c r="C51" s="138"/>
       <c r="D51" s="30" t="s">
         <v>242</v>
       </c>
@@ -60881,9 +63843,9 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="127"/>
-      <c r="B52" s="132"/>
-      <c r="C52" s="133"/>
+      <c r="A52" s="132"/>
+      <c r="B52" s="137"/>
+      <c r="C52" s="138"/>
       <c r="D52" s="30" t="s">
         <v>244</v>
       </c>
@@ -60892,9 +63854,9 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="127"/>
-      <c r="B53" s="132"/>
-      <c r="C53" s="133"/>
+      <c r="A53" s="132"/>
+      <c r="B53" s="137"/>
+      <c r="C53" s="138"/>
       <c r="D53" s="30" t="s">
         <v>246</v>
       </c>
@@ -60903,16 +63865,16 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="127"/>
-      <c r="B54" s="132"/>
-      <c r="C54" s="133"/>
+      <c r="A54" s="132"/>
+      <c r="B54" s="137"/>
+      <c r="C54" s="138"/>
       <c r="D54" s="28"/>
       <c r="E54" s="30"/>
     </row>
     <row r="55" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="127"/>
-      <c r="B55" s="132"/>
-      <c r="C55" s="133"/>
+      <c r="A55" s="132"/>
+      <c r="B55" s="137"/>
+      <c r="C55" s="138"/>
       <c r="D55" s="31" t="s">
         <v>248</v>
       </c>
@@ -60921,11 +63883,11 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="127" t="s">
+      <c r="A56" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B56" s="132"/>
-      <c r="C56" s="134" t="s">
+      <c r="B56" s="137"/>
+      <c r="C56" s="139" t="s">
         <v>109</v>
       </c>
       <c r="D56" s="28" t="s">
@@ -60936,9 +63898,9 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="127"/>
-      <c r="B57" s="132"/>
-      <c r="C57" s="134"/>
+      <c r="A57" s="132"/>
+      <c r="B57" s="137"/>
+      <c r="C57" s="139"/>
       <c r="D57" s="28" t="s">
         <v>252</v>
       </c>
@@ -60947,9 +63909,9 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="127"/>
-      <c r="B58" s="132"/>
-      <c r="C58" s="134"/>
+      <c r="A58" s="132"/>
+      <c r="B58" s="137"/>
+      <c r="C58" s="139"/>
       <c r="D58" s="31" t="s">
         <v>254</v>
       </c>
@@ -60961,10 +63923,10 @@
       <c r="A59" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="127" t="s">
+      <c r="B59" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="127"/>
+      <c r="C59" s="132"/>
       <c r="D59" s="31" t="s">
         <v>256</v>
       </c>
@@ -60976,7 +63938,7 @@
       <c r="A60" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="131" t="s">
+      <c r="B60" s="136" t="s">
         <v>82</v>
       </c>
       <c r="C60" s="31" t="s">
@@ -60990,11 +63952,11 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="127" t="s">
+      <c r="A61" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B61" s="131"/>
-      <c r="C61" s="127" t="s">
+      <c r="B61" s="136"/>
+      <c r="C61" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D61" s="40" t="s">
@@ -61005,9 +63967,9 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="127"/>
-      <c r="B62" s="127"/>
-      <c r="C62" s="127"/>
+      <c r="A62" s="132"/>
+      <c r="B62" s="132"/>
+      <c r="C62" s="132"/>
       <c r="D62" s="30" t="s">
         <v>242</v>
       </c>
@@ -61016,9 +63978,9 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="127"/>
-      <c r="B63" s="127"/>
-      <c r="C63" s="127"/>
+      <c r="A63" s="132"/>
+      <c r="B63" s="132"/>
+      <c r="C63" s="132"/>
       <c r="D63" s="30" t="s">
         <v>244</v>
       </c>
@@ -61027,9 +63989,9 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="127"/>
-      <c r="B64" s="127"/>
-      <c r="C64" s="127"/>
+      <c r="A64" s="132"/>
+      <c r="B64" s="132"/>
+      <c r="C64" s="132"/>
       <c r="D64" s="30" t="s">
         <v>246</v>
       </c>
@@ -61038,16 +64000,16 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="127"/>
-      <c r="B65" s="127"/>
-      <c r="C65" s="127"/>
+      <c r="A65" s="132"/>
+      <c r="B65" s="132"/>
+      <c r="C65" s="132"/>
       <c r="D65" s="28"/>
       <c r="E65" s="30"/>
     </row>
     <row r="66" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="127"/>
-      <c r="B66" s="131"/>
-      <c r="C66" s="127"/>
+      <c r="A66" s="132"/>
+      <c r="B66" s="136"/>
+      <c r="C66" s="132"/>
       <c r="D66" s="31" t="s">
         <v>248</v>
       </c>
@@ -61056,11 +64018,11 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="127" t="s">
+      <c r="A67" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="131"/>
-      <c r="C67" s="127" t="s">
+      <c r="B67" s="136"/>
+      <c r="C67" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D67" s="28" t="s">
@@ -61071,9 +64033,9 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="127"/>
-      <c r="B68" s="127"/>
-      <c r="C68" s="127"/>
+      <c r="A68" s="132"/>
+      <c r="B68" s="132"/>
+      <c r="C68" s="132"/>
       <c r="D68" s="28" t="s">
         <v>252</v>
       </c>
@@ -61082,9 +64044,9 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="127"/>
-      <c r="B69" s="131"/>
-      <c r="C69" s="127"/>
+      <c r="A69" s="132"/>
+      <c r="B69" s="136"/>
+      <c r="C69" s="132"/>
       <c r="D69" s="31" t="s">
         <v>254</v>
       </c>
@@ -61096,7 +64058,7 @@
       <c r="A70" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="131" t="s">
+      <c r="B70" s="136" t="s">
         <v>81</v>
       </c>
       <c r="C70" s="31" t="s">
@@ -61110,11 +64072,11 @@
       </c>
     </row>
     <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="127" t="s">
+      <c r="A71" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="131"/>
-      <c r="C71" s="127" t="s">
+      <c r="B71" s="136"/>
+      <c r="C71" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D71" s="40" t="s">
@@ -61125,9 +64087,9 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="127"/>
-      <c r="B72" s="127"/>
-      <c r="C72" s="127"/>
+      <c r="A72" s="132"/>
+      <c r="B72" s="132"/>
+      <c r="C72" s="132"/>
       <c r="D72" s="30" t="s">
         <v>242</v>
       </c>
@@ -61136,9 +64098,9 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="127"/>
-      <c r="B73" s="127"/>
-      <c r="C73" s="127"/>
+      <c r="A73" s="132"/>
+      <c r="B73" s="132"/>
+      <c r="C73" s="132"/>
       <c r="D73" s="30" t="s">
         <v>244</v>
       </c>
@@ -61147,9 +64109,9 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="127"/>
-      <c r="B74" s="127"/>
-      <c r="C74" s="127"/>
+      <c r="A74" s="132"/>
+      <c r="B74" s="132"/>
+      <c r="C74" s="132"/>
       <c r="D74" s="30" t="s">
         <v>246</v>
       </c>
@@ -61158,16 +64120,16 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="127"/>
-      <c r="B75" s="127"/>
-      <c r="C75" s="127"/>
+      <c r="A75" s="132"/>
+      <c r="B75" s="132"/>
+      <c r="C75" s="132"/>
       <c r="D75" s="28"/>
       <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="127"/>
-      <c r="B76" s="131"/>
-      <c r="C76" s="127"/>
+      <c r="A76" s="132"/>
+      <c r="B76" s="136"/>
+      <c r="C76" s="132"/>
       <c r="D76" s="31" t="s">
         <v>248</v>
       </c>
@@ -61176,11 +64138,11 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="127" t="s">
+      <c r="A77" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="131"/>
-      <c r="C77" s="127" t="s">
+      <c r="B77" s="136"/>
+      <c r="C77" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D77" s="28" t="s">
@@ -61191,9 +64153,9 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="127"/>
-      <c r="B78" s="127"/>
-      <c r="C78" s="127"/>
+      <c r="A78" s="132"/>
+      <c r="B78" s="132"/>
+      <c r="C78" s="132"/>
       <c r="D78" s="28" t="s">
         <v>252</v>
       </c>
@@ -61202,9 +64164,9 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="127"/>
-      <c r="B79" s="131"/>
-      <c r="C79" s="127"/>
+      <c r="A79" s="132"/>
+      <c r="B79" s="136"/>
+      <c r="C79" s="132"/>
       <c r="D79" s="31" t="s">
         <v>254</v>
       </c>
@@ -61213,13 +64175,13 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="127" t="s">
+      <c r="A80" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="127" t="s">
+      <c r="B80" s="132" t="s">
         <v>258</v>
       </c>
-      <c r="C80" s="127"/>
+      <c r="C80" s="132"/>
       <c r="D80" s="28" t="s">
         <v>259</v>
       </c>
@@ -61228,9 +64190,9 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="127"/>
-      <c r="B81" s="127"/>
-      <c r="C81" s="127"/>
+      <c r="A81" s="132"/>
+      <c r="B81" s="132"/>
+      <c r="C81" s="132"/>
       <c r="D81" s="28" t="s">
         <v>261</v>
       </c>
@@ -61239,9 +64201,9 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="127"/>
-      <c r="B82" s="127"/>
-      <c r="C82" s="127"/>
+      <c r="A82" s="132"/>
+      <c r="B82" s="132"/>
+      <c r="C82" s="132"/>
       <c r="D82" s="28" t="s">
         <v>263</v>
       </c>
@@ -61250,9 +64212,9 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="127"/>
-      <c r="B83" s="127"/>
-      <c r="C83" s="127"/>
+      <c r="A83" s="132"/>
+      <c r="B83" s="132"/>
+      <c r="C83" s="132"/>
       <c r="D83" s="28" t="s">
         <v>265</v>
       </c>
@@ -61261,9 +64223,9 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="127"/>
-      <c r="B84" s="127"/>
-      <c r="C84" s="127"/>
+      <c r="A84" s="132"/>
+      <c r="B84" s="132"/>
+      <c r="C84" s="132"/>
       <c r="D84" s="28" t="s">
         <v>267</v>
       </c>
@@ -61272,9 +64234,9 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="127"/>
-      <c r="B85" s="127"/>
-      <c r="C85" s="127"/>
+      <c r="A85" s="132"/>
+      <c r="B85" s="132"/>
+      <c r="C85" s="132"/>
       <c r="D85" s="31" t="s">
         <v>269</v>
       </c>
@@ -61286,10 +64248,10 @@
       <c r="A86" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="127" t="s">
+      <c r="B86" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="C86" s="127"/>
+      <c r="C86" s="132"/>
       <c r="D86" s="31" t="s">
         <v>271</v>
       </c>
@@ -61301,7 +64263,7 @@
       <c r="A87" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B87" s="131" t="s">
+      <c r="B87" s="136" t="s">
         <v>83</v>
       </c>
       <c r="C87" s="31" t="s">
@@ -61315,11 +64277,11 @@
       </c>
     </row>
     <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="127" t="s">
+      <c r="A88" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B88" s="131"/>
-      <c r="C88" s="127" t="s">
+      <c r="B88" s="136"/>
+      <c r="C88" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D88" s="40" t="s">
@@ -61330,9 +64292,9 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="127"/>
-      <c r="B89" s="127"/>
-      <c r="C89" s="127"/>
+      <c r="A89" s="132"/>
+      <c r="B89" s="132"/>
+      <c r="C89" s="132"/>
       <c r="D89" s="30" t="s">
         <v>242</v>
       </c>
@@ -61341,9 +64303,9 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="127"/>
-      <c r="B90" s="127"/>
-      <c r="C90" s="127"/>
+      <c r="A90" s="132"/>
+      <c r="B90" s="132"/>
+      <c r="C90" s="132"/>
       <c r="D90" s="30" t="s">
         <v>244</v>
       </c>
@@ -61352,9 +64314,9 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="127"/>
-      <c r="B91" s="127"/>
-      <c r="C91" s="127"/>
+      <c r="A91" s="132"/>
+      <c r="B91" s="132"/>
+      <c r="C91" s="132"/>
       <c r="D91" s="30" t="s">
         <v>246</v>
       </c>
@@ -61363,16 +64325,16 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="127"/>
-      <c r="B92" s="127"/>
-      <c r="C92" s="127"/>
+      <c r="A92" s="132"/>
+      <c r="B92" s="132"/>
+      <c r="C92" s="132"/>
       <c r="D92" s="28"/>
       <c r="E92" s="30"/>
     </row>
     <row r="93" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="127"/>
-      <c r="B93" s="131"/>
-      <c r="C93" s="127"/>
+      <c r="A93" s="132"/>
+      <c r="B93" s="136"/>
+      <c r="C93" s="132"/>
       <c r="D93" s="31" t="s">
         <v>248</v>
       </c>
@@ -61381,11 +64343,11 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="127" t="s">
+      <c r="A94" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B94" s="131"/>
-      <c r="C94" s="127" t="s">
+      <c r="B94" s="136"/>
+      <c r="C94" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D94" s="28" t="s">
@@ -61396,9 +64358,9 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="127"/>
-      <c r="B95" s="127"/>
-      <c r="C95" s="127"/>
+      <c r="A95" s="132"/>
+      <c r="B95" s="132"/>
+      <c r="C95" s="132"/>
       <c r="D95" s="28" t="s">
         <v>252</v>
       </c>
@@ -61407,9 +64369,9 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="127"/>
-      <c r="B96" s="131"/>
-      <c r="C96" s="127"/>
+      <c r="A96" s="132"/>
+      <c r="B96" s="136"/>
+      <c r="C96" s="132"/>
       <c r="D96" s="31" t="s">
         <v>254</v>
       </c>
@@ -61421,7 +64383,7 @@
       <c r="A97" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B97" s="131" t="s">
+      <c r="B97" s="136" t="s">
         <v>84</v>
       </c>
       <c r="C97" s="31" t="s">
@@ -61435,11 +64397,11 @@
       </c>
     </row>
     <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="127" t="s">
+      <c r="A98" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B98" s="131"/>
-      <c r="C98" s="127" t="s">
+      <c r="B98" s="136"/>
+      <c r="C98" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D98" s="40" t="s">
@@ -61450,9 +64412,9 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="127"/>
-      <c r="B99" s="127"/>
-      <c r="C99" s="127"/>
+      <c r="A99" s="132"/>
+      <c r="B99" s="132"/>
+      <c r="C99" s="132"/>
       <c r="D99" s="30" t="s">
         <v>242</v>
       </c>
@@ -61461,9 +64423,9 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="127"/>
-      <c r="B100" s="127"/>
-      <c r="C100" s="127"/>
+      <c r="A100" s="132"/>
+      <c r="B100" s="132"/>
+      <c r="C100" s="132"/>
       <c r="D100" s="30" t="s">
         <v>244</v>
       </c>
@@ -61472,9 +64434,9 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="127"/>
-      <c r="B101" s="127"/>
-      <c r="C101" s="127"/>
+      <c r="A101" s="132"/>
+      <c r="B101" s="132"/>
+      <c r="C101" s="132"/>
       <c r="D101" s="30" t="s">
         <v>246</v>
       </c>
@@ -61483,16 +64445,16 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="127"/>
-      <c r="B102" s="127"/>
-      <c r="C102" s="127"/>
+      <c r="A102" s="132"/>
+      <c r="B102" s="132"/>
+      <c r="C102" s="132"/>
       <c r="D102" s="28"/>
       <c r="E102" s="30"/>
     </row>
     <row r="103" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="127"/>
-      <c r="B103" s="131"/>
-      <c r="C103" s="127"/>
+      <c r="A103" s="132"/>
+      <c r="B103" s="136"/>
+      <c r="C103" s="132"/>
       <c r="D103" s="31" t="s">
         <v>248</v>
       </c>
@@ -61501,11 +64463,11 @@
       </c>
     </row>
     <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="127" t="s">
+      <c r="A104" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B104" s="131"/>
-      <c r="C104" s="127" t="s">
+      <c r="B104" s="136"/>
+      <c r="C104" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D104" s="28" t="s">
@@ -61516,9 +64478,9 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="127"/>
-      <c r="B105" s="127"/>
-      <c r="C105" s="127"/>
+      <c r="A105" s="132"/>
+      <c r="B105" s="132"/>
+      <c r="C105" s="132"/>
       <c r="D105" s="28" t="s">
         <v>252</v>
       </c>
@@ -61527,9 +64489,9 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="127"/>
-      <c r="B106" s="131"/>
-      <c r="C106" s="127"/>
+      <c r="A106" s="132"/>
+      <c r="B106" s="136"/>
+      <c r="C106" s="132"/>
       <c r="D106" s="31" t="s">
         <v>254</v>
       </c>
@@ -61541,10 +64503,10 @@
       <c r="A107" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B107" s="127" t="s">
+      <c r="B107" s="132" t="s">
         <v>273</v>
       </c>
-      <c r="C107" s="127"/>
+      <c r="C107" s="132"/>
       <c r="D107" s="31" t="s">
         <v>274</v>
       </c>
@@ -61556,10 +64518,10 @@
       <c r="A108" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B108" s="127" t="s">
+      <c r="B108" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="C108" s="127"/>
+      <c r="C108" s="132"/>
       <c r="D108" s="31" t="s">
         <v>277</v>
       </c>
@@ -61571,10 +64533,10 @@
       <c r="A109" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B109" s="127" t="s">
+      <c r="B109" s="132" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="127"/>
+      <c r="C109" s="132"/>
       <c r="D109" s="31" t="s">
         <v>280</v>
       </c>
@@ -61583,13 +64545,13 @@
       </c>
     </row>
     <row r="110" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="127" t="s">
+      <c r="A110" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B110" s="130" t="s">
+      <c r="B110" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="130"/>
+      <c r="C110" s="135"/>
       <c r="D110" s="39" t="s">
         <v>282</v>
       </c>
@@ -61598,16 +64560,16 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="127"/>
-      <c r="B111" s="130"/>
-      <c r="C111" s="130"/>
+      <c r="A111" s="132"/>
+      <c r="B111" s="135"/>
+      <c r="C111" s="135"/>
       <c r="D111" s="41"/>
       <c r="E111" s="30"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="127"/>
-      <c r="B112" s="130"/>
-      <c r="C112" s="130"/>
+      <c r="A112" s="132"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="135"/>
       <c r="D112" s="42" t="s">
         <v>284</v>
       </c>
@@ -61616,9 +64578,9 @@
       </c>
     </row>
     <row r="113" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A113" s="127"/>
-      <c r="B113" s="130"/>
-      <c r="C113" s="130"/>
+      <c r="A113" s="132"/>
+      <c r="B113" s="135"/>
+      <c r="C113" s="135"/>
       <c r="D113" s="42" t="s">
         <v>286</v>
       </c>
@@ -61627,9 +64589,9 @@
       </c>
     </row>
     <row r="114" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A114" s="127"/>
-      <c r="B114" s="130"/>
-      <c r="C114" s="130"/>
+      <c r="A114" s="132"/>
+      <c r="B114" s="135"/>
+      <c r="C114" s="135"/>
       <c r="D114" s="42" t="s">
         <v>288</v>
       </c>
@@ -61638,9 +64600,9 @@
       </c>
     </row>
     <row r="115" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A115" s="127"/>
-      <c r="B115" s="130"/>
-      <c r="C115" s="130"/>
+      <c r="A115" s="132"/>
+      <c r="B115" s="135"/>
+      <c r="C115" s="135"/>
       <c r="D115" s="43" t="s">
         <v>290</v>
       </c>
@@ -61686,10 +64648,10 @@
       <c r="A118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="129" t="s">
+      <c r="B118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="C118" s="129"/>
+      <c r="C118" s="134"/>
       <c r="D118" s="46" t="s">
         <v>296</v>
       </c>
@@ -61950,10 +64912,10 @@
       <c r="IW118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="IX118" s="129" t="s">
+      <c r="IX118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="IY118" s="129"/>
+      <c r="IY118" s="134"/>
       <c r="IZ118" s="46" t="s">
         <v>296</v>
       </c>
@@ -62214,10 +65176,10 @@
       <c r="SS118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ST118" s="129" t="s">
+      <c r="ST118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="SU118" s="129"/>
+      <c r="SU118" s="134"/>
       <c r="SV118" s="46" t="s">
         <v>296</v>
       </c>
@@ -62478,10 +65440,10 @@
       <c r="ACO118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ACP118" s="129" t="s">
+      <c r="ACP118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="ACQ118" s="129"/>
+      <c r="ACQ118" s="134"/>
       <c r="ACR118" s="46" t="s">
         <v>296</v>
       </c>
@@ -62744,10 +65706,10 @@
       <c r="A119" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B119" s="127" t="s">
+      <c r="B119" s="132" t="s">
         <v>298</v>
       </c>
-      <c r="C119" s="127"/>
+      <c r="C119" s="132"/>
       <c r="D119" s="31" t="s">
         <v>299</v>
       </c>
@@ -62759,7 +65721,7 @@
       <c r="A120" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B120" s="127" t="s">
+      <c r="B120" s="132" t="s">
         <v>301</v>
       </c>
       <c r="C120" s="31" t="s">
@@ -62776,7 +65738,7 @@
       <c r="A121" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B121" s="127"/>
+      <c r="B121" s="132"/>
       <c r="C121" s="31" t="s">
         <v>102</v>
       </c>
@@ -62791,10 +65753,10 @@
       <c r="A122" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B122" s="127" t="s">
+      <c r="B122" s="132" t="s">
         <v>306</v>
       </c>
-      <c r="C122" s="127"/>
+      <c r="C122" s="132"/>
       <c r="D122" s="31" t="s">
         <v>307</v>
       </c>
@@ -62806,10 +65768,10 @@
       <c r="A123" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B123" s="127" t="s">
+      <c r="B123" s="132" t="s">
         <v>72</v>
       </c>
-      <c r="C123" s="127"/>
+      <c r="C123" s="132"/>
       <c r="D123" s="31" t="s">
         <v>309</v>
       </c>
@@ -62821,10 +65783,10 @@
       <c r="A124" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B124" s="128" t="s">
+      <c r="B124" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="C124" s="128"/>
+      <c r="C124" s="133"/>
       <c r="D124" s="27" t="s">
         <v>311</v>
       </c>
@@ -62836,10 +65798,10 @@
       <c r="A125" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B125" s="127" t="s">
+      <c r="B125" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="C125" s="127"/>
+      <c r="C125" s="132"/>
       <c r="D125" s="27" t="s">
         <v>313</v>
       </c>
@@ -62851,10 +65813,10 @@
       <c r="A126" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="127" t="s">
+      <c r="B126" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="C126" s="127"/>
+      <c r="C126" s="132"/>
       <c r="D126" s="27" t="s">
         <v>315</v>
       </c>
@@ -62866,10 +65828,10 @@
       <c r="A127" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B127" s="127" t="s">
+      <c r="B127" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="C127" s="127"/>
+      <c r="C127" s="132"/>
       <c r="D127" s="27" t="s">
         <v>317</v>
       </c>
@@ -62878,13 +65840,13 @@
       </c>
     </row>
     <row r="128" spans="1:1024" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="127" t="s">
+      <c r="A128" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B128" s="127" t="s">
+      <c r="B128" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="C128" s="127"/>
+      <c r="C128" s="132"/>
       <c r="D128" s="28" t="s">
         <v>319</v>
       </c>
@@ -62893,16 +65855,16 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="127"/>
-      <c r="B129" s="127"/>
-      <c r="C129" s="127"/>
+      <c r="A129" s="132"/>
+      <c r="B129" s="132"/>
+      <c r="C129" s="132"/>
       <c r="D129" s="28"/>
       <c r="E129" s="30"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="127"/>
-      <c r="B130" s="127"/>
-      <c r="C130" s="127"/>
+      <c r="A130" s="132"/>
+      <c r="B130" s="132"/>
+      <c r="C130" s="132"/>
       <c r="D130" s="28" t="s">
         <v>321</v>
       </c>
@@ -62911,9 +65873,9 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="127"/>
-      <c r="B131" s="127"/>
-      <c r="C131" s="127"/>
+      <c r="A131" s="132"/>
+      <c r="B131" s="132"/>
+      <c r="C131" s="132"/>
       <c r="D131" s="28" t="s">
         <v>323</v>
       </c>
@@ -62922,9 +65884,9 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="127"/>
-      <c r="B132" s="127"/>
-      <c r="C132" s="127"/>
+      <c r="A132" s="132"/>
+      <c r="B132" s="132"/>
+      <c r="C132" s="132"/>
       <c r="D132" s="28" t="s">
         <v>325</v>
       </c>
@@ -62933,9 +65895,9 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="127"/>
-      <c r="B133" s="127"/>
-      <c r="C133" s="127"/>
+      <c r="A133" s="132"/>
+      <c r="B133" s="132"/>
+      <c r="C133" s="132"/>
       <c r="D133" s="31" t="s">
         <v>327</v>
       </c>
@@ -62947,10 +65909,10 @@
       <c r="A134" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="127" t="s">
+      <c r="B134" s="132" t="s">
         <v>89</v>
       </c>
-      <c r="C134" s="127"/>
+      <c r="C134" s="132"/>
       <c r="D134" s="31" t="s">
         <v>329</v>
       </c>
@@ -62962,10 +65924,10 @@
       <c r="A135" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B135" s="127" t="s">
+      <c r="B135" s="132" t="s">
         <v>66</v>
       </c>
-      <c r="C135" s="127"/>
+      <c r="C135" s="132"/>
       <c r="D135" s="31" t="s">
         <v>331</v>
       </c>
@@ -62977,10 +65939,10 @@
       <c r="A136" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B136" s="127" t="s">
+      <c r="B136" s="132" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="127"/>
+      <c r="C136" s="132"/>
       <c r="D136" s="31" t="s">
         <v>334</v>
       </c>
@@ -62992,10 +65954,10 @@
       <c r="A137" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B137" s="127" t="s">
+      <c r="B137" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="C137" s="127"/>
+      <c r="C137" s="132"/>
       <c r="D137" s="31" t="s">
         <v>336</v>
       </c>
@@ -63007,10 +65969,10 @@
       <c r="A138" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B138" s="127" t="s">
+      <c r="B138" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="C138" s="127"/>
+      <c r="C138" s="132"/>
       <c r="D138" s="31" t="s">
         <v>338</v>
       </c>
@@ -63019,12 +65981,12 @@
       </c>
     </row>
     <row r="140" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="128" t="s">
+      <c r="A140" s="133" t="s">
         <v>340</v>
       </c>
-      <c r="B140" s="128"/>
-      <c r="C140" s="128"/>
-      <c r="D140" s="128"/>
+      <c r="B140" s="133"/>
+      <c r="C140" s="133"/>
+      <c r="D140" s="133"/>
       <c r="E140" s="27" t="s">
         <v>341</v>
       </c>

--- a/zero-data/io_lists/ZERO mocked IO-List.xlsx
+++ b/zero-data/io_lists/ZERO mocked IO-List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\Git\zero\zero-data\io_lists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B93BC-BED7-4CB7-88A5-ADCEC14CA31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494725B5-9FCC-4DB1-B2FD-6C30BA26320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3270,20 +3270,24 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
@@ -3292,7 +3296,6 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3311,33 +3314,24 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3348,7 +3342,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4505,197 +4505,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" s="16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="111" t="s">
+      <c r="D1" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="111" t="s">
+      <c r="E1" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="111" t="s">
+      <c r="F1" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="111" t="s">
+      <c r="G1" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="115" t="s">
+      <c r="H1" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="127" t="s">
+      <c r="I1" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="120" t="s">
+      <c r="J1" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="128" t="s">
+      <c r="K1" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="129" t="s">
+      <c r="L1" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="130"/>
-      <c r="N1" s="111" t="s">
+      <c r="M1" s="115"/>
+      <c r="N1" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="111" t="s">
+      <c r="O1" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="111" t="s">
+      <c r="P1" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="111" t="s">
+      <c r="Q1" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="111" t="s">
+      <c r="R1" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="111" t="s">
+      <c r="S1" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="118" t="s">
+      <c r="T1" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="118"/>
-      <c r="V1" s="118"/>
-      <c r="W1" s="121" t="s">
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="122" t="s">
         <v>438</v>
       </c>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
-      <c r="Z1" s="123"/>
-      <c r="AA1" s="119" t="s">
+      <c r="X1" s="123"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="124" t="s">
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="121"/>
+      <c r="AI1" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="124"/>
-      <c r="AK1" s="120" t="s">
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="AL1" s="120" t="s">
+      <c r="AL1" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="AM1" s="117" t="s">
+      <c r="AM1" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="AN1" s="126" t="s">
+      <c r="AN1" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="126"/>
-      <c r="AP1" s="126"/>
-      <c r="AQ1" s="126"/>
-      <c r="AR1" s="126"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="AT1" s="111" t="s">
+      <c r="AT1" s="112" t="s">
         <v>71</v>
       </c>
-      <c r="AU1" s="111" t="s">
+      <c r="AU1" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="AV1" s="111" t="s">
+      <c r="AV1" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="AW1" s="125" t="s">
+      <c r="AW1" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="AX1" s="114" t="s">
+      <c r="AX1" s="130" t="s">
         <v>75</v>
       </c>
-      <c r="AY1" s="115" t="s">
+      <c r="AY1" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="AZ1" s="115" t="s">
+      <c r="AZ1" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="BA1" s="115" t="s">
+      <c r="BA1" s="116" t="s">
         <v>78</v>
       </c>
-      <c r="BB1" s="115" t="s">
+      <c r="BB1" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="BC1" s="113" t="s">
+      <c r="BC1" s="129" t="s">
         <v>80</v>
       </c>
-      <c r="BD1" s="113"/>
-      <c r="BE1" s="113"/>
-      <c r="BF1" s="113" t="s">
+      <c r="BD1" s="129"/>
+      <c r="BE1" s="129"/>
+      <c r="BF1" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="BG1" s="113"/>
-      <c r="BH1" s="113"/>
-      <c r="BI1" s="113" t="s">
+      <c r="BG1" s="129"/>
+      <c r="BH1" s="129"/>
+      <c r="BI1" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="BJ1" s="113"/>
-      <c r="BK1" s="113"/>
-      <c r="BL1" s="113" t="s">
+      <c r="BJ1" s="129"/>
+      <c r="BK1" s="129"/>
+      <c r="BL1" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="BM1" s="113"/>
-      <c r="BN1" s="113"/>
-      <c r="BO1" s="113" t="s">
+      <c r="BM1" s="129"/>
+      <c r="BN1" s="129"/>
+      <c r="BO1" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="BP1" s="113"/>
-      <c r="BQ1" s="113"/>
-      <c r="BR1" s="117" t="s">
+      <c r="BP1" s="129"/>
+      <c r="BQ1" s="129"/>
+      <c r="BR1" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="BS1" s="115" t="s">
+      <c r="BS1" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="BT1" s="116" t="s">
+      <c r="BT1" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="BU1" s="112" t="s">
+      <c r="BU1" s="128" t="s">
         <v>88</v>
       </c>
-      <c r="BV1" s="112" t="s">
+      <c r="BV1" s="128" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:74" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="131"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="128"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="113"/>
       <c r="L2" s="97" t="s">
         <v>93</v>
       </c>
       <c r="M2" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
       <c r="T2" s="17" t="s">
         <v>90</v>
       </c>
@@ -4747,9 +4747,9 @@
       <c r="AJ2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="120"/>
-      <c r="AL2" s="120"/>
-      <c r="AM2" s="117"/>
+      <c r="AK2" s="118"/>
+      <c r="AL2" s="118"/>
+      <c r="AM2" s="119"/>
       <c r="AN2" s="18" t="s">
         <v>103</v>
       </c>
@@ -4765,16 +4765,16 @@
       <c r="AR2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="AS2" s="111"/>
-      <c r="AT2" s="111"/>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
-      <c r="AW2" s="125"/>
-      <c r="AX2" s="114"/>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
-      <c r="BB2" s="115"/>
+      <c r="AS2" s="112"/>
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="126"/>
+      <c r="AX2" s="130"/>
+      <c r="AY2" s="116"/>
+      <c r="AZ2" s="116"/>
+      <c r="BA2" s="116"/>
+      <c r="BB2" s="116"/>
       <c r="BC2" s="21" t="s">
         <v>56</v>
       </c>
@@ -4820,11 +4820,11 @@
       <c r="BQ2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="BR2" s="117"/>
-      <c r="BS2" s="115"/>
-      <c r="BT2" s="116"/>
-      <c r="BU2" s="112"/>
-      <c r="BV2" s="112"/>
+      <c r="BR2" s="119"/>
+      <c r="BS2" s="116"/>
+      <c r="BT2" s="131"/>
+      <c r="BU2" s="128"/>
+      <c r="BV2" s="128"/>
     </row>
     <row r="3" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
@@ -7222,7 +7222,7 @@
         <v>376</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>521</v>
@@ -7257,7 +7257,7 @@
         <v>376</v>
       </c>
       <c r="C31" s="54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>521</v>
@@ -7292,7 +7292,7 @@
         <v>376</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>521</v>
@@ -7747,7 +7747,7 @@
         <v>376</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>557</v>
@@ -7782,7 +7782,7 @@
         <v>376</v>
       </c>
       <c r="C46" s="54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>557</v>
@@ -7817,7 +7817,7 @@
         <v>376</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>557</v>
@@ -63086,36 +63086,6 @@
     <filterColumn colId="67" showButton="0"/>
   </autoFilter>
   <mergeCells count="46">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="BR1:BR2"/>
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="AA1:AH1"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="AT1:AT2"/>
-    <mergeCell ref="AU1:AU2"/>
-    <mergeCell ref="AV1:AV2"/>
-    <mergeCell ref="AW1:AW2"/>
-    <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="BV1:BV2"/>
     <mergeCell ref="BC1:BE1"/>
@@ -63132,6 +63102,36 @@
     <mergeCell ref="BT1:BT2"/>
     <mergeCell ref="BU1:BU2"/>
     <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="BR1:BR2"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="AT1:AT2"/>
+    <mergeCell ref="AU1:AU2"/>
+    <mergeCell ref="AV1:AV2"/>
+    <mergeCell ref="AW1:AW2"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="1">
@@ -63226,10 +63226,10 @@
       <c r="A4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="140" t="s">
+      <c r="B4" s="132" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="140"/>
+      <c r="C4" s="132"/>
       <c r="D4" s="26" t="s">
         <v>59</v>
       </c>
@@ -63238,13 +63238,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="133" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="132"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="28" t="s">
         <v>158</v>
       </c>
@@ -63253,16 +63253,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="132"/>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
+      <c r="A6" s="133"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
       <c r="D6" s="28"/>
       <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="132"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="133"/>
+      <c r="C7" s="133"/>
       <c r="D7" s="28" t="s">
         <v>160</v>
       </c>
@@ -63271,9 +63271,9 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="132"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
       <c r="D8" s="28" t="s">
         <v>162</v>
       </c>
@@ -63282,9 +63282,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="132"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
       <c r="D9" s="28" t="s">
         <v>163</v>
       </c>
@@ -63293,9 +63293,9 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="132"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
       <c r="D10" s="28" t="s">
         <v>164</v>
       </c>
@@ -63304,9 +63304,9 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="132"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
       <c r="D11" s="31" t="s">
         <v>165</v>
       </c>
@@ -63318,7 +63318,7 @@
       <c r="A12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="133" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="31" t="s">
@@ -63335,7 +63335,7 @@
       <c r="A13" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="132"/>
+      <c r="B13" s="133"/>
       <c r="C13" s="31" t="s">
         <v>104</v>
       </c>
@@ -63350,7 +63350,7 @@
       <c r="A14" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="132"/>
+      <c r="B14" s="133"/>
       <c r="C14" s="31" t="s">
         <v>105</v>
       </c>
@@ -63365,7 +63365,7 @@
       <c r="A15" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="132"/>
+      <c r="B15" s="133"/>
       <c r="C15" s="31" t="s">
         <v>106</v>
       </c>
@@ -63380,7 +63380,7 @@
       <c r="A16" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="132"/>
+      <c r="B16" s="133"/>
       <c r="C16" s="31" t="s">
         <v>107</v>
       </c>
@@ -63395,10 +63395,10 @@
       <c r="A17" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="132" t="s">
+      <c r="B17" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="132"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="31" t="s">
         <v>177</v>
       </c>
@@ -63410,10 +63410,10 @@
       <c r="A18" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="132"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="31" t="s">
         <v>180</v>
       </c>
@@ -63425,10 +63425,10 @@
       <c r="A19" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="132" t="s">
+      <c r="B19" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="132"/>
+      <c r="C19" s="133"/>
       <c r="D19" s="31" t="s">
         <v>183</v>
       </c>
@@ -63440,10 +63440,10 @@
       <c r="A20" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="132" t="s">
+      <c r="B20" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="132"/>
+      <c r="C20" s="133"/>
       <c r="D20" s="31" t="s">
         <v>186</v>
       </c>
@@ -63455,10 +63455,10 @@
       <c r="A21" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="132" t="s">
+      <c r="B21" s="133" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="132"/>
+      <c r="C21" s="133"/>
       <c r="D21" s="31" t="s">
         <v>189</v>
       </c>
@@ -63470,10 +63470,10 @@
       <c r="A22" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="132" t="s">
+      <c r="B22" s="133" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="132"/>
+      <c r="C22" s="133"/>
       <c r="D22" s="31" t="s">
         <v>192</v>
       </c>
@@ -63482,13 +63482,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="132" t="s">
+      <c r="B23" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="132"/>
+      <c r="C23" s="133"/>
       <c r="D23" s="28" t="s">
         <v>194</v>
       </c>
@@ -63497,9 +63497,9 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="132"/>
-      <c r="B24" s="132"/>
-      <c r="C24" s="132"/>
+      <c r="A24" s="133"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
       <c r="D24" s="28" t="s">
         <v>196</v>
       </c>
@@ -63508,9 +63508,9 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="132"/>
-      <c r="B25" s="132"/>
-      <c r="C25" s="132"/>
+      <c r="A25" s="133"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="133"/>
       <c r="D25" s="28" t="s">
         <v>198</v>
       </c>
@@ -63519,9 +63519,9 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="132"/>
-      <c r="B26" s="132"/>
-      <c r="C26" s="132"/>
+      <c r="A26" s="133"/>
+      <c r="B26" s="133"/>
+      <c r="C26" s="133"/>
       <c r="D26" s="28" t="s">
         <v>199</v>
       </c>
@@ -63530,9 +63530,9 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="132"/>
-      <c r="B27" s="132"/>
-      <c r="C27" s="132"/>
+      <c r="A27" s="133"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="133"/>
       <c r="D27" s="28" t="s">
         <v>200</v>
       </c>
@@ -63541,9 +63541,9 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="132"/>
-      <c r="B28" s="132"/>
-      <c r="C28" s="132"/>
+      <c r="A28" s="133"/>
+      <c r="B28" s="133"/>
+      <c r="C28" s="133"/>
       <c r="D28" s="28" t="s">
         <v>201</v>
       </c>
@@ -63552,9 +63552,9 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="132"/>
-      <c r="B29" s="132"/>
-      <c r="C29" s="132"/>
+      <c r="A29" s="133"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="133"/>
       <c r="D29" s="28" t="s">
         <v>202</v>
       </c>
@@ -63563,9 +63563,9 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="132"/>
-      <c r="B30" s="132"/>
-      <c r="C30" s="132"/>
+      <c r="A30" s="133"/>
+      <c r="B30" s="133"/>
+      <c r="C30" s="133"/>
       <c r="D30" s="28" t="s">
         <v>203</v>
       </c>
@@ -63574,9 +63574,9 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="132"/>
-      <c r="B31" s="132"/>
-      <c r="C31" s="132"/>
+      <c r="A31" s="133"/>
+      <c r="B31" s="133"/>
+      <c r="C31" s="133"/>
       <c r="D31" s="28" t="s">
         <v>204</v>
       </c>
@@ -63585,9 +63585,9 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="132"/>
-      <c r="B32" s="132"/>
-      <c r="C32" s="132"/>
+      <c r="A32" s="133"/>
+      <c r="B32" s="133"/>
+      <c r="C32" s="133"/>
       <c r="D32" s="28" t="s">
         <v>205</v>
       </c>
@@ -63596,9 +63596,9 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="132"/>
-      <c r="B33" s="132"/>
-      <c r="C33" s="132"/>
+      <c r="A33" s="133"/>
+      <c r="B33" s="133"/>
+      <c r="C33" s="133"/>
       <c r="D33" s="28" t="s">
         <v>206</v>
       </c>
@@ -63607,16 +63607,16 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="132"/>
-      <c r="B34" s="132"/>
-      <c r="C34" s="132"/>
+      <c r="A34" s="133"/>
+      <c r="B34" s="133"/>
+      <c r="C34" s="133"/>
       <c r="D34" s="28"/>
       <c r="E34" s="30"/>
     </row>
     <row r="35" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="132"/>
-      <c r="B35" s="132"/>
-      <c r="C35" s="132"/>
+      <c r="A35" s="133"/>
+      <c r="B35" s="133"/>
+      <c r="C35" s="133"/>
       <c r="D35" s="28" t="s">
         <v>208</v>
       </c>
@@ -63625,9 +63625,9 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="132"/>
-      <c r="B36" s="132"/>
-      <c r="C36" s="132"/>
+      <c r="A36" s="133"/>
+      <c r="B36" s="133"/>
+      <c r="C36" s="133"/>
       <c r="D36" s="31" t="s">
         <v>210</v>
       </c>
@@ -63639,10 +63639,10 @@
       <c r="A37" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="133" t="s">
+      <c r="B37" s="134" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="133"/>
+      <c r="C37" s="134"/>
       <c r="D37" s="31" t="s">
         <v>212</v>
       </c>
@@ -63654,10 +63654,10 @@
       <c r="A38" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B38" s="132" t="s">
+      <c r="B38" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="132"/>
+      <c r="C38" s="133"/>
       <c r="D38" s="31" t="s">
         <v>214</v>
       </c>
@@ -63669,10 +63669,10 @@
       <c r="A39" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="132" t="s">
+      <c r="B39" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="132"/>
+      <c r="C39" s="133"/>
       <c r="D39" s="31" t="s">
         <v>216</v>
       </c>
@@ -63681,13 +63681,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="132" t="s">
+      <c r="A40" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B40" s="132" t="s">
+      <c r="B40" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="132"/>
+      <c r="C40" s="133"/>
       <c r="D40" s="28" t="s">
         <v>218</v>
       </c>
@@ -63696,9 +63696,9 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="132"/>
-      <c r="B41" s="132"/>
-      <c r="C41" s="132"/>
+      <c r="A41" s="133"/>
+      <c r="B41" s="133"/>
+      <c r="C41" s="133"/>
       <c r="D41" s="28" t="s">
         <v>220</v>
       </c>
@@ -63707,9 +63707,9 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="132"/>
-      <c r="B42" s="132"/>
-      <c r="C42" s="132"/>
+      <c r="A42" s="133"/>
+      <c r="B42" s="133"/>
+      <c r="C42" s="133"/>
       <c r="D42" s="28" t="s">
         <v>222</v>
       </c>
@@ -63718,9 +63718,9 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="132"/>
-      <c r="B43" s="132"/>
-      <c r="C43" s="132"/>
+      <c r="A43" s="133"/>
+      <c r="B43" s="133"/>
+      <c r="C43" s="133"/>
       <c r="D43" s="28" t="s">
         <v>224</v>
       </c>
@@ -63729,9 +63729,9 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="132"/>
-      <c r="B44" s="132"/>
-      <c r="C44" s="132"/>
+      <c r="A44" s="133"/>
+      <c r="B44" s="133"/>
+      <c r="C44" s="133"/>
       <c r="D44" s="28" t="s">
         <v>226</v>
       </c>
@@ -63743,10 +63743,10 @@
       <c r="A45" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="132" t="s">
+      <c r="B45" s="133" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="132"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="27" t="s">
         <v>227</v>
       </c>
@@ -63803,7 +63803,7 @@
       <c r="A49" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="137" t="s">
+      <c r="B49" s="135" t="s">
         <v>237</v>
       </c>
       <c r="C49" s="31" t="s">
@@ -63817,11 +63817,11 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="132" t="s">
+      <c r="A50" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B50" s="137"/>
-      <c r="C50" s="138" t="s">
+      <c r="B50" s="135"/>
+      <c r="C50" s="136" t="s">
         <v>108</v>
       </c>
       <c r="D50" s="40" t="s">
@@ -63832,9 +63832,9 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="132"/>
-      <c r="B51" s="137"/>
-      <c r="C51" s="138"/>
+      <c r="A51" s="133"/>
+      <c r="B51" s="135"/>
+      <c r="C51" s="136"/>
       <c r="D51" s="30" t="s">
         <v>242</v>
       </c>
@@ -63843,9 +63843,9 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="132"/>
-      <c r="B52" s="137"/>
-      <c r="C52" s="138"/>
+      <c r="A52" s="133"/>
+      <c r="B52" s="135"/>
+      <c r="C52" s="136"/>
       <c r="D52" s="30" t="s">
         <v>244</v>
       </c>
@@ -63854,9 +63854,9 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="132"/>
-      <c r="B53" s="137"/>
-      <c r="C53" s="138"/>
+      <c r="A53" s="133"/>
+      <c r="B53" s="135"/>
+      <c r="C53" s="136"/>
       <c r="D53" s="30" t="s">
         <v>246</v>
       </c>
@@ -63865,16 +63865,16 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="132"/>
-      <c r="B54" s="137"/>
-      <c r="C54" s="138"/>
+      <c r="A54" s="133"/>
+      <c r="B54" s="135"/>
+      <c r="C54" s="136"/>
       <c r="D54" s="28"/>
       <c r="E54" s="30"/>
     </row>
     <row r="55" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="132"/>
-      <c r="B55" s="137"/>
-      <c r="C55" s="138"/>
+      <c r="A55" s="133"/>
+      <c r="B55" s="135"/>
+      <c r="C55" s="136"/>
       <c r="D55" s="31" t="s">
         <v>248</v>
       </c>
@@ -63883,11 +63883,11 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="132" t="s">
+      <c r="A56" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B56" s="137"/>
-      <c r="C56" s="139" t="s">
+      <c r="B56" s="135"/>
+      <c r="C56" s="137" t="s">
         <v>109</v>
       </c>
       <c r="D56" s="28" t="s">
@@ -63898,9 +63898,9 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="132"/>
-      <c r="B57" s="137"/>
-      <c r="C57" s="139"/>
+      <c r="A57" s="133"/>
+      <c r="B57" s="135"/>
+      <c r="C57" s="137"/>
       <c r="D57" s="28" t="s">
         <v>252</v>
       </c>
@@ -63909,9 +63909,9 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="132"/>
-      <c r="B58" s="137"/>
-      <c r="C58" s="139"/>
+      <c r="A58" s="133"/>
+      <c r="B58" s="135"/>
+      <c r="C58" s="137"/>
       <c r="D58" s="31" t="s">
         <v>254</v>
       </c>
@@ -63923,10 +63923,10 @@
       <c r="A59" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="132" t="s">
+      <c r="B59" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="132"/>
+      <c r="C59" s="133"/>
       <c r="D59" s="31" t="s">
         <v>256</v>
       </c>
@@ -63938,7 +63938,7 @@
       <c r="A60" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="136" t="s">
+      <c r="B60" s="138" t="s">
         <v>82</v>
       </c>
       <c r="C60" s="31" t="s">
@@ -63952,11 +63952,11 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="132" t="s">
+      <c r="A61" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B61" s="136"/>
-      <c r="C61" s="132" t="s">
+      <c r="B61" s="138"/>
+      <c r="C61" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D61" s="40" t="s">
@@ -63967,9 +63967,9 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="132"/>
-      <c r="B62" s="132"/>
-      <c r="C62" s="132"/>
+      <c r="A62" s="133"/>
+      <c r="B62" s="133"/>
+      <c r="C62" s="133"/>
       <c r="D62" s="30" t="s">
         <v>242</v>
       </c>
@@ -63978,9 +63978,9 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="132"/>
-      <c r="B63" s="132"/>
-      <c r="C63" s="132"/>
+      <c r="A63" s="133"/>
+      <c r="B63" s="133"/>
+      <c r="C63" s="133"/>
       <c r="D63" s="30" t="s">
         <v>244</v>
       </c>
@@ -63989,9 +63989,9 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="132"/>
-      <c r="B64" s="132"/>
-      <c r="C64" s="132"/>
+      <c r="A64" s="133"/>
+      <c r="B64" s="133"/>
+      <c r="C64" s="133"/>
       <c r="D64" s="30" t="s">
         <v>246</v>
       </c>
@@ -64000,16 +64000,16 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="132"/>
-      <c r="B65" s="132"/>
-      <c r="C65" s="132"/>
+      <c r="A65" s="133"/>
+      <c r="B65" s="133"/>
+      <c r="C65" s="133"/>
       <c r="D65" s="28"/>
       <c r="E65" s="30"/>
     </row>
     <row r="66" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="132"/>
-      <c r="B66" s="136"/>
-      <c r="C66" s="132"/>
+      <c r="A66" s="133"/>
+      <c r="B66" s="138"/>
+      <c r="C66" s="133"/>
       <c r="D66" s="31" t="s">
         <v>248</v>
       </c>
@@ -64018,11 +64018,11 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="132" t="s">
+      <c r="A67" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="136"/>
-      <c r="C67" s="132" t="s">
+      <c r="B67" s="138"/>
+      <c r="C67" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D67" s="28" t="s">
@@ -64033,9 +64033,9 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="132"/>
-      <c r="B68" s="132"/>
-      <c r="C68" s="132"/>
+      <c r="A68" s="133"/>
+      <c r="B68" s="133"/>
+      <c r="C68" s="133"/>
       <c r="D68" s="28" t="s">
         <v>252</v>
       </c>
@@ -64044,9 +64044,9 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="132"/>
-      <c r="B69" s="136"/>
-      <c r="C69" s="132"/>
+      <c r="A69" s="133"/>
+      <c r="B69" s="138"/>
+      <c r="C69" s="133"/>
       <c r="D69" s="31" t="s">
         <v>254</v>
       </c>
@@ -64058,7 +64058,7 @@
       <c r="A70" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="136" t="s">
+      <c r="B70" s="138" t="s">
         <v>81</v>
       </c>
       <c r="C70" s="31" t="s">
@@ -64072,11 +64072,11 @@
       </c>
     </row>
     <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="132" t="s">
+      <c r="A71" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="136"/>
-      <c r="C71" s="132" t="s">
+      <c r="B71" s="138"/>
+      <c r="C71" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D71" s="40" t="s">
@@ -64087,9 +64087,9 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="132"/>
-      <c r="B72" s="132"/>
-      <c r="C72" s="132"/>
+      <c r="A72" s="133"/>
+      <c r="B72" s="133"/>
+      <c r="C72" s="133"/>
       <c r="D72" s="30" t="s">
         <v>242</v>
       </c>
@@ -64098,9 +64098,9 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="132"/>
-      <c r="B73" s="132"/>
-      <c r="C73" s="132"/>
+      <c r="A73" s="133"/>
+      <c r="B73" s="133"/>
+      <c r="C73" s="133"/>
       <c r="D73" s="30" t="s">
         <v>244</v>
       </c>
@@ -64109,9 +64109,9 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="132"/>
-      <c r="B74" s="132"/>
-      <c r="C74" s="132"/>
+      <c r="A74" s="133"/>
+      <c r="B74" s="133"/>
+      <c r="C74" s="133"/>
       <c r="D74" s="30" t="s">
         <v>246</v>
       </c>
@@ -64120,16 +64120,16 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="132"/>
-      <c r="B75" s="132"/>
-      <c r="C75" s="132"/>
+      <c r="A75" s="133"/>
+      <c r="B75" s="133"/>
+      <c r="C75" s="133"/>
       <c r="D75" s="28"/>
       <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="132"/>
-      <c r="B76" s="136"/>
-      <c r="C76" s="132"/>
+      <c r="A76" s="133"/>
+      <c r="B76" s="138"/>
+      <c r="C76" s="133"/>
       <c r="D76" s="31" t="s">
         <v>248</v>
       </c>
@@ -64138,11 +64138,11 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="132" t="s">
+      <c r="A77" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="136"/>
-      <c r="C77" s="132" t="s">
+      <c r="B77" s="138"/>
+      <c r="C77" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D77" s="28" t="s">
@@ -64153,9 +64153,9 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="132"/>
-      <c r="B78" s="132"/>
-      <c r="C78" s="132"/>
+      <c r="A78" s="133"/>
+      <c r="B78" s="133"/>
+      <c r="C78" s="133"/>
       <c r="D78" s="28" t="s">
         <v>252</v>
       </c>
@@ -64164,9 +64164,9 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="132"/>
-      <c r="B79" s="136"/>
-      <c r="C79" s="132"/>
+      <c r="A79" s="133"/>
+      <c r="B79" s="138"/>
+      <c r="C79" s="133"/>
       <c r="D79" s="31" t="s">
         <v>254</v>
       </c>
@@ -64175,13 +64175,13 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="132" t="s">
+      <c r="A80" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="132" t="s">
+      <c r="B80" s="133" t="s">
         <v>258</v>
       </c>
-      <c r="C80" s="132"/>
+      <c r="C80" s="133"/>
       <c r="D80" s="28" t="s">
         <v>259</v>
       </c>
@@ -64190,9 +64190,9 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="132"/>
-      <c r="B81" s="132"/>
-      <c r="C81" s="132"/>
+      <c r="A81" s="133"/>
+      <c r="B81" s="133"/>
+      <c r="C81" s="133"/>
       <c r="D81" s="28" t="s">
         <v>261</v>
       </c>
@@ -64201,9 +64201,9 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="132"/>
-      <c r="B82" s="132"/>
-      <c r="C82" s="132"/>
+      <c r="A82" s="133"/>
+      <c r="B82" s="133"/>
+      <c r="C82" s="133"/>
       <c r="D82" s="28" t="s">
         <v>263</v>
       </c>
@@ -64212,9 +64212,9 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="132"/>
-      <c r="B83" s="132"/>
-      <c r="C83" s="132"/>
+      <c r="A83" s="133"/>
+      <c r="B83" s="133"/>
+      <c r="C83" s="133"/>
       <c r="D83" s="28" t="s">
         <v>265</v>
       </c>
@@ -64223,9 +64223,9 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="132"/>
-      <c r="B84" s="132"/>
-      <c r="C84" s="132"/>
+      <c r="A84" s="133"/>
+      <c r="B84" s="133"/>
+      <c r="C84" s="133"/>
       <c r="D84" s="28" t="s">
         <v>267</v>
       </c>
@@ -64234,9 +64234,9 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="132"/>
-      <c r="B85" s="132"/>
-      <c r="C85" s="132"/>
+      <c r="A85" s="133"/>
+      <c r="B85" s="133"/>
+      <c r="C85" s="133"/>
       <c r="D85" s="31" t="s">
         <v>269</v>
       </c>
@@ -64248,10 +64248,10 @@
       <c r="A86" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="132" t="s">
+      <c r="B86" s="133" t="s">
         <v>74</v>
       </c>
-      <c r="C86" s="132"/>
+      <c r="C86" s="133"/>
       <c r="D86" s="31" t="s">
         <v>271</v>
       </c>
@@ -64263,7 +64263,7 @@
       <c r="A87" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B87" s="136" t="s">
+      <c r="B87" s="138" t="s">
         <v>83</v>
       </c>
       <c r="C87" s="31" t="s">
@@ -64277,11 +64277,11 @@
       </c>
     </row>
     <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="132" t="s">
+      <c r="A88" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B88" s="136"/>
-      <c r="C88" s="132" t="s">
+      <c r="B88" s="138"/>
+      <c r="C88" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D88" s="40" t="s">
@@ -64292,9 +64292,9 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="132"/>
-      <c r="B89" s="132"/>
-      <c r="C89" s="132"/>
+      <c r="A89" s="133"/>
+      <c r="B89" s="133"/>
+      <c r="C89" s="133"/>
       <c r="D89" s="30" t="s">
         <v>242</v>
       </c>
@@ -64303,9 +64303,9 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="132"/>
-      <c r="B90" s="132"/>
-      <c r="C90" s="132"/>
+      <c r="A90" s="133"/>
+      <c r="B90" s="133"/>
+      <c r="C90" s="133"/>
       <c r="D90" s="30" t="s">
         <v>244</v>
       </c>
@@ -64314,9 +64314,9 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="132"/>
-      <c r="B91" s="132"/>
-      <c r="C91" s="132"/>
+      <c r="A91" s="133"/>
+      <c r="B91" s="133"/>
+      <c r="C91" s="133"/>
       <c r="D91" s="30" t="s">
         <v>246</v>
       </c>
@@ -64325,16 +64325,16 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="132"/>
-      <c r="B92" s="132"/>
-      <c r="C92" s="132"/>
+      <c r="A92" s="133"/>
+      <c r="B92" s="133"/>
+      <c r="C92" s="133"/>
       <c r="D92" s="28"/>
       <c r="E92" s="30"/>
     </row>
     <row r="93" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="132"/>
-      <c r="B93" s="136"/>
-      <c r="C93" s="132"/>
+      <c r="A93" s="133"/>
+      <c r="B93" s="138"/>
+      <c r="C93" s="133"/>
       <c r="D93" s="31" t="s">
         <v>248</v>
       </c>
@@ -64343,11 +64343,11 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="132" t="s">
+      <c r="A94" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B94" s="136"/>
-      <c r="C94" s="132" t="s">
+      <c r="B94" s="138"/>
+      <c r="C94" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D94" s="28" t="s">
@@ -64358,9 +64358,9 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="132"/>
-      <c r="B95" s="132"/>
-      <c r="C95" s="132"/>
+      <c r="A95" s="133"/>
+      <c r="B95" s="133"/>
+      <c r="C95" s="133"/>
       <c r="D95" s="28" t="s">
         <v>252</v>
       </c>
@@ -64369,9 +64369,9 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="132"/>
-      <c r="B96" s="136"/>
-      <c r="C96" s="132"/>
+      <c r="A96" s="133"/>
+      <c r="B96" s="138"/>
+      <c r="C96" s="133"/>
       <c r="D96" s="31" t="s">
         <v>254</v>
       </c>
@@ -64383,7 +64383,7 @@
       <c r="A97" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B97" s="136" t="s">
+      <c r="B97" s="138" t="s">
         <v>84</v>
       </c>
       <c r="C97" s="31" t="s">
@@ -64397,11 +64397,11 @@
       </c>
     </row>
     <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="132" t="s">
+      <c r="A98" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B98" s="136"/>
-      <c r="C98" s="132" t="s">
+      <c r="B98" s="138"/>
+      <c r="C98" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D98" s="40" t="s">
@@ -64412,9 +64412,9 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="132"/>
-      <c r="B99" s="132"/>
-      <c r="C99" s="132"/>
+      <c r="A99" s="133"/>
+      <c r="B99" s="133"/>
+      <c r="C99" s="133"/>
       <c r="D99" s="30" t="s">
         <v>242</v>
       </c>
@@ -64423,9 +64423,9 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="132"/>
-      <c r="B100" s="132"/>
-      <c r="C100" s="132"/>
+      <c r="A100" s="133"/>
+      <c r="B100" s="133"/>
+      <c r="C100" s="133"/>
       <c r="D100" s="30" t="s">
         <v>244</v>
       </c>
@@ -64434,9 +64434,9 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="132"/>
-      <c r="B101" s="132"/>
-      <c r="C101" s="132"/>
+      <c r="A101" s="133"/>
+      <c r="B101" s="133"/>
+      <c r="C101" s="133"/>
       <c r="D101" s="30" t="s">
         <v>246</v>
       </c>
@@ -64445,16 +64445,16 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="132"/>
-      <c r="B102" s="132"/>
-      <c r="C102" s="132"/>
+      <c r="A102" s="133"/>
+      <c r="B102" s="133"/>
+      <c r="C102" s="133"/>
       <c r="D102" s="28"/>
       <c r="E102" s="30"/>
     </row>
     <row r="103" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="132"/>
-      <c r="B103" s="136"/>
-      <c r="C103" s="132"/>
+      <c r="A103" s="133"/>
+      <c r="B103" s="138"/>
+      <c r="C103" s="133"/>
       <c r="D103" s="31" t="s">
         <v>248</v>
       </c>
@@ -64463,11 +64463,11 @@
       </c>
     </row>
     <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="132" t="s">
+      <c r="A104" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B104" s="136"/>
-      <c r="C104" s="132" t="s">
+      <c r="B104" s="138"/>
+      <c r="C104" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D104" s="28" t="s">
@@ -64478,9 +64478,9 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="132"/>
-      <c r="B105" s="132"/>
-      <c r="C105" s="132"/>
+      <c r="A105" s="133"/>
+      <c r="B105" s="133"/>
+      <c r="C105" s="133"/>
       <c r="D105" s="28" t="s">
         <v>252</v>
       </c>
@@ -64489,9 +64489,9 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="132"/>
-      <c r="B106" s="136"/>
-      <c r="C106" s="132"/>
+      <c r="A106" s="133"/>
+      <c r="B106" s="138"/>
+      <c r="C106" s="133"/>
       <c r="D106" s="31" t="s">
         <v>254</v>
       </c>
@@ -64503,10 +64503,10 @@
       <c r="A107" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B107" s="132" t="s">
+      <c r="B107" s="133" t="s">
         <v>273</v>
       </c>
-      <c r="C107" s="132"/>
+      <c r="C107" s="133"/>
       <c r="D107" s="31" t="s">
         <v>274</v>
       </c>
@@ -64518,10 +64518,10 @@
       <c r="A108" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B108" s="132" t="s">
+      <c r="B108" s="133" t="s">
         <v>276</v>
       </c>
-      <c r="C108" s="132"/>
+      <c r="C108" s="133"/>
       <c r="D108" s="31" t="s">
         <v>277</v>
       </c>
@@ -64533,10 +64533,10 @@
       <c r="A109" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B109" s="132" t="s">
+      <c r="B109" s="133" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="132"/>
+      <c r="C109" s="133"/>
       <c r="D109" s="31" t="s">
         <v>280</v>
       </c>
@@ -64545,13 +64545,13 @@
       </c>
     </row>
     <row r="110" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="132" t="s">
+      <c r="A110" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B110" s="135" t="s">
+      <c r="B110" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="135"/>
+      <c r="C110" s="139"/>
       <c r="D110" s="39" t="s">
         <v>282</v>
       </c>
@@ -64560,16 +64560,16 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="132"/>
-      <c r="B111" s="135"/>
-      <c r="C111" s="135"/>
+      <c r="A111" s="133"/>
+      <c r="B111" s="139"/>
+      <c r="C111" s="139"/>
       <c r="D111" s="41"/>
       <c r="E111" s="30"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="132"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="135"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="139"/>
+      <c r="C112" s="139"/>
       <c r="D112" s="42" t="s">
         <v>284</v>
       </c>
@@ -64578,9 +64578,9 @@
       </c>
     </row>
     <row r="113" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A113" s="132"/>
-      <c r="B113" s="135"/>
-      <c r="C113" s="135"/>
+      <c r="A113" s="133"/>
+      <c r="B113" s="139"/>
+      <c r="C113" s="139"/>
       <c r="D113" s="42" t="s">
         <v>286</v>
       </c>
@@ -64589,9 +64589,9 @@
       </c>
     </row>
     <row r="114" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A114" s="132"/>
-      <c r="B114" s="135"/>
-      <c r="C114" s="135"/>
+      <c r="A114" s="133"/>
+      <c r="B114" s="139"/>
+      <c r="C114" s="139"/>
       <c r="D114" s="42" t="s">
         <v>288</v>
       </c>
@@ -64600,9 +64600,9 @@
       </c>
     </row>
     <row r="115" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A115" s="132"/>
-      <c r="B115" s="135"/>
-      <c r="C115" s="135"/>
+      <c r="A115" s="133"/>
+      <c r="B115" s="139"/>
+      <c r="C115" s="139"/>
       <c r="D115" s="43" t="s">
         <v>290</v>
       </c>
@@ -64648,10 +64648,10 @@
       <c r="A118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="134" t="s">
+      <c r="B118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="C118" s="134"/>
+      <c r="C118" s="140"/>
       <c r="D118" s="46" t="s">
         <v>296</v>
       </c>
@@ -64912,10 +64912,10 @@
       <c r="IW118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="IX118" s="134" t="s">
+      <c r="IX118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="IY118" s="134"/>
+      <c r="IY118" s="140"/>
       <c r="IZ118" s="46" t="s">
         <v>296</v>
       </c>
@@ -65176,10 +65176,10 @@
       <c r="SS118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ST118" s="134" t="s">
+      <c r="ST118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="SU118" s="134"/>
+      <c r="SU118" s="140"/>
       <c r="SV118" s="46" t="s">
         <v>296</v>
       </c>
@@ -65440,10 +65440,10 @@
       <c r="ACO118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ACP118" s="134" t="s">
+      <c r="ACP118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="ACQ118" s="134"/>
+      <c r="ACQ118" s="140"/>
       <c r="ACR118" s="46" t="s">
         <v>296</v>
       </c>
@@ -65706,10 +65706,10 @@
       <c r="A119" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B119" s="132" t="s">
+      <c r="B119" s="133" t="s">
         <v>298</v>
       </c>
-      <c r="C119" s="132"/>
+      <c r="C119" s="133"/>
       <c r="D119" s="31" t="s">
         <v>299</v>
       </c>
@@ -65721,7 +65721,7 @@
       <c r="A120" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B120" s="132" t="s">
+      <c r="B120" s="133" t="s">
         <v>301</v>
       </c>
       <c r="C120" s="31" t="s">
@@ -65738,7 +65738,7 @@
       <c r="A121" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B121" s="132"/>
+      <c r="B121" s="133"/>
       <c r="C121" s="31" t="s">
         <v>102</v>
       </c>
@@ -65753,10 +65753,10 @@
       <c r="A122" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B122" s="132" t="s">
+      <c r="B122" s="133" t="s">
         <v>306</v>
       </c>
-      <c r="C122" s="132"/>
+      <c r="C122" s="133"/>
       <c r="D122" s="31" t="s">
         <v>307</v>
       </c>
@@ -65768,10 +65768,10 @@
       <c r="A123" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B123" s="132" t="s">
+      <c r="B123" s="133" t="s">
         <v>72</v>
       </c>
-      <c r="C123" s="132"/>
+      <c r="C123" s="133"/>
       <c r="D123" s="31" t="s">
         <v>309</v>
       </c>
@@ -65783,10 +65783,10 @@
       <c r="A124" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B124" s="133" t="s">
+      <c r="B124" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="C124" s="133"/>
+      <c r="C124" s="134"/>
       <c r="D124" s="27" t="s">
         <v>311</v>
       </c>
@@ -65798,10 +65798,10 @@
       <c r="A125" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B125" s="132" t="s">
+      <c r="B125" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="C125" s="132"/>
+      <c r="C125" s="133"/>
       <c r="D125" s="27" t="s">
         <v>313</v>
       </c>
@@ -65813,10 +65813,10 @@
       <c r="A126" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="132" t="s">
+      <c r="B126" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="C126" s="132"/>
+      <c r="C126" s="133"/>
       <c r="D126" s="27" t="s">
         <v>315</v>
       </c>
@@ -65828,10 +65828,10 @@
       <c r="A127" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B127" s="132" t="s">
+      <c r="B127" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="C127" s="132"/>
+      <c r="C127" s="133"/>
       <c r="D127" s="27" t="s">
         <v>317</v>
       </c>
@@ -65840,13 +65840,13 @@
       </c>
     </row>
     <row r="128" spans="1:1024" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="132" t="s">
+      <c r="A128" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B128" s="132" t="s">
+      <c r="B128" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="C128" s="132"/>
+      <c r="C128" s="133"/>
       <c r="D128" s="28" t="s">
         <v>319</v>
       </c>
@@ -65855,16 +65855,16 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="132"/>
-      <c r="B129" s="132"/>
-      <c r="C129" s="132"/>
+      <c r="A129" s="133"/>
+      <c r="B129" s="133"/>
+      <c r="C129" s="133"/>
       <c r="D129" s="28"/>
       <c r="E129" s="30"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="132"/>
-      <c r="B130" s="132"/>
-      <c r="C130" s="132"/>
+      <c r="A130" s="133"/>
+      <c r="B130" s="133"/>
+      <c r="C130" s="133"/>
       <c r="D130" s="28" t="s">
         <v>321</v>
       </c>
@@ -65873,9 +65873,9 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="132"/>
-      <c r="B131" s="132"/>
-      <c r="C131" s="132"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="133"/>
+      <c r="C131" s="133"/>
       <c r="D131" s="28" t="s">
         <v>323</v>
       </c>
@@ -65884,9 +65884,9 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="132"/>
-      <c r="B132" s="132"/>
-      <c r="C132" s="132"/>
+      <c r="A132" s="133"/>
+      <c r="B132" s="133"/>
+      <c r="C132" s="133"/>
       <c r="D132" s="28" t="s">
         <v>325</v>
       </c>
@@ -65895,9 +65895,9 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="132"/>
-      <c r="B133" s="132"/>
-      <c r="C133" s="132"/>
+      <c r="A133" s="133"/>
+      <c r="B133" s="133"/>
+      <c r="C133" s="133"/>
       <c r="D133" s="31" t="s">
         <v>327</v>
       </c>
@@ -65909,10 +65909,10 @@
       <c r="A134" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="132" t="s">
+      <c r="B134" s="133" t="s">
         <v>89</v>
       </c>
-      <c r="C134" s="132"/>
+      <c r="C134" s="133"/>
       <c r="D134" s="31" t="s">
         <v>329</v>
       </c>
@@ -65924,10 +65924,10 @@
       <c r="A135" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B135" s="132" t="s">
+      <c r="B135" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="C135" s="132"/>
+      <c r="C135" s="133"/>
       <c r="D135" s="31" t="s">
         <v>331</v>
       </c>
@@ -65939,10 +65939,10 @@
       <c r="A136" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B136" s="132" t="s">
+      <c r="B136" s="133" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="132"/>
+      <c r="C136" s="133"/>
       <c r="D136" s="31" t="s">
         <v>334</v>
       </c>
@@ -65954,10 +65954,10 @@
       <c r="A137" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B137" s="132" t="s">
+      <c r="B137" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="C137" s="132"/>
+      <c r="C137" s="133"/>
       <c r="D137" s="31" t="s">
         <v>336</v>
       </c>
@@ -65969,10 +65969,10 @@
       <c r="A138" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B138" s="132" t="s">
+      <c r="B138" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="C138" s="132"/>
+      <c r="C138" s="133"/>
       <c r="D138" s="31" t="s">
         <v>338</v>
       </c>
@@ -65981,12 +65981,12 @@
       </c>
     </row>
     <row r="140" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="133" t="s">
+      <c r="A140" s="134" t="s">
         <v>340</v>
       </c>
-      <c r="B140" s="133"/>
-      <c r="C140" s="133"/>
-      <c r="D140" s="133"/>
+      <c r="B140" s="134"/>
+      <c r="C140" s="134"/>
+      <c r="D140" s="134"/>
       <c r="E140" s="27" t="s">
         <v>341</v>
       </c>
@@ -65998,21 +65998,55 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="B5:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A23:A36"/>
-    <mergeCell ref="B23:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="A128:A133"/>
+    <mergeCell ref="B128:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="IX118:IY118"/>
+    <mergeCell ref="ST118:SU118"/>
+    <mergeCell ref="ACP118:ACQ118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="A110:A115"/>
+    <mergeCell ref="B110:C115"/>
+    <mergeCell ref="B97:B106"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="C98:C103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="B80:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:B96"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="B70:B79"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:B69"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="C67:C69"/>
     <mergeCell ref="A40:A44"/>
     <mergeCell ref="B40:C44"/>
     <mergeCell ref="B45:C45"/>
@@ -66021,55 +66055,21 @@
     <mergeCell ref="C50:C55"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="C56:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:B69"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="B70:B79"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="C71:C76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="A80:A85"/>
-    <mergeCell ref="B80:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:B96"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="A94:A96"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="B97:B106"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="C98:C103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="A110:A115"/>
-    <mergeCell ref="B110:C115"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="IX118:IY118"/>
-    <mergeCell ref="ST118:SU118"/>
-    <mergeCell ref="ACP118:ACQ118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="A128:A133"/>
-    <mergeCell ref="B128:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="A23:A36"/>
+    <mergeCell ref="B23:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="B5:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/zero-data/io_lists/ZERO mocked IO-List.xlsx
+++ b/zero-data/io_lists/ZERO mocked IO-List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\Git\zero\zero-data\io_lists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66B4F66-0E40-4B8B-9AD5-3710699F5F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494725B5-9FCC-4DB1-B2FD-6C30BA26320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Internal lists" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IO-List'!$A$1:$BV$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IO-List'!$A$1:$BV$154</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="746">
   <si>
     <t>Revision</t>
   </si>
@@ -1708,6 +1708,681 @@
   <si>
     <t>24 Vdc DB General Service 14E1 Current Measurement</t>
   </si>
+  <si>
+    <t>KEB10</t>
+  </si>
+  <si>
+    <t>DI20</t>
+  </si>
+  <si>
+    <t>DI21</t>
+  </si>
+  <si>
+    <t>AFT THRUSTER</t>
+  </si>
+  <si>
+    <t>DI22</t>
+  </si>
+  <si>
+    <t>Azimuth0positionsensorAftThruster</t>
+  </si>
+  <si>
+    <t>Azimuth 0 position sensor Aft Thruster</t>
+  </si>
+  <si>
+    <t>PS HELM CONSOLE</t>
+  </si>
+  <si>
+    <t>AzimuthPositionFeedbackAbsoluteEncoderAFTThruster</t>
+  </si>
+  <si>
+    <t>PitchPositionFeedbackAbsoluteEncoderAFTThruster</t>
+  </si>
+  <si>
+    <t>Azimuth Position Feedback Absolute Encoder AFT Thruster</t>
+  </si>
+  <si>
+    <t>Pitch Position Feedback Absolute Encoder AFT Thruster</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalAFTThruster(Aradex1)</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalAFTThruster(Aradex2)</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveSpeedSignalAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveEnableAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpRun(Clockwise)AFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveRightRotationDirectionAFTThuster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveLeftRotationDirectionAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveForwardDirectionAFTThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveReverseDirectionAFTThruster</t>
+  </si>
+  <si>
+    <t>FlushValveMainThruster</t>
+  </si>
+  <si>
+    <t>AftThrusterAradex1(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>AftThrusterAradex2(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal AFT Thruster (Aradex1)</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal AFT Thruster (Aradex2)</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Speed Signal AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Enable AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Run ( Clockwise ) AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Right Rotation Direction AFT Thuster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Left Rotation Direction AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Forward Direction AFT Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Reverse Direction AFT Thruster</t>
+  </si>
+  <si>
+    <t>Flush Valve Main Thruster</t>
+  </si>
+  <si>
+    <t>Aft Thruster Aradex1 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>Aft Thruster Aradex2 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>KEB11</t>
+  </si>
+  <si>
+    <t>Azimuth0positionsensorFWDThruster</t>
+  </si>
+  <si>
+    <t>AzimuthPositionFeedbackAbsoluteEncoderFWDThruster</t>
+  </si>
+  <si>
+    <t>PitchPositionFeedbackAbsoluteEncoderFWDThruster</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalFWDThruster(Aradex1)</t>
+  </si>
+  <si>
+    <t>SpeedorTorqueSetpointSignalFWDThruster(Aradex2)</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveSpeedSignalFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpFrequencyDriveEnableFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPumpRun(Clockwise)FWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveRightRotationDirectionFWDThuster</t>
+  </si>
+  <si>
+    <t>HydraulicAzimuthValveLeftRotationDirectionFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveForwardDirectionFWDThruster</t>
+  </si>
+  <si>
+    <t>HydraulicPitchValveReverseDirectionFWDThruster</t>
+  </si>
+  <si>
+    <t>FlushValveFWDThruster</t>
+  </si>
+  <si>
+    <t>FWDThrusterAradex1(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>FWDThrusterAradex2(SpeedorTorqueModeSelection)</t>
+  </si>
+  <si>
+    <t>FWD THRUSTER</t>
+  </si>
+  <si>
+    <t>SB HELM CONSOLE</t>
+  </si>
+  <si>
+    <t>Azimuth 0 position sensor FWD Thruster</t>
+  </si>
+  <si>
+    <t>Azimuth Position Feedback Absolute Encoder FWD Thruster</t>
+  </si>
+  <si>
+    <t>Pitch Position Feedback Absolute Encoder FWD Thruster</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal FWD Thruster (Aradex1)</t>
+  </si>
+  <si>
+    <t>Speed or Torque Setpoint Signal FWD Thruster (Aradex2)</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Speed Signal FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Frequency Drive Enable FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pump Run ( Clockwise ) FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Right Rotation Direction FWD Thuster</t>
+  </si>
+  <si>
+    <t>Hydraulic Azimuth Valve Left Rotation Direction FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Forward Direction FWD Thruster</t>
+  </si>
+  <si>
+    <t>Hydraulic Pitch Valve Reverse Direction FWD Thruster</t>
+  </si>
+  <si>
+    <t>Flush Valve FWD Thruster</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex1 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex2 (Speed or Torque Mode Selection)</t>
+  </si>
+  <si>
+    <t>KEB12</t>
+  </si>
+  <si>
+    <t>PSHelmStationSelect</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmManeuveringModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmStationSelect</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmManeuveringModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>PSHelmStationSelected</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmMoeveringModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmStationSelected</t>
+  </si>
+  <si>
+    <t>PSHelmPropulsionModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmMoeveringModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>PSHelmRegenerationModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>PS Helm Station Select</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Maneuvering Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Station Select</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Maneuvering Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>PS Helm Station Selected</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Moevering Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Station Selected</t>
+  </si>
+  <si>
+    <t>PS Helm Propulsion Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Moevering Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>PS Helm Regeneration Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>KEB13</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmManeuveringModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmManeuveringModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverSpeedSignal</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverAzimuthSignal</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmMoeveringModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectedFWDThruster</t>
+  </si>
+  <si>
+    <t>SBHelmPropulsionModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmMoeveringModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SBHelmRegenerationModeSelectedAFTThruster</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Maneuvering Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Select FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Maneuvering Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Select AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Speed Signal</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Azimuth Signal</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Moevering Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Selected FWD Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Propulsion Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Moevering Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>SB Helm Regeneration Mode Selected AFT Thruster</t>
+  </si>
+  <si>
+    <t>AI20</t>
+  </si>
+  <si>
+    <t>AI21</t>
+  </si>
+  <si>
+    <t>DO60</t>
+  </si>
+  <si>
+    <t>DO61</t>
+  </si>
+  <si>
+    <t>AO61</t>
+  </si>
+  <si>
+    <t>AO62</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm value sensor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm value sensor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm setpoint motor 1</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm setpoint motor 2</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 1 speed feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 2 speed feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 1 speed feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 2 speed feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm Force Feedback enabled</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>PSHelmMAINThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverAzimuthSignal_X</t>
+  </si>
+  <si>
+    <t>PSHelmFWDThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>SBHelmMAINThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>SBHelmFWDThrusterLeverAzimuthSignal_Y</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Azimuth Signal X</t>
+  </si>
+  <si>
+    <t>SB Helm FWD Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>PS Helm MAIN Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>PS Helm FWD Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>SB Helm MAIN Thruster Lever Azimuth Signal Y</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 1 torque feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster Aradex 2 torque feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 1 torque feedback</t>
+  </si>
+  <si>
+    <t>FWD Thruster Aradex 2 torque feedback</t>
+  </si>
+  <si>
+    <t>AFT Thruster regeneration speed control</t>
+  </si>
+  <si>
+    <t>AFT Thruster regeneration torque control</t>
+  </si>
+  <si>
+    <t>FWD Thruster regeneration speed control</t>
+  </si>
+  <si>
+    <t>FWD Thruster regeneration torque control</t>
+  </si>
+  <si>
+    <t>AFT Thruster max torque regeneration</t>
+  </si>
+  <si>
+    <t>AFT Thruster min torque regeneration</t>
+  </si>
+  <si>
+    <t>FWD Thruster max torque regeneration</t>
+  </si>
+  <si>
+    <t>FWD Thruster min torque regeneration</t>
+  </si>
+  <si>
+    <t>AFT Thruster max pitch</t>
+  </si>
+  <si>
+    <t>AFT Thruster min pitch</t>
+  </si>
+  <si>
+    <t>AFT Thruster torque constant</t>
+  </si>
+  <si>
+    <t>FWD Thruster max pitch</t>
+  </si>
+  <si>
+    <t>FWD Thruster min pitch</t>
+  </si>
+  <si>
+    <t>FWD Thruster torque constant</t>
+  </si>
+  <si>
+    <t>AFT Thruster high trust control</t>
+  </si>
+  <si>
+    <t>AFT Thruster normal control</t>
+  </si>
+  <si>
+    <t>AFT Thruster motorsail control</t>
+  </si>
+  <si>
+    <t>FWD Thruster high trust control</t>
+  </si>
+  <si>
+    <t>FWD Thruster normal control</t>
+  </si>
+  <si>
+    <t>FWD Thruster motorsail control</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>AFT Thruster pitch rate of change</t>
+  </si>
+  <si>
+    <t>FWD Thruster pitch rate of change</t>
+  </si>
+  <si>
+    <t>helm-console/ps</t>
+  </si>
+  <si>
+    <t>helm-console/sb</t>
+  </si>
+  <si>
+    <t>thruster/aft</t>
+  </si>
+  <si>
+    <t>thruster/fwd</t>
+  </si>
+  <si>
+    <t>AFT Thruster PS Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>FWD Thruster PS Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>AFT Thruster SB Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>FWD Thruster SB Helm Master/Slave</t>
+  </si>
 </sst>
 </file>
 
@@ -1717,7 +2392,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
@@ -1853,8 +2528,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1918,6 +2605,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2351,7 +3056,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2560,20 +3265,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
@@ -2582,7 +3296,6 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2601,33 +3314,24 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2638,7 +3342,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3719,20 +4429,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BV8979"/>
+  <dimension ref="A1:BV8785"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="51" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="53" customWidth="1"/>
-    <col min="3" max="3" width="18" style="54" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="54" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="54" customWidth="1"/>
     <col min="5" max="5" width="8.140625" style="54" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="54" customWidth="1"/>
+    <col min="6" max="6" width="15" style="54" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" style="54" customWidth="1"/>
     <col min="8" max="8" width="6.85546875" style="54" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="49.7109375" style="11" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" style="58" customWidth="1"/>
+    <col min="10" max="10" width="68.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="58" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" style="10" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="17.7109375" style="10" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="25.140625" style="60" bestFit="1" customWidth="1"/>
@@ -3745,9 +4455,9 @@
     <col min="21" max="21" width="11.28515625" style="61" customWidth="1"/>
     <col min="22" max="22" width="11.28515625" style="63" customWidth="1"/>
     <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="48.28515625" customWidth="1"/>
-    <col min="26" max="26" width="48.7109375" customWidth="1"/>
+    <col min="26" max="26" width="57.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.28515625" style="12" customWidth="1"/>
     <col min="28" max="28" width="11.85546875" style="54" customWidth="1"/>
     <col min="29" max="29" width="10.85546875" style="64" customWidth="1"/>
@@ -3795,197 +4505,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" s="16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="106" t="s">
+      <c r="C1" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="F1" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="110" t="s">
+      <c r="H1" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="122" t="s">
+      <c r="I1" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="115" t="s">
+      <c r="J1" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="124" t="s">
+      <c r="L1" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="125"/>
-      <c r="N1" s="106" t="s">
+      <c r="M1" s="115"/>
+      <c r="N1" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="106" t="s">
+      <c r="P1" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="106" t="s">
+      <c r="Q1" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="106" t="s">
+      <c r="R1" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="106" t="s">
+      <c r="S1" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="113" t="s">
+      <c r="T1" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="116" t="s">
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="122" t="s">
         <v>438</v>
       </c>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="114" t="s">
+      <c r="X1" s="123"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="114"/>
-      <c r="AC1" s="114"/>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
-      <c r="AG1" s="114"/>
-      <c r="AH1" s="114"/>
-      <c r="AI1" s="119" t="s">
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="121"/>
+      <c r="AI1" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="115" t="s">
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="AL1" s="115" t="s">
+      <c r="AL1" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="AM1" s="112" t="s">
+      <c r="AM1" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="AN1" s="121" t="s">
+      <c r="AN1" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="121"/>
-      <c r="AP1" s="121"/>
-      <c r="AQ1" s="121"/>
-      <c r="AR1" s="121"/>
-      <c r="AS1" s="106" t="s">
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="AT1" s="106" t="s">
+      <c r="AT1" s="112" t="s">
         <v>71</v>
       </c>
-      <c r="AU1" s="106" t="s">
+      <c r="AU1" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="AV1" s="106" t="s">
+      <c r="AV1" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="AW1" s="120" t="s">
+      <c r="AW1" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="AX1" s="109" t="s">
+      <c r="AX1" s="130" t="s">
         <v>75</v>
       </c>
-      <c r="AY1" s="110" t="s">
+      <c r="AY1" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="AZ1" s="110" t="s">
+      <c r="AZ1" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="BA1" s="110" t="s">
+      <c r="BA1" s="116" t="s">
         <v>78</v>
       </c>
-      <c r="BB1" s="110" t="s">
+      <c r="BB1" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="BC1" s="108" t="s">
+      <c r="BC1" s="129" t="s">
         <v>80</v>
       </c>
-      <c r="BD1" s="108"/>
-      <c r="BE1" s="108"/>
-      <c r="BF1" s="108" t="s">
+      <c r="BD1" s="129"/>
+      <c r="BE1" s="129"/>
+      <c r="BF1" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="BG1" s="108"/>
-      <c r="BH1" s="108"/>
-      <c r="BI1" s="108" t="s">
+      <c r="BG1" s="129"/>
+      <c r="BH1" s="129"/>
+      <c r="BI1" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="BJ1" s="108"/>
-      <c r="BK1" s="108"/>
-      <c r="BL1" s="108" t="s">
+      <c r="BJ1" s="129"/>
+      <c r="BK1" s="129"/>
+      <c r="BL1" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="BM1" s="108"/>
-      <c r="BN1" s="108"/>
-      <c r="BO1" s="108" t="s">
+      <c r="BM1" s="129"/>
+      <c r="BN1" s="129"/>
+      <c r="BO1" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="BP1" s="108"/>
-      <c r="BQ1" s="108"/>
-      <c r="BR1" s="112" t="s">
+      <c r="BP1" s="129"/>
+      <c r="BQ1" s="129"/>
+      <c r="BR1" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="BS1" s="110" t="s">
+      <c r="BS1" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="BT1" s="111" t="s">
+      <c r="BT1" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="BU1" s="107" t="s">
+      <c r="BU1" s="128" t="s">
         <v>88</v>
       </c>
-      <c r="BV1" s="107" t="s">
+      <c r="BV1" s="128" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:74" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="126"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="123"/>
+    <row r="2" spans="1:74" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="113"/>
       <c r="L2" s="97" t="s">
         <v>93</v>
       </c>
       <c r="M2" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="106"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
       <c r="T2" s="17" t="s">
         <v>90</v>
       </c>
@@ -4037,9 +4747,9 @@
       <c r="AJ2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="115"/>
-      <c r="AL2" s="115"/>
-      <c r="AM2" s="112"/>
+      <c r="AK2" s="118"/>
+      <c r="AL2" s="118"/>
+      <c r="AM2" s="119"/>
       <c r="AN2" s="18" t="s">
         <v>103</v>
       </c>
@@ -4055,16 +4765,16 @@
       <c r="AR2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="AS2" s="106"/>
-      <c r="AT2" s="106"/>
-      <c r="AU2" s="106"/>
-      <c r="AV2" s="106"/>
-      <c r="AW2" s="120"/>
-      <c r="AX2" s="109"/>
-      <c r="AY2" s="110"/>
-      <c r="AZ2" s="110"/>
-      <c r="BA2" s="110"/>
-      <c r="BB2" s="110"/>
+      <c r="AS2" s="112"/>
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="126"/>
+      <c r="AX2" s="130"/>
+      <c r="AY2" s="116"/>
+      <c r="AZ2" s="116"/>
+      <c r="BA2" s="116"/>
+      <c r="BB2" s="116"/>
       <c r="BC2" s="21" t="s">
         <v>56</v>
       </c>
@@ -4110,11 +4820,11 @@
       <c r="BQ2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="BR2" s="112"/>
-      <c r="BS2" s="110"/>
-      <c r="BT2" s="111"/>
-      <c r="BU2" s="107"/>
-      <c r="BV2" s="107"/>
+      <c r="BR2" s="119"/>
+      <c r="BS2" s="116"/>
+      <c r="BT2" s="131"/>
+      <c r="BU2" s="128"/>
+      <c r="BV2" s="128"/>
     </row>
     <row r="3" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
@@ -6401,945 +7111,4335 @@
       <c r="BT26" s="11"/>
     </row>
     <row r="27" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="F27" s="55"/>
+      <c r="J27" s="109" t="s">
+        <v>526</v>
+      </c>
+      <c r="K27" s="57"/>
+      <c r="N27" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P27" s="107" t="s">
+        <v>527</v>
+      </c>
       <c r="W27" s="65"/>
-      <c r="X27" s="104"/>
-      <c r="Y27" s="54"/>
-      <c r="Z27" s="66"/>
+      <c r="X27" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y27" s="6" t="str">
+        <f>"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N27,"spare"),"",IF(X27&lt;&gt;"",X27,N27))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z27" s="64" t="str">
+        <f>IF(COUNTIF(N27,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J27,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Azimuth0positionsensor</v>
+      </c>
     </row>
     <row r="28" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J28" s="109" t="s">
+        <v>529</v>
+      </c>
+      <c r="N28" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P28" s="107" t="s">
+        <v>531</v>
+      </c>
       <c r="W28" s="65"/>
-      <c r="X28" s="104"/>
-      <c r="Y28" s="54"/>
-      <c r="Z28" s="66"/>
+      <c r="X28" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y28" s="6" t="str">
+        <f t="shared" ref="Y28:Y91" si="25">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N28,"spare"),"",IF(X28&lt;&gt;"",X28,N28))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z28" s="64" t="str">
+        <f t="shared" ref="Z28:Z56" si="26">IF(COUNTIF(N28,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J28,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.AzimuthPositionFeedbackAbsoluteEncoder</v>
+      </c>
     </row>
     <row r="29" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A29" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J29" s="109" t="s">
+        <v>530</v>
+      </c>
+      <c r="N29" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P29" s="107" t="s">
+        <v>532</v>
+      </c>
       <c r="W29" s="65"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="54"/>
-      <c r="Z29" s="66"/>
+      <c r="X29" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y29" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z29" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.PitchPositionFeedbackAbsoluteEncoder</v>
+      </c>
     </row>
     <row r="30" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J30" s="109" t="s">
+        <v>533</v>
+      </c>
+      <c r="N30" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P30" s="107" t="s">
+        <v>545</v>
+      </c>
       <c r="W30" s="65"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="54"/>
-      <c r="Z30" s="66"/>
+      <c r="X30" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y30" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z30" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex1)</v>
+      </c>
     </row>
     <row r="31" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A31" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J31" s="109" t="s">
+        <v>534</v>
+      </c>
+      <c r="N31" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P31" s="107" t="s">
+        <v>546</v>
+      </c>
       <c r="W31" s="65"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="54"/>
-      <c r="Z31" s="66"/>
+      <c r="X31" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y31" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z31" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex2)</v>
+      </c>
     </row>
     <row r="32" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="A32" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="J32" s="109" t="s">
+        <v>535</v>
+      </c>
+      <c r="N32" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P32" s="107" t="s">
+        <v>547</v>
+      </c>
       <c r="W32" s="65"/>
-      <c r="X32" s="104"/>
-      <c r="Y32" s="54"/>
-      <c r="Z32" s="66"/>
-    </row>
-    <row r="33" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X32" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y32" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z32" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveSpeedSignal</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A33" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J33" s="110" t="s">
+        <v>536</v>
+      </c>
+      <c r="N33" s="59" t="s">
+        <v>524</v>
+      </c>
+      <c r="P33" s="59" t="s">
+        <v>548</v>
+      </c>
       <c r="W33" s="65"/>
-      <c r="X33" s="104"/>
-      <c r="Y33" s="54"/>
-      <c r="Z33" s="66"/>
-    </row>
-    <row r="34" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X33" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y33" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z33" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveEnable</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A34" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J34" s="110" t="s">
+        <v>537</v>
+      </c>
+      <c r="N34" s="59" t="s">
+        <v>524</v>
+      </c>
+      <c r="P34" s="59" t="s">
+        <v>549</v>
+      </c>
       <c r="W34" s="65"/>
-      <c r="X34" s="104"/>
-      <c r="Y34" s="54"/>
-      <c r="Z34" s="66"/>
-    </row>
-    <row r="35" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X34" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y34" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z34" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpRun(Clockwise)</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A35" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J35" s="109" t="s">
+        <v>538</v>
+      </c>
+      <c r="N35" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P35" s="107" t="s">
+        <v>550</v>
+      </c>
       <c r="W35" s="65"/>
-      <c r="X35" s="104"/>
-      <c r="Y35" s="54"/>
-      <c r="Z35" s="66"/>
-    </row>
-    <row r="36" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X35" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y35" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z35" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveRightRotationDirection</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J36" s="109" t="s">
+        <v>539</v>
+      </c>
+      <c r="N36" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P36" s="107" t="s">
+        <v>551</v>
+      </c>
       <c r="W36" s="65"/>
-      <c r="X36" s="104"/>
-      <c r="Y36" s="54"/>
-      <c r="Z36" s="66"/>
-    </row>
-    <row r="37" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X36" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y36" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z36" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveLeftRotationDirection</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A37" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J37" s="109" t="s">
+        <v>540</v>
+      </c>
+      <c r="N37" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P37" s="107" t="s">
+        <v>552</v>
+      </c>
       <c r="W37" s="65"/>
-      <c r="X37" s="104"/>
-      <c r="Y37" s="54"/>
-      <c r="Z37" s="66"/>
-    </row>
-    <row r="38" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X37" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y37" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z37" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveForwardDirection</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A38" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J38" s="109" t="s">
+        <v>541</v>
+      </c>
+      <c r="N38" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P38" s="107" t="s">
+        <v>553</v>
+      </c>
       <c r="W38" s="65"/>
-      <c r="X38" s="104"/>
-      <c r="Y38" s="54"/>
-      <c r="Z38" s="66"/>
-    </row>
-    <row r="39" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X38" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y38" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z38" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveReverseDirection</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A39" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J39" s="109" t="s">
+        <v>542</v>
+      </c>
+      <c r="N39" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P39" s="107" t="s">
+        <v>554</v>
+      </c>
       <c r="W39" s="65"/>
-      <c r="X39" s="104"/>
-      <c r="Y39" s="54"/>
-      <c r="Z39" s="66"/>
-    </row>
-    <row r="40" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X39" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y39" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z39" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.FlushValve</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J40" s="109" t="s">
+        <v>543</v>
+      </c>
+      <c r="N40" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P40" s="107" t="s">
+        <v>555</v>
+      </c>
       <c r="W40" s="65"/>
-      <c r="X40" s="104"/>
-      <c r="Y40" s="54"/>
-      <c r="Z40" s="66"/>
-    </row>
-    <row r="41" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X40" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y40" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z40" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex1(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A41" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J41" s="109" t="s">
+        <v>544</v>
+      </c>
+      <c r="N41" s="107" t="s">
+        <v>524</v>
+      </c>
+      <c r="P41" s="107" t="s">
+        <v>556</v>
+      </c>
       <c r="W41" s="65"/>
-      <c r="X41" s="104"/>
-      <c r="Y41" s="54"/>
-      <c r="Z41" s="66"/>
-    </row>
-    <row r="42" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X41" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y41" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z41" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex2(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A42" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="J42" s="109" t="s">
+        <v>558</v>
+      </c>
+      <c r="N42" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P42" s="107" t="s">
+        <v>575</v>
+      </c>
       <c r="W42" s="65"/>
-      <c r="X42" s="104"/>
-      <c r="Y42" s="54"/>
-      <c r="Z42" s="66"/>
-    </row>
-    <row r="43" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X42" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y42" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z42" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Azimuth0positionsensor</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A43" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J43" s="109" t="s">
+        <v>559</v>
+      </c>
+      <c r="N43" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P43" s="107" t="s">
+        <v>576</v>
+      </c>
       <c r="W43" s="65"/>
-      <c r="X43" s="104"/>
-      <c r="Y43" s="54"/>
-      <c r="Z43" s="66"/>
-    </row>
-    <row r="44" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X43" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y43" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z43" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.AzimuthPositionFeedbackAbsoluteEncoder</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A44" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J44" s="109" t="s">
+        <v>560</v>
+      </c>
+      <c r="N44" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P44" s="107" t="s">
+        <v>577</v>
+      </c>
       <c r="W44" s="65"/>
-      <c r="X44" s="104"/>
-      <c r="Y44" s="54"/>
-      <c r="Z44" s="66"/>
-    </row>
-    <row r="45" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X44" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y44" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z44" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.PitchPositionFeedbackAbsoluteEncoder</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A45" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J45" s="109" t="s">
+        <v>561</v>
+      </c>
+      <c r="N45" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P45" s="107" t="s">
+        <v>578</v>
+      </c>
       <c r="W45" s="65"/>
-      <c r="X45" s="104"/>
-      <c r="Y45" s="54"/>
-      <c r="Z45" s="66"/>
-    </row>
-    <row r="46" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X45" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y45" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z45" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex1)</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A46" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J46" s="109" t="s">
+        <v>562</v>
+      </c>
+      <c r="N46" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P46" s="107" t="s">
+        <v>579</v>
+      </c>
       <c r="W46" s="65"/>
-      <c r="X46" s="104"/>
-      <c r="Y46" s="54"/>
-      <c r="Z46" s="66"/>
-    </row>
-    <row r="47" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X46" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y46" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z46" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.SpeedorTorqueSetpointSignal(Aradex2)</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C47" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="J47" s="110" t="s">
+        <v>563</v>
+      </c>
+      <c r="N47" s="59" t="s">
+        <v>573</v>
+      </c>
+      <c r="P47" s="59" t="s">
+        <v>580</v>
+      </c>
       <c r="W47" s="65"/>
-      <c r="X47" s="104"/>
-      <c r="Y47" s="54"/>
-      <c r="Z47" s="66"/>
-    </row>
-    <row r="48" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X47" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y47" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z47" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveSpeedSignal</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A48" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J48" s="110" t="s">
+        <v>564</v>
+      </c>
+      <c r="N48" s="59" t="s">
+        <v>573</v>
+      </c>
+      <c r="P48" s="59" t="s">
+        <v>581</v>
+      </c>
       <c r="W48" s="65"/>
-      <c r="X48" s="104"/>
-      <c r="Y48" s="54"/>
-      <c r="Z48" s="66"/>
-    </row>
-    <row r="49" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X48" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y48" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z48" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpFrequencyDriveEnable</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A49" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C49" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J49" s="110" t="s">
+        <v>565</v>
+      </c>
+      <c r="N49" s="59" t="s">
+        <v>573</v>
+      </c>
+      <c r="P49" s="59" t="s">
+        <v>582</v>
+      </c>
       <c r="W49" s="65"/>
-      <c r="X49" s="104"/>
-      <c r="Y49" s="54"/>
-      <c r="Z49" s="66"/>
-    </row>
-    <row r="50" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X49" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y49" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z49" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPumpRun(Clockwise)</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A50" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C50" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J50" s="109" t="s">
+        <v>566</v>
+      </c>
+      <c r="N50" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P50" s="107" t="s">
+        <v>583</v>
+      </c>
       <c r="W50" s="65"/>
-      <c r="X50" s="104"/>
-      <c r="Y50" s="54"/>
-      <c r="Z50" s="66"/>
-    </row>
-    <row r="51" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X50" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y50" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z50" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveRightRotationDirection</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A51" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C51" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J51" s="109" t="s">
+        <v>567</v>
+      </c>
+      <c r="N51" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P51" s="107" t="s">
+        <v>584</v>
+      </c>
       <c r="W51" s="65"/>
-      <c r="X51" s="104"/>
-      <c r="Y51" s="54"/>
-      <c r="Z51" s="66"/>
-    </row>
-    <row r="52" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X51" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y51" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z51" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicAzimuthValveLeftRotationDirection</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A52" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C52" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J52" s="109" t="s">
+        <v>568</v>
+      </c>
+      <c r="N52" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P52" s="107" t="s">
+        <v>585</v>
+      </c>
       <c r="W52" s="65"/>
-      <c r="X52" s="104"/>
-      <c r="Y52" s="54"/>
-      <c r="Z52" s="66"/>
-    </row>
-    <row r="53" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X52" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y52" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z52" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveForwardDirection</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A53" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C53" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J53" s="109" t="s">
+        <v>569</v>
+      </c>
+      <c r="N53" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P53" s="107" t="s">
+        <v>586</v>
+      </c>
       <c r="W53" s="65"/>
-      <c r="X53" s="104"/>
-      <c r="Y53" s="54"/>
-      <c r="Z53" s="66"/>
-    </row>
-    <row r="54" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X53" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y53" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z53" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.HydraulicPitchValveReverseDirection</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A54" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C54" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J54" s="109" t="s">
+        <v>570</v>
+      </c>
+      <c r="N54" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P54" s="107" t="s">
+        <v>587</v>
+      </c>
       <c r="W54" s="65"/>
-      <c r="X54" s="104"/>
-      <c r="Y54" s="54"/>
-      <c r="Z54" s="66"/>
-    </row>
-    <row r="55" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X54" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y54" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z54" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.FlushValve</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A55" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C55" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J55" s="109" t="s">
+        <v>571</v>
+      </c>
+      <c r="N55" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P55" s="107" t="s">
+        <v>588</v>
+      </c>
       <c r="W55" s="65"/>
-      <c r="X55" s="104"/>
-      <c r="Y55" s="54"/>
-      <c r="Z55" s="66"/>
-    </row>
-    <row r="56" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X55" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y55" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z55" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex1(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A56" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C56" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="J56" s="109" t="s">
+        <v>572</v>
+      </c>
+      <c r="N56" s="107" t="s">
+        <v>573</v>
+      </c>
+      <c r="P56" s="107" t="s">
+        <v>589</v>
+      </c>
       <c r="W56" s="65"/>
-      <c r="X56" s="104"/>
-      <c r="Y56" s="54"/>
-      <c r="Z56" s="66"/>
-    </row>
-    <row r="57" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X56" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y56" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z56" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>$.Aradex2(SpeedorTorqueModeSelection)</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A57" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="108" t="s">
+        <v>590</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J57" s="109" t="s">
+        <v>591</v>
+      </c>
+      <c r="N57" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P57" s="107" t="s">
+        <v>611</v>
+      </c>
       <c r="W57" s="65"/>
-      <c r="X57" s="104"/>
-      <c r="Y57" s="54"/>
-      <c r="Z57" s="66"/>
-    </row>
-    <row r="58" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X57" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y57" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z57" s="64" t="str">
+        <f>IF(COUNTIF(N57,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J57,"(SB|Sb|PS|Ps) ?Helm ?",""),"(\.| |/)","_"))</f>
+        <v>$.StationSelect</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A58" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J58" s="109" t="s">
+        <v>592</v>
+      </c>
+      <c r="N58" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P58" s="107" t="s">
+        <v>612</v>
+      </c>
       <c r="W58" s="65"/>
-      <c r="X58" s="104"/>
-      <c r="Y58" s="54"/>
-      <c r="Z58" s="66"/>
-    </row>
-    <row r="59" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X58" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y58" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z58" s="64" t="str">
+        <f t="shared" ref="Z58:Z112" si="27">IF(COUNTIF(N58,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J58,"(SB|Sb|PS|Ps) ?Helm ?",""),"(\.| |/)","_"))</f>
+        <v>$.PropulsionModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A59" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C59" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J59" s="109" t="s">
+        <v>593</v>
+      </c>
+      <c r="N59" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P59" s="107" t="s">
+        <v>613</v>
+      </c>
       <c r="W59" s="65"/>
-      <c r="X59" s="104"/>
-      <c r="Y59" s="54"/>
-      <c r="Z59" s="66"/>
-    </row>
-    <row r="60" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X59" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y59" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z59" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A60" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C60" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J60" s="109" t="s">
+        <v>594</v>
+      </c>
+      <c r="N60" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P60" s="107" t="s">
+        <v>614</v>
+      </c>
       <c r="W60" s="65"/>
-      <c r="X60" s="104"/>
-      <c r="Y60" s="54"/>
-      <c r="Z60" s="66"/>
-    </row>
-    <row r="61" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X60" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y60" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z60" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A61" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C61" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J61" s="109" t="s">
+        <v>596</v>
+      </c>
+      <c r="N61" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P61" s="107" t="s">
+        <v>616</v>
+      </c>
       <c r="W61" s="65"/>
-      <c r="X61" s="104"/>
-      <c r="Y61" s="54"/>
-      <c r="Z61" s="66"/>
-    </row>
-    <row r="62" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X61" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y61" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z61" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A62" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C62" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J62" s="109" t="s">
+        <v>597</v>
+      </c>
+      <c r="N62" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P62" s="107" t="s">
+        <v>617</v>
+      </c>
       <c r="W62" s="65"/>
-      <c r="X62" s="104"/>
-      <c r="Y62" s="54"/>
-      <c r="Z62" s="66"/>
-    </row>
-    <row r="63" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X62" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y62" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z62" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A63" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C63" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J63" s="109" t="s">
+        <v>598</v>
+      </c>
+      <c r="N63" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P63" s="107" t="s">
+        <v>618</v>
+      </c>
       <c r="W63" s="65"/>
-      <c r="X63" s="104"/>
-      <c r="Y63" s="54"/>
-      <c r="Z63" s="66"/>
-    </row>
-    <row r="64" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X63" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y63" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z63" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A64" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C64" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J64" s="109" t="s">
+        <v>599</v>
+      </c>
+      <c r="N64" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P64" s="107" t="s">
+        <v>619</v>
+      </c>
       <c r="W64" s="65"/>
-      <c r="X64" s="104"/>
-      <c r="Y64" s="54"/>
-      <c r="Z64" s="66"/>
-    </row>
-    <row r="65" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X64" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y64" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z64" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A65" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C65" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J65" s="109" t="s">
+        <v>600</v>
+      </c>
+      <c r="N65" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P65" s="107" t="s">
+        <v>620</v>
+      </c>
       <c r="W65" s="65"/>
-      <c r="X65" s="104"/>
-      <c r="Y65" s="54"/>
-      <c r="Z65" s="66"/>
-    </row>
-    <row r="66" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X65" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y65" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z65" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A66" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C66" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J66" s="109" t="s">
+        <v>601</v>
+      </c>
+      <c r="N66" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P66" s="107" t="s">
+        <v>621</v>
+      </c>
       <c r="W66" s="65"/>
-      <c r="X66" s="104"/>
-      <c r="Y66" s="54"/>
-      <c r="Z66" s="66"/>
-    </row>
-    <row r="67" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X66" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y66" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z66" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A67" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C67" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J67" s="109" t="s">
+        <v>602</v>
+      </c>
+      <c r="N67" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P67" s="107" t="s">
+        <v>622</v>
+      </c>
       <c r="W67" s="65"/>
-      <c r="X67" s="104"/>
-      <c r="Y67" s="54"/>
-      <c r="Z67" s="66"/>
-    </row>
-    <row r="68" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X67" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y67" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z67" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A68" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C68" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J68" s="109" t="s">
+        <v>603</v>
+      </c>
+      <c r="N68" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P68" s="107" t="s">
+        <v>623</v>
+      </c>
       <c r="W68" s="65"/>
-      <c r="X68" s="104"/>
-      <c r="Y68" s="54"/>
-      <c r="Z68" s="66"/>
-    </row>
-    <row r="69" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X68" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y68" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z68" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.StationSelected</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A69" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C69" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J69" s="109" t="s">
+        <v>604</v>
+      </c>
+      <c r="N69" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P69" s="107" t="s">
+        <v>624</v>
+      </c>
       <c r="W69" s="65"/>
-      <c r="X69" s="104"/>
-      <c r="Y69" s="54"/>
-      <c r="Z69" s="66"/>
-    </row>
-    <row r="70" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X69" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y69" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z69" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A70" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C70" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J70" s="109" t="s">
+        <v>605</v>
+      </c>
+      <c r="N70" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P70" s="107" t="s">
+        <v>625</v>
+      </c>
       <c r="W70" s="65"/>
-      <c r="X70" s="104"/>
-      <c r="Y70" s="54"/>
-      <c r="Z70" s="66"/>
-    </row>
-    <row r="71" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X70" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y70" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z70" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A71" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C71" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J71" s="109" t="s">
+        <v>606</v>
+      </c>
+      <c r="N71" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P71" s="107" t="s">
+        <v>626</v>
+      </c>
       <c r="W71" s="65"/>
-      <c r="X71" s="104"/>
-      <c r="Y71" s="54"/>
-      <c r="Z71" s="66"/>
-    </row>
-    <row r="72" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X71" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y71" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z71" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A72" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C72" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J72" s="109" t="s">
+        <v>608</v>
+      </c>
+      <c r="N72" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P72" s="107" t="s">
+        <v>628</v>
+      </c>
       <c r="W72" s="65"/>
-      <c r="X72" s="104"/>
-      <c r="Y72" s="54"/>
-      <c r="Z72" s="66"/>
-    </row>
-    <row r="73" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X72" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y72" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z72" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A73" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J73" s="109" t="s">
+        <v>609</v>
+      </c>
+      <c r="N73" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P73" s="107" t="s">
+        <v>629</v>
+      </c>
       <c r="W73" s="65"/>
-      <c r="X73" s="104"/>
-      <c r="Y73" s="54"/>
-      <c r="Z73" s="66"/>
-    </row>
-    <row r="74" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X73" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y73" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z73" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A74" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J74" s="109" t="s">
+        <v>610</v>
+      </c>
+      <c r="N74" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P74" s="107" t="s">
+        <v>630</v>
+      </c>
       <c r="W74" s="65"/>
-      <c r="X74" s="104"/>
-      <c r="Y74" s="54"/>
-      <c r="Z74" s="66"/>
-    </row>
-    <row r="75" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X74" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y74" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z74" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A75" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C75" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J75" s="109" t="s">
+        <v>595</v>
+      </c>
+      <c r="N75" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P75" s="107" t="s">
+        <v>615</v>
+      </c>
       <c r="W75" s="65"/>
-      <c r="X75" s="104"/>
-      <c r="Y75" s="54"/>
-      <c r="Z75" s="66"/>
-    </row>
-    <row r="76" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X75" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y75" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z75" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.StationSelect</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A76" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C76" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J76" s="109" t="s">
+        <v>632</v>
+      </c>
+      <c r="N76" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P76" s="107" t="s">
+        <v>648</v>
+      </c>
       <c r="W76" s="65"/>
-      <c r="X76" s="104"/>
-      <c r="Y76" s="54"/>
-      <c r="Z76" s="66"/>
-    </row>
-    <row r="77" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X76" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y76" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z76" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A77" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J77" s="109" t="s">
+        <v>633</v>
+      </c>
+      <c r="N77" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P77" s="107" t="s">
+        <v>649</v>
+      </c>
       <c r="W77" s="65"/>
-      <c r="X77" s="104"/>
-      <c r="Y77" s="54"/>
-      <c r="Z77" s="66"/>
-    </row>
-    <row r="78" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X77" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y77" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z77" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A78" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C78" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="J78" s="109" t="s">
+        <v>634</v>
+      </c>
+      <c r="N78" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P78" s="107" t="s">
+        <v>650</v>
+      </c>
       <c r="W78" s="65"/>
-      <c r="X78" s="104"/>
-      <c r="Y78" s="54"/>
-      <c r="Z78" s="66"/>
-    </row>
-    <row r="79" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X78" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y78" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z78" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectFWDThruster</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A79" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C79" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J79" s="109" t="s">
+        <v>635</v>
+      </c>
+      <c r="N79" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P79" s="107" t="s">
+        <v>651</v>
+      </c>
       <c r="W79" s="65"/>
-      <c r="X79" s="104"/>
-      <c r="Y79" s="54"/>
-      <c r="Z79" s="66"/>
-    </row>
-    <row r="80" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X79" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y79" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z79" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A80" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C80" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J80" s="109" t="s">
+        <v>636</v>
+      </c>
+      <c r="N80" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P80" s="107" t="s">
+        <v>652</v>
+      </c>
       <c r="W80" s="65"/>
-      <c r="X80" s="104"/>
-      <c r="Y80" s="54"/>
-      <c r="Z80" s="66"/>
-    </row>
-    <row r="81" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X80" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y80" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z80" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.ManeuveringModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A81" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C81" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J81" s="109" t="s">
+        <v>637</v>
+      </c>
+      <c r="N81" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P81" s="107" t="s">
+        <v>653</v>
+      </c>
       <c r="W81" s="65"/>
-      <c r="X81" s="104"/>
-      <c r="Y81" s="54"/>
-      <c r="Z81" s="66"/>
-    </row>
-    <row r="82" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X81" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y81" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z81" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectAFTThruster</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A82" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C82" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J82" s="109" t="s">
+        <v>638</v>
+      </c>
+      <c r="N82" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P82" s="107" t="s">
+        <v>654</v>
+      </c>
       <c r="W82" s="65"/>
-      <c r="X82" s="104"/>
-      <c r="Y82" s="54"/>
-      <c r="Z82" s="66"/>
-    </row>
-    <row r="83" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X82" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y82" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z82" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A83" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C83" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J83" s="109" t="s">
+        <v>639</v>
+      </c>
+      <c r="N83" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P83" s="107" t="s">
+        <v>655</v>
+      </c>
       <c r="W83" s="65"/>
-      <c r="X83" s="104"/>
-      <c r="Y83" s="54"/>
-      <c r="Z83" s="66"/>
-    </row>
-    <row r="84" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X83" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y83" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z83" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MAINThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A84" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C84" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J84" s="109" t="s">
+        <v>640</v>
+      </c>
+      <c r="N84" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P84" s="107" t="s">
+        <v>656</v>
+      </c>
       <c r="W84" s="65"/>
-      <c r="X84" s="104"/>
-      <c r="Y84" s="54"/>
-      <c r="Z84" s="66"/>
-    </row>
-    <row r="85" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X84" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y84" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z84" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverSpeedSignal</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A85" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C85" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J85" s="109" t="s">
+        <v>641</v>
+      </c>
+      <c r="N85" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P85" s="107" t="s">
+        <v>657</v>
+      </c>
       <c r="W85" s="65"/>
-      <c r="X85" s="104"/>
-      <c r="Y85" s="54"/>
-      <c r="Z85" s="66"/>
-    </row>
-    <row r="86" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X85" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y85" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z85" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWDThrusterLeverAzimuthSignal</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A86" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C86" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J86" s="109" t="s">
+        <v>607</v>
+      </c>
+      <c r="N86" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P86" s="107" t="s">
+        <v>627</v>
+      </c>
       <c r="W86" s="65"/>
-      <c r="X86" s="104"/>
-      <c r="Y86" s="54"/>
-      <c r="Z86" s="66"/>
-    </row>
-    <row r="87" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X86" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y86" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z86" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.StationSelected</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A87" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C87" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J87" s="109" t="s">
+        <v>642</v>
+      </c>
+      <c r="N87" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P87" s="107" t="s">
+        <v>658</v>
+      </c>
       <c r="W87" s="65"/>
-      <c r="X87" s="104"/>
-      <c r="Y87" s="54"/>
-      <c r="Z87" s="66"/>
-    </row>
-    <row r="88" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X87" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y87" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z87" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A88" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C88" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J88" s="109" t="s">
+        <v>643</v>
+      </c>
+      <c r="N88" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P88" s="107" t="s">
+        <v>659</v>
+      </c>
       <c r="W88" s="65"/>
-      <c r="X88" s="104"/>
-      <c r="Y88" s="54"/>
-      <c r="Z88" s="66"/>
-    </row>
-    <row r="89" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X88" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y88" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z88" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A89" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C89" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J89" s="109" t="s">
+        <v>644</v>
+      </c>
+      <c r="N89" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P89" s="107" t="s">
+        <v>660</v>
+      </c>
       <c r="W89" s="65"/>
-      <c r="X89" s="104"/>
-      <c r="Y89" s="54"/>
-      <c r="Z89" s="66"/>
-    </row>
-    <row r="90" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X89" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y89" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z89" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedFWDThruster</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A90" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C90" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J90" s="109" t="s">
+        <v>645</v>
+      </c>
+      <c r="N90" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P90" s="107" t="s">
+        <v>661</v>
+      </c>
       <c r="W90" s="65"/>
-      <c r="X90" s="104"/>
-      <c r="Y90" s="54"/>
-      <c r="Z90" s="66"/>
-    </row>
-    <row r="91" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X90" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y90" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z90" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.PropulsionModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A91" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C91" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J91" s="109" t="s">
+        <v>646</v>
+      </c>
+      <c r="N91" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P91" s="107" t="s">
+        <v>662</v>
+      </c>
       <c r="W91" s="65"/>
-      <c r="X91" s="104"/>
-      <c r="Y91" s="54"/>
-      <c r="Z91" s="66"/>
-    </row>
-    <row r="92" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X91" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y91" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z91" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.MoeveringModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A92" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C92" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="J92" s="109" t="s">
+        <v>647</v>
+      </c>
+      <c r="N92" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P92" s="107" t="s">
+        <v>663</v>
+      </c>
       <c r="W92" s="65"/>
-      <c r="X92" s="104"/>
-      <c r="Y92" s="54"/>
-      <c r="Z92" s="66"/>
-    </row>
-    <row r="93" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X92" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y92" s="6" t="str">
+        <f t="shared" ref="Y92:Y154" si="28">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N92,"spare"),"",IF(X92&lt;&gt;"",X92,N92))," ","-"))</f>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z92" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.RegenerationModeSelectedAFTThruster</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A93" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C93" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="N93" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W93" s="65"/>
-      <c r="X93" s="104"/>
-      <c r="Y93" s="54"/>
-      <c r="Z93" s="66"/>
-    </row>
-    <row r="94" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X93" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y93" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z93" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A94" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C94" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="N94" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W94" s="65"/>
-      <c r="X94" s="104"/>
-      <c r="Y94" s="54"/>
-      <c r="Z94" s="66"/>
-    </row>
-    <row r="95" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X94" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y94" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z94" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A95" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C95" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E95" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="N95" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W95" s="65"/>
-      <c r="X95" s="104"/>
-      <c r="Y95" s="54"/>
-      <c r="Z95" s="66"/>
-    </row>
-    <row r="96" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X95" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y95" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z95" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A96" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E96" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="N96" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W96" s="65"/>
-      <c r="X96" s="104"/>
-      <c r="Y96" s="54"/>
-      <c r="Z96" s="66"/>
-    </row>
-    <row r="97" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X96" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y96" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z96" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_Master_Slave</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A97" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="N97" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W97" s="65"/>
-      <c r="X97" s="104"/>
-      <c r="Y97" s="54"/>
-      <c r="Z97" s="66"/>
-    </row>
-    <row r="98" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X97" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y97" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z97" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A98" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C98" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="N98" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W98" s="65"/>
-      <c r="X98" s="104"/>
-      <c r="Y98" s="54"/>
-      <c r="Z98" s="66"/>
-    </row>
-    <row r="99" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X98" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y98" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z98" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A99" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C99" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E99" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="N99" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W99" s="65"/>
-      <c r="X99" s="104"/>
-      <c r="Y99" s="54"/>
-      <c r="Z99" s="66"/>
-    </row>
-    <row r="100" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X99" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y99" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z99" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A100" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C100" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E100" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="N100" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W100" s="65"/>
-      <c r="X100" s="104"/>
-      <c r="Y100" s="54"/>
-      <c r="Z100" s="66"/>
-    </row>
-    <row r="101" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X100" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y100" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z100" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A101" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C101" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="N101" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W101" s="65"/>
-      <c r="X101" s="104"/>
-      <c r="Y101" s="54"/>
-      <c r="Z101" s="66"/>
-    </row>
-    <row r="102" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X101" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y101" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z101" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A102" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C102" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="N102" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W102" s="65"/>
-      <c r="X102" s="104"/>
-      <c r="Y102" s="54"/>
-      <c r="Z102" s="66"/>
-    </row>
-    <row r="103" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X102" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y102" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z102" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A103" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C103" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="N103" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W103" s="65"/>
-      <c r="X103" s="104"/>
-      <c r="Y103" s="54"/>
-      <c r="Z103" s="66"/>
-    </row>
-    <row r="104" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X103" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y103" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z103" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A104" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C104" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E104" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="N104" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W104" s="65"/>
-      <c r="X104" s="104"/>
-      <c r="Y104" s="54"/>
-      <c r="Z104" s="66"/>
-    </row>
-    <row r="105" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X104" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y104" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z104" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_value_sensor_2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A105" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C105" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="N105" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W105" s="65"/>
-      <c r="X105" s="104"/>
-      <c r="Y105" s="54"/>
-      <c r="Z105" s="66"/>
-    </row>
-    <row r="106" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X105" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y105" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z105" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A106" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C106" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="N106" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W106" s="65"/>
-      <c r="X106" s="104"/>
-      <c r="Y106" s="54"/>
-      <c r="Z106" s="66"/>
-    </row>
-    <row r="107" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X106" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y106" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z106" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A107" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C107" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="N107" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W107" s="65"/>
-      <c r="X107" s="104"/>
-      <c r="Y107" s="54"/>
-      <c r="Z107" s="66"/>
-    </row>
-    <row r="108" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X107" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y107" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z107" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A108" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C108" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E108" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J108" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="N108" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W108" s="65"/>
-      <c r="X108" s="104"/>
-      <c r="Y108" s="54"/>
-      <c r="Z108" s="66"/>
-    </row>
-    <row r="109" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X108" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y108" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z108" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A109" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C109" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J109" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="N109" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W109" s="65"/>
-      <c r="X109" s="104"/>
-      <c r="Y109" s="54"/>
-      <c r="Z109" s="66"/>
-    </row>
-    <row r="110" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X109" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y109" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z109" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A110" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C110" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J110" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="N110" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W110" s="65"/>
-      <c r="X110" s="104"/>
-      <c r="Y110" s="54"/>
-      <c r="Z110" s="66"/>
-    </row>
-    <row r="111" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X110" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y110" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z110" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A111" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C111" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E111" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J111" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="N111" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W111" s="65"/>
-      <c r="X111" s="104"/>
-      <c r="Y111" s="54"/>
-      <c r="Z111" s="66"/>
-    </row>
-    <row r="112" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X111" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y111" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z111" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.AFT_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A112" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C112" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E112" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J112" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="N112" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W112" s="65"/>
-      <c r="X112" s="104"/>
-      <c r="Y112" s="54"/>
-      <c r="Z112" s="66"/>
-    </row>
-    <row r="113" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X112" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y112" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z112" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>$.FWD_Thruster_setpoint_motor_2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A113" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C113" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E113" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="N113" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W113" s="65"/>
-      <c r="X113" s="104"/>
-      <c r="Y113" s="54"/>
-      <c r="Z113" s="66"/>
-    </row>
-    <row r="114" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X113" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y113" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z113" s="64" t="str">
+        <f t="shared" ref="Z113:Z116" si="29">IF(COUNTIF(N113,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J113,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Aradex_1_speed_feedback</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A114" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C114" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E114" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="N114" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W114" s="65"/>
-      <c r="X114" s="104"/>
-      <c r="Y114" s="54"/>
-      <c r="Z114" s="66"/>
-    </row>
-    <row r="115" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X114" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y114" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z114" s="64" t="str">
+        <f t="shared" si="29"/>
+        <v>$.Aradex_2_speed_feedback</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A115" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C115" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E115" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="N115" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W115" s="65"/>
-      <c r="X115" s="104"/>
-      <c r="Y115" s="54"/>
-      <c r="Z115" s="66"/>
-    </row>
-    <row r="116" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X115" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y115" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z115" s="64" t="str">
+        <f t="shared" si="29"/>
+        <v>$.Aradex_1_speed_feedback</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A116" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C116" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E116" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="N116" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W116" s="65"/>
-      <c r="X116" s="104"/>
-      <c r="Y116" s="54"/>
-      <c r="Z116" s="66"/>
-    </row>
-    <row r="117" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X116" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y116" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z116" s="64" t="str">
+        <f t="shared" si="29"/>
+        <v>$.Aradex_2_speed_feedback</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A117" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C117" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E117" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J117" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="N117" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W117" s="65"/>
-      <c r="X117" s="104"/>
-      <c r="Y117" s="54"/>
-      <c r="Z117" s="66"/>
-    </row>
-    <row r="118" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X117" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y117" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z117" s="64" t="str">
+        <f t="shared" ref="Z117:Z128" si="30">IF(COUNTIF(N117,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J117,"(SB|Sb|PS|Ps) ?Helm ?",""),"(\.| |/)","_"))</f>
+        <v>$.AFT_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A118" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C118" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E118" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="N118" s="60" t="s">
+        <v>528</v>
+      </c>
       <c r="W118" s="65"/>
-      <c r="X118" s="104"/>
-      <c r="Y118" s="54"/>
-      <c r="Z118" s="66"/>
-    </row>
-    <row r="119" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X118" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y118" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z118" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWD_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A119" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C119" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E119" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="N119" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W119" s="65"/>
-      <c r="X119" s="104"/>
-      <c r="Y119" s="54"/>
-      <c r="Z119" s="66"/>
-    </row>
-    <row r="120" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X119" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y119" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z119" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.AFT_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A120" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C120" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E120" s="54" t="s">
+        <v>735</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="N120" s="60" t="s">
+        <v>574</v>
+      </c>
       <c r="W120" s="65"/>
-      <c r="X120" s="104"/>
-      <c r="Y120" s="54"/>
-      <c r="Z120" s="66"/>
-    </row>
-    <row r="121" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X120" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y120" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z120" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWD_Thruster_Force_Feedback_enabled</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A121" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C121" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J121" s="106" t="s">
+        <v>694</v>
+      </c>
+      <c r="N121" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P121" s="107" t="s">
+        <v>702</v>
+      </c>
       <c r="W121" s="65"/>
-      <c r="X121" s="104"/>
-      <c r="Y121" s="54"/>
-      <c r="Z121" s="66"/>
-    </row>
-    <row r="122" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X121" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y121" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z121" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A122" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C122" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J122" s="106" t="s">
+        <v>695</v>
+      </c>
+      <c r="N122" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P122" s="107" t="s">
+        <v>707</v>
+      </c>
       <c r="W122" s="65"/>
-      <c r="X122" s="104"/>
-      <c r="Y122" s="54"/>
-      <c r="Z122" s="66"/>
-    </row>
-    <row r="123" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X122" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y122" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z122" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A123" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J123" s="106" t="s">
+        <v>696</v>
+      </c>
+      <c r="N123" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P123" s="107" t="s">
+        <v>703</v>
+      </c>
       <c r="W123" s="65"/>
-      <c r="X123" s="104"/>
-      <c r="Y123" s="54"/>
-      <c r="Z123" s="66"/>
-    </row>
-    <row r="124" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X123" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y123" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z123" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A124" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C124" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J124" s="106" t="s">
+        <v>699</v>
+      </c>
+      <c r="N124" s="107" t="s">
+        <v>528</v>
+      </c>
+      <c r="P124" s="107" t="s">
+        <v>708</v>
+      </c>
       <c r="W124" s="65"/>
-      <c r="X124" s="104"/>
-      <c r="Y124" s="54"/>
-      <c r="Z124" s="66"/>
-    </row>
-    <row r="125" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X124" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y124" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/ps</v>
+      </c>
+      <c r="Z124" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A125" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C125" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J125" s="106" t="s">
+        <v>697</v>
+      </c>
+      <c r="N125" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P125" s="107" t="s">
+        <v>704</v>
+      </c>
       <c r="W125" s="65"/>
-      <c r="X125" s="104"/>
-      <c r="Y125" s="54"/>
-      <c r="Z125" s="66"/>
-    </row>
-    <row r="126" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X125" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y125" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z125" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A126" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C126" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J126" s="106" t="s">
+        <v>700</v>
+      </c>
+      <c r="N126" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P126" s="107" t="s">
+        <v>709</v>
+      </c>
       <c r="W126" s="65"/>
-      <c r="X126" s="104"/>
-      <c r="Y126" s="54"/>
-      <c r="Z126" s="66"/>
-    </row>
-    <row r="127" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X126" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y126" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z126" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.MAINThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A127" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C127" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J127" s="106" t="s">
+        <v>698</v>
+      </c>
+      <c r="N127" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P127" s="107" t="s">
+        <v>705</v>
+      </c>
       <c r="W127" s="65"/>
-      <c r="X127" s="104"/>
-      <c r="Y127" s="54"/>
-      <c r="Z127" s="66"/>
-    </row>
-    <row r="128" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X127" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y127" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z127" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_X</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A128" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="J128" s="106" t="s">
+        <v>701</v>
+      </c>
+      <c r="N128" s="107" t="s">
+        <v>574</v>
+      </c>
+      <c r="P128" s="107" t="s">
+        <v>706</v>
+      </c>
       <c r="W128" s="65"/>
-      <c r="X128" s="104"/>
-      <c r="Y128" s="54"/>
-      <c r="Z128" s="66"/>
-    </row>
-    <row r="129" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X128" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y128" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/helm-console/sb</v>
+      </c>
+      <c r="Z128" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v>$.FWDThrusterLeverAzimuthSignal_Y</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A129" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C129" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E129" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="N129" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W129" s="65"/>
-      <c r="X129" s="104"/>
-      <c r="Y129" s="54"/>
-      <c r="Z129" s="66"/>
-    </row>
-    <row r="130" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X129" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y129" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z129" s="64" t="str">
+        <f t="shared" ref="Z129:Z154" si="31">IF(COUNTIF(N129,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J129,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Aradex_1_torque_feedback</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A130" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C130" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E130" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J130" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="N130" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W130" s="65"/>
-      <c r="X130" s="104"/>
-      <c r="Y130" s="54"/>
-      <c r="Z130" s="66"/>
-    </row>
-    <row r="131" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X130" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y130" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z130" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Aradex_2_torque_feedback</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A131" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C131" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E131" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="N131" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W131" s="65"/>
-      <c r="X131" s="104"/>
-      <c r="Y131" s="54"/>
-      <c r="Z131" s="66"/>
-    </row>
-    <row r="132" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X131" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y131" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z131" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Aradex_1_torque_feedback</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A132" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C132" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E132" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J132" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="N132" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W132" s="65"/>
-      <c r="X132" s="104"/>
-      <c r="Y132" s="54"/>
-      <c r="Z132" s="66"/>
-    </row>
-    <row r="133" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X132" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y132" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z132" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Aradex_2_torque_feedback</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A133" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C133" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E133" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J133" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="N133" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W133" s="65"/>
-      <c r="X133" s="104"/>
-      <c r="Y133" s="54"/>
-      <c r="Z133" s="66"/>
-    </row>
-    <row r="134" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X133" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y133" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z133" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_speed_control</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A134" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C134" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E134" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="N134" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W134" s="65"/>
-      <c r="X134" s="104"/>
-      <c r="Y134" s="54"/>
-      <c r="Z134" s="66"/>
-    </row>
-    <row r="135" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X134" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y134" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z134" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_torque_control</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A135" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C135" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E135" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="N135" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W135" s="65"/>
-      <c r="X135" s="104"/>
-      <c r="Y135" s="54"/>
-      <c r="Z135" s="66"/>
-    </row>
-    <row r="136" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X135" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y135" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z135" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_speed_control</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A136" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C136" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E136" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J136" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="N136" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W136" s="65"/>
-      <c r="X136" s="104"/>
-      <c r="Y136" s="54"/>
-      <c r="Z136" s="66"/>
-    </row>
-    <row r="137" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X136" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y136" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z136" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.regeneration_torque_control</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A137" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C137" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E137" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J137" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="N137" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W137" s="65"/>
-      <c r="X137" s="104"/>
-      <c r="Y137" s="54"/>
-      <c r="Z137" s="66"/>
-    </row>
-    <row r="138" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X137" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y137" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z137" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A138" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C138" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E138" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J138" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="N138" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W138" s="65"/>
-      <c r="X138" s="104"/>
-      <c r="Y138" s="54"/>
-      <c r="Z138" s="66"/>
-    </row>
-    <row r="139" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X138" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y138" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z138" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A139" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C139" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E139" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J139" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="N139" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W139" s="65"/>
-      <c r="X139" s="104"/>
-      <c r="Y139" s="54"/>
-      <c r="Z139" s="66"/>
-    </row>
-    <row r="140" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X139" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y139" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z139" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A140" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C140" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E140" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J140" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="N140" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W140" s="65"/>
-      <c r="X140" s="104"/>
-      <c r="Y140" s="54"/>
-      <c r="Z140" s="66"/>
-    </row>
-    <row r="141" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X140" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y140" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z140" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_torque_regeneration</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A141" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C141" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E141" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J141" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="N141" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W141" s="65"/>
-      <c r="X141" s="104"/>
-      <c r="Y141" s="54"/>
-      <c r="Z141" s="66"/>
-    </row>
-    <row r="142" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X141" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y141" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z141" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.pitch_rate_of_change</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A142" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C142" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E142" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J142" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="N142" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W142" s="65"/>
-      <c r="X142" s="104"/>
-      <c r="Y142" s="54"/>
-      <c r="Z142" s="66"/>
-    </row>
-    <row r="143" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X142" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y142" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z142" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_pitch</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A143" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C143" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E143" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J143" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="N143" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W143" s="65"/>
-      <c r="X143" s="104"/>
-      <c r="Y143" s="54"/>
-      <c r="Z143" s="66"/>
-    </row>
-    <row r="144" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X143" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y143" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z143" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_pitch</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A144" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C144" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E144" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J144" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="N144" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W144" s="65"/>
-      <c r="X144" s="104"/>
-      <c r="Y144" s="54"/>
-      <c r="Z144" s="66"/>
-    </row>
-    <row r="145" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X144" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y144" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z144" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.torque_constant</v>
+      </c>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A145" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C145" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E145" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J145" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="N145" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W145" s="65"/>
-      <c r="X145" s="104"/>
-      <c r="Y145" s="54"/>
-      <c r="Z145" s="66"/>
-    </row>
-    <row r="146" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X145" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y145" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z145" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.pitch_rate_of_change</v>
+      </c>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A146" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C146" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E146" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J146" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="N146" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W146" s="65"/>
-      <c r="X146" s="104"/>
-      <c r="Y146" s="54"/>
-      <c r="Z146" s="66"/>
-    </row>
-    <row r="147" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X146" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y146" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z146" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.max_pitch</v>
+      </c>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A147" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C147" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E147" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J147" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="N147" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W147" s="65"/>
-      <c r="X147" s="104"/>
-      <c r="Y147" s="54"/>
-      <c r="Z147" s="66"/>
-    </row>
-    <row r="148" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X147" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y147" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z147" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.min_pitch</v>
+      </c>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A148" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C148" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="E148" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J148" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="N148" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W148" s="65"/>
-      <c r="X148" s="104"/>
-      <c r="Y148" s="54"/>
-      <c r="Z148" s="66"/>
-    </row>
-    <row r="149" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X148" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y148" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z148" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.torque_constant</v>
+      </c>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A149" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C149" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E149" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J149" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="N149" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W149" s="65"/>
-      <c r="X149" s="104"/>
-      <c r="Y149" s="54"/>
-      <c r="Z149" s="66"/>
-    </row>
-    <row r="150" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X149" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y149" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z149" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.high_trust_control</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A150" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C150" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E150" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J150" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="N150" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W150" s="65"/>
-      <c r="X150" s="104"/>
-      <c r="Y150" s="54"/>
-      <c r="Z150" s="66"/>
-    </row>
-    <row r="151" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X150" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y150" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z150" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.normal_control</v>
+      </c>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A151" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C151" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E151" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J151" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="N151" s="60" t="s">
+        <v>524</v>
+      </c>
       <c r="W151" s="65"/>
-      <c r="X151" s="104"/>
-      <c r="Y151" s="54"/>
-      <c r="Z151" s="66"/>
-    </row>
-    <row r="152" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X151" s="104" t="s">
+        <v>740</v>
+      </c>
+      <c r="Y151" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z151" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.motorsail_control</v>
+      </c>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A152" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C152" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E152" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="N152" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W152" s="65"/>
-      <c r="X152" s="104"/>
-      <c r="Y152" s="54"/>
-      <c r="Z152" s="66"/>
-    </row>
-    <row r="153" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X152" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y152" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z152" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.high_trust_control</v>
+      </c>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A153" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C153" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E153" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="N153" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W153" s="65"/>
-      <c r="X153" s="104"/>
-      <c r="Y153" s="54"/>
-      <c r="Z153" s="66"/>
-    </row>
-    <row r="154" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X153" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y153" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z153" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.normal_control</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A154" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="C154" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E154" s="54" t="s">
+        <v>734</v>
+      </c>
+      <c r="J154" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="N154" s="60" t="s">
+        <v>573</v>
+      </c>
       <c r="W154" s="65"/>
-      <c r="X154" s="104"/>
-      <c r="Y154" s="54"/>
-      <c r="Z154" s="66"/>
-    </row>
-    <row r="155" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X154" s="104" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y154" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z154" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>$.motorsail_control</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W155" s="65"/>
       <c r="X155" s="104"/>
-      <c r="Y155" s="54"/>
+      <c r="Y155" s="6"/>
       <c r="Z155" s="66"/>
     </row>
-    <row r="156" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W156" s="65"/>
       <c r="X156" s="104"/>
-      <c r="Y156" s="54"/>
+      <c r="Y156" s="6"/>
       <c r="Z156" s="66"/>
     </row>
-    <row r="157" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W157" s="65"/>
       <c r="X157" s="104"/>
-      <c r="Y157" s="54"/>
+      <c r="Y157" s="6"/>
       <c r="Z157" s="66"/>
     </row>
-    <row r="158" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W158" s="65"/>
       <c r="X158" s="104"/>
-      <c r="Y158" s="54"/>
+      <c r="Y158" s="6"/>
       <c r="Z158" s="66"/>
     </row>
-    <row r="159" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W159" s="65"/>
       <c r="X159" s="104"/>
-      <c r="Y159" s="54"/>
+      <c r="Y159" s="6"/>
       <c r="Z159" s="66"/>
     </row>
-    <row r="160" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="W160" s="65"/>
       <c r="X160" s="104"/>
-      <c r="Y160" s="54"/>
+      <c r="Y160" s="6"/>
       <c r="Z160" s="66"/>
     </row>
     <row r="161" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W161" s="65"/>
       <c r="X161" s="104"/>
-      <c r="Y161" s="54"/>
+      <c r="Y161" s="6"/>
       <c r="Z161" s="66"/>
     </row>
     <row r="162" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W162" s="65"/>
       <c r="X162" s="104"/>
-      <c r="Y162" s="54"/>
+      <c r="Y162" s="6"/>
       <c r="Z162" s="66"/>
     </row>
     <row r="163" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W163" s="65"/>
       <c r="X163" s="104"/>
-      <c r="Y163" s="54"/>
+      <c r="Y163" s="6"/>
       <c r="Z163" s="66"/>
     </row>
     <row r="164" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W164" s="65"/>
       <c r="X164" s="104"/>
-      <c r="Y164" s="54"/>
+      <c r="Y164" s="6"/>
       <c r="Z164" s="66"/>
     </row>
     <row r="165" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W165" s="65"/>
       <c r="X165" s="104"/>
-      <c r="Y165" s="54"/>
+      <c r="Y165" s="6"/>
       <c r="Z165" s="66"/>
     </row>
     <row r="166" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W166" s="65"/>
       <c r="X166" s="104"/>
-      <c r="Y166" s="54"/>
+      <c r="Y166" s="6"/>
       <c r="Z166" s="66"/>
     </row>
     <row r="167" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W167" s="65"/>
       <c r="X167" s="104"/>
-      <c r="Y167" s="54"/>
+      <c r="Y167" s="6"/>
       <c r="Z167" s="66"/>
     </row>
     <row r="168" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W168" s="65"/>
       <c r="X168" s="104"/>
-      <c r="Y168" s="54"/>
+      <c r="Y168" s="6"/>
       <c r="Z168" s="66"/>
     </row>
     <row r="169" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W169" s="65"/>
       <c r="X169" s="104"/>
-      <c r="Y169" s="54"/>
+      <c r="Y169" s="6"/>
       <c r="Z169" s="66"/>
     </row>
     <row r="170" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W170" s="65"/>
       <c r="X170" s="104"/>
-      <c r="Y170" s="54"/>
+      <c r="Y170" s="6"/>
       <c r="Z170" s="66"/>
     </row>
     <row r="171" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W171" s="65"/>
       <c r="X171" s="104"/>
-      <c r="Y171" s="54"/>
+      <c r="Y171" s="6"/>
       <c r="Z171" s="66"/>
     </row>
     <row r="172" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W172" s="65"/>
       <c r="X172" s="104"/>
-      <c r="Y172" s="54"/>
+      <c r="Y172" s="6"/>
       <c r="Z172" s="66"/>
     </row>
     <row r="173" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W173" s="65"/>
       <c r="X173" s="104"/>
-      <c r="Y173" s="54"/>
+      <c r="Y173" s="6"/>
       <c r="Z173" s="66"/>
     </row>
     <row r="174" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W174" s="65"/>
       <c r="X174" s="104"/>
-      <c r="Y174" s="54"/>
+      <c r="Y174" s="6"/>
       <c r="Z174" s="66"/>
     </row>
     <row r="175" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W175" s="65"/>
       <c r="X175" s="104"/>
-      <c r="Y175" s="54"/>
+      <c r="Y175" s="6"/>
       <c r="Z175" s="66"/>
     </row>
     <row r="176" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W176" s="65"/>
       <c r="X176" s="104"/>
-      <c r="Y176" s="54"/>
+      <c r="Y176" s="6"/>
       <c r="Z176" s="66"/>
     </row>
     <row r="177" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W177" s="65"/>
       <c r="X177" s="104"/>
-      <c r="Y177" s="54"/>
+      <c r="Y177" s="6"/>
       <c r="Z177" s="66"/>
     </row>
     <row r="178" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W178" s="65"/>
       <c r="X178" s="104"/>
-      <c r="Y178" s="54"/>
+      <c r="Y178" s="6"/>
       <c r="Z178" s="66"/>
     </row>
     <row r="179" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W179" s="65"/>
       <c r="X179" s="104"/>
-      <c r="Y179" s="54"/>
+      <c r="Y179" s="6"/>
       <c r="Z179" s="66"/>
     </row>
     <row r="180" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W180" s="65"/>
       <c r="X180" s="104"/>
-      <c r="Y180" s="54"/>
+      <c r="Y180" s="6"/>
       <c r="Z180" s="66"/>
     </row>
     <row r="181" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W181" s="65"/>
       <c r="X181" s="104"/>
-      <c r="Y181" s="54"/>
+      <c r="Y181" s="6"/>
       <c r="Z181" s="66"/>
     </row>
     <row r="182" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W182" s="65"/>
       <c r="X182" s="104"/>
-      <c r="Y182" s="54"/>
+      <c r="Y182" s="6"/>
       <c r="Z182" s="66"/>
     </row>
     <row r="183" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W183" s="65"/>
       <c r="X183" s="104"/>
-      <c r="Y183" s="54"/>
+      <c r="Y183" s="6"/>
       <c r="Z183" s="66"/>
     </row>
     <row r="184" spans="23:26" x14ac:dyDescent="0.25">
@@ -58954,1206 +63054,38 @@
       <c r="Y8785" s="54"/>
       <c r="Z8785" s="66"/>
     </row>
-    <row r="8786" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8786" s="65"/>
-      <c r="X8786" s="104"/>
-      <c r="Y8786" s="54"/>
-      <c r="Z8786" s="66"/>
-    </row>
-    <row r="8787" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8787" s="65"/>
-      <c r="X8787" s="104"/>
-      <c r="Y8787" s="54"/>
-      <c r="Z8787" s="66"/>
-    </row>
-    <row r="8788" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8788" s="65"/>
-      <c r="X8788" s="104"/>
-      <c r="Y8788" s="54"/>
-      <c r="Z8788" s="66"/>
-    </row>
-    <row r="8789" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8789" s="65"/>
-      <c r="X8789" s="104"/>
-      <c r="Y8789" s="54"/>
-      <c r="Z8789" s="66"/>
-    </row>
-    <row r="8790" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8790" s="65"/>
-      <c r="X8790" s="104"/>
-      <c r="Y8790" s="54"/>
-      <c r="Z8790" s="66"/>
-    </row>
-    <row r="8791" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8791" s="65"/>
-      <c r="X8791" s="104"/>
-      <c r="Y8791" s="54"/>
-      <c r="Z8791" s="66"/>
-    </row>
-    <row r="8792" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8792" s="65"/>
-      <c r="X8792" s="104"/>
-      <c r="Y8792" s="54"/>
-      <c r="Z8792" s="66"/>
-    </row>
-    <row r="8793" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8793" s="65"/>
-      <c r="X8793" s="104"/>
-      <c r="Y8793" s="54"/>
-      <c r="Z8793" s="66"/>
-    </row>
-    <row r="8794" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8794" s="65"/>
-      <c r="X8794" s="104"/>
-      <c r="Y8794" s="54"/>
-      <c r="Z8794" s="66"/>
-    </row>
-    <row r="8795" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8795" s="65"/>
-      <c r="X8795" s="104"/>
-      <c r="Y8795" s="54"/>
-      <c r="Z8795" s="66"/>
-    </row>
-    <row r="8796" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8796" s="65"/>
-      <c r="X8796" s="104"/>
-      <c r="Y8796" s="54"/>
-      <c r="Z8796" s="66"/>
-    </row>
-    <row r="8797" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8797" s="65"/>
-      <c r="X8797" s="104"/>
-      <c r="Y8797" s="54"/>
-      <c r="Z8797" s="66"/>
-    </row>
-    <row r="8798" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8798" s="65"/>
-      <c r="X8798" s="104"/>
-      <c r="Y8798" s="54"/>
-      <c r="Z8798" s="66"/>
-    </row>
-    <row r="8799" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8799" s="65"/>
-      <c r="X8799" s="104"/>
-      <c r="Y8799" s="54"/>
-      <c r="Z8799" s="66"/>
-    </row>
-    <row r="8800" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8800" s="65"/>
-      <c r="X8800" s="104"/>
-      <c r="Y8800" s="54"/>
-      <c r="Z8800" s="66"/>
-    </row>
-    <row r="8801" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8801" s="65"/>
-      <c r="X8801" s="104"/>
-      <c r="Y8801" s="54"/>
-      <c r="Z8801" s="66"/>
-    </row>
-    <row r="8802" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8802" s="65"/>
-      <c r="X8802" s="104"/>
-      <c r="Y8802" s="54"/>
-      <c r="Z8802" s="66"/>
-    </row>
-    <row r="8803" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8803" s="65"/>
-      <c r="X8803" s="104"/>
-      <c r="Y8803" s="54"/>
-      <c r="Z8803" s="66"/>
-    </row>
-    <row r="8804" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8804" s="65"/>
-      <c r="X8804" s="104"/>
-      <c r="Y8804" s="54"/>
-      <c r="Z8804" s="66"/>
-    </row>
-    <row r="8805" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8805" s="65"/>
-      <c r="X8805" s="104"/>
-      <c r="Y8805" s="54"/>
-      <c r="Z8805" s="66"/>
-    </row>
-    <row r="8806" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8806" s="65"/>
-      <c r="X8806" s="104"/>
-      <c r="Y8806" s="54"/>
-      <c r="Z8806" s="66"/>
-    </row>
-    <row r="8807" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8807" s="65"/>
-      <c r="X8807" s="104"/>
-      <c r="Y8807" s="54"/>
-      <c r="Z8807" s="66"/>
-    </row>
-    <row r="8808" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8808" s="65"/>
-      <c r="X8808" s="104"/>
-      <c r="Y8808" s="54"/>
-      <c r="Z8808" s="66"/>
-    </row>
-    <row r="8809" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8809" s="65"/>
-      <c r="X8809" s="104"/>
-      <c r="Y8809" s="54"/>
-      <c r="Z8809" s="66"/>
-    </row>
-    <row r="8810" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8810" s="65"/>
-      <c r="X8810" s="104"/>
-      <c r="Y8810" s="54"/>
-      <c r="Z8810" s="66"/>
-    </row>
-    <row r="8811" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8811" s="65"/>
-      <c r="X8811" s="104"/>
-      <c r="Y8811" s="54"/>
-      <c r="Z8811" s="66"/>
-    </row>
-    <row r="8812" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8812" s="65"/>
-      <c r="X8812" s="104"/>
-      <c r="Y8812" s="54"/>
-      <c r="Z8812" s="66"/>
-    </row>
-    <row r="8813" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8813" s="65"/>
-      <c r="X8813" s="104"/>
-      <c r="Y8813" s="54"/>
-      <c r="Z8813" s="66"/>
-    </row>
-    <row r="8814" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8814" s="65"/>
-      <c r="X8814" s="104"/>
-      <c r="Y8814" s="54"/>
-      <c r="Z8814" s="66"/>
-    </row>
-    <row r="8815" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8815" s="65"/>
-      <c r="X8815" s="104"/>
-      <c r="Y8815" s="54"/>
-      <c r="Z8815" s="66"/>
-    </row>
-    <row r="8816" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8816" s="65"/>
-      <c r="X8816" s="104"/>
-      <c r="Y8816" s="54"/>
-      <c r="Z8816" s="66"/>
-    </row>
-    <row r="8817" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8817" s="65"/>
-      <c r="X8817" s="104"/>
-      <c r="Y8817" s="54"/>
-      <c r="Z8817" s="66"/>
-    </row>
-    <row r="8818" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8818" s="65"/>
-      <c r="X8818" s="104"/>
-      <c r="Y8818" s="54"/>
-      <c r="Z8818" s="66"/>
-    </row>
-    <row r="8819" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8819" s="65"/>
-      <c r="X8819" s="104"/>
-      <c r="Y8819" s="54"/>
-      <c r="Z8819" s="66"/>
-    </row>
-    <row r="8820" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8820" s="65"/>
-      <c r="X8820" s="104"/>
-      <c r="Y8820" s="54"/>
-      <c r="Z8820" s="66"/>
-    </row>
-    <row r="8821" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8821" s="65"/>
-      <c r="X8821" s="104"/>
-      <c r="Y8821" s="54"/>
-      <c r="Z8821" s="66"/>
-    </row>
-    <row r="8822" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8822" s="65"/>
-      <c r="X8822" s="104"/>
-      <c r="Y8822" s="54"/>
-      <c r="Z8822" s="66"/>
-    </row>
-    <row r="8823" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8823" s="65"/>
-      <c r="X8823" s="104"/>
-      <c r="Y8823" s="54"/>
-      <c r="Z8823" s="66"/>
-    </row>
-    <row r="8824" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8824" s="65"/>
-      <c r="X8824" s="104"/>
-      <c r="Y8824" s="54"/>
-      <c r="Z8824" s="66"/>
-    </row>
-    <row r="8825" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8825" s="65"/>
-      <c r="X8825" s="104"/>
-      <c r="Y8825" s="54"/>
-      <c r="Z8825" s="66"/>
-    </row>
-    <row r="8826" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8826" s="65"/>
-      <c r="X8826" s="104"/>
-      <c r="Y8826" s="54"/>
-      <c r="Z8826" s="66"/>
-    </row>
-    <row r="8827" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8827" s="65"/>
-      <c r="X8827" s="104"/>
-      <c r="Y8827" s="54"/>
-      <c r="Z8827" s="66"/>
-    </row>
-    <row r="8828" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8828" s="65"/>
-      <c r="X8828" s="104"/>
-      <c r="Y8828" s="54"/>
-      <c r="Z8828" s="66"/>
-    </row>
-    <row r="8829" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8829" s="65"/>
-      <c r="X8829" s="104"/>
-      <c r="Y8829" s="54"/>
-      <c r="Z8829" s="66"/>
-    </row>
-    <row r="8830" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8830" s="65"/>
-      <c r="X8830" s="104"/>
-      <c r="Y8830" s="54"/>
-      <c r="Z8830" s="66"/>
-    </row>
-    <row r="8831" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8831" s="65"/>
-      <c r="X8831" s="104"/>
-      <c r="Y8831" s="54"/>
-      <c r="Z8831" s="66"/>
-    </row>
-    <row r="8832" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8832" s="65"/>
-      <c r="X8832" s="104"/>
-      <c r="Y8832" s="54"/>
-      <c r="Z8832" s="66"/>
-    </row>
-    <row r="8833" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8833" s="65"/>
-      <c r="X8833" s="104"/>
-      <c r="Y8833" s="54"/>
-      <c r="Z8833" s="66"/>
-    </row>
-    <row r="8834" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8834" s="65"/>
-      <c r="X8834" s="104"/>
-      <c r="Y8834" s="54"/>
-      <c r="Z8834" s="66"/>
-    </row>
-    <row r="8835" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8835" s="65"/>
-      <c r="X8835" s="104"/>
-      <c r="Y8835" s="54"/>
-      <c r="Z8835" s="66"/>
-    </row>
-    <row r="8836" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8836" s="65"/>
-      <c r="X8836" s="104"/>
-      <c r="Y8836" s="54"/>
-      <c r="Z8836" s="66"/>
-    </row>
-    <row r="8837" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8837" s="65"/>
-      <c r="X8837" s="104"/>
-      <c r="Y8837" s="54"/>
-      <c r="Z8837" s="66"/>
-    </row>
-    <row r="8838" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8838" s="65"/>
-      <c r="X8838" s="104"/>
-      <c r="Y8838" s="54"/>
-      <c r="Z8838" s="66"/>
-    </row>
-    <row r="8839" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8839" s="65"/>
-      <c r="X8839" s="104"/>
-      <c r="Y8839" s="54"/>
-      <c r="Z8839" s="66"/>
-    </row>
-    <row r="8840" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8840" s="65"/>
-      <c r="X8840" s="104"/>
-      <c r="Y8840" s="54"/>
-      <c r="Z8840" s="66"/>
-    </row>
-    <row r="8841" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8841" s="65"/>
-      <c r="X8841" s="104"/>
-      <c r="Y8841" s="54"/>
-      <c r="Z8841" s="66"/>
-    </row>
-    <row r="8842" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8842" s="65"/>
-      <c r="X8842" s="104"/>
-      <c r="Y8842" s="54"/>
-      <c r="Z8842" s="66"/>
-    </row>
-    <row r="8843" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8843" s="65"/>
-      <c r="X8843" s="104"/>
-      <c r="Y8843" s="54"/>
-      <c r="Z8843" s="66"/>
-    </row>
-    <row r="8844" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8844" s="65"/>
-      <c r="X8844" s="104"/>
-      <c r="Y8844" s="54"/>
-      <c r="Z8844" s="66"/>
-    </row>
-    <row r="8845" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8845" s="65"/>
-      <c r="X8845" s="104"/>
-      <c r="Y8845" s="54"/>
-      <c r="Z8845" s="66"/>
-    </row>
-    <row r="8846" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8846" s="65"/>
-      <c r="X8846" s="104"/>
-      <c r="Y8846" s="54"/>
-      <c r="Z8846" s="66"/>
-    </row>
-    <row r="8847" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8847" s="65"/>
-      <c r="X8847" s="104"/>
-      <c r="Y8847" s="54"/>
-      <c r="Z8847" s="66"/>
-    </row>
-    <row r="8848" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8848" s="65"/>
-      <c r="X8848" s="104"/>
-      <c r="Y8848" s="54"/>
-      <c r="Z8848" s="66"/>
-    </row>
-    <row r="8849" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8849" s="65"/>
-      <c r="X8849" s="104"/>
-      <c r="Y8849" s="54"/>
-      <c r="Z8849" s="66"/>
-    </row>
-    <row r="8850" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8850" s="65"/>
-      <c r="X8850" s="104"/>
-      <c r="Y8850" s="54"/>
-      <c r="Z8850" s="66"/>
-    </row>
-    <row r="8851" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8851" s="65"/>
-      <c r="X8851" s="104"/>
-      <c r="Y8851" s="54"/>
-      <c r="Z8851" s="66"/>
-    </row>
-    <row r="8852" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8852" s="65"/>
-      <c r="X8852" s="104"/>
-      <c r="Y8852" s="54"/>
-      <c r="Z8852" s="66"/>
-    </row>
-    <row r="8853" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8853" s="65"/>
-      <c r="X8853" s="104"/>
-      <c r="Y8853" s="54"/>
-      <c r="Z8853" s="66"/>
-    </row>
-    <row r="8854" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8854" s="65"/>
-      <c r="X8854" s="104"/>
-      <c r="Y8854" s="54"/>
-      <c r="Z8854" s="66"/>
-    </row>
-    <row r="8855" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8855" s="65"/>
-      <c r="X8855" s="104"/>
-      <c r="Y8855" s="54"/>
-      <c r="Z8855" s="66"/>
-    </row>
-    <row r="8856" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8856" s="65"/>
-      <c r="X8856" s="104"/>
-      <c r="Y8856" s="54"/>
-      <c r="Z8856" s="66"/>
-    </row>
-    <row r="8857" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8857" s="65"/>
-      <c r="X8857" s="104"/>
-      <c r="Y8857" s="54"/>
-      <c r="Z8857" s="66"/>
-    </row>
-    <row r="8858" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8858" s="65"/>
-      <c r="X8858" s="104"/>
-      <c r="Y8858" s="54"/>
-      <c r="Z8858" s="66"/>
-    </row>
-    <row r="8859" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8859" s="65"/>
-      <c r="X8859" s="104"/>
-      <c r="Y8859" s="54"/>
-      <c r="Z8859" s="66"/>
-    </row>
-    <row r="8860" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8860" s="65"/>
-      <c r="X8860" s="104"/>
-      <c r="Y8860" s="54"/>
-      <c r="Z8860" s="66"/>
-    </row>
-    <row r="8861" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8861" s="65"/>
-      <c r="X8861" s="104"/>
-      <c r="Y8861" s="54"/>
-      <c r="Z8861" s="66"/>
-    </row>
-    <row r="8862" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8862" s="65"/>
-      <c r="X8862" s="104"/>
-      <c r="Y8862" s="54"/>
-      <c r="Z8862" s="66"/>
-    </row>
-    <row r="8863" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8863" s="65"/>
-      <c r="X8863" s="104"/>
-      <c r="Y8863" s="54"/>
-      <c r="Z8863" s="66"/>
-    </row>
-    <row r="8864" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8864" s="65"/>
-      <c r="X8864" s="104"/>
-      <c r="Y8864" s="54"/>
-      <c r="Z8864" s="66"/>
-    </row>
-    <row r="8865" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8865" s="65"/>
-      <c r="X8865" s="104"/>
-      <c r="Y8865" s="54"/>
-      <c r="Z8865" s="66"/>
-    </row>
-    <row r="8866" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8866" s="65"/>
-      <c r="X8866" s="104"/>
-      <c r="Y8866" s="54"/>
-      <c r="Z8866" s="66"/>
-    </row>
-    <row r="8867" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8867" s="65"/>
-      <c r="X8867" s="104"/>
-      <c r="Y8867" s="54"/>
-      <c r="Z8867" s="66"/>
-    </row>
-    <row r="8868" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8868" s="65"/>
-      <c r="X8868" s="104"/>
-      <c r="Y8868" s="54"/>
-      <c r="Z8868" s="66"/>
-    </row>
-    <row r="8869" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8869" s="65"/>
-      <c r="X8869" s="104"/>
-      <c r="Y8869" s="54"/>
-      <c r="Z8869" s="66"/>
-    </row>
-    <row r="8870" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8870" s="65"/>
-      <c r="X8870" s="104"/>
-      <c r="Y8870" s="54"/>
-      <c r="Z8870" s="66"/>
-    </row>
-    <row r="8871" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8871" s="65"/>
-      <c r="X8871" s="104"/>
-      <c r="Y8871" s="54"/>
-      <c r="Z8871" s="66"/>
-    </row>
-    <row r="8872" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8872" s="65"/>
-      <c r="X8872" s="104"/>
-      <c r="Y8872" s="54"/>
-      <c r="Z8872" s="66"/>
-    </row>
-    <row r="8873" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8873" s="65"/>
-      <c r="X8873" s="104"/>
-      <c r="Y8873" s="54"/>
-      <c r="Z8873" s="66"/>
-    </row>
-    <row r="8874" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8874" s="65"/>
-      <c r="X8874" s="104"/>
-      <c r="Y8874" s="54"/>
-      <c r="Z8874" s="66"/>
-    </row>
-    <row r="8875" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8875" s="65"/>
-      <c r="X8875" s="104"/>
-      <c r="Y8875" s="54"/>
-      <c r="Z8875" s="66"/>
-    </row>
-    <row r="8876" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8876" s="65"/>
-      <c r="X8876" s="104"/>
-      <c r="Y8876" s="54"/>
-      <c r="Z8876" s="66"/>
-    </row>
-    <row r="8877" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8877" s="65"/>
-      <c r="X8877" s="104"/>
-      <c r="Y8877" s="54"/>
-      <c r="Z8877" s="66"/>
-    </row>
-    <row r="8878" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8878" s="65"/>
-      <c r="X8878" s="104"/>
-      <c r="Y8878" s="54"/>
-      <c r="Z8878" s="66"/>
-    </row>
-    <row r="8879" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8879" s="65"/>
-      <c r="X8879" s="104"/>
-      <c r="Y8879" s="54"/>
-      <c r="Z8879" s="66"/>
-    </row>
-    <row r="8880" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8880" s="65"/>
-      <c r="X8880" s="104"/>
-      <c r="Y8880" s="54"/>
-      <c r="Z8880" s="66"/>
-    </row>
-    <row r="8881" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8881" s="65"/>
-      <c r="X8881" s="104"/>
-      <c r="Y8881" s="54"/>
-      <c r="Z8881" s="66"/>
-    </row>
-    <row r="8882" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8882" s="65"/>
-      <c r="X8882" s="104"/>
-      <c r="Y8882" s="54"/>
-      <c r="Z8882" s="66"/>
-    </row>
-    <row r="8883" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8883" s="65"/>
-      <c r="X8883" s="104"/>
-      <c r="Y8883" s="54"/>
-      <c r="Z8883" s="66"/>
-    </row>
-    <row r="8884" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8884" s="65"/>
-      <c r="X8884" s="104"/>
-      <c r="Y8884" s="54"/>
-      <c r="Z8884" s="66"/>
-    </row>
-    <row r="8885" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8885" s="65"/>
-      <c r="X8885" s="104"/>
-      <c r="Y8885" s="54"/>
-      <c r="Z8885" s="66"/>
-    </row>
-    <row r="8886" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8886" s="65"/>
-      <c r="X8886" s="104"/>
-      <c r="Y8886" s="54"/>
-      <c r="Z8886" s="66"/>
-    </row>
-    <row r="8887" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8887" s="65"/>
-      <c r="X8887" s="104"/>
-      <c r="Y8887" s="54"/>
-      <c r="Z8887" s="66"/>
-    </row>
-    <row r="8888" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8888" s="65"/>
-      <c r="X8888" s="104"/>
-      <c r="Y8888" s="54"/>
-      <c r="Z8888" s="66"/>
-    </row>
-    <row r="8889" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8889" s="65"/>
-      <c r="X8889" s="104"/>
-      <c r="Y8889" s="54"/>
-      <c r="Z8889" s="66"/>
-    </row>
-    <row r="8890" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8890" s="65"/>
-      <c r="X8890" s="104"/>
-      <c r="Y8890" s="54"/>
-      <c r="Z8890" s="66"/>
-    </row>
-    <row r="8891" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8891" s="65"/>
-      <c r="X8891" s="104"/>
-      <c r="Y8891" s="54"/>
-      <c r="Z8891" s="66"/>
-    </row>
-    <row r="8892" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8892" s="65"/>
-      <c r="X8892" s="104"/>
-      <c r="Y8892" s="54"/>
-      <c r="Z8892" s="66"/>
-    </row>
-    <row r="8893" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8893" s="65"/>
-      <c r="X8893" s="104"/>
-      <c r="Y8893" s="54"/>
-      <c r="Z8893" s="66"/>
-    </row>
-    <row r="8894" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8894" s="65"/>
-      <c r="X8894" s="104"/>
-      <c r="Y8894" s="54"/>
-      <c r="Z8894" s="66"/>
-    </row>
-    <row r="8895" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8895" s="65"/>
-      <c r="X8895" s="104"/>
-      <c r="Y8895" s="54"/>
-      <c r="Z8895" s="66"/>
-    </row>
-    <row r="8896" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8896" s="65"/>
-      <c r="X8896" s="104"/>
-      <c r="Y8896" s="54"/>
-      <c r="Z8896" s="66"/>
-    </row>
-    <row r="8897" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8897" s="65"/>
-      <c r="X8897" s="104"/>
-      <c r="Y8897" s="54"/>
-      <c r="Z8897" s="66"/>
-    </row>
-    <row r="8898" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8898" s="65"/>
-      <c r="X8898" s="104"/>
-      <c r="Y8898" s="54"/>
-      <c r="Z8898" s="66"/>
-    </row>
-    <row r="8899" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8899" s="65"/>
-      <c r="X8899" s="104"/>
-      <c r="Y8899" s="54"/>
-      <c r="Z8899" s="66"/>
-    </row>
-    <row r="8900" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8900" s="65"/>
-      <c r="X8900" s="104"/>
-      <c r="Y8900" s="54"/>
-      <c r="Z8900" s="66"/>
-    </row>
-    <row r="8901" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8901" s="65"/>
-      <c r="X8901" s="104"/>
-      <c r="Y8901" s="54"/>
-      <c r="Z8901" s="66"/>
-    </row>
-    <row r="8902" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8902" s="65"/>
-      <c r="X8902" s="104"/>
-      <c r="Y8902" s="54"/>
-      <c r="Z8902" s="66"/>
-    </row>
-    <row r="8903" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8903" s="65"/>
-      <c r="X8903" s="104"/>
-      <c r="Y8903" s="54"/>
-      <c r="Z8903" s="66"/>
-    </row>
-    <row r="8904" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8904" s="65"/>
-      <c r="X8904" s="104"/>
-      <c r="Y8904" s="54"/>
-      <c r="Z8904" s="66"/>
-    </row>
-    <row r="8905" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8905" s="65"/>
-      <c r="X8905" s="104"/>
-      <c r="Y8905" s="54"/>
-      <c r="Z8905" s="66"/>
-    </row>
-    <row r="8906" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8906" s="65"/>
-      <c r="X8906" s="104"/>
-      <c r="Y8906" s="54"/>
-      <c r="Z8906" s="66"/>
-    </row>
-    <row r="8907" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8907" s="65"/>
-      <c r="X8907" s="104"/>
-      <c r="Y8907" s="54"/>
-      <c r="Z8907" s="66"/>
-    </row>
-    <row r="8908" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8908" s="65"/>
-      <c r="X8908" s="104"/>
-      <c r="Y8908" s="54"/>
-      <c r="Z8908" s="66"/>
-    </row>
-    <row r="8909" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8909" s="65"/>
-      <c r="X8909" s="104"/>
-      <c r="Y8909" s="54"/>
-      <c r="Z8909" s="66"/>
-    </row>
-    <row r="8910" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8910" s="65"/>
-      <c r="X8910" s="104"/>
-      <c r="Y8910" s="54"/>
-      <c r="Z8910" s="66"/>
-    </row>
-    <row r="8911" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8911" s="65"/>
-      <c r="X8911" s="104"/>
-      <c r="Y8911" s="54"/>
-      <c r="Z8911" s="66"/>
-    </row>
-    <row r="8912" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8912" s="65"/>
-      <c r="X8912" s="104"/>
-      <c r="Y8912" s="54"/>
-      <c r="Z8912" s="66"/>
-    </row>
-    <row r="8913" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8913" s="65"/>
-      <c r="X8913" s="104"/>
-      <c r="Y8913" s="54"/>
-      <c r="Z8913" s="66"/>
-    </row>
-    <row r="8914" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8914" s="65"/>
-      <c r="X8914" s="104"/>
-      <c r="Y8914" s="54"/>
-      <c r="Z8914" s="66"/>
-    </row>
-    <row r="8915" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8915" s="65"/>
-      <c r="X8915" s="104"/>
-      <c r="Y8915" s="54"/>
-      <c r="Z8915" s="66"/>
-    </row>
-    <row r="8916" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8916" s="65"/>
-      <c r="X8916" s="104"/>
-      <c r="Y8916" s="54"/>
-      <c r="Z8916" s="66"/>
-    </row>
-    <row r="8917" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8917" s="65"/>
-      <c r="X8917" s="104"/>
-      <c r="Y8917" s="54"/>
-      <c r="Z8917" s="66"/>
-    </row>
-    <row r="8918" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8918" s="65"/>
-      <c r="X8918" s="104"/>
-      <c r="Y8918" s="54"/>
-      <c r="Z8918" s="66"/>
-    </row>
-    <row r="8919" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8919" s="65"/>
-      <c r="X8919" s="104"/>
-      <c r="Y8919" s="54"/>
-      <c r="Z8919" s="66"/>
-    </row>
-    <row r="8920" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8920" s="65"/>
-      <c r="X8920" s="104"/>
-      <c r="Y8920" s="54"/>
-      <c r="Z8920" s="66"/>
-    </row>
-    <row r="8921" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8921" s="65"/>
-      <c r="X8921" s="104"/>
-      <c r="Y8921" s="54"/>
-      <c r="Z8921" s="66"/>
-    </row>
-    <row r="8922" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8922" s="65"/>
-      <c r="X8922" s="104"/>
-      <c r="Y8922" s="54"/>
-      <c r="Z8922" s="66"/>
-    </row>
-    <row r="8923" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8923" s="65"/>
-      <c r="X8923" s="104"/>
-      <c r="Y8923" s="54"/>
-      <c r="Z8923" s="66"/>
-    </row>
-    <row r="8924" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8924" s="65"/>
-      <c r="X8924" s="104"/>
-      <c r="Y8924" s="54"/>
-      <c r="Z8924" s="66"/>
-    </row>
-    <row r="8925" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8925" s="65"/>
-      <c r="X8925" s="104"/>
-      <c r="Y8925" s="54"/>
-      <c r="Z8925" s="66"/>
-    </row>
-    <row r="8926" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8926" s="65"/>
-      <c r="X8926" s="104"/>
-      <c r="Y8926" s="54"/>
-      <c r="Z8926" s="66"/>
-    </row>
-    <row r="8927" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8927" s="65"/>
-      <c r="X8927" s="104"/>
-      <c r="Y8927" s="54"/>
-      <c r="Z8927" s="66"/>
-    </row>
-    <row r="8928" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8928" s="65"/>
-      <c r="X8928" s="104"/>
-      <c r="Y8928" s="54"/>
-      <c r="Z8928" s="66"/>
-    </row>
-    <row r="8929" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8929" s="65"/>
-      <c r="X8929" s="104"/>
-      <c r="Y8929" s="54"/>
-      <c r="Z8929" s="66"/>
-    </row>
-    <row r="8930" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8930" s="65"/>
-      <c r="X8930" s="104"/>
-      <c r="Y8930" s="54"/>
-      <c r="Z8930" s="66"/>
-    </row>
-    <row r="8931" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8931" s="65"/>
-      <c r="X8931" s="104"/>
-      <c r="Y8931" s="54"/>
-      <c r="Z8931" s="66"/>
-    </row>
-    <row r="8932" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8932" s="65"/>
-      <c r="X8932" s="104"/>
-      <c r="Y8932" s="54"/>
-      <c r="Z8932" s="66"/>
-    </row>
-    <row r="8933" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8933" s="65"/>
-      <c r="X8933" s="104"/>
-      <c r="Y8933" s="54"/>
-      <c r="Z8933" s="66"/>
-    </row>
-    <row r="8934" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8934" s="65"/>
-      <c r="X8934" s="104"/>
-      <c r="Y8934" s="54"/>
-      <c r="Z8934" s="66"/>
-    </row>
-    <row r="8935" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8935" s="65"/>
-      <c r="X8935" s="104"/>
-      <c r="Y8935" s="54"/>
-      <c r="Z8935" s="66"/>
-    </row>
-    <row r="8936" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8936" s="65"/>
-      <c r="X8936" s="104"/>
-      <c r="Y8936" s="54"/>
-      <c r="Z8936" s="66"/>
-    </row>
-    <row r="8937" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8937" s="65"/>
-      <c r="X8937" s="104"/>
-      <c r="Y8937" s="54"/>
-      <c r="Z8937" s="66"/>
-    </row>
-    <row r="8938" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8938" s="65"/>
-      <c r="X8938" s="104"/>
-      <c r="Y8938" s="54"/>
-      <c r="Z8938" s="66"/>
-    </row>
-    <row r="8939" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8939" s="65"/>
-      <c r="X8939" s="104"/>
-      <c r="Y8939" s="54"/>
-      <c r="Z8939" s="66"/>
-    </row>
-    <row r="8940" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8940" s="65"/>
-      <c r="X8940" s="104"/>
-      <c r="Y8940" s="54"/>
-      <c r="Z8940" s="66"/>
-    </row>
-    <row r="8941" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8941" s="65"/>
-      <c r="X8941" s="104"/>
-      <c r="Y8941" s="54"/>
-      <c r="Z8941" s="66"/>
-    </row>
-    <row r="8942" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8942" s="65"/>
-      <c r="X8942" s="104"/>
-      <c r="Y8942" s="54"/>
-      <c r="Z8942" s="66"/>
-    </row>
-    <row r="8943" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8943" s="65"/>
-      <c r="X8943" s="104"/>
-      <c r="Y8943" s="54"/>
-      <c r="Z8943" s="66"/>
-    </row>
-    <row r="8944" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8944" s="65"/>
-      <c r="X8944" s="104"/>
-      <c r="Y8944" s="54"/>
-      <c r="Z8944" s="66"/>
-    </row>
-    <row r="8945" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8945" s="65"/>
-      <c r="X8945" s="104"/>
-      <c r="Y8945" s="54"/>
-      <c r="Z8945" s="66"/>
-    </row>
-    <row r="8946" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8946" s="65"/>
-      <c r="X8946" s="104"/>
-      <c r="Y8946" s="54"/>
-      <c r="Z8946" s="66"/>
-    </row>
-    <row r="8947" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8947" s="65"/>
-      <c r="X8947" s="104"/>
-      <c r="Y8947" s="54"/>
-      <c r="Z8947" s="66"/>
-    </row>
-    <row r="8948" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8948" s="65"/>
-      <c r="X8948" s="104"/>
-      <c r="Y8948" s="54"/>
-      <c r="Z8948" s="66"/>
-    </row>
-    <row r="8949" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8949" s="65"/>
-      <c r="X8949" s="104"/>
-      <c r="Y8949" s="54"/>
-      <c r="Z8949" s="66"/>
-    </row>
-    <row r="8950" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8950" s="65"/>
-      <c r="X8950" s="104"/>
-      <c r="Y8950" s="54"/>
-      <c r="Z8950" s="66"/>
-    </row>
-    <row r="8951" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8951" s="65"/>
-      <c r="X8951" s="104"/>
-      <c r="Y8951" s="54"/>
-      <c r="Z8951" s="66"/>
-    </row>
-    <row r="8952" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8952" s="65"/>
-      <c r="X8952" s="104"/>
-      <c r="Y8952" s="54"/>
-      <c r="Z8952" s="66"/>
-    </row>
-    <row r="8953" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8953" s="65"/>
-      <c r="X8953" s="104"/>
-      <c r="Y8953" s="54"/>
-      <c r="Z8953" s="66"/>
-    </row>
-    <row r="8954" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8954" s="65"/>
-      <c r="X8954" s="104"/>
-      <c r="Y8954" s="54"/>
-      <c r="Z8954" s="66"/>
-    </row>
-    <row r="8955" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8955" s="65"/>
-      <c r="X8955" s="104"/>
-      <c r="Y8955" s="54"/>
-      <c r="Z8955" s="66"/>
-    </row>
-    <row r="8956" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8956" s="65"/>
-      <c r="X8956" s="104"/>
-      <c r="Y8956" s="54"/>
-      <c r="Z8956" s="66"/>
-    </row>
-    <row r="8957" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8957" s="65"/>
-      <c r="X8957" s="104"/>
-      <c r="Y8957" s="54"/>
-      <c r="Z8957" s="66"/>
-    </row>
-    <row r="8958" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8958" s="65"/>
-      <c r="X8958" s="104"/>
-      <c r="Y8958" s="54"/>
-      <c r="Z8958" s="66"/>
-    </row>
-    <row r="8959" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8959" s="65"/>
-      <c r="X8959" s="104"/>
-      <c r="Y8959" s="54"/>
-      <c r="Z8959" s="66"/>
-    </row>
-    <row r="8960" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8960" s="65"/>
-      <c r="X8960" s="104"/>
-      <c r="Y8960" s="54"/>
-      <c r="Z8960" s="66"/>
-    </row>
-    <row r="8961" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8961" s="65"/>
-      <c r="X8961" s="104"/>
-      <c r="Y8961" s="54"/>
-      <c r="Z8961" s="66"/>
-    </row>
-    <row r="8962" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8962" s="65"/>
-      <c r="X8962" s="104"/>
-      <c r="Y8962" s="54"/>
-      <c r="Z8962" s="66"/>
-    </row>
-    <row r="8963" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8963" s="65"/>
-      <c r="X8963" s="104"/>
-      <c r="Y8963" s="54"/>
-      <c r="Z8963" s="66"/>
-    </row>
-    <row r="8964" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8964" s="65"/>
-      <c r="X8964" s="104"/>
-      <c r="Y8964" s="54"/>
-      <c r="Z8964" s="66"/>
-    </row>
-    <row r="8965" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8965" s="65"/>
-      <c r="X8965" s="104"/>
-      <c r="Y8965" s="54"/>
-      <c r="Z8965" s="66"/>
-    </row>
-    <row r="8966" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8966" s="65"/>
-      <c r="X8966" s="104"/>
-      <c r="Y8966" s="54"/>
-      <c r="Z8966" s="66"/>
-    </row>
-    <row r="8967" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8967" s="65"/>
-      <c r="X8967" s="104"/>
-      <c r="Y8967" s="54"/>
-      <c r="Z8967" s="66"/>
-    </row>
-    <row r="8968" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8968" s="65"/>
-      <c r="X8968" s="104"/>
-      <c r="Y8968" s="54"/>
-      <c r="Z8968" s="66"/>
-    </row>
-    <row r="8969" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8969" s="65"/>
-      <c r="X8969" s="104"/>
-      <c r="Y8969" s="54"/>
-      <c r="Z8969" s="66"/>
-    </row>
-    <row r="8970" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8970" s="65"/>
-      <c r="X8970" s="104"/>
-      <c r="Y8970" s="54"/>
-      <c r="Z8970" s="66"/>
-    </row>
-    <row r="8971" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8971" s="65"/>
-      <c r="X8971" s="104"/>
-      <c r="Y8971" s="54"/>
-      <c r="Z8971" s="66"/>
-    </row>
-    <row r="8972" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8972" s="65"/>
-      <c r="X8972" s="104"/>
-      <c r="Y8972" s="54"/>
-      <c r="Z8972" s="66"/>
-    </row>
-    <row r="8973" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8973" s="65"/>
-      <c r="X8973" s="104"/>
-      <c r="Y8973" s="54"/>
-      <c r="Z8973" s="66"/>
-    </row>
-    <row r="8974" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8974" s="65"/>
-      <c r="X8974" s="104"/>
-      <c r="Y8974" s="54"/>
-      <c r="Z8974" s="66"/>
-    </row>
-    <row r="8975" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8975" s="65"/>
-      <c r="X8975" s="104"/>
-      <c r="Y8975" s="54"/>
-      <c r="Z8975" s="66"/>
-    </row>
-    <row r="8976" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8976" s="65"/>
-      <c r="X8976" s="104"/>
-      <c r="Y8976" s="54"/>
-      <c r="Z8976" s="66"/>
-    </row>
-    <row r="8977" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8977" s="65"/>
-      <c r="X8977" s="104"/>
-      <c r="Y8977" s="54"/>
-      <c r="Z8977" s="66"/>
-    </row>
-    <row r="8978" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8978" s="65"/>
-      <c r="X8978" s="104"/>
-      <c r="Y8978" s="54"/>
-      <c r="Z8978" s="66"/>
-    </row>
-    <row r="8979" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8979" s="65"/>
-      <c r="X8979" s="104"/>
-      <c r="Y8979" s="54"/>
-      <c r="Z8979" s="66"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BV24" xr:uid="{00000000-0009-0000-0000-000002000000}">
+  <autoFilter ref="A1:BV154" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="11" showButton="0"/>
+    <filterColumn colId="19" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="22" showButton="0"/>
     <filterColumn colId="23" showButton="0"/>
     <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+    <filterColumn colId="27" showButton="0"/>
+    <filterColumn colId="28" showButton="0"/>
+    <filterColumn colId="29" showButton="0"/>
+    <filterColumn colId="30" showButton="0"/>
+    <filterColumn colId="31" showButton="0"/>
+    <filterColumn colId="32" showButton="0"/>
+    <filterColumn colId="34" showButton="0"/>
+    <filterColumn colId="39" showButton="0"/>
+    <filterColumn colId="40" showButton="0"/>
+    <filterColumn colId="41" showButton="0"/>
+    <filterColumn colId="42" showButton="0"/>
+    <filterColumn colId="54" showButton="0"/>
+    <filterColumn colId="55" showButton="0"/>
+    <filterColumn colId="57" showButton="0"/>
+    <filterColumn colId="58" showButton="0"/>
+    <filterColumn colId="60" showButton="0"/>
+    <filterColumn colId="61" showButton="0"/>
+    <filterColumn colId="63" showButton="0"/>
+    <filterColumn colId="64" showButton="0"/>
+    <filterColumn colId="66" showButton="0"/>
+    <filterColumn colId="67" showButton="0"/>
   </autoFilter>
   <mergeCells count="46">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="BR1:BR2"/>
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="AA1:AH1"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="AT1:AT2"/>
-    <mergeCell ref="AU1:AU2"/>
-    <mergeCell ref="AV1:AV2"/>
-    <mergeCell ref="AW1:AW2"/>
-    <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="BV1:BV2"/>
     <mergeCell ref="BC1:BE1"/>
@@ -60170,9 +63102,39 @@
     <mergeCell ref="BT1:BT2"/>
     <mergeCell ref="BU1:BU2"/>
     <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="BR1:BR2"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="AT1:AT2"/>
+    <mergeCell ref="AU1:AU2"/>
+    <mergeCell ref="AV1:AV2"/>
+    <mergeCell ref="AW1:AW2"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation operator="equal" allowBlank="1" showErrorMessage="1" sqref="BC1:BC2 J1:J2" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -60182,7 +63144,7 @@
   <pageSetup paperSize="8" scale="28" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
           <x14:formula1>
             <xm:f>'Internal lists'!$F$2:$F$5</xm:f>
@@ -60264,10 +63226,10 @@
       <c r="A4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="135" t="s">
+      <c r="B4" s="132" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="135"/>
+      <c r="C4" s="132"/>
       <c r="D4" s="26" t="s">
         <v>59</v>
       </c>
@@ -60276,13 +63238,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="127" t="s">
+      <c r="B5" s="133" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="127"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="28" t="s">
         <v>158</v>
       </c>
@@ -60291,16 +63253,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="127"/>
-      <c r="B6" s="127"/>
-      <c r="C6" s="127"/>
+      <c r="A6" s="133"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
       <c r="D6" s="28"/>
       <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="127"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="133"/>
+      <c r="C7" s="133"/>
       <c r="D7" s="28" t="s">
         <v>160</v>
       </c>
@@ -60309,9 +63271,9 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
       <c r="D8" s="28" t="s">
         <v>162</v>
       </c>
@@ -60320,9 +63282,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
       <c r="D9" s="28" t="s">
         <v>163</v>
       </c>
@@ -60331,9 +63293,9 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="127"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
       <c r="D10" s="28" t="s">
         <v>164</v>
       </c>
@@ -60342,9 +63304,9 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
       <c r="D11" s="31" t="s">
         <v>165</v>
       </c>
@@ -60356,7 +63318,7 @@
       <c r="A12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="133" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="31" t="s">
@@ -60373,7 +63335,7 @@
       <c r="A13" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="127"/>
+      <c r="B13" s="133"/>
       <c r="C13" s="31" t="s">
         <v>104</v>
       </c>
@@ -60388,7 +63350,7 @@
       <c r="A14" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="127"/>
+      <c r="B14" s="133"/>
       <c r="C14" s="31" t="s">
         <v>105</v>
       </c>
@@ -60403,7 +63365,7 @@
       <c r="A15" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="127"/>
+      <c r="B15" s="133"/>
       <c r="C15" s="31" t="s">
         <v>106</v>
       </c>
@@ -60418,7 +63380,7 @@
       <c r="A16" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="127"/>
+      <c r="B16" s="133"/>
       <c r="C16" s="31" t="s">
         <v>107</v>
       </c>
@@ -60433,10 +63395,10 @@
       <c r="A17" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="127"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="31" t="s">
         <v>177</v>
       </c>
@@ -60448,10 +63410,10 @@
       <c r="A18" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="127" t="s">
+      <c r="B18" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="127"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="31" t="s">
         <v>180</v>
       </c>
@@ -60463,10 +63425,10 @@
       <c r="A19" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="127"/>
+      <c r="C19" s="133"/>
       <c r="D19" s="31" t="s">
         <v>183</v>
       </c>
@@ -60478,10 +63440,10 @@
       <c r="A20" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="127" t="s">
+      <c r="B20" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="127"/>
+      <c r="C20" s="133"/>
       <c r="D20" s="31" t="s">
         <v>186</v>
       </c>
@@ -60493,10 +63455,10 @@
       <c r="A21" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="127" t="s">
+      <c r="B21" s="133" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="127"/>
+      <c r="C21" s="133"/>
       <c r="D21" s="31" t="s">
         <v>189</v>
       </c>
@@ -60508,10 +63470,10 @@
       <c r="A22" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="127" t="s">
+      <c r="B22" s="133" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="127"/>
+      <c r="C22" s="133"/>
       <c r="D22" s="31" t="s">
         <v>192</v>
       </c>
@@ -60520,13 +63482,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="127" t="s">
+      <c r="A23" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="127" t="s">
+      <c r="B23" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="127"/>
+      <c r="C23" s="133"/>
       <c r="D23" s="28" t="s">
         <v>194</v>
       </c>
@@ -60535,9 +63497,9 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="127"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
+      <c r="A24" s="133"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
       <c r="D24" s="28" t="s">
         <v>196</v>
       </c>
@@ -60546,9 +63508,9 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="127"/>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
+      <c r="A25" s="133"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="133"/>
       <c r="D25" s="28" t="s">
         <v>198</v>
       </c>
@@ -60557,9 +63519,9 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="127"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
+      <c r="A26" s="133"/>
+      <c r="B26" s="133"/>
+      <c r="C26" s="133"/>
       <c r="D26" s="28" t="s">
         <v>199</v>
       </c>
@@ -60568,9 +63530,9 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="127"/>
-      <c r="B27" s="127"/>
-      <c r="C27" s="127"/>
+      <c r="A27" s="133"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="133"/>
       <c r="D27" s="28" t="s">
         <v>200</v>
       </c>
@@ -60579,9 +63541,9 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="127"/>
-      <c r="B28" s="127"/>
-      <c r="C28" s="127"/>
+      <c r="A28" s="133"/>
+      <c r="B28" s="133"/>
+      <c r="C28" s="133"/>
       <c r="D28" s="28" t="s">
         <v>201</v>
       </c>
@@ -60590,9 +63552,9 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="127"/>
-      <c r="B29" s="127"/>
-      <c r="C29" s="127"/>
+      <c r="A29" s="133"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="133"/>
       <c r="D29" s="28" t="s">
         <v>202</v>
       </c>
@@ -60601,9 +63563,9 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="127"/>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127"/>
+      <c r="A30" s="133"/>
+      <c r="B30" s="133"/>
+      <c r="C30" s="133"/>
       <c r="D30" s="28" t="s">
         <v>203</v>
       </c>
@@ -60612,9 +63574,9 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="127"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
+      <c r="A31" s="133"/>
+      <c r="B31" s="133"/>
+      <c r="C31" s="133"/>
       <c r="D31" s="28" t="s">
         <v>204</v>
       </c>
@@ -60623,9 +63585,9 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="127"/>
-      <c r="B32" s="127"/>
-      <c r="C32" s="127"/>
+      <c r="A32" s="133"/>
+      <c r="B32" s="133"/>
+      <c r="C32" s="133"/>
       <c r="D32" s="28" t="s">
         <v>205</v>
       </c>
@@ -60634,9 +63596,9 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="127"/>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
+      <c r="A33" s="133"/>
+      <c r="B33" s="133"/>
+      <c r="C33" s="133"/>
       <c r="D33" s="28" t="s">
         <v>206</v>
       </c>
@@ -60645,16 +63607,16 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="127"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="127"/>
+      <c r="A34" s="133"/>
+      <c r="B34" s="133"/>
+      <c r="C34" s="133"/>
       <c r="D34" s="28"/>
       <c r="E34" s="30"/>
     </row>
     <row r="35" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="127"/>
-      <c r="B35" s="127"/>
-      <c r="C35" s="127"/>
+      <c r="A35" s="133"/>
+      <c r="B35" s="133"/>
+      <c r="C35" s="133"/>
       <c r="D35" s="28" t="s">
         <v>208</v>
       </c>
@@ -60663,9 +63625,9 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="127"/>
-      <c r="B36" s="127"/>
-      <c r="C36" s="127"/>
+      <c r="A36" s="133"/>
+      <c r="B36" s="133"/>
+      <c r="C36" s="133"/>
       <c r="D36" s="31" t="s">
         <v>210</v>
       </c>
@@ -60677,10 +63639,10 @@
       <c r="A37" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="128" t="s">
+      <c r="B37" s="134" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="128"/>
+      <c r="C37" s="134"/>
       <c r="D37" s="31" t="s">
         <v>212</v>
       </c>
@@ -60692,10 +63654,10 @@
       <c r="A38" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B38" s="127" t="s">
+      <c r="B38" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="127"/>
+      <c r="C38" s="133"/>
       <c r="D38" s="31" t="s">
         <v>214</v>
       </c>
@@ -60707,10 +63669,10 @@
       <c r="A39" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="127" t="s">
+      <c r="B39" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="127"/>
+      <c r="C39" s="133"/>
       <c r="D39" s="31" t="s">
         <v>216</v>
       </c>
@@ -60719,13 +63681,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="127" t="s">
+      <c r="A40" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B40" s="127" t="s">
+      <c r="B40" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="127"/>
+      <c r="C40" s="133"/>
       <c r="D40" s="28" t="s">
         <v>218</v>
       </c>
@@ -60734,9 +63696,9 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="127"/>
-      <c r="B41" s="127"/>
-      <c r="C41" s="127"/>
+      <c r="A41" s="133"/>
+      <c r="B41" s="133"/>
+      <c r="C41" s="133"/>
       <c r="D41" s="28" t="s">
         <v>220</v>
       </c>
@@ -60745,9 +63707,9 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="127"/>
-      <c r="B42" s="127"/>
-      <c r="C42" s="127"/>
+      <c r="A42" s="133"/>
+      <c r="B42" s="133"/>
+      <c r="C42" s="133"/>
       <c r="D42" s="28" t="s">
         <v>222</v>
       </c>
@@ -60756,9 +63718,9 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="127"/>
-      <c r="B43" s="127"/>
-      <c r="C43" s="127"/>
+      <c r="A43" s="133"/>
+      <c r="B43" s="133"/>
+      <c r="C43" s="133"/>
       <c r="D43" s="28" t="s">
         <v>224</v>
       </c>
@@ -60767,9 +63729,9 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="127"/>
-      <c r="B44" s="127"/>
-      <c r="C44" s="127"/>
+      <c r="A44" s="133"/>
+      <c r="B44" s="133"/>
+      <c r="C44" s="133"/>
       <c r="D44" s="28" t="s">
         <v>226</v>
       </c>
@@ -60781,10 +63743,10 @@
       <c r="A45" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="127" t="s">
+      <c r="B45" s="133" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="127"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="27" t="s">
         <v>227</v>
       </c>
@@ -60841,7 +63803,7 @@
       <c r="A49" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="132" t="s">
+      <c r="B49" s="135" t="s">
         <v>237</v>
       </c>
       <c r="C49" s="31" t="s">
@@ -60855,11 +63817,11 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="127" t="s">
+      <c r="A50" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B50" s="132"/>
-      <c r="C50" s="133" t="s">
+      <c r="B50" s="135"/>
+      <c r="C50" s="136" t="s">
         <v>108</v>
       </c>
       <c r="D50" s="40" t="s">
@@ -60870,9 +63832,9 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="127"/>
-      <c r="B51" s="132"/>
-      <c r="C51" s="133"/>
+      <c r="A51" s="133"/>
+      <c r="B51" s="135"/>
+      <c r="C51" s="136"/>
       <c r="D51" s="30" t="s">
         <v>242</v>
       </c>
@@ -60881,9 +63843,9 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="127"/>
-      <c r="B52" s="132"/>
-      <c r="C52" s="133"/>
+      <c r="A52" s="133"/>
+      <c r="B52" s="135"/>
+      <c r="C52" s="136"/>
       <c r="D52" s="30" t="s">
         <v>244</v>
       </c>
@@ -60892,9 +63854,9 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="127"/>
-      <c r="B53" s="132"/>
-      <c r="C53" s="133"/>
+      <c r="A53" s="133"/>
+      <c r="B53" s="135"/>
+      <c r="C53" s="136"/>
       <c r="D53" s="30" t="s">
         <v>246</v>
       </c>
@@ -60903,16 +63865,16 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="127"/>
-      <c r="B54" s="132"/>
-      <c r="C54" s="133"/>
+      <c r="A54" s="133"/>
+      <c r="B54" s="135"/>
+      <c r="C54" s="136"/>
       <c r="D54" s="28"/>
       <c r="E54" s="30"/>
     </row>
     <row r="55" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="127"/>
-      <c r="B55" s="132"/>
-      <c r="C55" s="133"/>
+      <c r="A55" s="133"/>
+      <c r="B55" s="135"/>
+      <c r="C55" s="136"/>
       <c r="D55" s="31" t="s">
         <v>248</v>
       </c>
@@ -60921,11 +63883,11 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="127" t="s">
+      <c r="A56" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B56" s="132"/>
-      <c r="C56" s="134" t="s">
+      <c r="B56" s="135"/>
+      <c r="C56" s="137" t="s">
         <v>109</v>
       </c>
       <c r="D56" s="28" t="s">
@@ -60936,9 +63898,9 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="127"/>
-      <c r="B57" s="132"/>
-      <c r="C57" s="134"/>
+      <c r="A57" s="133"/>
+      <c r="B57" s="135"/>
+      <c r="C57" s="137"/>
       <c r="D57" s="28" t="s">
         <v>252</v>
       </c>
@@ -60947,9 +63909,9 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="127"/>
-      <c r="B58" s="132"/>
-      <c r="C58" s="134"/>
+      <c r="A58" s="133"/>
+      <c r="B58" s="135"/>
+      <c r="C58" s="137"/>
       <c r="D58" s="31" t="s">
         <v>254</v>
       </c>
@@ -60961,10 +63923,10 @@
       <c r="A59" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="127" t="s">
+      <c r="B59" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="127"/>
+      <c r="C59" s="133"/>
       <c r="D59" s="31" t="s">
         <v>256</v>
       </c>
@@ -60976,7 +63938,7 @@
       <c r="A60" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="131" t="s">
+      <c r="B60" s="138" t="s">
         <v>82</v>
       </c>
       <c r="C60" s="31" t="s">
@@ -60990,11 +63952,11 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="127" t="s">
+      <c r="A61" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B61" s="131"/>
-      <c r="C61" s="127" t="s">
+      <c r="B61" s="138"/>
+      <c r="C61" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D61" s="40" t="s">
@@ -61005,9 +63967,9 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="127"/>
-      <c r="B62" s="127"/>
-      <c r="C62" s="127"/>
+      <c r="A62" s="133"/>
+      <c r="B62" s="133"/>
+      <c r="C62" s="133"/>
       <c r="D62" s="30" t="s">
         <v>242</v>
       </c>
@@ -61016,9 +63978,9 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="127"/>
-      <c r="B63" s="127"/>
-      <c r="C63" s="127"/>
+      <c r="A63" s="133"/>
+      <c r="B63" s="133"/>
+      <c r="C63" s="133"/>
       <c r="D63" s="30" t="s">
         <v>244</v>
       </c>
@@ -61027,9 +63989,9 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="127"/>
-      <c r="B64" s="127"/>
-      <c r="C64" s="127"/>
+      <c r="A64" s="133"/>
+      <c r="B64" s="133"/>
+      <c r="C64" s="133"/>
       <c r="D64" s="30" t="s">
         <v>246</v>
       </c>
@@ -61038,16 +64000,16 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="127"/>
-      <c r="B65" s="127"/>
-      <c r="C65" s="127"/>
+      <c r="A65" s="133"/>
+      <c r="B65" s="133"/>
+      <c r="C65" s="133"/>
       <c r="D65" s="28"/>
       <c r="E65" s="30"/>
     </row>
     <row r="66" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="127"/>
-      <c r="B66" s="131"/>
-      <c r="C66" s="127"/>
+      <c r="A66" s="133"/>
+      <c r="B66" s="138"/>
+      <c r="C66" s="133"/>
       <c r="D66" s="31" t="s">
         <v>248</v>
       </c>
@@ -61056,11 +64018,11 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="127" t="s">
+      <c r="A67" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="131"/>
-      <c r="C67" s="127" t="s">
+      <c r="B67" s="138"/>
+      <c r="C67" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D67" s="28" t="s">
@@ -61071,9 +64033,9 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="127"/>
-      <c r="B68" s="127"/>
-      <c r="C68" s="127"/>
+      <c r="A68" s="133"/>
+      <c r="B68" s="133"/>
+      <c r="C68" s="133"/>
       <c r="D68" s="28" t="s">
         <v>252</v>
       </c>
@@ -61082,9 +64044,9 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="127"/>
-      <c r="B69" s="131"/>
-      <c r="C69" s="127"/>
+      <c r="A69" s="133"/>
+      <c r="B69" s="138"/>
+      <c r="C69" s="133"/>
       <c r="D69" s="31" t="s">
         <v>254</v>
       </c>
@@ -61096,7 +64058,7 @@
       <c r="A70" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="131" t="s">
+      <c r="B70" s="138" t="s">
         <v>81</v>
       </c>
       <c r="C70" s="31" t="s">
@@ -61110,11 +64072,11 @@
       </c>
     </row>
     <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="127" t="s">
+      <c r="A71" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="131"/>
-      <c r="C71" s="127" t="s">
+      <c r="B71" s="138"/>
+      <c r="C71" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D71" s="40" t="s">
@@ -61125,9 +64087,9 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="127"/>
-      <c r="B72" s="127"/>
-      <c r="C72" s="127"/>
+      <c r="A72" s="133"/>
+      <c r="B72" s="133"/>
+      <c r="C72" s="133"/>
       <c r="D72" s="30" t="s">
         <v>242</v>
       </c>
@@ -61136,9 +64098,9 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="127"/>
-      <c r="B73" s="127"/>
-      <c r="C73" s="127"/>
+      <c r="A73" s="133"/>
+      <c r="B73" s="133"/>
+      <c r="C73" s="133"/>
       <c r="D73" s="30" t="s">
         <v>244</v>
       </c>
@@ -61147,9 +64109,9 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="127"/>
-      <c r="B74" s="127"/>
-      <c r="C74" s="127"/>
+      <c r="A74" s="133"/>
+      <c r="B74" s="133"/>
+      <c r="C74" s="133"/>
       <c r="D74" s="30" t="s">
         <v>246</v>
       </c>
@@ -61158,16 +64120,16 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="127"/>
-      <c r="B75" s="127"/>
-      <c r="C75" s="127"/>
+      <c r="A75" s="133"/>
+      <c r="B75" s="133"/>
+      <c r="C75" s="133"/>
       <c r="D75" s="28"/>
       <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="127"/>
-      <c r="B76" s="131"/>
-      <c r="C76" s="127"/>
+      <c r="A76" s="133"/>
+      <c r="B76" s="138"/>
+      <c r="C76" s="133"/>
       <c r="D76" s="31" t="s">
         <v>248</v>
       </c>
@@ -61176,11 +64138,11 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="127" t="s">
+      <c r="A77" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="131"/>
-      <c r="C77" s="127" t="s">
+      <c r="B77" s="138"/>
+      <c r="C77" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D77" s="28" t="s">
@@ -61191,9 +64153,9 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="127"/>
-      <c r="B78" s="127"/>
-      <c r="C78" s="127"/>
+      <c r="A78" s="133"/>
+      <c r="B78" s="133"/>
+      <c r="C78" s="133"/>
       <c r="D78" s="28" t="s">
         <v>252</v>
       </c>
@@ -61202,9 +64164,9 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="127"/>
-      <c r="B79" s="131"/>
-      <c r="C79" s="127"/>
+      <c r="A79" s="133"/>
+      <c r="B79" s="138"/>
+      <c r="C79" s="133"/>
       <c r="D79" s="31" t="s">
         <v>254</v>
       </c>
@@ -61213,13 +64175,13 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="127" t="s">
+      <c r="A80" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="127" t="s">
+      <c r="B80" s="133" t="s">
         <v>258</v>
       </c>
-      <c r="C80" s="127"/>
+      <c r="C80" s="133"/>
       <c r="D80" s="28" t="s">
         <v>259</v>
       </c>
@@ -61228,9 +64190,9 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="127"/>
-      <c r="B81" s="127"/>
-      <c r="C81" s="127"/>
+      <c r="A81" s="133"/>
+      <c r="B81" s="133"/>
+      <c r="C81" s="133"/>
       <c r="D81" s="28" t="s">
         <v>261</v>
       </c>
@@ -61239,9 +64201,9 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="127"/>
-      <c r="B82" s="127"/>
-      <c r="C82" s="127"/>
+      <c r="A82" s="133"/>
+      <c r="B82" s="133"/>
+      <c r="C82" s="133"/>
       <c r="D82" s="28" t="s">
         <v>263</v>
       </c>
@@ -61250,9 +64212,9 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="127"/>
-      <c r="B83" s="127"/>
-      <c r="C83" s="127"/>
+      <c r="A83" s="133"/>
+      <c r="B83" s="133"/>
+      <c r="C83" s="133"/>
       <c r="D83" s="28" t="s">
         <v>265</v>
       </c>
@@ -61261,9 +64223,9 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="127"/>
-      <c r="B84" s="127"/>
-      <c r="C84" s="127"/>
+      <c r="A84" s="133"/>
+      <c r="B84" s="133"/>
+      <c r="C84" s="133"/>
       <c r="D84" s="28" t="s">
         <v>267</v>
       </c>
@@ -61272,9 +64234,9 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="127"/>
-      <c r="B85" s="127"/>
-      <c r="C85" s="127"/>
+      <c r="A85" s="133"/>
+      <c r="B85" s="133"/>
+      <c r="C85" s="133"/>
       <c r="D85" s="31" t="s">
         <v>269</v>
       </c>
@@ -61286,10 +64248,10 @@
       <c r="A86" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="127" t="s">
+      <c r="B86" s="133" t="s">
         <v>74</v>
       </c>
-      <c r="C86" s="127"/>
+      <c r="C86" s="133"/>
       <c r="D86" s="31" t="s">
         <v>271</v>
       </c>
@@ -61301,7 +64263,7 @@
       <c r="A87" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B87" s="131" t="s">
+      <c r="B87" s="138" t="s">
         <v>83</v>
       </c>
       <c r="C87" s="31" t="s">
@@ -61315,11 +64277,11 @@
       </c>
     </row>
     <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="127" t="s">
+      <c r="A88" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B88" s="131"/>
-      <c r="C88" s="127" t="s">
+      <c r="B88" s="138"/>
+      <c r="C88" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D88" s="40" t="s">
@@ -61330,9 +64292,9 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="127"/>
-      <c r="B89" s="127"/>
-      <c r="C89" s="127"/>
+      <c r="A89" s="133"/>
+      <c r="B89" s="133"/>
+      <c r="C89" s="133"/>
       <c r="D89" s="30" t="s">
         <v>242</v>
       </c>
@@ -61341,9 +64303,9 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="127"/>
-      <c r="B90" s="127"/>
-      <c r="C90" s="127"/>
+      <c r="A90" s="133"/>
+      <c r="B90" s="133"/>
+      <c r="C90" s="133"/>
       <c r="D90" s="30" t="s">
         <v>244</v>
       </c>
@@ -61352,9 +64314,9 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="127"/>
-      <c r="B91" s="127"/>
-      <c r="C91" s="127"/>
+      <c r="A91" s="133"/>
+      <c r="B91" s="133"/>
+      <c r="C91" s="133"/>
       <c r="D91" s="30" t="s">
         <v>246</v>
       </c>
@@ -61363,16 +64325,16 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="127"/>
-      <c r="B92" s="127"/>
-      <c r="C92" s="127"/>
+      <c r="A92" s="133"/>
+      <c r="B92" s="133"/>
+      <c r="C92" s="133"/>
       <c r="D92" s="28"/>
       <c r="E92" s="30"/>
     </row>
     <row r="93" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="127"/>
-      <c r="B93" s="131"/>
-      <c r="C93" s="127"/>
+      <c r="A93" s="133"/>
+      <c r="B93" s="138"/>
+      <c r="C93" s="133"/>
       <c r="D93" s="31" t="s">
         <v>248</v>
       </c>
@@ -61381,11 +64343,11 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="127" t="s">
+      <c r="A94" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B94" s="131"/>
-      <c r="C94" s="127" t="s">
+      <c r="B94" s="138"/>
+      <c r="C94" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D94" s="28" t="s">
@@ -61396,9 +64358,9 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="127"/>
-      <c r="B95" s="127"/>
-      <c r="C95" s="127"/>
+      <c r="A95" s="133"/>
+      <c r="B95" s="133"/>
+      <c r="C95" s="133"/>
       <c r="D95" s="28" t="s">
         <v>252</v>
       </c>
@@ -61407,9 +64369,9 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="127"/>
-      <c r="B96" s="131"/>
-      <c r="C96" s="127"/>
+      <c r="A96" s="133"/>
+      <c r="B96" s="138"/>
+      <c r="C96" s="133"/>
       <c r="D96" s="31" t="s">
         <v>254</v>
       </c>
@@ -61421,7 +64383,7 @@
       <c r="A97" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B97" s="131" t="s">
+      <c r="B97" s="138" t="s">
         <v>84</v>
       </c>
       <c r="C97" s="31" t="s">
@@ -61435,11 +64397,11 @@
       </c>
     </row>
     <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="127" t="s">
+      <c r="A98" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B98" s="131"/>
-      <c r="C98" s="127" t="s">
+      <c r="B98" s="138"/>
+      <c r="C98" s="133" t="s">
         <v>108</v>
       </c>
       <c r="D98" s="40" t="s">
@@ -61450,9 +64412,9 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="127"/>
-      <c r="B99" s="127"/>
-      <c r="C99" s="127"/>
+      <c r="A99" s="133"/>
+      <c r="B99" s="133"/>
+      <c r="C99" s="133"/>
       <c r="D99" s="30" t="s">
         <v>242</v>
       </c>
@@ -61461,9 +64423,9 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="127"/>
-      <c r="B100" s="127"/>
-      <c r="C100" s="127"/>
+      <c r="A100" s="133"/>
+      <c r="B100" s="133"/>
+      <c r="C100" s="133"/>
       <c r="D100" s="30" t="s">
         <v>244</v>
       </c>
@@ -61472,9 +64434,9 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="127"/>
-      <c r="B101" s="127"/>
-      <c r="C101" s="127"/>
+      <c r="A101" s="133"/>
+      <c r="B101" s="133"/>
+      <c r="C101" s="133"/>
       <c r="D101" s="30" t="s">
         <v>246</v>
       </c>
@@ -61483,16 +64445,16 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="127"/>
-      <c r="B102" s="127"/>
-      <c r="C102" s="127"/>
+      <c r="A102" s="133"/>
+      <c r="B102" s="133"/>
+      <c r="C102" s="133"/>
       <c r="D102" s="28"/>
       <c r="E102" s="30"/>
     </row>
     <row r="103" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="127"/>
-      <c r="B103" s="131"/>
-      <c r="C103" s="127"/>
+      <c r="A103" s="133"/>
+      <c r="B103" s="138"/>
+      <c r="C103" s="133"/>
       <c r="D103" s="31" t="s">
         <v>248</v>
       </c>
@@ -61501,11 +64463,11 @@
       </c>
     </row>
     <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="127" t="s">
+      <c r="A104" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B104" s="131"/>
-      <c r="C104" s="127" t="s">
+      <c r="B104" s="138"/>
+      <c r="C104" s="133" t="s">
         <v>109</v>
       </c>
       <c r="D104" s="28" t="s">
@@ -61516,9 +64478,9 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="127"/>
-      <c r="B105" s="127"/>
-      <c r="C105" s="127"/>
+      <c r="A105" s="133"/>
+      <c r="B105" s="133"/>
+      <c r="C105" s="133"/>
       <c r="D105" s="28" t="s">
         <v>252</v>
       </c>
@@ -61527,9 +64489,9 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="127"/>
-      <c r="B106" s="131"/>
-      <c r="C106" s="127"/>
+      <c r="A106" s="133"/>
+      <c r="B106" s="138"/>
+      <c r="C106" s="133"/>
       <c r="D106" s="31" t="s">
         <v>254</v>
       </c>
@@ -61541,10 +64503,10 @@
       <c r="A107" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B107" s="127" t="s">
+      <c r="B107" s="133" t="s">
         <v>273</v>
       </c>
-      <c r="C107" s="127"/>
+      <c r="C107" s="133"/>
       <c r="D107" s="31" t="s">
         <v>274</v>
       </c>
@@ -61556,10 +64518,10 @@
       <c r="A108" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B108" s="127" t="s">
+      <c r="B108" s="133" t="s">
         <v>276</v>
       </c>
-      <c r="C108" s="127"/>
+      <c r="C108" s="133"/>
       <c r="D108" s="31" t="s">
         <v>277</v>
       </c>
@@ -61571,10 +64533,10 @@
       <c r="A109" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B109" s="127" t="s">
+      <c r="B109" s="133" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="127"/>
+      <c r="C109" s="133"/>
       <c r="D109" s="31" t="s">
         <v>280</v>
       </c>
@@ -61583,13 +64545,13 @@
       </c>
     </row>
     <row r="110" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="127" t="s">
+      <c r="A110" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B110" s="130" t="s">
+      <c r="B110" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="130"/>
+      <c r="C110" s="139"/>
       <c r="D110" s="39" t="s">
         <v>282</v>
       </c>
@@ -61598,16 +64560,16 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="127"/>
-      <c r="B111" s="130"/>
-      <c r="C111" s="130"/>
+      <c r="A111" s="133"/>
+      <c r="B111" s="139"/>
+      <c r="C111" s="139"/>
       <c r="D111" s="41"/>
       <c r="E111" s="30"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="127"/>
-      <c r="B112" s="130"/>
-      <c r="C112" s="130"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="139"/>
+      <c r="C112" s="139"/>
       <c r="D112" s="42" t="s">
         <v>284</v>
       </c>
@@ -61616,9 +64578,9 @@
       </c>
     </row>
     <row r="113" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A113" s="127"/>
-      <c r="B113" s="130"/>
-      <c r="C113" s="130"/>
+      <c r="A113" s="133"/>
+      <c r="B113" s="139"/>
+      <c r="C113" s="139"/>
       <c r="D113" s="42" t="s">
         <v>286</v>
       </c>
@@ -61627,9 +64589,9 @@
       </c>
     </row>
     <row r="114" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A114" s="127"/>
-      <c r="B114" s="130"/>
-      <c r="C114" s="130"/>
+      <c r="A114" s="133"/>
+      <c r="B114" s="139"/>
+      <c r="C114" s="139"/>
       <c r="D114" s="42" t="s">
         <v>288</v>
       </c>
@@ -61638,9 +64600,9 @@
       </c>
     </row>
     <row r="115" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A115" s="127"/>
-      <c r="B115" s="130"/>
-      <c r="C115" s="130"/>
+      <c r="A115" s="133"/>
+      <c r="B115" s="139"/>
+      <c r="C115" s="139"/>
       <c r="D115" s="43" t="s">
         <v>290</v>
       </c>
@@ -61686,10 +64648,10 @@
       <c r="A118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="129" t="s">
+      <c r="B118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="C118" s="129"/>
+      <c r="C118" s="140"/>
       <c r="D118" s="46" t="s">
         <v>296</v>
       </c>
@@ -61950,10 +64912,10 @@
       <c r="IW118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="IX118" s="129" t="s">
+      <c r="IX118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="IY118" s="129"/>
+      <c r="IY118" s="140"/>
       <c r="IZ118" s="46" t="s">
         <v>296</v>
       </c>
@@ -62214,10 +65176,10 @@
       <c r="SS118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ST118" s="129" t="s">
+      <c r="ST118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="SU118" s="129"/>
+      <c r="SU118" s="140"/>
       <c r="SV118" s="46" t="s">
         <v>296</v>
       </c>
@@ -62478,10 +65440,10 @@
       <c r="ACO118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ACP118" s="129" t="s">
+      <c r="ACP118" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="ACQ118" s="129"/>
+      <c r="ACQ118" s="140"/>
       <c r="ACR118" s="46" t="s">
         <v>296</v>
       </c>
@@ -62744,10 +65706,10 @@
       <c r="A119" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B119" s="127" t="s">
+      <c r="B119" s="133" t="s">
         <v>298</v>
       </c>
-      <c r="C119" s="127"/>
+      <c r="C119" s="133"/>
       <c r="D119" s="31" t="s">
         <v>299</v>
       </c>
@@ -62759,7 +65721,7 @@
       <c r="A120" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B120" s="127" t="s">
+      <c r="B120" s="133" t="s">
         <v>301</v>
       </c>
       <c r="C120" s="31" t="s">
@@ -62776,7 +65738,7 @@
       <c r="A121" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B121" s="127"/>
+      <c r="B121" s="133"/>
       <c r="C121" s="31" t="s">
         <v>102</v>
       </c>
@@ -62791,10 +65753,10 @@
       <c r="A122" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B122" s="127" t="s">
+      <c r="B122" s="133" t="s">
         <v>306</v>
       </c>
-      <c r="C122" s="127"/>
+      <c r="C122" s="133"/>
       <c r="D122" s="31" t="s">
         <v>307</v>
       </c>
@@ -62806,10 +65768,10 @@
       <c r="A123" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B123" s="127" t="s">
+      <c r="B123" s="133" t="s">
         <v>72</v>
       </c>
-      <c r="C123" s="127"/>
+      <c r="C123" s="133"/>
       <c r="D123" s="31" t="s">
         <v>309</v>
       </c>
@@ -62821,10 +65783,10 @@
       <c r="A124" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B124" s="128" t="s">
+      <c r="B124" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="C124" s="128"/>
+      <c r="C124" s="134"/>
       <c r="D124" s="27" t="s">
         <v>311</v>
       </c>
@@ -62836,10 +65798,10 @@
       <c r="A125" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B125" s="127" t="s">
+      <c r="B125" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="C125" s="127"/>
+      <c r="C125" s="133"/>
       <c r="D125" s="27" t="s">
         <v>313</v>
       </c>
@@ -62851,10 +65813,10 @@
       <c r="A126" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="127" t="s">
+      <c r="B126" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="C126" s="127"/>
+      <c r="C126" s="133"/>
       <c r="D126" s="27" t="s">
         <v>315</v>
       </c>
@@ -62866,10 +65828,10 @@
       <c r="A127" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B127" s="127" t="s">
+      <c r="B127" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="C127" s="127"/>
+      <c r="C127" s="133"/>
       <c r="D127" s="27" t="s">
         <v>317</v>
       </c>
@@ -62878,13 +65840,13 @@
       </c>
     </row>
     <row r="128" spans="1:1024" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="127" t="s">
+      <c r="A128" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="B128" s="127" t="s">
+      <c r="B128" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="C128" s="127"/>
+      <c r="C128" s="133"/>
       <c r="D128" s="28" t="s">
         <v>319</v>
       </c>
@@ -62893,16 +65855,16 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="127"/>
-      <c r="B129" s="127"/>
-      <c r="C129" s="127"/>
+      <c r="A129" s="133"/>
+      <c r="B129" s="133"/>
+      <c r="C129" s="133"/>
       <c r="D129" s="28"/>
       <c r="E129" s="30"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="127"/>
-      <c r="B130" s="127"/>
-      <c r="C130" s="127"/>
+      <c r="A130" s="133"/>
+      <c r="B130" s="133"/>
+      <c r="C130" s="133"/>
       <c r="D130" s="28" t="s">
         <v>321</v>
       </c>
@@ -62911,9 +65873,9 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="127"/>
-      <c r="B131" s="127"/>
-      <c r="C131" s="127"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="133"/>
+      <c r="C131" s="133"/>
       <c r="D131" s="28" t="s">
         <v>323</v>
       </c>
@@ -62922,9 +65884,9 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="127"/>
-      <c r="B132" s="127"/>
-      <c r="C132" s="127"/>
+      <c r="A132" s="133"/>
+      <c r="B132" s="133"/>
+      <c r="C132" s="133"/>
       <c r="D132" s="28" t="s">
         <v>325</v>
       </c>
@@ -62933,9 +65895,9 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="127"/>
-      <c r="B133" s="127"/>
-      <c r="C133" s="127"/>
+      <c r="A133" s="133"/>
+      <c r="B133" s="133"/>
+      <c r="C133" s="133"/>
       <c r="D133" s="31" t="s">
         <v>327</v>
       </c>
@@ -62947,10 +65909,10 @@
       <c r="A134" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="127" t="s">
+      <c r="B134" s="133" t="s">
         <v>89</v>
       </c>
-      <c r="C134" s="127"/>
+      <c r="C134" s="133"/>
       <c r="D134" s="31" t="s">
         <v>329</v>
       </c>
@@ -62962,10 +65924,10 @@
       <c r="A135" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B135" s="127" t="s">
+      <c r="B135" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="C135" s="127"/>
+      <c r="C135" s="133"/>
       <c r="D135" s="31" t="s">
         <v>331</v>
       </c>
@@ -62977,10 +65939,10 @@
       <c r="A136" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B136" s="127" t="s">
+      <c r="B136" s="133" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="127"/>
+      <c r="C136" s="133"/>
       <c r="D136" s="31" t="s">
         <v>334</v>
       </c>
@@ -62992,10 +65954,10 @@
       <c r="A137" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B137" s="127" t="s">
+      <c r="B137" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="C137" s="127"/>
+      <c r="C137" s="133"/>
       <c r="D137" s="31" t="s">
         <v>336</v>
       </c>
@@ -63007,10 +65969,10 @@
       <c r="A138" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B138" s="127" t="s">
+      <c r="B138" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="C138" s="127"/>
+      <c r="C138" s="133"/>
       <c r="D138" s="31" t="s">
         <v>338</v>
       </c>
@@ -63019,12 +65981,12 @@
       </c>
     </row>
     <row r="140" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="128" t="s">
+      <c r="A140" s="134" t="s">
         <v>340</v>
       </c>
-      <c r="B140" s="128"/>
-      <c r="C140" s="128"/>
-      <c r="D140" s="128"/>
+      <c r="B140" s="134"/>
+      <c r="C140" s="134"/>
+      <c r="D140" s="134"/>
       <c r="E140" s="27" t="s">
         <v>341</v>
       </c>
@@ -63036,21 +65998,55 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="B5:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A23:A36"/>
-    <mergeCell ref="B23:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="A128:A133"/>
+    <mergeCell ref="B128:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="IX118:IY118"/>
+    <mergeCell ref="ST118:SU118"/>
+    <mergeCell ref="ACP118:ACQ118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="A110:A115"/>
+    <mergeCell ref="B110:C115"/>
+    <mergeCell ref="B97:B106"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="C98:C103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="B80:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:B96"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="B70:B79"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:B69"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="C67:C69"/>
     <mergeCell ref="A40:A44"/>
     <mergeCell ref="B40:C44"/>
     <mergeCell ref="B45:C45"/>
@@ -63059,55 +66055,21 @@
     <mergeCell ref="C50:C55"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="C56:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:B69"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="B70:B79"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="C71:C76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="A80:A85"/>
-    <mergeCell ref="B80:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:B96"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="A94:A96"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="B97:B106"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="C98:C103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="A110:A115"/>
-    <mergeCell ref="B110:C115"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="IX118:IY118"/>
-    <mergeCell ref="ST118:SU118"/>
-    <mergeCell ref="ACP118:ACQ118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="A128:A133"/>
-    <mergeCell ref="B128:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="A23:A36"/>
+    <mergeCell ref="B23:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="B5:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/zero-data/io_lists/ZERO mocked IO-List.xlsx
+++ b/zero-data/io_lists/ZERO mocked IO-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\Git\zero\zero-data\io_lists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494725B5-9FCC-4DB1-B2FD-6C30BA26320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467AB19F-8C20-4B43-9D1C-456950F82989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-8475" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rev" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Internal lists" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IO-List'!$A$1:$BV$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IO-List'!$A$1:$BV$161</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="772">
   <si>
     <t>Revision</t>
   </si>
@@ -1568,18 +1568,12 @@
     <t>Shore power Total Power Factor</t>
   </si>
   <si>
-    <t>Shore</t>
-  </si>
-  <si>
     <t>SHORE1_Total_Active_Power</t>
   </si>
   <si>
     <t>SHORE1_Total_Power_Factor</t>
   </si>
   <si>
-    <t>Hydro</t>
-  </si>
-  <si>
     <t>HYDRO1_Total_Active_Power</t>
   </si>
   <si>
@@ -2382,6 +2376,90 @@
   </si>
   <si>
     <t>FWD Thruster SB Helm Master/Slave</t>
+  </si>
+  <si>
+    <t>Hydrogeneration</t>
+  </si>
+  <si>
+    <t>Shore power</t>
+  </si>
+  <si>
+    <t>ExternalMotor</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>GearboxOilTemperature</t>
+  </si>
+  <si>
+    <t>Aradex1Temperature</t>
+  </si>
+  <si>
+    <t>Aradex2Temperature</t>
+  </si>
+  <si>
+    <t>AftThrusterTemperatureIn</t>
+  </si>
+  <si>
+    <t>AftThrusterTemperatureOut</t>
+  </si>
+  <si>
+    <t>FwdThrusterTemperatureIn</t>
+  </si>
+  <si>
+    <t>FwdThrusterTemperatureOut</t>
+  </si>
+  <si>
+    <t>Aradex1TemperatureIn</t>
+  </si>
+  <si>
+    <t>Aradex1TemperatureOut</t>
+  </si>
+  <si>
+    <t>Aradex2TemperatureIn</t>
+  </si>
+  <si>
+    <t>Aradex2TemperatureOut</t>
+  </si>
+  <si>
+    <t>OilTemperatureIn</t>
+  </si>
+  <si>
+    <t>OilTemperatureOut</t>
+  </si>
+  <si>
+    <t>AftThrusterFlow</t>
+  </si>
+  <si>
+    <t>AftThrusterPressure</t>
+  </si>
+  <si>
+    <t>FwdThrusterFlow</t>
+  </si>
+  <si>
+    <t>FwdThrusterPressure</t>
+  </si>
+  <si>
+    <t>Aradex1Flow</t>
+  </si>
+  <si>
+    <t>Aradex1Pressure</t>
+  </si>
+  <si>
+    <t>Aradex2Flow</t>
+  </si>
+  <si>
+    <t>Aradex2Pressure</t>
+  </si>
+  <si>
+    <t>OilFlow</t>
+  </si>
+  <si>
+    <t>OilPressure</t>
   </si>
 </sst>
 </file>
@@ -3270,24 +3348,20 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
@@ -3296,6 +3370,7 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3314,24 +3389,33 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3342,13 +3426,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4429,7 +4507,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BV8785"/>
+  <dimension ref="A1:BV8781"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="51" customWidth="1"/>
@@ -4505,197 +4583,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" s="16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="112" t="s">
+      <c r="B1" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="112" t="s">
+      <c r="C1" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="112" t="s">
+      <c r="D1" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="112" t="s">
+      <c r="F1" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="112" t="s">
+      <c r="G1" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="116" t="s">
+      <c r="H1" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="118" t="s">
+      <c r="J1" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="113" t="s">
+      <c r="K1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="114" t="s">
+      <c r="L1" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="115"/>
-      <c r="N1" s="112" t="s">
+      <c r="M1" s="130"/>
+      <c r="N1" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="112" t="s">
+      <c r="O1" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="112" t="s">
+      <c r="P1" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="112" t="s">
+      <c r="Q1" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="112" t="s">
+      <c r="R1" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="112" t="s">
+      <c r="S1" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="120" t="s">
+      <c r="T1" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="122" t="s">
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="121" t="s">
         <v>438</v>
       </c>
-      <c r="X1" s="123"/>
-      <c r="Y1" s="123"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="121" t="s">
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="125" t="s">
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="118" t="s">
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="120" t="s">
         <v>66</v>
       </c>
-      <c r="AL1" s="118" t="s">
+      <c r="AL1" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="AM1" s="119" t="s">
+      <c r="AM1" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="127"/>
-      <c r="AP1" s="127"/>
-      <c r="AQ1" s="127"/>
-      <c r="AR1" s="127"/>
-      <c r="AS1" s="112" t="s">
+      <c r="AO1" s="126"/>
+      <c r="AP1" s="126"/>
+      <c r="AQ1" s="126"/>
+      <c r="AR1" s="126"/>
+      <c r="AS1" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="AT1" s="112" t="s">
+      <c r="AT1" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="AU1" s="112" t="s">
+      <c r="AU1" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="AV1" s="112" t="s">
+      <c r="AV1" s="111" t="s">
         <v>73</v>
       </c>
-      <c r="AW1" s="126" t="s">
+      <c r="AW1" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="AX1" s="130" t="s">
+      <c r="AX1" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="AY1" s="116" t="s">
+      <c r="AY1" s="115" t="s">
         <v>76</v>
       </c>
-      <c r="AZ1" s="116" t="s">
+      <c r="AZ1" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="BA1" s="116" t="s">
+      <c r="BA1" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="BB1" s="116" t="s">
+      <c r="BB1" s="115" t="s">
         <v>79</v>
       </c>
-      <c r="BC1" s="129" t="s">
+      <c r="BC1" s="113" t="s">
         <v>80</v>
       </c>
-      <c r="BD1" s="129"/>
-      <c r="BE1" s="129"/>
-      <c r="BF1" s="129" t="s">
+      <c r="BD1" s="113"/>
+      <c r="BE1" s="113"/>
+      <c r="BF1" s="113" t="s">
         <v>81</v>
       </c>
-      <c r="BG1" s="129"/>
-      <c r="BH1" s="129"/>
-      <c r="BI1" s="129" t="s">
+      <c r="BG1" s="113"/>
+      <c r="BH1" s="113"/>
+      <c r="BI1" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="BJ1" s="129"/>
-      <c r="BK1" s="129"/>
-      <c r="BL1" s="129" t="s">
+      <c r="BJ1" s="113"/>
+      <c r="BK1" s="113"/>
+      <c r="BL1" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="BM1" s="129"/>
-      <c r="BN1" s="129"/>
-      <c r="BO1" s="129" t="s">
+      <c r="BM1" s="113"/>
+      <c r="BN1" s="113"/>
+      <c r="BO1" s="113" t="s">
         <v>84</v>
       </c>
-      <c r="BP1" s="129"/>
-      <c r="BQ1" s="129"/>
-      <c r="BR1" s="119" t="s">
+      <c r="BP1" s="113"/>
+      <c r="BQ1" s="113"/>
+      <c r="BR1" s="117" t="s">
         <v>85</v>
       </c>
-      <c r="BS1" s="116" t="s">
+      <c r="BS1" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="BT1" s="131" t="s">
+      <c r="BT1" s="116" t="s">
         <v>87</v>
       </c>
-      <c r="BU1" s="128" t="s">
+      <c r="BU1" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="BV1" s="128" t="s">
+      <c r="BV1" s="112" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:74" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="113"/>
+      <c r="A2" s="131"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="128"/>
       <c r="L2" s="97" t="s">
         <v>93</v>
       </c>
       <c r="M2" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
       <c r="T2" s="17" t="s">
         <v>90</v>
       </c>
@@ -4747,9 +4825,9 @@
       <c r="AJ2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="118"/>
-      <c r="AL2" s="118"/>
-      <c r="AM2" s="119"/>
+      <c r="AK2" s="120"/>
+      <c r="AL2" s="120"/>
+      <c r="AM2" s="117"/>
       <c r="AN2" s="18" t="s">
         <v>103</v>
       </c>
@@ -4765,16 +4843,16 @@
       <c r="AR2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="AS2" s="112"/>
-      <c r="AT2" s="112"/>
-      <c r="AU2" s="112"/>
-      <c r="AV2" s="112"/>
-      <c r="AW2" s="126"/>
-      <c r="AX2" s="130"/>
-      <c r="AY2" s="116"/>
-      <c r="AZ2" s="116"/>
-      <c r="BA2" s="116"/>
-      <c r="BB2" s="116"/>
+      <c r="AS2" s="111"/>
+      <c r="AT2" s="111"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
+      <c r="AW2" s="125"/>
+      <c r="AX2" s="114"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
+      <c r="BB2" s="115"/>
       <c r="BC2" s="21" t="s">
         <v>56</v>
       </c>
@@ -4820,15 +4898,15 @@
       <c r="BQ2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="BR2" s="119"/>
-      <c r="BS2" s="116"/>
-      <c r="BT2" s="131"/>
-      <c r="BU2" s="128"/>
-      <c r="BV2" s="128"/>
+      <c r="BR2" s="117"/>
+      <c r="BS2" s="115"/>
+      <c r="BT2" s="116"/>
+      <c r="BU2" s="112"/>
+      <c r="BV2" s="112"/>
     </row>
     <row r="3" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B3" s="52"/>
       <c r="C3" s="7" t="s">
@@ -4925,7 +5003,7 @@
     </row>
     <row r="4" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B4" s="52"/>
       <c r="C4" s="7" t="s">
@@ -5022,7 +5100,7 @@
     </row>
     <row r="5" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="7" t="s">
@@ -5119,7 +5197,7 @@
     </row>
     <row r="6" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B6" s="52"/>
       <c r="C6" s="7" t="s">
@@ -5216,7 +5294,7 @@
     </row>
     <row r="7" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B7" s="52"/>
       <c r="C7" s="7" t="s">
@@ -5313,7 +5391,7 @@
     </row>
     <row r="8" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B8" s="52"/>
       <c r="C8" s="7" t="s">
@@ -5410,14 +5488,14 @@
     </row>
     <row r="9" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>474</v>
+        <v>745</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="55"/>
@@ -5427,7 +5505,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K9" s="102" t="s">
         <v>377</v>
@@ -5437,7 +5515,7 @@
         <v>1000</v>
       </c>
       <c r="N9" s="60" t="s">
-        <v>474</v>
+        <v>745</v>
       </c>
       <c r="O9" s="88"/>
       <c r="P9" s="60" t="s">
@@ -5455,8 +5533,8 @@
       </c>
       <c r="X9" s="103"/>
       <c r="Y9" s="6" t="str">
-        <f>"marpower/shore/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P9, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
-        <v>marpower/shore/shore-power</v>
+        <f>"marpower/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P9, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
+        <v>marpower/shore-power</v>
       </c>
       <c r="Z9" s="64" t="str" cm="1">
         <f t="array" ref="Z9">IF(COUNTIF(N9,"spare"),"","$."&amp;_xlfn.REGEXEXTRACT(J9,"SHORE\d+_(.*)", 2))</f>
@@ -5507,14 +5585,14 @@
     </row>
     <row r="10" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B10" s="52"/>
       <c r="C10" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>474</v>
+        <v>745</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="55"/>
@@ -5524,7 +5602,7 @@
         <v>110</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K10" s="102" t="s">
         <v>377</v>
@@ -5534,7 +5612,7 @@
         <v>1000</v>
       </c>
       <c r="N10" s="60" t="s">
-        <v>474</v>
+        <v>745</v>
       </c>
       <c r="O10" s="88"/>
       <c r="P10" s="60" t="s">
@@ -5552,8 +5630,8 @@
       </c>
       <c r="X10" s="103"/>
       <c r="Y10" s="6" t="str">
-        <f>"marpower/shore/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P10, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
-        <v>marpower/shore/shore-power</v>
+        <f>"marpower/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P10, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
+        <v>marpower/shore-power</v>
       </c>
       <c r="Z10" s="64" t="str" cm="1">
         <f t="array" ref="Z10">IF(COUNTIF(N10,"spare"),"","$."&amp;_xlfn.REGEXEXTRACT(J10,"SHORE\d+_(.*)", 2))</f>
@@ -5604,14 +5682,14 @@
     </row>
     <row r="11" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B11" s="52"/>
       <c r="C11" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="55"/>
@@ -5621,7 +5699,7 @@
         <v>110</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K11" s="102" t="s">
         <v>377</v>
@@ -5631,11 +5709,11 @@
         <v>1000</v>
       </c>
       <c r="N11" s="60" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="O11" s="88"/>
       <c r="P11" s="60" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="Q11" s="60"/>
       <c r="R11" s="60"/>
@@ -5649,8 +5727,8 @@
       </c>
       <c r="X11" s="103"/>
       <c r="Y11" s="6" t="str">
-        <f>"marpower/hydro/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P11, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
-        <v>marpower/hydro/thruster1</v>
+        <f>"marpower/hydrogeneration/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P11, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
+        <v>marpower/hydrogeneration/thruster1</v>
       </c>
       <c r="Z11" s="64" t="str" cm="1">
         <f t="array" ref="Z11">IF(COUNTIF(N11,"spare"),"","$."&amp;_xlfn.REGEXEXTRACT(J11,"HYDRO\d+_(.*)", 2))</f>
@@ -5701,14 +5779,14 @@
     </row>
     <row r="12" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B12" s="52"/>
       <c r="C12" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="55"/>
@@ -5718,7 +5796,7 @@
         <v>110</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K12" s="102" t="s">
         <v>377</v>
@@ -5728,11 +5806,11 @@
         <v>1000</v>
       </c>
       <c r="N12" s="60" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="O12" s="88"/>
       <c r="P12" s="60" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q12" s="60"/>
       <c r="R12" s="60"/>
@@ -5746,8 +5824,8 @@
       </c>
       <c r="X12" s="103"/>
       <c r="Y12" s="6" t="str">
-        <f>"marpower/hydro/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P12, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
-        <v>marpower/hydro/thruster1</v>
+        <f>"marpower/hydrogeneration/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P12, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
+        <v>marpower/hydrogeneration/thruster1</v>
       </c>
       <c r="Z12" s="64" t="str" cm="1">
         <f t="array" ref="Z12">IF(COUNTIF(N12,"spare"),"","$."&amp;_xlfn.REGEXEXTRACT(J12,"HYDRO\d+_(.*)", 2))</f>
@@ -5798,14 +5876,14 @@
     </row>
     <row r="13" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B13" s="52"/>
       <c r="C13" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="55"/>
@@ -5815,7 +5893,7 @@
         <v>110</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K13" s="102" t="s">
         <v>377</v>
@@ -5825,11 +5903,11 @@
         <v>1000</v>
       </c>
       <c r="N13" s="60" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="O13" s="88"/>
       <c r="P13" s="60" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Q13" s="60"/>
       <c r="R13" s="60"/>
@@ -5843,8 +5921,8 @@
       </c>
       <c r="X13" s="103"/>
       <c r="Y13" s="6" t="str">
-        <f>"marpower/hydro/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P13, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
-        <v>marpower/hydro/thruster2</v>
+        <f>"marpower/hydrogeneration/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P13, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
+        <v>marpower/hydrogeneration/thruster2</v>
       </c>
       <c r="Z13" s="64" t="str" cm="1">
         <f t="array" ref="Z13">IF(COUNTIF(N13,"spare"),"","$."&amp;_xlfn.REGEXEXTRACT(J13,"HYDRO\d+_(.*)", 2))</f>
@@ -5895,14 +5973,14 @@
     </row>
     <row r="14" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B14" s="52"/>
       <c r="C14" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="55"/>
@@ -5912,7 +5990,7 @@
         <v>110</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="K14" s="102" t="s">
         <v>377</v>
@@ -5922,11 +6000,11 @@
         <v>1000</v>
       </c>
       <c r="N14" s="60" t="s">
-        <v>477</v>
+        <v>744</v>
       </c>
       <c r="O14" s="88"/>
       <c r="P14" s="60" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q14" s="60"/>
       <c r="R14" s="60"/>
@@ -5940,8 +6018,8 @@
       </c>
       <c r="X14" s="103"/>
       <c r="Y14" s="6" t="str">
-        <f>"marpower/hydro/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P14, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
-        <v>marpower/hydro/thruster2</v>
+        <f>"marpower/hydrogeneration/" &amp; LOWER(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(TRIM(_xlfn.REGEXREPLACE(P14, " (RMS (Current|Voltage) .+)|(Active Power Phase [ABC])|(Total Active Power)|(Power Factor .+)|(Total Power Factor) *", "")), "[ /\(\)&amp;:\.#]", "-"), "\-+", "-"), "-$", ""))</f>
+        <v>marpower/hydrogeneration/thruster2</v>
       </c>
       <c r="Z14" s="64" t="str" cm="1">
         <f t="array" ref="Z14">IF(COUNTIF(N14,"spare"),"","$."&amp;_xlfn.REGEXEXTRACT(J14,"HYDRO\d+_(.*)", 2))</f>
@@ -5992,14 +6070,14 @@
     </row>
     <row r="15" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B15" s="52"/>
       <c r="C15" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="55"/>
@@ -6009,7 +6087,7 @@
         <v>110</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K15" s="102" t="s">
         <v>377</v>
@@ -6019,11 +6097,11 @@
         <v>1000</v>
       </c>
       <c r="N15" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O15" s="88"/>
       <c r="P15" s="60" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q15" s="60"/>
       <c r="R15" s="60"/>
@@ -6089,14 +6167,14 @@
     </row>
     <row r="16" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B16" s="52"/>
       <c r="C16" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="55"/>
@@ -6106,7 +6184,7 @@
         <v>110</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K16" s="102" t="s">
         <v>377</v>
@@ -6116,11 +6194,11 @@
         <v>1000</v>
       </c>
       <c r="N16" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O16" s="88"/>
       <c r="P16" s="60" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q16" s="60"/>
       <c r="R16" s="60"/>
@@ -6186,14 +6264,14 @@
     </row>
     <row r="17" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B17" s="52"/>
       <c r="C17" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="55"/>
@@ -6203,7 +6281,7 @@
         <v>110</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K17" s="102" t="s">
         <v>377</v>
@@ -6213,11 +6291,11 @@
         <v>1000</v>
       </c>
       <c r="N17" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O17" s="88"/>
       <c r="P17" s="60" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Q17" s="60"/>
       <c r="R17" s="60"/>
@@ -6283,14 +6361,14 @@
     </row>
     <row r="18" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B18" s="52"/>
       <c r="C18" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="55"/>
@@ -6300,7 +6378,7 @@
         <v>110</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K18" s="102" t="s">
         <v>377</v>
@@ -6310,11 +6388,11 @@
         <v>1000</v>
       </c>
       <c r="N18" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O18" s="88"/>
       <c r="P18" s="60" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q18" s="60"/>
       <c r="R18" s="60"/>
@@ -6380,14 +6458,14 @@
     </row>
     <row r="19" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B19" s="52"/>
       <c r="C19" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="55"/>
@@ -6397,7 +6475,7 @@
         <v>110</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K19" s="102" t="s">
         <v>377</v>
@@ -6407,11 +6485,11 @@
         <v>1000</v>
       </c>
       <c r="N19" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O19" s="88"/>
       <c r="P19" s="60" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q19" s="60"/>
       <c r="R19" s="60"/>
@@ -6477,14 +6555,14 @@
     </row>
     <row r="20" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B20" s="52"/>
       <c r="C20" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="55"/>
@@ -6494,7 +6572,7 @@
         <v>110</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="K20" s="102" t="s">
         <v>377</v>
@@ -6504,11 +6582,11 @@
         <v>1000</v>
       </c>
       <c r="N20" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O20" s="88"/>
       <c r="P20" s="60" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q20" s="60"/>
       <c r="R20" s="60"/>
@@ -6574,14 +6652,14 @@
     </row>
     <row r="21" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B21" s="52"/>
       <c r="C21" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="55"/>
@@ -6591,7 +6669,7 @@
         <v>110</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K21" s="102" t="s">
         <v>377</v>
@@ -6601,11 +6679,11 @@
         <v>1000</v>
       </c>
       <c r="N21" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O21" s="88"/>
       <c r="P21" s="60" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="Q21" s="60"/>
       <c r="R21" s="60"/>
@@ -6671,14 +6749,14 @@
     </row>
     <row r="22" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B22" s="52"/>
       <c r="C22" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="55"/>
@@ -6688,7 +6766,7 @@
         <v>110</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K22" s="102" t="s">
         <v>377</v>
@@ -6698,11 +6776,11 @@
         <v>1000</v>
       </c>
       <c r="N22" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O22" s="88"/>
       <c r="P22" s="60" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Q22" s="60"/>
       <c r="R22" s="60"/>
@@ -6768,14 +6846,14 @@
     </row>
     <row r="23" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B23" s="52"/>
       <c r="C23" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="55"/>
@@ -6785,7 +6863,7 @@
         <v>110</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K23" s="102" t="s">
         <v>377</v>
@@ -6795,11 +6873,11 @@
         <v>1000</v>
       </c>
       <c r="N23" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O23" s="88"/>
       <c r="P23" s="60" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Q23" s="60"/>
       <c r="R23" s="60"/>
@@ -6865,14 +6943,14 @@
     </row>
     <row r="24" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B24" s="52"/>
       <c r="C24" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="55"/>
@@ -6882,7 +6960,7 @@
         <v>110</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K24" s="102" t="s">
         <v>377</v>
@@ -6892,11 +6970,11 @@
         <v>1000</v>
       </c>
       <c r="N24" s="60" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="O24" s="88"/>
       <c r="P24" s="60" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q24" s="60"/>
       <c r="R24" s="60"/>
@@ -6962,7 +7040,7 @@
     </row>
     <row r="25" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B25" s="52"/>
       <c r="C25" s="7" t="s">
@@ -6977,24 +7055,24 @@
         <v>110</v>
       </c>
       <c r="J25" s="56" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K25" s="57" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="M25" s="10">
         <v>1000</v>
       </c>
       <c r="N25" s="59" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P25" s="59" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="R25" s="60"/>
       <c r="S25" s="62"/>
       <c r="W25" s="65" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="X25" s="104"/>
       <c r="Y25" s="6" t="str">
@@ -7014,22 +7092,22 @@
       <c r="AH25" s="56"/>
       <c r="AI25" s="69"/>
       <c r="AK25" s="68" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AL25" s="68"/>
       <c r="AM25" s="70" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AR25" s="72"/>
       <c r="AT25" s="7"/>
       <c r="AU25" s="7"/>
       <c r="AV25" s="73"/>
       <c r="AW25" s="71" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AX25" s="77"/>
       <c r="BB25" s="81" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="BQ25" s="83"/>
       <c r="BS25" s="6"/>
@@ -7037,7 +7115,7 @@
     </row>
     <row r="26" spans="1:74" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B26" s="52"/>
       <c r="C26" s="7" t="s">
@@ -7052,24 +7130,24 @@
         <v>110</v>
       </c>
       <c r="J26" s="56" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K26" s="57" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="M26" s="10">
         <v>1000</v>
       </c>
       <c r="N26" s="59" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="P26" s="59" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="R26" s="60"/>
       <c r="S26" s="62"/>
       <c r="W26" s="65" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="X26" s="104"/>
       <c r="Y26" s="6" t="str">
@@ -7089,22 +7167,22 @@
       <c r="AH26" s="56"/>
       <c r="AI26" s="69"/>
       <c r="AK26" s="68" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AL26" s="68"/>
       <c r="AM26" s="70" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AR26" s="72"/>
       <c r="AT26" s="7"/>
       <c r="AU26" s="7"/>
       <c r="AV26" s="73"/>
       <c r="AW26" s="71" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AX26" s="77"/>
       <c r="BB26" s="81" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="BQ26" s="83"/>
       <c r="BS26" s="6"/>
@@ -7118,25 +7196,25 @@
         <v>111</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F27" s="55"/>
       <c r="J27" s="109" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K27" s="57"/>
       <c r="N27" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P27" s="107" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="W27" s="65"/>
       <c r="X27" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y27" s="6" t="str">
         <f>"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N27,"spare"),"",IF(X27&lt;&gt;"",X27,N27))," ","-"))</f>
@@ -7155,23 +7233,23 @@
         <v>118</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J28" s="109" t="s">
+        <v>527</v>
+      </c>
+      <c r="N28" s="107" t="s">
+        <v>522</v>
+      </c>
+      <c r="P28" s="107" t="s">
         <v>529</v>
-      </c>
-      <c r="N28" s="107" t="s">
-        <v>524</v>
-      </c>
-      <c r="P28" s="107" t="s">
-        <v>531</v>
       </c>
       <c r="W28" s="65"/>
       <c r="X28" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y28" s="6" t="str">
         <f t="shared" ref="Y28:Y91" si="25">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N28,"spare"),"",IF(X28&lt;&gt;"",X28,N28))," ","-"))</f>
@@ -7190,23 +7268,23 @@
         <v>118</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J29" s="109" t="s">
+        <v>528</v>
+      </c>
+      <c r="N29" s="107" t="s">
+        <v>522</v>
+      </c>
+      <c r="P29" s="107" t="s">
         <v>530</v>
-      </c>
-      <c r="N29" s="107" t="s">
-        <v>524</v>
-      </c>
-      <c r="P29" s="107" t="s">
-        <v>532</v>
       </c>
       <c r="W29" s="65"/>
       <c r="X29" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y29" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7225,23 +7303,23 @@
         <v>118</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J30" s="109" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N30" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P30" s="107" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="W30" s="65"/>
       <c r="X30" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y30" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7260,23 +7338,23 @@
         <v>118</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J31" s="109" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N31" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P31" s="107" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="W31" s="65"/>
       <c r="X31" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y31" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7295,23 +7373,23 @@
         <v>118</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J32" s="109" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="N32" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P32" s="107" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="W32" s="65"/>
       <c r="X32" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y32" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7330,23 +7408,23 @@
         <v>111</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J33" s="110" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N33" s="59" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="W33" s="65"/>
       <c r="X33" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y33" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7365,23 +7443,23 @@
         <v>111</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J34" s="110" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N34" s="59" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P34" s="59" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="W34" s="65"/>
       <c r="X34" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y34" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7400,23 +7478,23 @@
         <v>111</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J35" s="109" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="N35" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P35" s="107" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="W35" s="65"/>
       <c r="X35" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y35" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7435,23 +7513,23 @@
         <v>111</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J36" s="109" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N36" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P36" s="107" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="W36" s="65"/>
       <c r="X36" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y36" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7470,23 +7548,23 @@
         <v>111</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J37" s="109" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="N37" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P37" s="107" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="W37" s="65"/>
       <c r="X37" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y37" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7505,23 +7583,23 @@
         <v>111</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J38" s="109" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="N38" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P38" s="107" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="W38" s="65"/>
       <c r="X38" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y38" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7540,23 +7618,23 @@
         <v>111</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J39" s="109" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N39" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P39" s="107" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="W39" s="65"/>
       <c r="X39" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y39" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7575,23 +7653,23 @@
         <v>111</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J40" s="109" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N40" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P40" s="107" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="W40" s="65"/>
       <c r="X40" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y40" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7610,23 +7688,23 @@
         <v>111</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J41" s="109" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N41" s="107" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P41" s="107" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="W41" s="65"/>
       <c r="X41" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y41" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7645,23 +7723,23 @@
         <v>111</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J42" s="109" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="N42" s="107" t="s">
+        <v>571</v>
+      </c>
+      <c r="P42" s="107" t="s">
         <v>573</v>
-      </c>
-      <c r="P42" s="107" t="s">
-        <v>575</v>
       </c>
       <c r="W42" s="65"/>
       <c r="X42" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y42" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7680,23 +7758,23 @@
         <v>118</v>
       </c>
       <c r="D43" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="J43" s="109" t="s">
         <v>557</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="J43" s="109" t="s">
-        <v>559</v>
-      </c>
       <c r="N43" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P43" s="107" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="W43" s="65"/>
       <c r="X43" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y43" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7715,23 +7793,23 @@
         <v>118</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J44" s="109" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N44" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P44" s="107" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="W44" s="65"/>
       <c r="X44" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y44" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7750,23 +7828,23 @@
         <v>118</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J45" s="109" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="N45" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P45" s="107" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="W45" s="65"/>
       <c r="X45" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y45" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7785,23 +7863,23 @@
         <v>118</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J46" s="109" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N46" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P46" s="107" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="W46" s="65"/>
       <c r="X46" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y46" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7820,23 +7898,23 @@
         <v>118</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J47" s="110" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="N47" s="59" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P47" s="59" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="W47" s="65"/>
       <c r="X47" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y47" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7855,23 +7933,23 @@
         <v>111</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J48" s="110" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N48" s="59" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P48" s="59" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="W48" s="65"/>
       <c r="X48" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y48" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7890,23 +7968,23 @@
         <v>111</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J49" s="110" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N49" s="59" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P49" s="59" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="W49" s="65"/>
       <c r="X49" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y49" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7925,23 +8003,23 @@
         <v>111</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J50" s="109" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N50" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P50" s="107" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="W50" s="65"/>
       <c r="X50" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y50" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7960,23 +8038,23 @@
         <v>111</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J51" s="109" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="N51" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P51" s="107" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="W51" s="65"/>
       <c r="X51" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y51" s="6" t="str">
         <f t="shared" si="25"/>
@@ -7995,23 +8073,23 @@
         <v>111</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J52" s="109" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N52" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P52" s="107" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="W52" s="65"/>
       <c r="X52" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y52" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8030,23 +8108,23 @@
         <v>111</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J53" s="109" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N53" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P53" s="107" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="W53" s="65"/>
       <c r="X53" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y53" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8065,23 +8143,23 @@
         <v>111</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J54" s="109" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N54" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P54" s="107" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="W54" s="65"/>
       <c r="X54" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y54" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8100,23 +8178,23 @@
         <v>111</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J55" s="109" t="s">
+        <v>569</v>
+      </c>
+      <c r="N55" s="107" t="s">
         <v>571</v>
       </c>
-      <c r="N55" s="107" t="s">
-        <v>573</v>
-      </c>
       <c r="P55" s="107" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="W55" s="65"/>
       <c r="X55" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y55" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8135,23 +8213,23 @@
         <v>111</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J56" s="109" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N56" s="107" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P56" s="107" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="W56" s="65"/>
       <c r="X56" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y56" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8170,23 +8248,23 @@
         <v>111</v>
       </c>
       <c r="D57" s="108" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J57" s="109" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="N57" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P57" s="107" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="W57" s="65"/>
       <c r="X57" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y57" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8205,23 +8283,23 @@
         <v>111</v>
       </c>
       <c r="D58" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="J58" s="109" t="s">
         <v>590</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="J58" s="109" t="s">
-        <v>592</v>
-      </c>
       <c r="N58" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P58" s="107" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="W58" s="65"/>
       <c r="X58" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y58" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8240,23 +8318,23 @@
         <v>111</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J59" s="109" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N59" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P59" s="107" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="W59" s="65"/>
       <c r="X59" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y59" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8275,23 +8353,23 @@
         <v>111</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J60" s="109" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="N60" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P60" s="107" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="W60" s="65"/>
       <c r="X60" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y60" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8310,23 +8388,23 @@
         <v>111</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J61" s="109" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="N61" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P61" s="107" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="W61" s="65"/>
       <c r="X61" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y61" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8345,23 +8423,23 @@
         <v>111</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J62" s="109" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N62" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P62" s="107" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="W62" s="65"/>
       <c r="X62" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y62" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8380,23 +8458,23 @@
         <v>111</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J63" s="109" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N63" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P63" s="107" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="W63" s="65"/>
       <c r="X63" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y63" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8415,23 +8493,23 @@
         <v>118</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J64" s="109" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N64" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P64" s="107" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="W64" s="65"/>
       <c r="X64" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y64" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8450,23 +8528,23 @@
         <v>118</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J65" s="109" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N65" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P65" s="107" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="W65" s="65"/>
       <c r="X65" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y65" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8485,23 +8563,23 @@
         <v>118</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J66" s="109" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N66" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P66" s="107" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="W66" s="65"/>
       <c r="X66" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y66" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8520,23 +8598,23 @@
         <v>118</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J67" s="109" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N67" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P67" s="107" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="W67" s="65"/>
       <c r="X67" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y67" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8555,23 +8633,23 @@
         <v>111</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J68" s="109" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N68" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P68" s="107" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="W68" s="65"/>
       <c r="X68" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y68" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8590,23 +8668,23 @@
         <v>111</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J69" s="109" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="N69" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P69" s="107" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="W69" s="65"/>
       <c r="X69" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y69" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8625,23 +8703,23 @@
         <v>111</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J70" s="109" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="N70" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P70" s="107" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="W70" s="65"/>
       <c r="X70" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y70" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8660,23 +8738,23 @@
         <v>111</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J71" s="109" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N71" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P71" s="107" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="W71" s="65"/>
       <c r="X71" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y71" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8695,23 +8773,23 @@
         <v>111</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J72" s="109" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="N72" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P72" s="107" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="W72" s="65"/>
       <c r="X72" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y72" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8730,23 +8808,23 @@
         <v>111</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J73" s="109" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="N73" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P73" s="107" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="W73" s="65"/>
       <c r="X73" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y73" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8765,23 +8843,23 @@
         <v>111</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J74" s="109" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="N74" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P74" s="107" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="W74" s="65"/>
       <c r="X74" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y74" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8800,23 +8878,23 @@
         <v>111</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J75" s="109" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="N75" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P75" s="107" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="W75" s="65"/>
       <c r="X75" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y75" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8835,23 +8913,23 @@
         <v>111</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J76" s="109" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="N76" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P76" s="107" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="W76" s="65"/>
       <c r="X76" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y76" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8870,23 +8948,23 @@
         <v>111</v>
       </c>
       <c r="D77" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="J77" s="109" t="s">
         <v>631</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="J77" s="109" t="s">
-        <v>633</v>
-      </c>
       <c r="N77" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P77" s="107" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="W77" s="65"/>
       <c r="X77" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y77" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8905,23 +8983,23 @@
         <v>111</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J78" s="109" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N78" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P78" s="107" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="W78" s="65"/>
       <c r="X78" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y78" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8940,23 +9018,23 @@
         <v>111</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J79" s="109" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="N79" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P79" s="107" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="W79" s="65"/>
       <c r="X79" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y79" s="6" t="str">
         <f t="shared" si="25"/>
@@ -8975,23 +9053,23 @@
         <v>111</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J80" s="109" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="N80" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P80" s="107" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="W80" s="65"/>
       <c r="X80" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y80" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9010,23 +9088,23 @@
         <v>111</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J81" s="109" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="N81" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P81" s="107" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="W81" s="65"/>
       <c r="X81" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y81" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9045,23 +9123,23 @@
         <v>118</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J82" s="109" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N82" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P82" s="107" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="W82" s="65"/>
       <c r="X82" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y82" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9080,23 +9158,23 @@
         <v>118</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J83" s="109" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="N83" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P83" s="107" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="W83" s="65"/>
       <c r="X83" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y83" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9115,23 +9193,23 @@
         <v>118</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J84" s="109" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="N84" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P84" s="107" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="W84" s="65"/>
       <c r="X84" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y84" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9150,23 +9228,23 @@
         <v>118</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J85" s="109" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="N85" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P85" s="107" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="W85" s="65"/>
       <c r="X85" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y85" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9185,23 +9263,23 @@
         <v>111</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J86" s="109" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="N86" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P86" s="107" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="W86" s="65"/>
       <c r="X86" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y86" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9220,23 +9298,23 @@
         <v>111</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J87" s="109" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="N87" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P87" s="107" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="W87" s="65"/>
       <c r="X87" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y87" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9255,23 +9333,23 @@
         <v>111</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J88" s="109" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N88" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P88" s="107" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="W88" s="65"/>
       <c r="X88" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y88" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9290,23 +9368,23 @@
         <v>111</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J89" s="109" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="N89" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P89" s="107" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="W89" s="65"/>
       <c r="X89" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y89" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9325,23 +9403,23 @@
         <v>111</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J90" s="109" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="N90" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P90" s="107" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="W90" s="65"/>
       <c r="X90" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y90" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9360,23 +9438,23 @@
         <v>111</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J91" s="109" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="N91" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P91" s="107" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="W91" s="65"/>
       <c r="X91" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y91" s="6" t="str">
         <f t="shared" si="25"/>
@@ -9395,26 +9473,26 @@
         <v>111</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J92" s="109" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="N92" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P92" s="107" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="W92" s="65"/>
       <c r="X92" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y92" s="6" t="str">
-        <f t="shared" ref="Y92:Y154" si="28">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N92,"spare"),"",IF(X92&lt;&gt;"",X92,N92))," ","-"))</f>
+        <f t="shared" ref="Y92:Y158" si="28">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N92,"spare"),"",IF(X92&lt;&gt;"",X92,N92))," ","-"))</f>
         <v>marpower/helm-console/sb</v>
       </c>
       <c r="Z92" s="64" t="str">
@@ -9430,17 +9508,17 @@
         <v>111</v>
       </c>
       <c r="E93" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J93" s="11" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="N93" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W93" s="65"/>
       <c r="X93" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y93" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9459,17 +9537,17 @@
         <v>111</v>
       </c>
       <c r="E94" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J94" s="11" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="N94" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W94" s="65"/>
       <c r="X94" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y94" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9488,17 +9566,17 @@
         <v>111</v>
       </c>
       <c r="E95" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="N95" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W95" s="65"/>
       <c r="X95" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y95" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9517,17 +9595,17 @@
         <v>111</v>
       </c>
       <c r="E96" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="N96" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W96" s="65"/>
       <c r="X96" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y96" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9546,17 +9624,17 @@
         <v>118</v>
       </c>
       <c r="E97" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J97" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="N97" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W97" s="65"/>
       <c r="X97" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y97" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9575,17 +9653,17 @@
         <v>118</v>
       </c>
       <c r="E98" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="N98" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W98" s="65"/>
       <c r="X98" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y98" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9604,17 +9682,17 @@
         <v>118</v>
       </c>
       <c r="E99" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J99" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="N99" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W99" s="65"/>
       <c r="X99" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y99" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9633,17 +9711,17 @@
         <v>118</v>
       </c>
       <c r="E100" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="N100" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W100" s="65"/>
       <c r="X100" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y100" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9662,17 +9740,17 @@
         <v>118</v>
       </c>
       <c r="E101" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="N101" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W101" s="65"/>
       <c r="X101" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y101" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9691,17 +9769,17 @@
         <v>118</v>
       </c>
       <c r="E102" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="N102" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W102" s="65"/>
       <c r="X102" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y102" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9720,17 +9798,17 @@
         <v>118</v>
       </c>
       <c r="E103" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="N103" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W103" s="65"/>
       <c r="X103" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y103" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9749,17 +9827,17 @@
         <v>118</v>
       </c>
       <c r="E104" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="N104" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W104" s="65"/>
       <c r="X104" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y104" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9778,17 +9856,17 @@
         <v>118</v>
       </c>
       <c r="E105" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="N105" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W105" s="65"/>
       <c r="X105" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y105" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9807,17 +9885,17 @@
         <v>118</v>
       </c>
       <c r="E106" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J106" s="11" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="N106" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W106" s="65"/>
       <c r="X106" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y106" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9836,17 +9914,17 @@
         <v>118</v>
       </c>
       <c r="E107" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J107" s="11" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N107" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W107" s="65"/>
       <c r="X107" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y107" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9865,17 +9943,17 @@
         <v>118</v>
       </c>
       <c r="E108" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="N108" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W108" s="65"/>
       <c r="X108" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y108" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9894,17 +9972,17 @@
         <v>118</v>
       </c>
       <c r="E109" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J109" s="11" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="N109" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W109" s="65"/>
       <c r="X109" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y109" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9923,17 +10001,17 @@
         <v>118</v>
       </c>
       <c r="E110" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J110" s="11" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="N110" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W110" s="65"/>
       <c r="X110" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y110" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9952,17 +10030,17 @@
         <v>118</v>
       </c>
       <c r="E111" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J111" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N111" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W111" s="65"/>
       <c r="X111" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y111" s="6" t="str">
         <f t="shared" si="28"/>
@@ -9981,17 +10059,17 @@
         <v>118</v>
       </c>
       <c r="E112" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="N112" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W112" s="65"/>
       <c r="X112" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y112" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10010,17 +10088,17 @@
         <v>118</v>
       </c>
       <c r="E113" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J113" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="N113" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W113" s="65"/>
       <c r="X113" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y113" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10039,17 +10117,17 @@
         <v>118</v>
       </c>
       <c r="E114" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="N114" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W114" s="65"/>
       <c r="X114" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y114" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10068,17 +10146,17 @@
         <v>118</v>
       </c>
       <c r="E115" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="N115" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W115" s="65"/>
       <c r="X115" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y115" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10097,17 +10175,17 @@
         <v>118</v>
       </c>
       <c r="E116" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J116" s="11" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="N116" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W116" s="65"/>
       <c r="X116" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y116" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10126,17 +10204,17 @@
         <v>111</v>
       </c>
       <c r="E117" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J117" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="N117" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W117" s="65"/>
       <c r="X117" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y117" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10155,17 +10233,17 @@
         <v>111</v>
       </c>
       <c r="E118" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="N118" s="60" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="W118" s="65"/>
       <c r="X118" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y118" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10184,17 +10262,17 @@
         <v>111</v>
       </c>
       <c r="E119" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J119" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="N119" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W119" s="65"/>
       <c r="X119" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y119" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10213,17 +10291,17 @@
         <v>111</v>
       </c>
       <c r="E120" s="54" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="J120" s="11" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="N120" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="W120" s="65"/>
       <c r="X120" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y120" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10242,23 +10320,23 @@
         <v>118</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J121" s="106" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="N121" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P121" s="107" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="W121" s="65"/>
       <c r="X121" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y121" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10277,23 +10355,23 @@
         <v>118</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J122" s="106" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="N122" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P122" s="107" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="W122" s="65"/>
       <c r="X122" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y122" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10312,23 +10390,23 @@
         <v>118</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J123" s="106" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="N123" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P123" s="107" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="W123" s="65"/>
       <c r="X123" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y123" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10347,23 +10425,23 @@
         <v>118</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J124" s="106" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="N124" s="107" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="P124" s="107" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="W124" s="65"/>
       <c r="X124" s="104" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Y124" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10382,23 +10460,23 @@
         <v>118</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J125" s="106" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="N125" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P125" s="107" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="W125" s="65"/>
       <c r="X125" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y125" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10417,23 +10495,23 @@
         <v>118</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J126" s="106" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N126" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P126" s="107" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="W126" s="65"/>
       <c r="X126" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y126" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10452,23 +10530,23 @@
         <v>118</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J127" s="106" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="N127" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P127" s="107" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="W127" s="65"/>
       <c r="X127" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y127" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10487,23 +10565,23 @@
         <v>118</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J128" s="106" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="N128" s="107" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P128" s="107" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="W128" s="65"/>
       <c r="X128" s="104" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="Y128" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10522,24 +10600,24 @@
         <v>118</v>
       </c>
       <c r="E129" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="N129" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W129" s="65"/>
       <c r="X129" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y129" s="6" t="str">
         <f t="shared" si="28"/>
         <v>marpower/thruster/aft</v>
       </c>
       <c r="Z129" s="64" t="str">
-        <f t="shared" ref="Z129:Z154" si="31">IF(COUNTIF(N129,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J129,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <f t="shared" ref="Z129:Z158" si="31">IF(COUNTIF(N129,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J129,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
         <v>$.Aradex_1_torque_feedback</v>
       </c>
     </row>
@@ -10551,17 +10629,17 @@
         <v>118</v>
       </c>
       <c r="E130" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="N130" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W130" s="65"/>
       <c r="X130" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y130" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10580,17 +10658,17 @@
         <v>118</v>
       </c>
       <c r="E131" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J131" s="11" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="N131" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W131" s="65"/>
       <c r="X131" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y131" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10609,17 +10687,17 @@
         <v>118</v>
       </c>
       <c r="E132" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="N132" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W132" s="65"/>
       <c r="X132" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y132" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10638,17 +10716,17 @@
         <v>111</v>
       </c>
       <c r="E133" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="N133" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W133" s="65"/>
       <c r="X133" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y133" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10667,17 +10745,17 @@
         <v>111</v>
       </c>
       <c r="E134" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="N134" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W134" s="65"/>
       <c r="X134" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y134" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10696,17 +10774,17 @@
         <v>111</v>
       </c>
       <c r="E135" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="N135" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W135" s="65"/>
       <c r="X135" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y135" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10725,17 +10803,17 @@
         <v>111</v>
       </c>
       <c r="E136" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="N136" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W136" s="65"/>
       <c r="X136" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y136" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10754,17 +10832,17 @@
         <v>118</v>
       </c>
       <c r="E137" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J137" s="11" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="N137" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W137" s="65"/>
       <c r="X137" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y137" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10783,17 +10861,17 @@
         <v>118</v>
       </c>
       <c r="E138" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J138" s="11" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="N138" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W138" s="65"/>
       <c r="X138" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y138" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10812,17 +10890,17 @@
         <v>118</v>
       </c>
       <c r="E139" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J139" s="11" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="N139" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W139" s="65"/>
       <c r="X139" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y139" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10841,17 +10919,17 @@
         <v>118</v>
       </c>
       <c r="E140" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J140" s="11" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="N140" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W140" s="65"/>
       <c r="X140" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y140" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10870,17 +10948,17 @@
         <v>118</v>
       </c>
       <c r="E141" s="54" t="s">
+        <v>732</v>
+      </c>
+      <c r="J141" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="J141" s="11" t="s">
-        <v>736</v>
-      </c>
       <c r="N141" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W141" s="65"/>
       <c r="X141" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y141" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10899,17 +10977,17 @@
         <v>118</v>
       </c>
       <c r="E142" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J142" s="11" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="N142" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W142" s="65"/>
       <c r="X142" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y142" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10928,17 +11006,17 @@
         <v>118</v>
       </c>
       <c r="E143" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J143" s="11" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="N143" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W143" s="65"/>
       <c r="X143" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y143" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10957,17 +11035,17 @@
         <v>118</v>
       </c>
       <c r="E144" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J144" s="11" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="N144" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W144" s="65"/>
       <c r="X144" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y144" s="6" t="str">
         <f t="shared" si="28"/>
@@ -10986,17 +11064,17 @@
         <v>118</v>
       </c>
       <c r="E145" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J145" s="11" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="N145" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W145" s="65"/>
       <c r="X145" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y145" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11015,17 +11093,17 @@
         <v>118</v>
       </c>
       <c r="E146" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J146" s="11" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="N146" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W146" s="65"/>
       <c r="X146" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y146" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11044,17 +11122,17 @@
         <v>118</v>
       </c>
       <c r="E147" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J147" s="11" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="N147" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W147" s="65"/>
       <c r="X147" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y147" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11073,17 +11151,17 @@
         <v>118</v>
       </c>
       <c r="E148" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J148" s="11" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="N148" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W148" s="65"/>
       <c r="X148" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y148" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11102,17 +11180,17 @@
         <v>111</v>
       </c>
       <c r="E149" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J149" s="11" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="N149" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W149" s="65"/>
       <c r="X149" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y149" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11131,17 +11209,17 @@
         <v>111</v>
       </c>
       <c r="E150" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J150" s="11" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="N150" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W150" s="65"/>
       <c r="X150" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y150" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11160,17 +11238,17 @@
         <v>111</v>
       </c>
       <c r="E151" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J151" s="11" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="N151" s="60" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="W151" s="65"/>
       <c r="X151" s="104" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="Y151" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11189,17 +11267,17 @@
         <v>111</v>
       </c>
       <c r="E152" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J152" s="11" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="N152" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W152" s="65"/>
       <c r="X152" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y152" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11218,17 +11296,17 @@
         <v>111</v>
       </c>
       <c r="E153" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J153" s="11" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="N153" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W153" s="65"/>
       <c r="X153" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y153" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11247,17 +11325,17 @@
         <v>111</v>
       </c>
       <c r="E154" s="54" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="J154" s="11" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="N154" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="W154" s="65"/>
       <c r="X154" s="104" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="Y154" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11269,324 +11347,1000 @@
       </c>
     </row>
     <row r="155" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C155" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>748</v>
+      </c>
+      <c r="N155" s="60" t="s">
+        <v>746</v>
+      </c>
       <c r="W155" s="65"/>
       <c r="X155" s="104"/>
-      <c r="Y155" s="6"/>
-      <c r="Z155" s="66"/>
+      <c r="Y155" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/externalmotor</v>
+      </c>
+      <c r="Z155" s="66" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Speed</v>
+      </c>
     </row>
     <row r="156" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C156" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J156" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="N156" s="60" t="s">
+        <v>746</v>
+      </c>
       <c r="W156" s="65"/>
       <c r="X156" s="104"/>
-      <c r="Y156" s="6"/>
-      <c r="Z156" s="66"/>
+      <c r="Y156" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/externalmotor</v>
+      </c>
+      <c r="Z156" s="66" t="str">
+        <f t="shared" si="31"/>
+        <v>$.Torque</v>
+      </c>
     </row>
     <row r="157" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C157" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J157" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="N157" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W157" s="65"/>
-      <c r="X157" s="104"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="66"/>
+      <c r="X157" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y157" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z157" s="66" t="str">
+        <f t="shared" si="31"/>
+        <v>$.GearboxOilTemperature</v>
+      </c>
     </row>
     <row r="158" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C158" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J158" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="N158" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W158" s="65"/>
-      <c r="X158" s="104"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="66"/>
+      <c r="X158" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y158" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z158" s="66" t="str">
+        <f t="shared" si="31"/>
+        <v>$.GearboxOilTemperature</v>
+      </c>
     </row>
     <row r="159" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C159" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J159" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="N159" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W159" s="65"/>
-      <c r="X159" s="104"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="66"/>
+      <c r="X159" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y159" s="6" t="str">
+        <f t="shared" ref="Y159:Y162" si="32">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N159,"spare"),"",IF(X159&lt;&gt;"",X159,N159))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z159" s="66" t="str">
+        <f t="shared" ref="Z159:Z162" si="33">IF(COUNTIF(N159,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J159,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Aradex1Temperature</v>
+      </c>
     </row>
     <row r="160" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C160" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J160" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="N160" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W160" s="65"/>
-      <c r="X160" s="104"/>
-      <c r="Y160" s="6"/>
-      <c r="Z160" s="66"/>
-    </row>
-    <row r="161" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X160" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y160" s="6" t="str">
+        <f t="shared" si="32"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z160" s="66" t="str">
+        <f t="shared" si="33"/>
+        <v>$.Aradex2Temperature</v>
+      </c>
+    </row>
+    <row r="161" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C161" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J161" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="N161" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W161" s="65"/>
-      <c r="X161" s="104"/>
-      <c r="Y161" s="6"/>
-      <c r="Z161" s="66"/>
-    </row>
-    <row r="162" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X161" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y161" s="6" t="str">
+        <f t="shared" si="32"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z161" s="66" t="str">
+        <f t="shared" si="33"/>
+        <v>$.Aradex1Temperature</v>
+      </c>
+    </row>
+    <row r="162" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C162" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J162" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="N162" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W162" s="65"/>
-      <c r="X162" s="104"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="66"/>
-    </row>
-    <row r="163" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X162" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y162" s="6" t="str">
+        <f t="shared" si="32"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z162" s="66" t="str">
+        <f t="shared" si="33"/>
+        <v>$.Aradex2Temperature</v>
+      </c>
+    </row>
+    <row r="163" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C163" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="N163" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W163" s="65"/>
-      <c r="X163" s="104"/>
-      <c r="Y163" s="6"/>
-      <c r="Z163" s="66"/>
-    </row>
-    <row r="164" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X163" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y163" s="6" t="str">
+        <f t="shared" ref="Y163:Y178" si="34">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N163,"spare"),"",IF(X163&lt;&gt;"",X163,N163))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z163" s="66" t="str">
+        <f t="shared" ref="Z163:Z178" si="35">IF(COUNTIF(N163,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J163,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.TemperatureIn</v>
+      </c>
+    </row>
+    <row r="164" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C164" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J164" s="11" t="s">
+        <v>753</v>
+      </c>
+      <c r="N164" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W164" s="65"/>
-      <c r="X164" s="104"/>
-      <c r="Y164" s="6"/>
-      <c r="Z164" s="66"/>
-    </row>
-    <row r="165" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X164" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y164" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z164" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.TemperatureOut</v>
+      </c>
+    </row>
+    <row r="165" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C165" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J165" s="11" t="s">
+        <v>754</v>
+      </c>
+      <c r="N165" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W165" s="65"/>
-      <c r="X165" s="104"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="66"/>
-    </row>
-    <row r="166" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X165" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y165" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z165" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.TemperatureIn</v>
+      </c>
+    </row>
+    <row r="166" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C166" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J166" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="N166" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W166" s="65"/>
-      <c r="X166" s="104"/>
-      <c r="Y166" s="6"/>
-      <c r="Z166" s="66"/>
-    </row>
-    <row r="167" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X166" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y166" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z166" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.TemperatureOut</v>
+      </c>
+    </row>
+    <row r="167" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C167" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J167" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="N167" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W167" s="65"/>
-      <c r="X167" s="104"/>
-      <c r="Y167" s="6"/>
-      <c r="Z167" s="66"/>
-    </row>
-    <row r="168" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X167" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y167" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z167" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex1TemperatureIn</v>
+      </c>
+    </row>
+    <row r="168" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C168" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J168" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="N168" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W168" s="65"/>
-      <c r="X168" s="104"/>
-      <c r="Y168" s="6"/>
-      <c r="Z168" s="66"/>
-    </row>
-    <row r="169" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X168" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y168" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z168" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex1TemperatureOut</v>
+      </c>
+    </row>
+    <row r="169" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C169" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J169" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="N169" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W169" s="65"/>
-      <c r="X169" s="104"/>
-      <c r="Y169" s="6"/>
-      <c r="Z169" s="66"/>
-    </row>
-    <row r="170" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X169" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y169" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z169" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex2TemperatureIn</v>
+      </c>
+    </row>
+    <row r="170" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C170" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J170" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="N170" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W170" s="65"/>
-      <c r="X170" s="104"/>
-      <c r="Y170" s="6"/>
-      <c r="Z170" s="66"/>
-    </row>
-    <row r="171" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X170" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y170" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z170" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex2TemperatureOut</v>
+      </c>
+    </row>
+    <row r="171" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C171" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J171" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="N171" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W171" s="65"/>
-      <c r="X171" s="104"/>
-      <c r="Y171" s="6"/>
-      <c r="Z171" s="66"/>
-    </row>
-    <row r="172" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X171" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y171" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z171" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex1TemperatureIn</v>
+      </c>
+    </row>
+    <row r="172" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C172" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J172" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="N172" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W172" s="65"/>
-      <c r="X172" s="104"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="66"/>
-    </row>
-    <row r="173" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X172" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y172" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z172" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex1TemperatureOut</v>
+      </c>
+    </row>
+    <row r="173" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C173" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J173" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="N173" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W173" s="65"/>
-      <c r="X173" s="104"/>
-      <c r="Y173" s="6"/>
-      <c r="Z173" s="66"/>
-    </row>
-    <row r="174" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X173" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y173" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z173" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex2TemperatureIn</v>
+      </c>
+    </row>
+    <row r="174" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C174" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J174" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="N174" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W174" s="65"/>
-      <c r="X174" s="104"/>
-      <c r="Y174" s="6"/>
-      <c r="Z174" s="66"/>
-    </row>
-    <row r="175" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X174" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y174" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z174" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.Aradex2TemperatureOut</v>
+      </c>
+    </row>
+    <row r="175" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C175" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J175" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="N175" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W175" s="65"/>
-      <c r="X175" s="104"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="66"/>
-    </row>
-    <row r="176" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X175" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y175" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z175" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.OilTemperatureIn</v>
+      </c>
+    </row>
+    <row r="176" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C176" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J176" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="N176" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W176" s="65"/>
-      <c r="X176" s="104"/>
-      <c r="Y176" s="6"/>
-      <c r="Z176" s="66"/>
-    </row>
-    <row r="177" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X176" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y176" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z176" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.OilTemperatureOut</v>
+      </c>
+    </row>
+    <row r="177" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C177" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J177" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="N177" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W177" s="65"/>
-      <c r="X177" s="104"/>
-      <c r="Y177" s="6"/>
-      <c r="Z177" s="66"/>
-    </row>
-    <row r="178" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X177" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y177" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z177" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.OilTemperatureIn</v>
+      </c>
+    </row>
+    <row r="178" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C178" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J178" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="N178" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W178" s="65"/>
-      <c r="X178" s="104"/>
-      <c r="Y178" s="6"/>
-      <c r="Z178" s="66"/>
-    </row>
-    <row r="179" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X178" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y178" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z178" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v>$.OilTemperatureOut</v>
+      </c>
+    </row>
+    <row r="179" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C179" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J179" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="N179" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W179" s="65"/>
-      <c r="X179" s="104"/>
-      <c r="Y179" s="6"/>
-      <c r="Z179" s="66"/>
-    </row>
-    <row r="180" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X179" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y179" s="6" t="str">
+        <f t="shared" ref="Y179:Y190" si="36">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N179,"spare"),"",IF(X179&lt;&gt;"",X179,N179))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z179" s="66" t="str">
+        <f t="shared" ref="Z179:Z190" si="37">IF(COUNTIF(N179,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J179,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.Flow</v>
+      </c>
+    </row>
+    <row r="180" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C180" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J180" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="N180" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W180" s="65"/>
-      <c r="X180" s="104"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="66"/>
-    </row>
-    <row r="181" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X180" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y180" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z180" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Pressure</v>
+      </c>
+    </row>
+    <row r="181" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C181" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J181" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="N181" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W181" s="65"/>
-      <c r="X181" s="104"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="66"/>
-    </row>
-    <row r="182" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X181" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y181" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z181" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Flow</v>
+      </c>
+    </row>
+    <row r="182" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C182" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J182" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="N182" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W182" s="65"/>
-      <c r="X182" s="104"/>
-      <c r="Y182" s="6"/>
-      <c r="Z182" s="66"/>
-    </row>
-    <row r="183" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X182" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y182" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z182" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Pressure</v>
+      </c>
+    </row>
+    <row r="183" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C183" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J183" s="11" t="s">
+        <v>766</v>
+      </c>
+      <c r="N183" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W183" s="65"/>
-      <c r="X183" s="104"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="66"/>
-    </row>
-    <row r="184" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X183" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y183" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z183" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex1Flow</v>
+      </c>
+    </row>
+    <row r="184" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C184" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J184" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="N184" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W184" s="65"/>
-      <c r="X184" s="104"/>
-      <c r="Y184" s="54"/>
-      <c r="Z184" s="66"/>
-    </row>
-    <row r="185" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X184" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y184" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z184" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex1Pressure</v>
+      </c>
+    </row>
+    <row r="185" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C185" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J185" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="N185" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W185" s="65"/>
-      <c r="X185" s="104"/>
-      <c r="Y185" s="54"/>
-      <c r="Z185" s="66"/>
-    </row>
-    <row r="186" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X185" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y185" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z185" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex2Flow</v>
+      </c>
+    </row>
+    <row r="186" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C186" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J186" s="11" t="s">
+        <v>769</v>
+      </c>
+      <c r="N186" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W186" s="65"/>
-      <c r="X186" s="104"/>
-      <c r="Y186" s="54"/>
-      <c r="Z186" s="66"/>
-    </row>
-    <row r="187" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X186" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y186" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z186" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex2Pressure</v>
+      </c>
+    </row>
+    <row r="187" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C187" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J187" s="11" t="s">
+        <v>766</v>
+      </c>
+      <c r="N187" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W187" s="65"/>
-      <c r="X187" s="104"/>
-      <c r="Y187" s="54"/>
-      <c r="Z187" s="66"/>
-    </row>
-    <row r="188" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X187" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y187" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z187" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex1Flow</v>
+      </c>
+    </row>
+    <row r="188" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C188" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J188" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="N188" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W188" s="65"/>
-      <c r="X188" s="104"/>
-      <c r="Y188" s="54"/>
-      <c r="Z188" s="66"/>
-    </row>
-    <row r="189" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X188" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y188" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z188" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex1Pressure</v>
+      </c>
+    </row>
+    <row r="189" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C189" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J189" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="N189" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W189" s="65"/>
-      <c r="X189" s="104"/>
-      <c r="Y189" s="54"/>
-      <c r="Z189" s="66"/>
-    </row>
-    <row r="190" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X189" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y189" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z189" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex2Flow</v>
+      </c>
+    </row>
+    <row r="190" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C190" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J190" s="11" t="s">
+        <v>769</v>
+      </c>
+      <c r="N190" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W190" s="65"/>
-      <c r="X190" s="104"/>
-      <c r="Y190" s="54"/>
-      <c r="Z190" s="66"/>
-    </row>
-    <row r="191" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X190" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y190" s="6" t="str">
+        <f t="shared" si="36"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z190" s="66" t="str">
+        <f t="shared" si="37"/>
+        <v>$.Aradex2Pressure</v>
+      </c>
+    </row>
+    <row r="191" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C191" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J191" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="N191" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W191" s="65"/>
-      <c r="X191" s="104"/>
-      <c r="Y191" s="54"/>
-      <c r="Z191" s="66"/>
-    </row>
-    <row r="192" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X191" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y191" s="6" t="str">
+        <f t="shared" ref="Y191:Y194" si="38">"marpower/"&amp;LOWER(_xlfn.REGEXREPLACE(IF(COUNTIF(N191,"spare"),"",IF(X191&lt;&gt;"",X191,N191))," ","-"))</f>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z191" s="66" t="str">
+        <f t="shared" ref="Z191:Z194" si="39">IF(COUNTIF(N191,"spare"),"","$."&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(J191,"(Aft|AFT|Fwd|FWD|Main) ?Thr?uster ?",""),"(\.| |/)","_"))</f>
+        <v>$.OilFlow</v>
+      </c>
+    </row>
+    <row r="192" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C192" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J192" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="N192" s="60" t="s">
+        <v>522</v>
+      </c>
       <c r="W192" s="65"/>
-      <c r="X192" s="104"/>
-      <c r="Y192" s="54"/>
-      <c r="Z192" s="66"/>
-    </row>
-    <row r="193" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X192" s="104" t="s">
+        <v>738</v>
+      </c>
+      <c r="Y192" s="6" t="str">
+        <f t="shared" si="38"/>
+        <v>marpower/thruster/aft</v>
+      </c>
+      <c r="Z192" s="66" t="str">
+        <f t="shared" si="39"/>
+        <v>$.OilPressure</v>
+      </c>
+    </row>
+    <row r="193" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C193" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J193" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="N193" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W193" s="65"/>
-      <c r="X193" s="104"/>
-      <c r="Y193" s="54"/>
-      <c r="Z193" s="66"/>
-    </row>
-    <row r="194" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X193" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y193" s="6" t="str">
+        <f t="shared" si="38"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z193" s="66" t="str">
+        <f t="shared" si="39"/>
+        <v>$.OilFlow</v>
+      </c>
+    </row>
+    <row r="194" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C194" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="J194" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="N194" s="60" t="s">
+        <v>571</v>
+      </c>
       <c r="W194" s="65"/>
-      <c r="X194" s="104"/>
-      <c r="Y194" s="54"/>
-      <c r="Z194" s="66"/>
-    </row>
-    <row r="195" spans="23:26" x14ac:dyDescent="0.25">
+      <c r="X194" s="104" t="s">
+        <v>739</v>
+      </c>
+      <c r="Y194" s="6" t="str">
+        <f t="shared" si="38"/>
+        <v>marpower/thruster/fwd</v>
+      </c>
+      <c r="Z194" s="66" t="str">
+        <f t="shared" si="39"/>
+        <v>$.OilPressure</v>
+      </c>
+    </row>
+    <row r="195" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W195" s="65"/>
       <c r="X195" s="104"/>
       <c r="Y195" s="54"/>
       <c r="Z195" s="66"/>
     </row>
-    <row r="196" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W196" s="65"/>
       <c r="X196" s="104"/>
       <c r="Y196" s="54"/>
       <c r="Z196" s="66"/>
     </row>
-    <row r="197" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W197" s="65"/>
       <c r="X197" s="104"/>
       <c r="Y197" s="54"/>
       <c r="Z197" s="66"/>
     </row>
-    <row r="198" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W198" s="65"/>
       <c r="X198" s="104"/>
       <c r="Y198" s="54"/>
       <c r="Z198" s="66"/>
     </row>
-    <row r="199" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W199" s="65"/>
       <c r="X199" s="104"/>
       <c r="Y199" s="54"/>
       <c r="Z199" s="66"/>
     </row>
-    <row r="200" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W200" s="65"/>
       <c r="X200" s="104"/>
       <c r="Y200" s="54"/>
       <c r="Z200" s="66"/>
     </row>
-    <row r="201" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W201" s="65"/>
       <c r="X201" s="104"/>
       <c r="Y201" s="54"/>
       <c r="Z201" s="66"/>
     </row>
-    <row r="202" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W202" s="65"/>
       <c r="X202" s="104"/>
       <c r="Y202" s="54"/>
       <c r="Z202" s="66"/>
     </row>
-    <row r="203" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W203" s="65"/>
       <c r="X203" s="104"/>
       <c r="Y203" s="54"/>
       <c r="Z203" s="66"/>
     </row>
-    <row r="204" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W204" s="65"/>
       <c r="X204" s="104"/>
       <c r="Y204" s="54"/>
       <c r="Z204" s="66"/>
     </row>
-    <row r="205" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W205" s="65"/>
       <c r="X205" s="104"/>
       <c r="Y205" s="54"/>
       <c r="Z205" s="66"/>
     </row>
-    <row r="206" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W206" s="65"/>
       <c r="X206" s="104"/>
       <c r="Y206" s="54"/>
       <c r="Z206" s="66"/>
     </row>
-    <row r="207" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W207" s="65"/>
       <c r="X207" s="104"/>
       <c r="Y207" s="54"/>
       <c r="Z207" s="66"/>
     </row>
-    <row r="208" spans="23:26" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:26" x14ac:dyDescent="0.25">
       <c r="W208" s="65"/>
       <c r="X208" s="104"/>
       <c r="Y208" s="54"/>
@@ -63030,32 +63784,8 @@
       <c r="Y8781" s="54"/>
       <c r="Z8781" s="66"/>
     </row>
-    <row r="8782" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8782" s="65"/>
-      <c r="X8782" s="104"/>
-      <c r="Y8782" s="54"/>
-      <c r="Z8782" s="66"/>
-    </row>
-    <row r="8783" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8783" s="65"/>
-      <c r="X8783" s="104"/>
-      <c r="Y8783" s="54"/>
-      <c r="Z8783" s="66"/>
-    </row>
-    <row r="8784" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8784" s="65"/>
-      <c r="X8784" s="104"/>
-      <c r="Y8784" s="54"/>
-      <c r="Z8784" s="66"/>
-    </row>
-    <row r="8785" spans="23:26" x14ac:dyDescent="0.25">
-      <c r="W8785" s="65"/>
-      <c r="X8785" s="104"/>
-      <c r="Y8785" s="54"/>
-      <c r="Z8785" s="66"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BV154" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <autoFilter ref="A1:BV161" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="11" showButton="0"/>
     <filterColumn colId="19" showButton="0"/>
     <filterColumn colId="20" showButton="0"/>
@@ -63086,6 +63816,36 @@
     <filterColumn colId="67" showButton="0"/>
   </autoFilter>
   <mergeCells count="46">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="BR1:BR2"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="AT1:AT2"/>
+    <mergeCell ref="AU1:AU2"/>
+    <mergeCell ref="AV1:AV2"/>
+    <mergeCell ref="AW1:AW2"/>
+    <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="BV1:BV2"/>
     <mergeCell ref="BC1:BE1"/>
@@ -63102,36 +63862,6 @@
     <mergeCell ref="BT1:BT2"/>
     <mergeCell ref="BU1:BU2"/>
     <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="BR1:BR2"/>
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="AA1:AH1"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="AT1:AT2"/>
-    <mergeCell ref="AU1:AU2"/>
-    <mergeCell ref="AV1:AV2"/>
-    <mergeCell ref="AW1:AW2"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="1">
@@ -63226,10 +63956,10 @@
       <c r="A4" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="140" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="132"/>
+      <c r="C4" s="140"/>
       <c r="D4" s="26" t="s">
         <v>59</v>
       </c>
@@ -63238,13 +63968,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="133"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="28" t="s">
         <v>158</v>
       </c>
@@ -63253,16 +63983,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="133"/>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
+      <c r="A6" s="132"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
       <c r="D6" s="28"/>
       <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="133"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
+      <c r="A7" s="132"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="28" t="s">
         <v>160</v>
       </c>
@@ -63271,9 +64001,9 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="133"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
+      <c r="A8" s="132"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
       <c r="D8" s="28" t="s">
         <v>162</v>
       </c>
@@ -63282,9 +64012,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="133"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
+      <c r="A9" s="132"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
       <c r="D9" s="28" t="s">
         <v>163</v>
       </c>
@@ -63293,9 +64023,9 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="133"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
+      <c r="A10" s="132"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
       <c r="D10" s="28" t="s">
         <v>164</v>
       </c>
@@ -63304,9 +64034,9 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="133"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
       <c r="D11" s="31" t="s">
         <v>165</v>
       </c>
@@ -63318,7 +64048,7 @@
       <c r="A12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="133" t="s">
+      <c r="B12" s="132" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="31" t="s">
@@ -63335,7 +64065,7 @@
       <c r="A13" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="133"/>
+      <c r="B13" s="132"/>
       <c r="C13" s="31" t="s">
         <v>104</v>
       </c>
@@ -63350,7 +64080,7 @@
       <c r="A14" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="133"/>
+      <c r="B14" s="132"/>
       <c r="C14" s="31" t="s">
         <v>105</v>
       </c>
@@ -63365,7 +64095,7 @@
       <c r="A15" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B15" s="133"/>
+      <c r="B15" s="132"/>
       <c r="C15" s="31" t="s">
         <v>106</v>
       </c>
@@ -63380,7 +64110,7 @@
       <c r="A16" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="133"/>
+      <c r="B16" s="132"/>
       <c r="C16" s="31" t="s">
         <v>107</v>
       </c>
@@ -63395,10 +64125,10 @@
       <c r="A17" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="133" t="s">
+      <c r="B17" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="133"/>
+      <c r="C17" s="132"/>
       <c r="D17" s="31" t="s">
         <v>177</v>
       </c>
@@ -63410,10 +64140,10 @@
       <c r="A18" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="133" t="s">
+      <c r="B18" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="133"/>
+      <c r="C18" s="132"/>
       <c r="D18" s="31" t="s">
         <v>180</v>
       </c>
@@ -63425,10 +64155,10 @@
       <c r="A19" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="133" t="s">
+      <c r="B19" s="132" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="133"/>
+      <c r="C19" s="132"/>
       <c r="D19" s="31" t="s">
         <v>183</v>
       </c>
@@ -63440,10 +64170,10 @@
       <c r="A20" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="133" t="s">
+      <c r="B20" s="132" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="133"/>
+      <c r="C20" s="132"/>
       <c r="D20" s="31" t="s">
         <v>186</v>
       </c>
@@ -63455,10 +64185,10 @@
       <c r="A21" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="133" t="s">
+      <c r="B21" s="132" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="133"/>
+      <c r="C21" s="132"/>
       <c r="D21" s="31" t="s">
         <v>189</v>
       </c>
@@ -63470,10 +64200,10 @@
       <c r="A22" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="133" t="s">
+      <c r="B22" s="132" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="133"/>
+      <c r="C22" s="132"/>
       <c r="D22" s="31" t="s">
         <v>192</v>
       </c>
@@ -63482,13 +64212,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="133" t="s">
+      <c r="A23" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="133" t="s">
+      <c r="B23" s="132" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="133"/>
+      <c r="C23" s="132"/>
       <c r="D23" s="28" t="s">
         <v>194</v>
       </c>
@@ -63497,9 +64227,9 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="133"/>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
+      <c r="A24" s="132"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
       <c r="D24" s="28" t="s">
         <v>196</v>
       </c>
@@ -63508,9 +64238,9 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="133"/>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
+      <c r="A25" s="132"/>
+      <c r="B25" s="132"/>
+      <c r="C25" s="132"/>
       <c r="D25" s="28" t="s">
         <v>198</v>
       </c>
@@ -63519,9 +64249,9 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="133"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="133"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="132"/>
       <c r="D26" s="28" t="s">
         <v>199</v>
       </c>
@@ -63530,9 +64260,9 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="133"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="133"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="132"/>
+      <c r="C27" s="132"/>
       <c r="D27" s="28" t="s">
         <v>200</v>
       </c>
@@ -63541,9 +64271,9 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="133"/>
-      <c r="B28" s="133"/>
-      <c r="C28" s="133"/>
+      <c r="A28" s="132"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
       <c r="D28" s="28" t="s">
         <v>201</v>
       </c>
@@ -63552,9 +64282,9 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="133"/>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133"/>
+      <c r="A29" s="132"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
       <c r="D29" s="28" t="s">
         <v>202</v>
       </c>
@@ -63563,9 +64293,9 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="133"/>
-      <c r="B30" s="133"/>
-      <c r="C30" s="133"/>
+      <c r="A30" s="132"/>
+      <c r="B30" s="132"/>
+      <c r="C30" s="132"/>
       <c r="D30" s="28" t="s">
         <v>203</v>
       </c>
@@ -63574,9 +64304,9 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="133"/>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="132"/>
+      <c r="C31" s="132"/>
       <c r="D31" s="28" t="s">
         <v>204</v>
       </c>
@@ -63585,9 +64315,9 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="133"/>
-      <c r="B32" s="133"/>
-      <c r="C32" s="133"/>
+      <c r="A32" s="132"/>
+      <c r="B32" s="132"/>
+      <c r="C32" s="132"/>
       <c r="D32" s="28" t="s">
         <v>205</v>
       </c>
@@ -63596,9 +64326,9 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="133"/>
-      <c r="B33" s="133"/>
-      <c r="C33" s="133"/>
+      <c r="A33" s="132"/>
+      <c r="B33" s="132"/>
+      <c r="C33" s="132"/>
       <c r="D33" s="28" t="s">
         <v>206</v>
       </c>
@@ -63607,16 +64337,16 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="133"/>
-      <c r="B34" s="133"/>
-      <c r="C34" s="133"/>
+      <c r="A34" s="132"/>
+      <c r="B34" s="132"/>
+      <c r="C34" s="132"/>
       <c r="D34" s="28"/>
       <c r="E34" s="30"/>
     </row>
     <row r="35" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="133"/>
-      <c r="B35" s="133"/>
-      <c r="C35" s="133"/>
+      <c r="A35" s="132"/>
+      <c r="B35" s="132"/>
+      <c r="C35" s="132"/>
       <c r="D35" s="28" t="s">
         <v>208</v>
       </c>
@@ -63625,9 +64355,9 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="133"/>
-      <c r="B36" s="133"/>
-      <c r="C36" s="133"/>
+      <c r="A36" s="132"/>
+      <c r="B36" s="132"/>
+      <c r="C36" s="132"/>
       <c r="D36" s="31" t="s">
         <v>210</v>
       </c>
@@ -63639,10 +64369,10 @@
       <c r="A37" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="134" t="s">
+      <c r="B37" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="134"/>
+      <c r="C37" s="133"/>
       <c r="D37" s="31" t="s">
         <v>212</v>
       </c>
@@ -63654,10 +64384,10 @@
       <c r="A38" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B38" s="133" t="s">
+      <c r="B38" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="133"/>
+      <c r="C38" s="132"/>
       <c r="D38" s="31" t="s">
         <v>214</v>
       </c>
@@ -63669,10 +64399,10 @@
       <c r="A39" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="133" t="s">
+      <c r="B39" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="133"/>
+      <c r="C39" s="132"/>
       <c r="D39" s="31" t="s">
         <v>216</v>
       </c>
@@ -63681,13 +64411,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="133" t="s">
+      <c r="A40" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B40" s="133" t="s">
+      <c r="B40" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="133"/>
+      <c r="C40" s="132"/>
       <c r="D40" s="28" t="s">
         <v>218</v>
       </c>
@@ -63696,9 +64426,9 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="133"/>
-      <c r="B41" s="133"/>
-      <c r="C41" s="133"/>
+      <c r="A41" s="132"/>
+      <c r="B41" s="132"/>
+      <c r="C41" s="132"/>
       <c r="D41" s="28" t="s">
         <v>220</v>
       </c>
@@ -63707,9 +64437,9 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="133"/>
-      <c r="B42" s="133"/>
-      <c r="C42" s="133"/>
+      <c r="A42" s="132"/>
+      <c r="B42" s="132"/>
+      <c r="C42" s="132"/>
       <c r="D42" s="28" t="s">
         <v>222</v>
       </c>
@@ -63718,9 +64448,9 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="133"/>
-      <c r="B43" s="133"/>
-      <c r="C43" s="133"/>
+      <c r="A43" s="132"/>
+      <c r="B43" s="132"/>
+      <c r="C43" s="132"/>
       <c r="D43" s="28" t="s">
         <v>224</v>
       </c>
@@ -63729,9 +64459,9 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="133"/>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
+      <c r="A44" s="132"/>
+      <c r="B44" s="132"/>
+      <c r="C44" s="132"/>
       <c r="D44" s="28" t="s">
         <v>226</v>
       </c>
@@ -63743,10 +64473,10 @@
       <c r="A45" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="133" t="s">
+      <c r="B45" s="132" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="133"/>
+      <c r="C45" s="132"/>
       <c r="D45" s="27" t="s">
         <v>227</v>
       </c>
@@ -63803,7 +64533,7 @@
       <c r="A49" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="135" t="s">
+      <c r="B49" s="137" t="s">
         <v>237</v>
       </c>
       <c r="C49" s="31" t="s">
@@ -63817,11 +64547,11 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="133" t="s">
+      <c r="A50" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B50" s="135"/>
-      <c r="C50" s="136" t="s">
+      <c r="B50" s="137"/>
+      <c r="C50" s="138" t="s">
         <v>108</v>
       </c>
       <c r="D50" s="40" t="s">
@@ -63832,9 +64562,9 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="133"/>
-      <c r="B51" s="135"/>
-      <c r="C51" s="136"/>
+      <c r="A51" s="132"/>
+      <c r="B51" s="137"/>
+      <c r="C51" s="138"/>
       <c r="D51" s="30" t="s">
         <v>242</v>
       </c>
@@ -63843,9 +64573,9 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="133"/>
-      <c r="B52" s="135"/>
-      <c r="C52" s="136"/>
+      <c r="A52" s="132"/>
+      <c r="B52" s="137"/>
+      <c r="C52" s="138"/>
       <c r="D52" s="30" t="s">
         <v>244</v>
       </c>
@@ -63854,9 +64584,9 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="133"/>
-      <c r="B53" s="135"/>
-      <c r="C53" s="136"/>
+      <c r="A53" s="132"/>
+      <c r="B53" s="137"/>
+      <c r="C53" s="138"/>
       <c r="D53" s="30" t="s">
         <v>246</v>
       </c>
@@ -63865,16 +64595,16 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="133"/>
-      <c r="B54" s="135"/>
-      <c r="C54" s="136"/>
+      <c r="A54" s="132"/>
+      <c r="B54" s="137"/>
+      <c r="C54" s="138"/>
       <c r="D54" s="28"/>
       <c r="E54" s="30"/>
     </row>
     <row r="55" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="133"/>
-      <c r="B55" s="135"/>
-      <c r="C55" s="136"/>
+      <c r="A55" s="132"/>
+      <c r="B55" s="137"/>
+      <c r="C55" s="138"/>
       <c r="D55" s="31" t="s">
         <v>248</v>
       </c>
@@ -63883,11 +64613,11 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="133" t="s">
+      <c r="A56" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B56" s="135"/>
-      <c r="C56" s="137" t="s">
+      <c r="B56" s="137"/>
+      <c r="C56" s="139" t="s">
         <v>109</v>
       </c>
       <c r="D56" s="28" t="s">
@@ -63898,9 +64628,9 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="133"/>
-      <c r="B57" s="135"/>
-      <c r="C57" s="137"/>
+      <c r="A57" s="132"/>
+      <c r="B57" s="137"/>
+      <c r="C57" s="139"/>
       <c r="D57" s="28" t="s">
         <v>252</v>
       </c>
@@ -63909,9 +64639,9 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="133"/>
-      <c r="B58" s="135"/>
-      <c r="C58" s="137"/>
+      <c r="A58" s="132"/>
+      <c r="B58" s="137"/>
+      <c r="C58" s="139"/>
       <c r="D58" s="31" t="s">
         <v>254</v>
       </c>
@@ -63923,10 +64653,10 @@
       <c r="A59" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="133" t="s">
+      <c r="B59" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="133"/>
+      <c r="C59" s="132"/>
       <c r="D59" s="31" t="s">
         <v>256</v>
       </c>
@@ -63938,7 +64668,7 @@
       <c r="A60" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="138" t="s">
+      <c r="B60" s="136" t="s">
         <v>82</v>
       </c>
       <c r="C60" s="31" t="s">
@@ -63952,11 +64682,11 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="133" t="s">
+      <c r="A61" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B61" s="138"/>
-      <c r="C61" s="133" t="s">
+      <c r="B61" s="136"/>
+      <c r="C61" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D61" s="40" t="s">
@@ -63967,9 +64697,9 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="133"/>
-      <c r="B62" s="133"/>
-      <c r="C62" s="133"/>
+      <c r="A62" s="132"/>
+      <c r="B62" s="132"/>
+      <c r="C62" s="132"/>
       <c r="D62" s="30" t="s">
         <v>242</v>
       </c>
@@ -63978,9 +64708,9 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="133"/>
-      <c r="B63" s="133"/>
-      <c r="C63" s="133"/>
+      <c r="A63" s="132"/>
+      <c r="B63" s="132"/>
+      <c r="C63" s="132"/>
       <c r="D63" s="30" t="s">
         <v>244</v>
       </c>
@@ -63989,9 +64719,9 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="133"/>
-      <c r="B64" s="133"/>
-      <c r="C64" s="133"/>
+      <c r="A64" s="132"/>
+      <c r="B64" s="132"/>
+      <c r="C64" s="132"/>
       <c r="D64" s="30" t="s">
         <v>246</v>
       </c>
@@ -64000,16 +64730,16 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="133"/>
-      <c r="B65" s="133"/>
-      <c r="C65" s="133"/>
+      <c r="A65" s="132"/>
+      <c r="B65" s="132"/>
+      <c r="C65" s="132"/>
       <c r="D65" s="28"/>
       <c r="E65" s="30"/>
     </row>
     <row r="66" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="133"/>
-      <c r="B66" s="138"/>
-      <c r="C66" s="133"/>
+      <c r="A66" s="132"/>
+      <c r="B66" s="136"/>
+      <c r="C66" s="132"/>
       <c r="D66" s="31" t="s">
         <v>248</v>
       </c>
@@ -64018,11 +64748,11 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="133" t="s">
+      <c r="A67" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="138"/>
-      <c r="C67" s="133" t="s">
+      <c r="B67" s="136"/>
+      <c r="C67" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D67" s="28" t="s">
@@ -64033,9 +64763,9 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="133"/>
-      <c r="B68" s="133"/>
-      <c r="C68" s="133"/>
+      <c r="A68" s="132"/>
+      <c r="B68" s="132"/>
+      <c r="C68" s="132"/>
       <c r="D68" s="28" t="s">
         <v>252</v>
       </c>
@@ -64044,9 +64774,9 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="133"/>
-      <c r="B69" s="138"/>
-      <c r="C69" s="133"/>
+      <c r="A69" s="132"/>
+      <c r="B69" s="136"/>
+      <c r="C69" s="132"/>
       <c r="D69" s="31" t="s">
         <v>254</v>
       </c>
@@ -64058,7 +64788,7 @@
       <c r="A70" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="138" t="s">
+      <c r="B70" s="136" t="s">
         <v>81</v>
       </c>
       <c r="C70" s="31" t="s">
@@ -64072,11 +64802,11 @@
       </c>
     </row>
     <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="133" t="s">
+      <c r="A71" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="138"/>
-      <c r="C71" s="133" t="s">
+      <c r="B71" s="136"/>
+      <c r="C71" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D71" s="40" t="s">
@@ -64087,9 +64817,9 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="133"/>
-      <c r="B72" s="133"/>
-      <c r="C72" s="133"/>
+      <c r="A72" s="132"/>
+      <c r="B72" s="132"/>
+      <c r="C72" s="132"/>
       <c r="D72" s="30" t="s">
         <v>242</v>
       </c>
@@ -64098,9 +64828,9 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="133"/>
-      <c r="B73" s="133"/>
-      <c r="C73" s="133"/>
+      <c r="A73" s="132"/>
+      <c r="B73" s="132"/>
+      <c r="C73" s="132"/>
       <c r="D73" s="30" t="s">
         <v>244</v>
       </c>
@@ -64109,9 +64839,9 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="133"/>
-      <c r="B74" s="133"/>
-      <c r="C74" s="133"/>
+      <c r="A74" s="132"/>
+      <c r="B74" s="132"/>
+      <c r="C74" s="132"/>
       <c r="D74" s="30" t="s">
         <v>246</v>
       </c>
@@ -64120,16 +64850,16 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="133"/>
-      <c r="B75" s="133"/>
-      <c r="C75" s="133"/>
+      <c r="A75" s="132"/>
+      <c r="B75" s="132"/>
+      <c r="C75" s="132"/>
       <c r="D75" s="28"/>
       <c r="E75" s="30"/>
     </row>
     <row r="76" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="133"/>
-      <c r="B76" s="138"/>
-      <c r="C76" s="133"/>
+      <c r="A76" s="132"/>
+      <c r="B76" s="136"/>
+      <c r="C76" s="132"/>
       <c r="D76" s="31" t="s">
         <v>248</v>
       </c>
@@ -64138,11 +64868,11 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="133" t="s">
+      <c r="A77" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B77" s="138"/>
-      <c r="C77" s="133" t="s">
+      <c r="B77" s="136"/>
+      <c r="C77" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D77" s="28" t="s">
@@ -64153,9 +64883,9 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="133"/>
-      <c r="B78" s="133"/>
-      <c r="C78" s="133"/>
+      <c r="A78" s="132"/>
+      <c r="B78" s="132"/>
+      <c r="C78" s="132"/>
       <c r="D78" s="28" t="s">
         <v>252</v>
       </c>
@@ -64164,9 +64894,9 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="133"/>
-      <c r="B79" s="138"/>
-      <c r="C79" s="133"/>
+      <c r="A79" s="132"/>
+      <c r="B79" s="136"/>
+      <c r="C79" s="132"/>
       <c r="D79" s="31" t="s">
         <v>254</v>
       </c>
@@ -64175,13 +64905,13 @@
       </c>
     </row>
     <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="133" t="s">
+      <c r="A80" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="133" t="s">
+      <c r="B80" s="132" t="s">
         <v>258</v>
       </c>
-      <c r="C80" s="133"/>
+      <c r="C80" s="132"/>
       <c r="D80" s="28" t="s">
         <v>259</v>
       </c>
@@ -64190,9 +64920,9 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="133"/>
-      <c r="B81" s="133"/>
-      <c r="C81" s="133"/>
+      <c r="A81" s="132"/>
+      <c r="B81" s="132"/>
+      <c r="C81" s="132"/>
       <c r="D81" s="28" t="s">
         <v>261</v>
       </c>
@@ -64201,9 +64931,9 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="133"/>
-      <c r="B82" s="133"/>
-      <c r="C82" s="133"/>
+      <c r="A82" s="132"/>
+      <c r="B82" s="132"/>
+      <c r="C82" s="132"/>
       <c r="D82" s="28" t="s">
         <v>263</v>
       </c>
@@ -64212,9 +64942,9 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="133"/>
-      <c r="B83" s="133"/>
-      <c r="C83" s="133"/>
+      <c r="A83" s="132"/>
+      <c r="B83" s="132"/>
+      <c r="C83" s="132"/>
       <c r="D83" s="28" t="s">
         <v>265</v>
       </c>
@@ -64223,9 +64953,9 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="133"/>
-      <c r="B84" s="133"/>
-      <c r="C84" s="133"/>
+      <c r="A84" s="132"/>
+      <c r="B84" s="132"/>
+      <c r="C84" s="132"/>
       <c r="D84" s="28" t="s">
         <v>267</v>
       </c>
@@ -64234,9 +64964,9 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="133"/>
-      <c r="B85" s="133"/>
-      <c r="C85" s="133"/>
+      <c r="A85" s="132"/>
+      <c r="B85" s="132"/>
+      <c r="C85" s="132"/>
       <c r="D85" s="31" t="s">
         <v>269</v>
       </c>
@@ -64248,10 +64978,10 @@
       <c r="A86" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="133" t="s">
+      <c r="B86" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="C86" s="133"/>
+      <c r="C86" s="132"/>
       <c r="D86" s="31" t="s">
         <v>271</v>
       </c>
@@ -64263,7 +64993,7 @@
       <c r="A87" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B87" s="138" t="s">
+      <c r="B87" s="136" t="s">
         <v>83</v>
       </c>
       <c r="C87" s="31" t="s">
@@ -64277,11 +65007,11 @@
       </c>
     </row>
     <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="133" t="s">
+      <c r="A88" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B88" s="138"/>
-      <c r="C88" s="133" t="s">
+      <c r="B88" s="136"/>
+      <c r="C88" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D88" s="40" t="s">
@@ -64292,9 +65022,9 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="133"/>
-      <c r="B89" s="133"/>
-      <c r="C89" s="133"/>
+      <c r="A89" s="132"/>
+      <c r="B89" s="132"/>
+      <c r="C89" s="132"/>
       <c r="D89" s="30" t="s">
         <v>242</v>
       </c>
@@ -64303,9 +65033,9 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="133"/>
-      <c r="B90" s="133"/>
-      <c r="C90" s="133"/>
+      <c r="A90" s="132"/>
+      <c r="B90" s="132"/>
+      <c r="C90" s="132"/>
       <c r="D90" s="30" t="s">
         <v>244</v>
       </c>
@@ -64314,9 +65044,9 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="133"/>
-      <c r="B91" s="133"/>
-      <c r="C91" s="133"/>
+      <c r="A91" s="132"/>
+      <c r="B91" s="132"/>
+      <c r="C91" s="132"/>
       <c r="D91" s="30" t="s">
         <v>246</v>
       </c>
@@ -64325,16 +65055,16 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="133"/>
-      <c r="B92" s="133"/>
-      <c r="C92" s="133"/>
+      <c r="A92" s="132"/>
+      <c r="B92" s="132"/>
+      <c r="C92" s="132"/>
       <c r="D92" s="28"/>
       <c r="E92" s="30"/>
     </row>
     <row r="93" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="133"/>
-      <c r="B93" s="138"/>
-      <c r="C93" s="133"/>
+      <c r="A93" s="132"/>
+      <c r="B93" s="136"/>
+      <c r="C93" s="132"/>
       <c r="D93" s="31" t="s">
         <v>248</v>
       </c>
@@ -64343,11 +65073,11 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="133" t="s">
+      <c r="A94" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B94" s="138"/>
-      <c r="C94" s="133" t="s">
+      <c r="B94" s="136"/>
+      <c r="C94" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D94" s="28" t="s">
@@ -64358,9 +65088,9 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="133"/>
-      <c r="B95" s="133"/>
-      <c r="C95" s="133"/>
+      <c r="A95" s="132"/>
+      <c r="B95" s="132"/>
+      <c r="C95" s="132"/>
       <c r="D95" s="28" t="s">
         <v>252</v>
       </c>
@@ -64369,9 +65099,9 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="133"/>
-      <c r="B96" s="138"/>
-      <c r="C96" s="133"/>
+      <c r="A96" s="132"/>
+      <c r="B96" s="136"/>
+      <c r="C96" s="132"/>
       <c r="D96" s="31" t="s">
         <v>254</v>
       </c>
@@ -64383,7 +65113,7 @@
       <c r="A97" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B97" s="138" t="s">
+      <c r="B97" s="136" t="s">
         <v>84</v>
       </c>
       <c r="C97" s="31" t="s">
@@ -64397,11 +65127,11 @@
       </c>
     </row>
     <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="133" t="s">
+      <c r="A98" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B98" s="138"/>
-      <c r="C98" s="133" t="s">
+      <c r="B98" s="136"/>
+      <c r="C98" s="132" t="s">
         <v>108</v>
       </c>
       <c r="D98" s="40" t="s">
@@ -64412,9 +65142,9 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="133"/>
-      <c r="B99" s="133"/>
-      <c r="C99" s="133"/>
+      <c r="A99" s="132"/>
+      <c r="B99" s="132"/>
+      <c r="C99" s="132"/>
       <c r="D99" s="30" t="s">
         <v>242</v>
       </c>
@@ -64423,9 +65153,9 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="133"/>
-      <c r="B100" s="133"/>
-      <c r="C100" s="133"/>
+      <c r="A100" s="132"/>
+      <c r="B100" s="132"/>
+      <c r="C100" s="132"/>
       <c r="D100" s="30" t="s">
         <v>244</v>
       </c>
@@ -64434,9 +65164,9 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="133"/>
-      <c r="B101" s="133"/>
-      <c r="C101" s="133"/>
+      <c r="A101" s="132"/>
+      <c r="B101" s="132"/>
+      <c r="C101" s="132"/>
       <c r="D101" s="30" t="s">
         <v>246</v>
       </c>
@@ -64445,16 +65175,16 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="133"/>
-      <c r="B102" s="133"/>
-      <c r="C102" s="133"/>
+      <c r="A102" s="132"/>
+      <c r="B102" s="132"/>
+      <c r="C102" s="132"/>
       <c r="D102" s="28"/>
       <c r="E102" s="30"/>
     </row>
     <row r="103" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="133"/>
-      <c r="B103" s="138"/>
-      <c r="C103" s="133"/>
+      <c r="A103" s="132"/>
+      <c r="B103" s="136"/>
+      <c r="C103" s="132"/>
       <c r="D103" s="31" t="s">
         <v>248</v>
       </c>
@@ -64463,11 +65193,11 @@
       </c>
     </row>
     <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="133" t="s">
+      <c r="A104" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B104" s="138"/>
-      <c r="C104" s="133" t="s">
+      <c r="B104" s="136"/>
+      <c r="C104" s="132" t="s">
         <v>109</v>
       </c>
       <c r="D104" s="28" t="s">
@@ -64478,9 +65208,9 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="133"/>
-      <c r="B105" s="133"/>
-      <c r="C105" s="133"/>
+      <c r="A105" s="132"/>
+      <c r="B105" s="132"/>
+      <c r="C105" s="132"/>
       <c r="D105" s="28" t="s">
         <v>252</v>
       </c>
@@ -64489,9 +65219,9 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="133"/>
-      <c r="B106" s="138"/>
-      <c r="C106" s="133"/>
+      <c r="A106" s="132"/>
+      <c r="B106" s="136"/>
+      <c r="C106" s="132"/>
       <c r="D106" s="31" t="s">
         <v>254</v>
       </c>
@@ -64503,10 +65233,10 @@
       <c r="A107" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B107" s="133" t="s">
+      <c r="B107" s="132" t="s">
         <v>273</v>
       </c>
-      <c r="C107" s="133"/>
+      <c r="C107" s="132"/>
       <c r="D107" s="31" t="s">
         <v>274</v>
       </c>
@@ -64518,10 +65248,10 @@
       <c r="A108" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B108" s="133" t="s">
+      <c r="B108" s="132" t="s">
         <v>276</v>
       </c>
-      <c r="C108" s="133"/>
+      <c r="C108" s="132"/>
       <c r="D108" s="31" t="s">
         <v>277</v>
       </c>
@@ -64533,10 +65263,10 @@
       <c r="A109" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B109" s="133" t="s">
+      <c r="B109" s="132" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="133"/>
+      <c r="C109" s="132"/>
       <c r="D109" s="31" t="s">
         <v>280</v>
       </c>
@@ -64545,13 +65275,13 @@
       </c>
     </row>
     <row r="110" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="133" t="s">
+      <c r="A110" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B110" s="139" t="s">
+      <c r="B110" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="139"/>
+      <c r="C110" s="135"/>
       <c r="D110" s="39" t="s">
         <v>282</v>
       </c>
@@ -64560,16 +65290,16 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="133"/>
-      <c r="B111" s="139"/>
-      <c r="C111" s="139"/>
+      <c r="A111" s="132"/>
+      <c r="B111" s="135"/>
+      <c r="C111" s="135"/>
       <c r="D111" s="41"/>
       <c r="E111" s="30"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="139"/>
-      <c r="C112" s="139"/>
+      <c r="A112" s="132"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="135"/>
       <c r="D112" s="42" t="s">
         <v>284</v>
       </c>
@@ -64578,9 +65308,9 @@
       </c>
     </row>
     <row r="113" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A113" s="133"/>
-      <c r="B113" s="139"/>
-      <c r="C113" s="139"/>
+      <c r="A113" s="132"/>
+      <c r="B113" s="135"/>
+      <c r="C113" s="135"/>
       <c r="D113" s="42" t="s">
         <v>286</v>
       </c>
@@ -64589,9 +65319,9 @@
       </c>
     </row>
     <row r="114" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A114" s="133"/>
-      <c r="B114" s="139"/>
-      <c r="C114" s="139"/>
+      <c r="A114" s="132"/>
+      <c r="B114" s="135"/>
+      <c r="C114" s="135"/>
       <c r="D114" s="42" t="s">
         <v>288</v>
       </c>
@@ -64600,9 +65330,9 @@
       </c>
     </row>
     <row r="115" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A115" s="133"/>
-      <c r="B115" s="139"/>
-      <c r="C115" s="139"/>
+      <c r="A115" s="132"/>
+      <c r="B115" s="135"/>
+      <c r="C115" s="135"/>
       <c r="D115" s="43" t="s">
         <v>290</v>
       </c>
@@ -64648,10 +65378,10 @@
       <c r="A118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="B118" s="140" t="s">
+      <c r="B118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="C118" s="140"/>
+      <c r="C118" s="134"/>
       <c r="D118" s="46" t="s">
         <v>296</v>
       </c>
@@ -64912,10 +65642,10 @@
       <c r="IW118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="IX118" s="140" t="s">
+      <c r="IX118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="IY118" s="140"/>
+      <c r="IY118" s="134"/>
       <c r="IZ118" s="46" t="s">
         <v>296</v>
       </c>
@@ -65176,10 +65906,10 @@
       <c r="SS118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ST118" s="140" t="s">
+      <c r="ST118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="SU118" s="140"/>
+      <c r="SU118" s="134"/>
       <c r="SV118" s="46" t="s">
         <v>296</v>
       </c>
@@ -65440,10 +66170,10 @@
       <c r="ACO118" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="ACP118" s="140" t="s">
+      <c r="ACP118" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="ACQ118" s="140"/>
+      <c r="ACQ118" s="134"/>
       <c r="ACR118" s="46" t="s">
         <v>296</v>
       </c>
@@ -65706,10 +66436,10 @@
       <c r="A119" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B119" s="133" t="s">
+      <c r="B119" s="132" t="s">
         <v>298</v>
       </c>
-      <c r="C119" s="133"/>
+      <c r="C119" s="132"/>
       <c r="D119" s="31" t="s">
         <v>299</v>
       </c>
@@ -65721,7 +66451,7 @@
       <c r="A120" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B120" s="133" t="s">
+      <c r="B120" s="132" t="s">
         <v>301</v>
       </c>
       <c r="C120" s="31" t="s">
@@ -65738,7 +66468,7 @@
       <c r="A121" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B121" s="133"/>
+      <c r="B121" s="132"/>
       <c r="C121" s="31" t="s">
         <v>102</v>
       </c>
@@ -65753,10 +66483,10 @@
       <c r="A122" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B122" s="133" t="s">
+      <c r="B122" s="132" t="s">
         <v>306</v>
       </c>
-      <c r="C122" s="133"/>
+      <c r="C122" s="132"/>
       <c r="D122" s="31" t="s">
         <v>307</v>
       </c>
@@ -65768,10 +66498,10 @@
       <c r="A123" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B123" s="133" t="s">
+      <c r="B123" s="132" t="s">
         <v>72</v>
       </c>
-      <c r="C123" s="133"/>
+      <c r="C123" s="132"/>
       <c r="D123" s="31" t="s">
         <v>309</v>
       </c>
@@ -65783,10 +66513,10 @@
       <c r="A124" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B124" s="134" t="s">
+      <c r="B124" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="C124" s="134"/>
+      <c r="C124" s="133"/>
       <c r="D124" s="27" t="s">
         <v>311</v>
       </c>
@@ -65798,10 +66528,10 @@
       <c r="A125" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B125" s="133" t="s">
+      <c r="B125" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="C125" s="133"/>
+      <c r="C125" s="132"/>
       <c r="D125" s="27" t="s">
         <v>313</v>
       </c>
@@ -65813,10 +66543,10 @@
       <c r="A126" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="133" t="s">
+      <c r="B126" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="C126" s="133"/>
+      <c r="C126" s="132"/>
       <c r="D126" s="27" t="s">
         <v>315</v>
       </c>
@@ -65828,10 +66558,10 @@
       <c r="A127" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B127" s="133" t="s">
+      <c r="B127" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="C127" s="133"/>
+      <c r="C127" s="132"/>
       <c r="D127" s="27" t="s">
         <v>317</v>
       </c>
@@ -65840,13 +66570,13 @@
       </c>
     </row>
     <row r="128" spans="1:1024" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="133" t="s">
+      <c r="A128" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="B128" s="133" t="s">
+      <c r="B128" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="C128" s="133"/>
+      <c r="C128" s="132"/>
       <c r="D128" s="28" t="s">
         <v>319</v>
       </c>
@@ -65855,16 +66585,16 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="133"/>
-      <c r="B129" s="133"/>
-      <c r="C129" s="133"/>
+      <c r="A129" s="132"/>
+      <c r="B129" s="132"/>
+      <c r="C129" s="132"/>
       <c r="D129" s="28"/>
       <c r="E129" s="30"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="133"/>
-      <c r="B130" s="133"/>
-      <c r="C130" s="133"/>
+      <c r="A130" s="132"/>
+      <c r="B130" s="132"/>
+      <c r="C130" s="132"/>
       <c r="D130" s="28" t="s">
         <v>321</v>
       </c>
@@ -65873,9 +66603,9 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="133"/>
-      <c r="C131" s="133"/>
+      <c r="A131" s="132"/>
+      <c r="B131" s="132"/>
+      <c r="C131" s="132"/>
       <c r="D131" s="28" t="s">
         <v>323</v>
       </c>
@@ -65884,9 +66614,9 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="133"/>
-      <c r="B132" s="133"/>
-      <c r="C132" s="133"/>
+      <c r="A132" s="132"/>
+      <c r="B132" s="132"/>
+      <c r="C132" s="132"/>
       <c r="D132" s="28" t="s">
         <v>325</v>
       </c>
@@ -65895,9 +66625,9 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="133"/>
-      <c r="B133" s="133"/>
-      <c r="C133" s="133"/>
+      <c r="A133" s="132"/>
+      <c r="B133" s="132"/>
+      <c r="C133" s="132"/>
       <c r="D133" s="31" t="s">
         <v>327</v>
       </c>
@@ -65909,10 +66639,10 @@
       <c r="A134" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="133" t="s">
+      <c r="B134" s="132" t="s">
         <v>89</v>
       </c>
-      <c r="C134" s="133"/>
+      <c r="C134" s="132"/>
       <c r="D134" s="31" t="s">
         <v>329</v>
       </c>
@@ -65924,10 +66654,10 @@
       <c r="A135" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B135" s="133" t="s">
+      <c r="B135" s="132" t="s">
         <v>66</v>
       </c>
-      <c r="C135" s="133"/>
+      <c r="C135" s="132"/>
       <c r="D135" s="31" t="s">
         <v>331</v>
       </c>
@@ -65939,10 +66669,10 @@
       <c r="A136" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B136" s="133" t="s">
+      <c r="B136" s="132" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="133"/>
+      <c r="C136" s="132"/>
       <c r="D136" s="31" t="s">
         <v>334</v>
       </c>
@@ -65954,10 +66684,10 @@
       <c r="A137" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B137" s="133" t="s">
+      <c r="B137" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="C137" s="133"/>
+      <c r="C137" s="132"/>
       <c r="D137" s="31" t="s">
         <v>336</v>
       </c>
@@ -65969,10 +66699,10 @@
       <c r="A138" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B138" s="133" t="s">
+      <c r="B138" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="C138" s="133"/>
+      <c r="C138" s="132"/>
       <c r="D138" s="31" t="s">
         <v>338</v>
       </c>
@@ -65981,12 +66711,12 @@
       </c>
     </row>
     <row r="140" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="134" t="s">
+      <c r="A140" s="133" t="s">
         <v>340</v>
       </c>
-      <c r="B140" s="134"/>
-      <c r="C140" s="134"/>
-      <c r="D140" s="134"/>
+      <c r="B140" s="133"/>
+      <c r="C140" s="133"/>
+      <c r="D140" s="133"/>
       <c r="E140" s="27" t="s">
         <v>341</v>
       </c>
@@ -65998,36 +66728,40 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="A140:D140"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="A128:A133"/>
-    <mergeCell ref="B128:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="IX118:IY118"/>
-    <mergeCell ref="ST118:SU118"/>
-    <mergeCell ref="ACP118:ACQ118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="A110:A115"/>
-    <mergeCell ref="B110:C115"/>
-    <mergeCell ref="B97:B106"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="C98:C103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="B5:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A23:A36"/>
+    <mergeCell ref="B23:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B40:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B49:B58"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="C50:C55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:B69"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="B70:B79"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="C71:C76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="C77:C79"/>
     <mergeCell ref="A80:A85"/>
     <mergeCell ref="B80:C85"/>
     <mergeCell ref="B86:C86"/>
@@ -66036,40 +66770,36 @@
     <mergeCell ref="C88:C93"/>
     <mergeCell ref="A94:A96"/>
     <mergeCell ref="C94:C96"/>
-    <mergeCell ref="B70:B79"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="C71:C76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:B69"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="B40:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B49:B58"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="C50:C55"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="A23:A36"/>
-    <mergeCell ref="B23:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="B5:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B97:B106"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="C98:C103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="A110:A115"/>
+    <mergeCell ref="B110:C115"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="IX118:IY118"/>
+    <mergeCell ref="ST118:SU118"/>
+    <mergeCell ref="ACP118:ACQ118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="A128:A133"/>
+    <mergeCell ref="B128:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="A140:D140"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
